--- a/models/Tarnoc_v2_2026-09-01.xlsx
+++ b/models/Tarnoc_v2_2026-09-01.xlsx
@@ -175,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -347,12 +347,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1263,13 +1257,6 @@
     <row r="27">
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Revenue Forecast row 35 names which of the three stopped us in each month, and the Dashboard shows it by year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="14" t="inlineStr">
-        <is>
           <t>There is no market size or market share anywhere in the model.</t>
         </is>
       </c>
@@ -18568,7 +18555,7 @@
     <row r="2">
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Units sold is an output: marketing spend generates orders, selling and build capacity cap them, and row 35 says which one bit.</t>
+          <t>Units sold is an output: marketing spend generates orders, and selling and build capacity cap them.</t>
         </is>
       </c>
     </row>
@@ -25126,541 +25113,274 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Why we did not sell more</t>
-        </is>
-      </c>
-      <c r="E35" s="67">
-        <f>IF(E34&gt;=E31-0.5,"Build capacity",IF(E34&gt;=E22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="F35" s="67">
-        <f>IF(F34&gt;=F31-0.5,"Build capacity",IF(F34&gt;=F22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="G35" s="67">
-        <f>IF(G34&gt;=G31-0.5,"Build capacity",IF(G34&gt;=G22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="H35" s="67">
-        <f>IF(H34&gt;=H31-0.5,"Build capacity",IF(H34&gt;=H22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="I35" s="67">
-        <f>IF(I34&gt;=I31-0.5,"Build capacity",IF(I34&gt;=I22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="J35" s="67">
-        <f>IF(J34&gt;=J31-0.5,"Build capacity",IF(J34&gt;=J22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="K35" s="67">
-        <f>IF(K34&gt;=K31-0.5,"Build capacity",IF(K34&gt;=K22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="L35" s="67">
-        <f>IF(L34&gt;=L31-0.5,"Build capacity",IF(L34&gt;=L22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="M35" s="67">
-        <f>IF(M34&gt;=M31-0.5,"Build capacity",IF(M34&gt;=M22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="N35" s="67">
-        <f>IF(N34&gt;=N31-0.5,"Build capacity",IF(N34&gt;=N22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="O35" s="67">
-        <f>IF(O34&gt;=O31-0.5,"Build capacity",IF(O34&gt;=O22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="P35" s="67">
-        <f>IF(P34&gt;=P31-0.5,"Build capacity",IF(P34&gt;=P22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="Q35" s="67">
-        <f>IF(Q34&gt;=Q31-0.5,"Build capacity",IF(Q34&gt;=Q22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="R35" s="67">
-        <f>IF(R34&gt;=R31-0.5,"Build capacity",IF(R34&gt;=R22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="S35" s="67">
-        <f>IF(S34&gt;=S31-0.5,"Build capacity",IF(S34&gt;=S22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="T35" s="67">
-        <f>IF(T34&gt;=T31-0.5,"Build capacity",IF(T34&gt;=T22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="U35" s="67">
-        <f>IF(U34&gt;=U31-0.5,"Build capacity",IF(U34&gt;=U22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="V35" s="67">
-        <f>IF(V34&gt;=V31-0.5,"Build capacity",IF(V34&gt;=V22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="W35" s="67">
-        <f>IF(W34&gt;=W31-0.5,"Build capacity",IF(W34&gt;=W22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="X35" s="67">
-        <f>IF(X34&gt;=X31-0.5,"Build capacity",IF(X34&gt;=X22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="Y35" s="67">
-        <f>IF(Y34&gt;=Y31-0.5,"Build capacity",IF(Y34&gt;=Y22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="Z35" s="67">
-        <f>IF(Z34&gt;=Z31-0.5,"Build capacity",IF(Z34&gt;=Z22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AA35" s="67">
-        <f>IF(AA34&gt;=AA31-0.5,"Build capacity",IF(AA34&gt;=AA22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AB35" s="67">
-        <f>IF(AB34&gt;=AB31-0.5,"Build capacity",IF(AB34&gt;=AB22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AC35" s="67">
-        <f>IF(AC34&gt;=AC31-0.5,"Build capacity",IF(AC34&gt;=AC22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AD35" s="67">
-        <f>IF(AD34&gt;=AD31-0.5,"Build capacity",IF(AD34&gt;=AD22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AE35" s="67">
-        <f>IF(AE34&gt;=AE31-0.5,"Build capacity",IF(AE34&gt;=AE22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AF35" s="67">
-        <f>IF(AF34&gt;=AF31-0.5,"Build capacity",IF(AF34&gt;=AF22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AG35" s="67">
-        <f>IF(AG34&gt;=AG31-0.5,"Build capacity",IF(AG34&gt;=AG22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AH35" s="67">
-        <f>IF(AH34&gt;=AH31-0.5,"Build capacity",IF(AH34&gt;=AH22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AI35" s="67">
-        <f>IF(AI34&gt;=AI31-0.5,"Build capacity",IF(AI34&gt;=AI22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AJ35" s="67">
-        <f>IF(AJ34&gt;=AJ31-0.5,"Build capacity",IF(AJ34&gt;=AJ22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AK35" s="67">
-        <f>IF(AK34&gt;=AK31-0.5,"Build capacity",IF(AK34&gt;=AK22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AL35" s="67">
-        <f>IF(AL34&gt;=AL31-0.5,"Build capacity",IF(AL34&gt;=AL22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AM35" s="67">
-        <f>IF(AM34&gt;=AM31-0.5,"Build capacity",IF(AM34&gt;=AM22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AN35" s="67">
-        <f>IF(AN34&gt;=AN31-0.5,"Build capacity",IF(AN34&gt;=AN22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AO35" s="67">
-        <f>IF(AO34&gt;=AO31-0.5,"Build capacity",IF(AO34&gt;=AO22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AP35" s="67">
-        <f>IF(AP34&gt;=AP31-0.5,"Build capacity",IF(AP34&gt;=AP22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AQ35" s="67">
-        <f>IF(AQ34&gt;=AQ31-0.5,"Build capacity",IF(AQ34&gt;=AQ22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AR35" s="67">
-        <f>IF(AR34&gt;=AR31-0.5,"Build capacity",IF(AR34&gt;=AR22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AS35" s="67">
-        <f>IF(AS34&gt;=AS31-0.5,"Build capacity",IF(AS34&gt;=AS22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AT35" s="67">
-        <f>IF(AT34&gt;=AT31-0.5,"Build capacity",IF(AT34&gt;=AT22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AU35" s="67">
-        <f>IF(AU34&gt;=AU31-0.5,"Build capacity",IF(AU34&gt;=AU22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AV35" s="67">
-        <f>IF(AV34&gt;=AV31-0.5,"Build capacity",IF(AV34&gt;=AV22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AW35" s="67">
-        <f>IF(AW34&gt;=AW31-0.5,"Build capacity",IF(AW34&gt;=AW22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AX35" s="67">
-        <f>IF(AX34&gt;=AX31-0.5,"Build capacity",IF(AX34&gt;=AX22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AY35" s="67">
-        <f>IF(AY34&gt;=AY31-0.5,"Build capacity",IF(AY34&gt;=AY22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="AZ35" s="67">
-        <f>IF(AZ34&gt;=AZ31-0.5,"Build capacity",IF(AZ34&gt;=AZ22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BA35" s="67">
-        <f>IF(BA34&gt;=BA31-0.5,"Build capacity",IF(BA34&gt;=BA22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BB35" s="67">
-        <f>IF(BB34&gt;=BB31-0.5,"Build capacity",IF(BB34&gt;=BB22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BC35" s="67">
-        <f>IF(BC34&gt;=BC31-0.5,"Build capacity",IF(BC34&gt;=BC22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BD35" s="67">
-        <f>IF(BD34&gt;=BD31-0.5,"Build capacity",IF(BD34&gt;=BD22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BE35" s="67">
-        <f>IF(BE34&gt;=BE31-0.5,"Build capacity",IF(BE34&gt;=BE22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BF35" s="67">
-        <f>IF(BF34&gt;=BF31-0.5,"Build capacity",IF(BF34&gt;=BF22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BG35" s="67">
-        <f>IF(BG34&gt;=BG31-0.5,"Build capacity",IF(BG34&gt;=BG22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BH35" s="67">
-        <f>IF(BH34&gt;=BH31-0.5,"Build capacity",IF(BH34&gt;=BH22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BI35" s="67">
-        <f>IF(BI34&gt;=BI31-0.5,"Build capacity",IF(BI34&gt;=BI22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BJ35" s="67">
-        <f>IF(BJ34&gt;=BJ31-0.5,"Build capacity",IF(BJ34&gt;=BJ22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BK35" s="67">
-        <f>IF(BK34&gt;=BK31-0.5,"Build capacity",IF(BK34&gt;=BK22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BL35" s="67">
-        <f>IF(BL34&gt;=BL31-0.5,"Build capacity",IF(BL34&gt;=BL22-0.5,"Selling capacity","Demand"))</f>
-        <v/>
-      </c>
-      <c r="BN35" s="68">
-        <f>P35</f>
-        <v/>
-      </c>
-      <c r="BO35" s="68">
-        <f>AB35</f>
-        <v/>
-      </c>
-      <c r="BP35" s="68">
-        <f>AN35</f>
-        <v/>
-      </c>
-      <c r="BQ35" s="68">
-        <f>AZ35</f>
-        <v/>
-      </c>
-      <c r="BR35" s="68">
-        <f>BL35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="47" t="inlineStr">
+      <c r="B35" s="47" t="inlineStr">
         <is>
           <t>Build capacity used</t>
         </is>
       </c>
-      <c r="C36" s="42" t="inlineStr">
+      <c r="C35" s="42" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E36" s="64">
+      <c r="E35" s="64">
         <f>IFERROR(E34/E31,0)</f>
         <v/>
       </c>
-      <c r="F36" s="64">
+      <c r="F35" s="64">
         <f>IFERROR(F34/F31,0)</f>
         <v/>
       </c>
-      <c r="G36" s="64">
+      <c r="G35" s="64">
         <f>IFERROR(G34/G31,0)</f>
         <v/>
       </c>
-      <c r="H36" s="64">
+      <c r="H35" s="64">
         <f>IFERROR(H34/H31,0)</f>
         <v/>
       </c>
-      <c r="I36" s="64">
+      <c r="I35" s="64">
         <f>IFERROR(I34/I31,0)</f>
         <v/>
       </c>
-      <c r="J36" s="64">
+      <c r="J35" s="64">
         <f>IFERROR(J34/J31,0)</f>
         <v/>
       </c>
-      <c r="K36" s="64">
+      <c r="K35" s="64">
         <f>IFERROR(K34/K31,0)</f>
         <v/>
       </c>
-      <c r="L36" s="64">
+      <c r="L35" s="64">
         <f>IFERROR(L34/L31,0)</f>
         <v/>
       </c>
-      <c r="M36" s="64">
+      <c r="M35" s="64">
         <f>IFERROR(M34/M31,0)</f>
         <v/>
       </c>
-      <c r="N36" s="64">
+      <c r="N35" s="64">
         <f>IFERROR(N34/N31,0)</f>
         <v/>
       </c>
-      <c r="O36" s="64">
+      <c r="O35" s="64">
         <f>IFERROR(O34/O31,0)</f>
         <v/>
       </c>
-      <c r="P36" s="64">
+      <c r="P35" s="64">
         <f>IFERROR(P34/P31,0)</f>
         <v/>
       </c>
-      <c r="Q36" s="64">
+      <c r="Q35" s="64">
         <f>IFERROR(Q34/Q31,0)</f>
         <v/>
       </c>
-      <c r="R36" s="64">
+      <c r="R35" s="64">
         <f>IFERROR(R34/R31,0)</f>
         <v/>
       </c>
-      <c r="S36" s="64">
+      <c r="S35" s="64">
         <f>IFERROR(S34/S31,0)</f>
         <v/>
       </c>
-      <c r="T36" s="64">
+      <c r="T35" s="64">
         <f>IFERROR(T34/T31,0)</f>
         <v/>
       </c>
-      <c r="U36" s="64">
+      <c r="U35" s="64">
         <f>IFERROR(U34/U31,0)</f>
         <v/>
       </c>
-      <c r="V36" s="64">
+      <c r="V35" s="64">
         <f>IFERROR(V34/V31,0)</f>
         <v/>
       </c>
-      <c r="W36" s="64">
+      <c r="W35" s="64">
         <f>IFERROR(W34/W31,0)</f>
         <v/>
       </c>
-      <c r="X36" s="64">
+      <c r="X35" s="64">
         <f>IFERROR(X34/X31,0)</f>
         <v/>
       </c>
-      <c r="Y36" s="64">
+      <c r="Y35" s="64">
         <f>IFERROR(Y34/Y31,0)</f>
         <v/>
       </c>
-      <c r="Z36" s="64">
+      <c r="Z35" s="64">
         <f>IFERROR(Z34/Z31,0)</f>
         <v/>
       </c>
-      <c r="AA36" s="64">
+      <c r="AA35" s="64">
         <f>IFERROR(AA34/AA31,0)</f>
         <v/>
       </c>
-      <c r="AB36" s="64">
+      <c r="AB35" s="64">
         <f>IFERROR(AB34/AB31,0)</f>
         <v/>
       </c>
-      <c r="AC36" s="64">
+      <c r="AC35" s="64">
         <f>IFERROR(AC34/AC31,0)</f>
         <v/>
       </c>
-      <c r="AD36" s="64">
+      <c r="AD35" s="64">
         <f>IFERROR(AD34/AD31,0)</f>
         <v/>
       </c>
-      <c r="AE36" s="64">
+      <c r="AE35" s="64">
         <f>IFERROR(AE34/AE31,0)</f>
         <v/>
       </c>
-      <c r="AF36" s="64">
+      <c r="AF35" s="64">
         <f>IFERROR(AF34/AF31,0)</f>
         <v/>
       </c>
-      <c r="AG36" s="64">
+      <c r="AG35" s="64">
         <f>IFERROR(AG34/AG31,0)</f>
         <v/>
       </c>
-      <c r="AH36" s="64">
+      <c r="AH35" s="64">
         <f>IFERROR(AH34/AH31,0)</f>
         <v/>
       </c>
-      <c r="AI36" s="64">
+      <c r="AI35" s="64">
         <f>IFERROR(AI34/AI31,0)</f>
         <v/>
       </c>
-      <c r="AJ36" s="64">
+      <c r="AJ35" s="64">
         <f>IFERROR(AJ34/AJ31,0)</f>
         <v/>
       </c>
-      <c r="AK36" s="64">
+      <c r="AK35" s="64">
         <f>IFERROR(AK34/AK31,0)</f>
         <v/>
       </c>
-      <c r="AL36" s="64">
+      <c r="AL35" s="64">
         <f>IFERROR(AL34/AL31,0)</f>
         <v/>
       </c>
-      <c r="AM36" s="64">
+      <c r="AM35" s="64">
         <f>IFERROR(AM34/AM31,0)</f>
         <v/>
       </c>
-      <c r="AN36" s="64">
+      <c r="AN35" s="64">
         <f>IFERROR(AN34/AN31,0)</f>
         <v/>
       </c>
-      <c r="AO36" s="64">
+      <c r="AO35" s="64">
         <f>IFERROR(AO34/AO31,0)</f>
         <v/>
       </c>
-      <c r="AP36" s="64">
+      <c r="AP35" s="64">
         <f>IFERROR(AP34/AP31,0)</f>
         <v/>
       </c>
-      <c r="AQ36" s="64">
+      <c r="AQ35" s="64">
         <f>IFERROR(AQ34/AQ31,0)</f>
         <v/>
       </c>
-      <c r="AR36" s="64">
+      <c r="AR35" s="64">
         <f>IFERROR(AR34/AR31,0)</f>
         <v/>
       </c>
-      <c r="AS36" s="64">
+      <c r="AS35" s="64">
         <f>IFERROR(AS34/AS31,0)</f>
         <v/>
       </c>
-      <c r="AT36" s="64">
+      <c r="AT35" s="64">
         <f>IFERROR(AT34/AT31,0)</f>
         <v/>
       </c>
-      <c r="AU36" s="64">
+      <c r="AU35" s="64">
         <f>IFERROR(AU34/AU31,0)</f>
         <v/>
       </c>
-      <c r="AV36" s="64">
+      <c r="AV35" s="64">
         <f>IFERROR(AV34/AV31,0)</f>
         <v/>
       </c>
-      <c r="AW36" s="64">
+      <c r="AW35" s="64">
         <f>IFERROR(AW34/AW31,0)</f>
         <v/>
       </c>
-      <c r="AX36" s="64">
+      <c r="AX35" s="64">
         <f>IFERROR(AX34/AX31,0)</f>
         <v/>
       </c>
-      <c r="AY36" s="64">
+      <c r="AY35" s="64">
         <f>IFERROR(AY34/AY31,0)</f>
         <v/>
       </c>
-      <c r="AZ36" s="64">
+      <c r="AZ35" s="64">
         <f>IFERROR(AZ34/AZ31,0)</f>
         <v/>
       </c>
-      <c r="BA36" s="64">
+      <c r="BA35" s="64">
         <f>IFERROR(BA34/BA31,0)</f>
         <v/>
       </c>
-      <c r="BB36" s="64">
+      <c r="BB35" s="64">
         <f>IFERROR(BB34/BB31,0)</f>
         <v/>
       </c>
-      <c r="BC36" s="64">
+      <c r="BC35" s="64">
         <f>IFERROR(BC34/BC31,0)</f>
         <v/>
       </c>
-      <c r="BD36" s="64">
+      <c r="BD35" s="64">
         <f>IFERROR(BD34/BD31,0)</f>
         <v/>
       </c>
-      <c r="BE36" s="64">
+      <c r="BE35" s="64">
         <f>IFERROR(BE34/BE31,0)</f>
         <v/>
       </c>
-      <c r="BF36" s="64">
+      <c r="BF35" s="64">
         <f>IFERROR(BF34/BF31,0)</f>
         <v/>
       </c>
-      <c r="BG36" s="64">
+      <c r="BG35" s="64">
         <f>IFERROR(BG34/BG31,0)</f>
         <v/>
       </c>
-      <c r="BH36" s="64">
+      <c r="BH35" s="64">
         <f>IFERROR(BH34/BH31,0)</f>
         <v/>
       </c>
-      <c r="BI36" s="64">
+      <c r="BI35" s="64">
         <f>IFERROR(BI34/BI31,0)</f>
         <v/>
       </c>
-      <c r="BJ36" s="64">
+      <c r="BJ35" s="64">
         <f>IFERROR(BJ34/BJ31,0)</f>
         <v/>
       </c>
-      <c r="BK36" s="64">
+      <c r="BK35" s="64">
         <f>IFERROR(BK34/BK31,0)</f>
         <v/>
       </c>
-      <c r="BL36" s="64">
+      <c r="BL35" s="64">
         <f>IFERROR(BL34/BL31,0)</f>
         <v/>
       </c>
-      <c r="BN36" s="65">
-        <f>IFERROR(AVERAGE(E36:P36),0)</f>
-        <v/>
-      </c>
-      <c r="BO36" s="65">
-        <f>IFERROR(AVERAGE(Q36:AB36),0)</f>
-        <v/>
-      </c>
-      <c r="BP36" s="65">
-        <f>IFERROR(AVERAGE(AC36:AN36),0)</f>
-        <v/>
-      </c>
-      <c r="BQ36" s="65">
-        <f>IFERROR(AVERAGE(AO36:AZ36),0)</f>
-        <v/>
-      </c>
-      <c r="BR36" s="65">
-        <f>IFERROR(AVERAGE(BA36:BL36),0)</f>
+      <c r="BN35" s="65">
+        <f>IFERROR(AVERAGE(E35:P35),0)</f>
+        <v/>
+      </c>
+      <c r="BO35" s="65">
+        <f>IFERROR(AVERAGE(Q35:AB35),0)</f>
+        <v/>
+      </c>
+      <c r="BP35" s="65">
+        <f>IFERROR(AVERAGE(AC35:AN35),0)</f>
+        <v/>
+      </c>
+      <c r="BQ35" s="65">
+        <f>IFERROR(AVERAGE(AO35:AZ35),0)</f>
+        <v/>
+      </c>
+      <c r="BR35" s="65">
+        <f>IFERROR(AVERAGE(BA35:BL35),0)</f>
         <v/>
       </c>
     </row>
@@ -41510,263 +41230,263 @@
           <t>FTE</t>
         </is>
       </c>
-      <c r="E7" s="69">
+      <c r="E7" s="67">
         <f>'Revenue Forecast'!E23</f>
         <v/>
       </c>
-      <c r="F7" s="69">
+      <c r="F7" s="67">
         <f>'Revenue Forecast'!F23</f>
         <v/>
       </c>
-      <c r="G7" s="69">
+      <c r="G7" s="67">
         <f>'Revenue Forecast'!G23</f>
         <v/>
       </c>
-      <c r="H7" s="69">
+      <c r="H7" s="67">
         <f>'Revenue Forecast'!H23</f>
         <v/>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="67">
         <f>'Revenue Forecast'!I23</f>
         <v/>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="67">
         <f>'Revenue Forecast'!J23</f>
         <v/>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="67">
         <f>'Revenue Forecast'!K23</f>
         <v/>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="67">
         <f>'Revenue Forecast'!L23</f>
         <v/>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="67">
         <f>'Revenue Forecast'!M23</f>
         <v/>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="67">
         <f>'Revenue Forecast'!N23</f>
         <v/>
       </c>
-      <c r="O7" s="69">
+      <c r="O7" s="67">
         <f>'Revenue Forecast'!O23</f>
         <v/>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="67">
         <f>'Revenue Forecast'!P23</f>
         <v/>
       </c>
-      <c r="Q7" s="69">
+      <c r="Q7" s="67">
         <f>'Revenue Forecast'!Q23</f>
         <v/>
       </c>
-      <c r="R7" s="69">
+      <c r="R7" s="67">
         <f>'Revenue Forecast'!R23</f>
         <v/>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="67">
         <f>'Revenue Forecast'!S23</f>
         <v/>
       </c>
-      <c r="T7" s="69">
+      <c r="T7" s="67">
         <f>'Revenue Forecast'!T23</f>
         <v/>
       </c>
-      <c r="U7" s="69">
+      <c r="U7" s="67">
         <f>'Revenue Forecast'!U23</f>
         <v/>
       </c>
-      <c r="V7" s="69">
+      <c r="V7" s="67">
         <f>'Revenue Forecast'!V23</f>
         <v/>
       </c>
-      <c r="W7" s="69">
+      <c r="W7" s="67">
         <f>'Revenue Forecast'!W23</f>
         <v/>
       </c>
-      <c r="X7" s="69">
+      <c r="X7" s="67">
         <f>'Revenue Forecast'!X23</f>
         <v/>
       </c>
-      <c r="Y7" s="69">
+      <c r="Y7" s="67">
         <f>'Revenue Forecast'!Y23</f>
         <v/>
       </c>
-      <c r="Z7" s="69">
+      <c r="Z7" s="67">
         <f>'Revenue Forecast'!Z23</f>
         <v/>
       </c>
-      <c r="AA7" s="69">
+      <c r="AA7" s="67">
         <f>'Revenue Forecast'!AA23</f>
         <v/>
       </c>
-      <c r="AB7" s="69">
+      <c r="AB7" s="67">
         <f>'Revenue Forecast'!AB23</f>
         <v/>
       </c>
-      <c r="AC7" s="69">
+      <c r="AC7" s="67">
         <f>'Revenue Forecast'!AC23</f>
         <v/>
       </c>
-      <c r="AD7" s="69">
+      <c r="AD7" s="67">
         <f>'Revenue Forecast'!AD23</f>
         <v/>
       </c>
-      <c r="AE7" s="69">
+      <c r="AE7" s="67">
         <f>'Revenue Forecast'!AE23</f>
         <v/>
       </c>
-      <c r="AF7" s="69">
+      <c r="AF7" s="67">
         <f>'Revenue Forecast'!AF23</f>
         <v/>
       </c>
-      <c r="AG7" s="69">
+      <c r="AG7" s="67">
         <f>'Revenue Forecast'!AG23</f>
         <v/>
       </c>
-      <c r="AH7" s="69">
+      <c r="AH7" s="67">
         <f>'Revenue Forecast'!AH23</f>
         <v/>
       </c>
-      <c r="AI7" s="69">
+      <c r="AI7" s="67">
         <f>'Revenue Forecast'!AI23</f>
         <v/>
       </c>
-      <c r="AJ7" s="69">
+      <c r="AJ7" s="67">
         <f>'Revenue Forecast'!AJ23</f>
         <v/>
       </c>
-      <c r="AK7" s="69">
+      <c r="AK7" s="67">
         <f>'Revenue Forecast'!AK23</f>
         <v/>
       </c>
-      <c r="AL7" s="69">
+      <c r="AL7" s="67">
         <f>'Revenue Forecast'!AL23</f>
         <v/>
       </c>
-      <c r="AM7" s="69">
+      <c r="AM7" s="67">
         <f>'Revenue Forecast'!AM23</f>
         <v/>
       </c>
-      <c r="AN7" s="69">
+      <c r="AN7" s="67">
         <f>'Revenue Forecast'!AN23</f>
         <v/>
       </c>
-      <c r="AO7" s="69">
+      <c r="AO7" s="67">
         <f>'Revenue Forecast'!AO23</f>
         <v/>
       </c>
-      <c r="AP7" s="69">
+      <c r="AP7" s="67">
         <f>'Revenue Forecast'!AP23</f>
         <v/>
       </c>
-      <c r="AQ7" s="69">
+      <c r="AQ7" s="67">
         <f>'Revenue Forecast'!AQ23</f>
         <v/>
       </c>
-      <c r="AR7" s="69">
+      <c r="AR7" s="67">
         <f>'Revenue Forecast'!AR23</f>
         <v/>
       </c>
-      <c r="AS7" s="69">
+      <c r="AS7" s="67">
         <f>'Revenue Forecast'!AS23</f>
         <v/>
       </c>
-      <c r="AT7" s="69">
+      <c r="AT7" s="67">
         <f>'Revenue Forecast'!AT23</f>
         <v/>
       </c>
-      <c r="AU7" s="69">
+      <c r="AU7" s="67">
         <f>'Revenue Forecast'!AU23</f>
         <v/>
       </c>
-      <c r="AV7" s="69">
+      <c r="AV7" s="67">
         <f>'Revenue Forecast'!AV23</f>
         <v/>
       </c>
-      <c r="AW7" s="69">
+      <c r="AW7" s="67">
         <f>'Revenue Forecast'!AW23</f>
         <v/>
       </c>
-      <c r="AX7" s="69">
+      <c r="AX7" s="67">
         <f>'Revenue Forecast'!AX23</f>
         <v/>
       </c>
-      <c r="AY7" s="69">
+      <c r="AY7" s="67">
         <f>'Revenue Forecast'!AY23</f>
         <v/>
       </c>
-      <c r="AZ7" s="69">
+      <c r="AZ7" s="67">
         <f>'Revenue Forecast'!AZ23</f>
         <v/>
       </c>
-      <c r="BA7" s="69">
+      <c r="BA7" s="67">
         <f>'Revenue Forecast'!BA23</f>
         <v/>
       </c>
-      <c r="BB7" s="69">
+      <c r="BB7" s="67">
         <f>'Revenue Forecast'!BB23</f>
         <v/>
       </c>
-      <c r="BC7" s="69">
+      <c r="BC7" s="67">
         <f>'Revenue Forecast'!BC23</f>
         <v/>
       </c>
-      <c r="BD7" s="69">
+      <c r="BD7" s="67">
         <f>'Revenue Forecast'!BD23</f>
         <v/>
       </c>
-      <c r="BE7" s="69">
+      <c r="BE7" s="67">
         <f>'Revenue Forecast'!BE23</f>
         <v/>
       </c>
-      <c r="BF7" s="69">
+      <c r="BF7" s="67">
         <f>'Revenue Forecast'!BF23</f>
         <v/>
       </c>
-      <c r="BG7" s="69">
+      <c r="BG7" s="67">
         <f>'Revenue Forecast'!BG23</f>
         <v/>
       </c>
-      <c r="BH7" s="69">
+      <c r="BH7" s="67">
         <f>'Revenue Forecast'!BH23</f>
         <v/>
       </c>
-      <c r="BI7" s="69">
+      <c r="BI7" s="67">
         <f>'Revenue Forecast'!BI23</f>
         <v/>
       </c>
-      <c r="BJ7" s="69">
+      <c r="BJ7" s="67">
         <f>'Revenue Forecast'!BJ23</f>
         <v/>
       </c>
-      <c r="BK7" s="69">
+      <c r="BK7" s="67">
         <f>'Revenue Forecast'!BK23</f>
         <v/>
       </c>
-      <c r="BL7" s="69">
+      <c r="BL7" s="67">
         <f>'Revenue Forecast'!BL23</f>
         <v/>
       </c>
-      <c r="BN7" s="70">
+      <c r="BN7" s="68">
         <f>P7</f>
         <v/>
       </c>
-      <c r="BO7" s="70">
+      <c r="BO7" s="68">
         <f>AB7</f>
         <v/>
       </c>
-      <c r="BP7" s="70">
+      <c r="BP7" s="68">
         <f>AN7</f>
         <v/>
       </c>
-      <c r="BQ7" s="70">
+      <c r="BQ7" s="68">
         <f>AZ7</f>
         <v/>
       </c>
-      <c r="BR7" s="70">
+      <c r="BR7" s="68">
         <f>BL7</f>
         <v/>
       </c>
@@ -45893,264 +45613,264 @@
         </is>
       </c>
       <c r="D23" s="1" t="n"/>
-      <c r="E23" s="71">
+      <c r="E23" s="69">
         <f>E21+E22</f>
         <v/>
       </c>
-      <c r="F23" s="71">
+      <c r="F23" s="69">
         <f>F21+F22</f>
         <v/>
       </c>
-      <c r="G23" s="71">
+      <c r="G23" s="69">
         <f>G21+G22</f>
         <v/>
       </c>
-      <c r="H23" s="71">
+      <c r="H23" s="69">
         <f>H21+H22</f>
         <v/>
       </c>
-      <c r="I23" s="71">
+      <c r="I23" s="69">
         <f>I21+I22</f>
         <v/>
       </c>
-      <c r="J23" s="71">
+      <c r="J23" s="69">
         <f>J21+J22</f>
         <v/>
       </c>
-      <c r="K23" s="71">
+      <c r="K23" s="69">
         <f>K21+K22</f>
         <v/>
       </c>
-      <c r="L23" s="71">
+      <c r="L23" s="69">
         <f>L21+L22</f>
         <v/>
       </c>
-      <c r="M23" s="71">
+      <c r="M23" s="69">
         <f>M21+M22</f>
         <v/>
       </c>
-      <c r="N23" s="71">
+      <c r="N23" s="69">
         <f>N21+N22</f>
         <v/>
       </c>
-      <c r="O23" s="71">
+      <c r="O23" s="69">
         <f>O21+O22</f>
         <v/>
       </c>
-      <c r="P23" s="71">
+      <c r="P23" s="69">
         <f>P21+P22</f>
         <v/>
       </c>
-      <c r="Q23" s="71">
+      <c r="Q23" s="69">
         <f>Q21+Q22</f>
         <v/>
       </c>
-      <c r="R23" s="71">
+      <c r="R23" s="69">
         <f>R21+R22</f>
         <v/>
       </c>
-      <c r="S23" s="71">
+      <c r="S23" s="69">
         <f>S21+S22</f>
         <v/>
       </c>
-      <c r="T23" s="71">
+      <c r="T23" s="69">
         <f>T21+T22</f>
         <v/>
       </c>
-      <c r="U23" s="71">
+      <c r="U23" s="69">
         <f>U21+U22</f>
         <v/>
       </c>
-      <c r="V23" s="71">
+      <c r="V23" s="69">
         <f>V21+V22</f>
         <v/>
       </c>
-      <c r="W23" s="71">
+      <c r="W23" s="69">
         <f>W21+W22</f>
         <v/>
       </c>
-      <c r="X23" s="71">
+      <c r="X23" s="69">
         <f>X21+X22</f>
         <v/>
       </c>
-      <c r="Y23" s="71">
+      <c r="Y23" s="69">
         <f>Y21+Y22</f>
         <v/>
       </c>
-      <c r="Z23" s="71">
+      <c r="Z23" s="69">
         <f>Z21+Z22</f>
         <v/>
       </c>
-      <c r="AA23" s="71">
+      <c r="AA23" s="69">
         <f>AA21+AA22</f>
         <v/>
       </c>
-      <c r="AB23" s="71">
+      <c r="AB23" s="69">
         <f>AB21+AB22</f>
         <v/>
       </c>
-      <c r="AC23" s="71">
+      <c r="AC23" s="69">
         <f>AC21+AC22</f>
         <v/>
       </c>
-      <c r="AD23" s="71">
+      <c r="AD23" s="69">
         <f>AD21+AD22</f>
         <v/>
       </c>
-      <c r="AE23" s="71">
+      <c r="AE23" s="69">
         <f>AE21+AE22</f>
         <v/>
       </c>
-      <c r="AF23" s="71">
+      <c r="AF23" s="69">
         <f>AF21+AF22</f>
         <v/>
       </c>
-      <c r="AG23" s="71">
+      <c r="AG23" s="69">
         <f>AG21+AG22</f>
         <v/>
       </c>
-      <c r="AH23" s="71">
+      <c r="AH23" s="69">
         <f>AH21+AH22</f>
         <v/>
       </c>
-      <c r="AI23" s="71">
+      <c r="AI23" s="69">
         <f>AI21+AI22</f>
         <v/>
       </c>
-      <c r="AJ23" s="71">
+      <c r="AJ23" s="69">
         <f>AJ21+AJ22</f>
         <v/>
       </c>
-      <c r="AK23" s="71">
+      <c r="AK23" s="69">
         <f>AK21+AK22</f>
         <v/>
       </c>
-      <c r="AL23" s="71">
+      <c r="AL23" s="69">
         <f>AL21+AL22</f>
         <v/>
       </c>
-      <c r="AM23" s="71">
+      <c r="AM23" s="69">
         <f>AM21+AM22</f>
         <v/>
       </c>
-      <c r="AN23" s="71">
+      <c r="AN23" s="69">
         <f>AN21+AN22</f>
         <v/>
       </c>
-      <c r="AO23" s="71">
+      <c r="AO23" s="69">
         <f>AO21+AO22</f>
         <v/>
       </c>
-      <c r="AP23" s="71">
+      <c r="AP23" s="69">
         <f>AP21+AP22</f>
         <v/>
       </c>
-      <c r="AQ23" s="71">
+      <c r="AQ23" s="69">
         <f>AQ21+AQ22</f>
         <v/>
       </c>
-      <c r="AR23" s="71">
+      <c r="AR23" s="69">
         <f>AR21+AR22</f>
         <v/>
       </c>
-      <c r="AS23" s="71">
+      <c r="AS23" s="69">
         <f>AS21+AS22</f>
         <v/>
       </c>
-      <c r="AT23" s="71">
+      <c r="AT23" s="69">
         <f>AT21+AT22</f>
         <v/>
       </c>
-      <c r="AU23" s="71">
+      <c r="AU23" s="69">
         <f>AU21+AU22</f>
         <v/>
       </c>
-      <c r="AV23" s="71">
+      <c r="AV23" s="69">
         <f>AV21+AV22</f>
         <v/>
       </c>
-      <c r="AW23" s="71">
+      <c r="AW23" s="69">
         <f>AW21+AW22</f>
         <v/>
       </c>
-      <c r="AX23" s="71">
+      <c r="AX23" s="69">
         <f>AX21+AX22</f>
         <v/>
       </c>
-      <c r="AY23" s="71">
+      <c r="AY23" s="69">
         <f>AY21+AY22</f>
         <v/>
       </c>
-      <c r="AZ23" s="71">
+      <c r="AZ23" s="69">
         <f>AZ21+AZ22</f>
         <v/>
       </c>
-      <c r="BA23" s="71">
+      <c r="BA23" s="69">
         <f>BA21+BA22</f>
         <v/>
       </c>
-      <c r="BB23" s="71">
+      <c r="BB23" s="69">
         <f>BB21+BB22</f>
         <v/>
       </c>
-      <c r="BC23" s="71">
+      <c r="BC23" s="69">
         <f>BC21+BC22</f>
         <v/>
       </c>
-      <c r="BD23" s="71">
+      <c r="BD23" s="69">
         <f>BD21+BD22</f>
         <v/>
       </c>
-      <c r="BE23" s="71">
+      <c r="BE23" s="69">
         <f>BE21+BE22</f>
         <v/>
       </c>
-      <c r="BF23" s="71">
+      <c r="BF23" s="69">
         <f>BF21+BF22</f>
         <v/>
       </c>
-      <c r="BG23" s="71">
+      <c r="BG23" s="69">
         <f>BG21+BG22</f>
         <v/>
       </c>
-      <c r="BH23" s="71">
+      <c r="BH23" s="69">
         <f>BH21+BH22</f>
         <v/>
       </c>
-      <c r="BI23" s="71">
+      <c r="BI23" s="69">
         <f>BI21+BI22</f>
         <v/>
       </c>
-      <c r="BJ23" s="71">
+      <c r="BJ23" s="69">
         <f>BJ21+BJ22</f>
         <v/>
       </c>
-      <c r="BK23" s="71">
+      <c r="BK23" s="69">
         <f>BK21+BK22</f>
         <v/>
       </c>
-      <c r="BL23" s="71">
+      <c r="BL23" s="69">
         <f>BL21+BL22</f>
         <v/>
       </c>
       <c r="BM23" s="1" t="n"/>
-      <c r="BN23" s="71">
+      <c r="BN23" s="69">
         <f>P23</f>
         <v/>
       </c>
-      <c r="BO23" s="71">
+      <c r="BO23" s="69">
         <f>AB23</f>
         <v/>
       </c>
-      <c r="BP23" s="71">
+      <c r="BP23" s="69">
         <f>AN23</f>
         <v/>
       </c>
-      <c r="BQ23" s="71">
+      <c r="BQ23" s="69">
         <f>AZ23</f>
         <v/>
       </c>
-      <c r="BR23" s="71">
+      <c r="BR23" s="69">
         <f>BL23</f>
         <v/>
       </c>
@@ -47733,112 +47453,80 @@
     <row r="8">
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Why we did not sell more, December</t>
-        </is>
-      </c>
-      <c r="D8" s="67">
-        <f>'Revenue Forecast'!P35</f>
-        <v/>
-      </c>
-      <c r="E8" s="67">
-        <f>'Revenue Forecast'!AB35</f>
-        <v/>
-      </c>
-      <c r="F8" s="67">
-        <f>'Revenue Forecast'!AN35</f>
-        <v/>
-      </c>
-      <c r="G8" s="67">
-        <f>'Revenue Forecast'!AZ35</f>
-        <v/>
-      </c>
-      <c r="H8" s="67">
-        <f>'Revenue Forecast'!BL35</f>
-        <v/>
-      </c>
-      <c r="J8" s="20" t="inlineStr">
-        <is>
-          <t>the reason the plan could not sell more in the last month of the year</t>
-        </is>
+          <t>Build capacity used</t>
+        </is>
+      </c>
+      <c r="D8" s="48">
+        <f>'Revenue Forecast'!BN35</f>
+        <v/>
+      </c>
+      <c r="E8" s="48">
+        <f>'Revenue Forecast'!BO35</f>
+        <v/>
+      </c>
+      <c r="F8" s="48">
+        <f>'Revenue Forecast'!BP35</f>
+        <v/>
+      </c>
+      <c r="G8" s="48">
+        <f>'Revenue Forecast'!BQ35</f>
+        <v/>
+      </c>
+      <c r="H8" s="48">
+        <f>'Revenue Forecast'!BR35</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Build capacity used</t>
-        </is>
-      </c>
-      <c r="D9" s="48">
-        <f>'Revenue Forecast'!BN36</f>
-        <v/>
-      </c>
-      <c r="E9" s="48">
-        <f>'Revenue Forecast'!BO36</f>
-        <v/>
-      </c>
-      <c r="F9" s="48">
-        <f>'Revenue Forecast'!BP36</f>
-        <v/>
-      </c>
-      <c r="G9" s="48">
-        <f>'Revenue Forecast'!BQ36</f>
-        <v/>
-      </c>
-      <c r="H9" s="48">
-        <f>'Revenue Forecast'!BR36</f>
+          <t>Installer partners at year end</t>
+        </is>
+      </c>
+      <c r="D9" s="62">
+        <f>'Revenue Forecast'!BN20</f>
+        <v/>
+      </c>
+      <c r="E9" s="62">
+        <f>'Revenue Forecast'!BO20</f>
+        <v/>
+      </c>
+      <c r="F9" s="62">
+        <f>'Revenue Forecast'!BP20</f>
+        <v/>
+      </c>
+      <c r="G9" s="62">
+        <f>'Revenue Forecast'!BQ20</f>
+        <v/>
+      </c>
+      <c r="H9" s="62">
+        <f>'Revenue Forecast'!BR20</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Installer partners at year end</t>
-        </is>
-      </c>
-      <c r="D10" s="62">
-        <f>'Revenue Forecast'!BN20</f>
-        <v/>
-      </c>
-      <c r="E10" s="62">
-        <f>'Revenue Forecast'!BO20</f>
-        <v/>
-      </c>
-      <c r="F10" s="62">
-        <f>'Revenue Forecast'!BP20</f>
-        <v/>
-      </c>
-      <c r="G10" s="62">
-        <f>'Revenue Forecast'!BQ20</f>
-        <v/>
-      </c>
-      <c r="H10" s="62">
-        <f>'Revenue Forecast'!BR20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="9" t="inlineStr">
-        <is>
           <t>Marketing cost per unit sold</t>
         </is>
       </c>
-      <c r="D11" s="43">
+      <c r="D10" s="43">
         <f>'Revenue Forecast'!BN12</f>
         <v/>
       </c>
-      <c r="E11" s="43">
+      <c r="E10" s="43">
         <f>'Revenue Forecast'!BO12</f>
         <v/>
       </c>
-      <c r="F11" s="43">
+      <c r="F10" s="43">
         <f>'Revenue Forecast'!BP12</f>
         <v/>
       </c>
-      <c r="G11" s="43">
+      <c r="G10" s="43">
         <f>'Revenue Forecast'!BQ12</f>
         <v/>
       </c>
-      <c r="H11" s="43">
+      <c r="H10" s="43">
         <f>'Revenue Forecast'!BR12</f>
         <v/>
       </c>
@@ -48309,7 +47997,7 @@
           <t>Balance sheet check, worst month across the whole model</t>
         </is>
       </c>
-      <c r="D34" s="72">
+      <c r="D34" s="70">
         <f>MAX(ABS(MIN('Financial Statements'!$E$58:$BL$58)),ABS(MAX('Financial Statements'!$E$58:$BL$58)))</f>
         <v/>
       </c>
@@ -48356,7 +48044,7 @@
           <t>The month it happens</t>
         </is>
       </c>
-      <c r="D38" s="73">
+      <c r="D38" s="71">
         <f>INDEX('Financial Statements'!$E$3:$BL$3,MATCH(D37,'Financial Statements'!$N$40:$BL$40,0)+9)</f>
         <v/>
       </c>
@@ -48507,7 +48195,7 @@
           <t>Share of the raise the plan actually uses</t>
         </is>
       </c>
-      <c r="D52" s="74">
+      <c r="D52" s="72">
         <f>IFERROR(D51/SUM('Financial Statements'!N35:BL35),0)</f>
         <v/>
       </c>

--- a/models/Tarnoc_v2_2026-09-01.xlsx
+++ b/models/Tarnoc_v2_2026-09-01.xlsx
@@ -1315,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J149"/>
+  <dimension ref="B1:J148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3786,7 +3786,7 @@
     <row r="113">
       <c r="B113" s="31" t="inlineStr">
         <is>
-          <t>Leadership and administration, core team</t>
+          <t>Leadership, finance, HR, IT and legal</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -3812,7 +3812,7 @@
       <c r="I113" s="21" t="n"/>
       <c r="J113" s="34" t="inlineStr">
         <is>
-          <t>the leadership team is in post by the end of 2026</t>
+          <t>the whole back office, typed per year: leadership in post by end 2026, then finance, HR, IT and legal as the company grows</t>
         </is>
       </c>
     </row>
@@ -3826,16 +3826,16 @@
         <v>3</v>
       </c>
       <c r="E114" s="29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" s="29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G114" s="29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H114" s="29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115">
@@ -3848,16 +3848,16 @@
         <v>3</v>
       </c>
       <c r="E115" s="29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F115" s="29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G115" s="29" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H115" s="29" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116">
@@ -3913,94 +3913,89 @@
     <row r="118">
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Staff per G&amp;A FTE</t>
+          <t>Service visits per engineer per year</t>
         </is>
       </c>
       <c r="C118" s="18" t="inlineStr">
         <is>
-          <t>FTE</t>
+          <t>visits</t>
         </is>
       </c>
       <c r="D118" s="29" t="n">
-        <v>9</v>
+        <v>750</v>
       </c>
       <c r="E118" s="29" t="n">
-        <v>9</v>
+        <v>750</v>
       </c>
       <c r="F118" s="30">
         <f>IF(Assumptions!$E$5=2,E118,D118)</f>
         <v/>
       </c>
-      <c r="J118" s="20" t="inlineStr">
-        <is>
-          <t>finance, HR, IT, legal and office</t>
-        </is>
-      </c>
     </row>
     <row r="119">
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>Service visits per engineer per year</t>
-        </is>
-      </c>
-      <c r="C119" s="18" t="inlineStr">
-        <is>
-          <t>visits</t>
-        </is>
-      </c>
-      <c r="D119" s="29" t="n">
-        <v>750</v>
-      </c>
-      <c r="E119" s="29" t="n">
-        <v>750</v>
-      </c>
-      <c r="F119" s="30">
-        <f>IF(Assumptions!$E$5=2,E119,D119)</f>
-        <v/>
-      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>LOADED COST PER PERSON  (employer cost, including taxes)</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n"/>
+      <c r="D119" s="1" t="n"/>
+      <c r="E119" s="1" t="n"/>
+      <c r="F119" s="1" t="n"/>
+      <c r="G119" s="1" t="n"/>
+      <c r="H119" s="1" t="n"/>
+      <c r="I119" s="1" t="n"/>
+      <c r="J119" s="1" t="n"/>
     </row>
     <row r="120">
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>LOADED COST PER PERSON  (employer cost, including taxes)</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="n"/>
-      <c r="D120" s="1" t="n"/>
-      <c r="E120" s="1" t="n"/>
-      <c r="F120" s="1" t="n"/>
-      <c r="G120" s="1" t="n"/>
-      <c r="H120" s="1" t="n"/>
-      <c r="I120" s="1" t="n"/>
-      <c r="J120" s="1" t="n"/>
+      <c r="B120" s="21" t="n"/>
+      <c r="C120" s="21" t="n"/>
+      <c r="D120" s="22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E120" s="22" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G120" s="21" t="n"/>
+      <c r="H120" s="21" t="n"/>
+      <c r="I120" s="21" t="n"/>
+      <c r="J120" s="21" t="n"/>
     </row>
     <row r="121">
-      <c r="B121" s="21" t="n"/>
-      <c r="C121" s="21" t="n"/>
-      <c r="D121" s="22" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E121" s="22" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F121" s="22" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G121" s="21" t="n"/>
-      <c r="H121" s="21" t="n"/>
-      <c r="I121" s="21" t="n"/>
-      <c r="J121" s="21" t="n"/>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>Sales rep</t>
+        </is>
+      </c>
+      <c r="C121" s="18" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D121" s="23" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E121" s="23" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F121" s="24">
+        <f>IF(Assumptions!$E$5=2,E121,D121)</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Sales rep</t>
+          <t>Partner manager</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
@@ -4009,10 +4004,10 @@
         </is>
       </c>
       <c r="D122" s="23" t="n">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="E122" s="23" t="n">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="F122" s="24">
         <f>IF(Assumptions!$E$5=2,E122,D122)</f>
@@ -4022,7 +4017,7 @@
     <row r="123">
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Partner manager</t>
+          <t>Trainer, order desk, marketing</t>
         </is>
       </c>
       <c r="C123" s="18" t="inlineStr">
@@ -4031,10 +4026,10 @@
         </is>
       </c>
       <c r="D123" s="23" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="E123" s="23" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="F123" s="24">
         <f>IF(Assumptions!$E$5=2,E123,D123)</f>
@@ -4044,7 +4039,7 @@
     <row r="124">
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Trainer, order desk, marketing</t>
+          <t>Supply chain and production</t>
         </is>
       </c>
       <c r="C124" s="18" t="inlineStr">
@@ -4053,10 +4048,10 @@
         </is>
       </c>
       <c r="D124" s="23" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="E124" s="23" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="F124" s="24">
         <f>IF(Assumptions!$E$5=2,E124,D124)</f>
@@ -4066,7 +4061,7 @@
     <row r="125">
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Supply chain and production</t>
+          <t>Support and escalation</t>
         </is>
       </c>
       <c r="C125" s="18" t="inlineStr">
@@ -4075,10 +4070,10 @@
         </is>
       </c>
       <c r="D125" s="23" t="n">
-        <v>5000</v>
+        <v>4800</v>
       </c>
       <c r="E125" s="23" t="n">
-        <v>5000</v>
+        <v>4800</v>
       </c>
       <c r="F125" s="24">
         <f>IF(Assumptions!$E$5=2,E125,D125)</f>
@@ -4088,7 +4083,7 @@
     <row r="126">
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Support and escalation</t>
+          <t>Quality, certification and G&amp;A</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
@@ -4097,10 +4092,10 @@
         </is>
       </c>
       <c r="D126" s="23" t="n">
-        <v>4800</v>
+        <v>7000</v>
       </c>
       <c r="E126" s="23" t="n">
-        <v>4800</v>
+        <v>7000</v>
       </c>
       <c r="F126" s="24">
         <f>IF(Assumptions!$E$5=2,E126,D126)</f>
@@ -4110,7 +4105,7 @@
     <row r="127">
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Quality, certification and G&amp;A</t>
+          <t>R&amp;D engineer</t>
         </is>
       </c>
       <c r="C127" s="18" t="inlineStr">
@@ -4119,20 +4114,25 @@
         </is>
       </c>
       <c r="D127" s="23" t="n">
-        <v>7000</v>
+        <v>5700</v>
       </c>
       <c r="E127" s="23" t="n">
-        <v>7000</v>
+        <v>5700</v>
       </c>
       <c r="F127" s="24">
         <f>IF(Assumptions!$E$5=2,E127,D127)</f>
         <v/>
+      </c>
+      <c r="J127" s="20" t="inlineStr">
+        <is>
+          <t>the blended cost of the seven engineers already in post</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>R&amp;D engineer</t>
+          <t>Field service engineer</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D128" s="23" t="n">
-        <v>5700</v>
+        <v>6500</v>
       </c>
       <c r="E128" s="23" t="n">
-        <v>5700</v>
+        <v>6500</v>
       </c>
       <c r="F128" s="24">
         <f>IF(Assumptions!$E$5=2,E128,D128)</f>
@@ -4152,79 +4152,74 @@
       </c>
       <c r="J128" s="20" t="inlineStr">
         <is>
-          <t>the blended cost of the seven engineers already in post</t>
+          <t>shown for reference: their cost sits in service COGS, not in OPEX</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="B129" s="9" t="inlineStr">
-        <is>
-          <t>Field service engineer</t>
-        </is>
-      </c>
-      <c r="C129" s="18" t="inlineStr">
-        <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D129" s="23" t="n">
-        <v>6500</v>
-      </c>
-      <c r="E129" s="23" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F129" s="24">
-        <f>IF(Assumptions!$E$5=2,E129,D129)</f>
-        <v/>
-      </c>
-      <c r="J129" s="20" t="inlineStr">
-        <is>
-          <t>shown for reference: their cost sits in service COGS, not in OPEX</t>
-        </is>
-      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>OVERHEADS AND OTHER OPERATING COSTS</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n"/>
+      <c r="D129" s="1" t="n"/>
+      <c r="E129" s="1" t="n"/>
+      <c r="F129" s="1" t="n"/>
+      <c r="G129" s="1" t="n"/>
+      <c r="H129" s="1" t="n"/>
+      <c r="I129" s="1" t="n"/>
+      <c r="J129" s="1" t="n"/>
     </row>
     <row r="130">
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>OVERHEADS AND OTHER OPERATING COSTS</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="n"/>
-      <c r="D130" s="1" t="n"/>
-      <c r="E130" s="1" t="n"/>
-      <c r="F130" s="1" t="n"/>
-      <c r="G130" s="1" t="n"/>
-      <c r="H130" s="1" t="n"/>
-      <c r="I130" s="1" t="n"/>
-      <c r="J130" s="1" t="n"/>
+      <c r="B130" s="21" t="n"/>
+      <c r="C130" s="21" t="n"/>
+      <c r="D130" s="22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E130" s="22" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F130" s="22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G130" s="21" t="n"/>
+      <c r="H130" s="21" t="n"/>
+      <c r="I130" s="21" t="n"/>
+      <c r="J130" s="21" t="n"/>
     </row>
     <row r="131">
-      <c r="B131" s="21" t="n"/>
-      <c r="C131" s="21" t="n"/>
-      <c r="D131" s="22" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E131" s="22" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F131" s="22" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G131" s="21" t="n"/>
-      <c r="H131" s="21" t="n"/>
-      <c r="I131" s="21" t="n"/>
-      <c r="J131" s="21" t="n"/>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>Offices and facilities per person</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D131" s="23" t="n">
+        <v>700</v>
+      </c>
+      <c r="E131" s="23" t="n">
+        <v>700</v>
+      </c>
+      <c r="F131" s="24">
+        <f>IF(Assumptions!$E$5=2,E131,D131)</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Offices and facilities per person</t>
+          <t>IT and software per person</t>
         </is>
       </c>
       <c r="C132" s="18" t="inlineStr">
@@ -4233,10 +4228,10 @@
         </is>
       </c>
       <c r="D132" s="23" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="F132" s="24">
         <f>IF(Assumptions!$E$5=2,E132,D132)</f>
@@ -4246,7 +4241,7 @@
     <row r="133">
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>IT and software per person</t>
+          <t>Travel per person</t>
         </is>
       </c>
       <c r="C133" s="18" t="inlineStr">
@@ -4255,10 +4250,10 @@
         </is>
       </c>
       <c r="D133" s="23" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F133" s="24">
         <f>IF(Assumptions!$E$5=2,E133,D133)</f>
@@ -4268,19 +4263,19 @@
     <row r="134">
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Travel per person</t>
+          <t>Recruitment per net new hire</t>
         </is>
       </c>
       <c r="C134" s="18" t="inlineStr">
         <is>
-          <t>EUR/month</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D134" s="23" t="n">
-        <v>300</v>
+        <v>8000</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>300</v>
+        <v>8000</v>
       </c>
       <c r="F134" s="24">
         <f>IF(Assumptions!$E$5=2,E134,D134)</f>
@@ -4290,7 +4285,7 @@
     <row r="135">
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Recruitment per net new hire</t>
+          <t>Installer training and demo unit per new partner</t>
         </is>
       </c>
       <c r="C135" s="18" t="inlineStr">
@@ -4299,10 +4294,10 @@
         </is>
       </c>
       <c r="D135" s="23" t="n">
-        <v>8000</v>
+        <v>3500</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>8000</v>
+        <v>3500</v>
       </c>
       <c r="F135" s="24">
         <f>IF(Assumptions!$E$5=2,E135,D135)</f>
@@ -4312,19 +4307,19 @@
     <row r="136">
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Installer training and demo unit per new partner</t>
+          <t>Finance and legal</t>
         </is>
       </c>
       <c r="C136" s="18" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>EUR/month</t>
         </is>
       </c>
       <c r="D136" s="23" t="n">
-        <v>3500</v>
+        <v>7000</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>3500</v>
+        <v>7000</v>
       </c>
       <c r="F136" s="24">
         <f>IF(Assumptions!$E$5=2,E136,D136)</f>
@@ -4334,7 +4329,7 @@
     <row r="137">
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>Finance and legal</t>
+          <t>Other general</t>
         </is>
       </c>
       <c r="C137" s="18" t="inlineStr">
@@ -4343,10 +4338,10 @@
         </is>
       </c>
       <c r="D137" s="23" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="F137" s="24">
         <f>IF(Assumptions!$E$5=2,E137,D137)</f>
@@ -4356,7 +4351,7 @@
     <row r="138">
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>Other general</t>
+          <t>Ongoing development</t>
         </is>
       </c>
       <c r="C138" s="18" t="inlineStr">
@@ -4365,10 +4360,10 @@
         </is>
       </c>
       <c r="D138" s="23" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="E138" s="23" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="F138" s="24">
         <f>IF(Assumptions!$E$5=2,E138,D138)</f>
@@ -4378,7 +4373,7 @@
     <row r="139">
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>Ongoing development</t>
+          <t>Third party product development</t>
         </is>
       </c>
       <c r="C139" s="18" t="inlineStr">
@@ -4387,10 +4382,10 @@
         </is>
       </c>
       <c r="D139" s="23" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F139" s="24">
         <f>IF(Assumptions!$E$5=2,E139,D139)</f>
@@ -4400,103 +4395,103 @@
     <row r="140">
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>Third party product development</t>
+          <t>Annual increase on the costs above</t>
         </is>
       </c>
       <c r="C140" s="18" t="inlineStr">
         <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D140" s="23" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E140" s="23" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F140" s="24">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D140" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E140" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F140" s="26">
         <f>IF(Assumptions!$E$5=2,E140,D140)</f>
         <v/>
       </c>
     </row>
     <row r="141">
-      <c r="B141" s="9" t="inlineStr">
-        <is>
-          <t>Annual increase on the costs above</t>
-        </is>
-      </c>
-      <c r="C141" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D141" s="25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E141" s="25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F141" s="26">
-        <f>IF(Assumptions!$E$5=2,E141,D141)</f>
-        <v/>
-      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>FUNDING</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="n"/>
+      <c r="D141" s="1" t="n"/>
+      <c r="E141" s="1" t="n"/>
+      <c r="F141" s="1" t="n"/>
+      <c r="G141" s="1" t="n"/>
+      <c r="H141" s="1" t="n"/>
+      <c r="I141" s="1" t="n"/>
+      <c r="J141" s="1" t="n"/>
     </row>
     <row r="142">
-      <c r="B142" s="7" t="inlineStr">
-        <is>
-          <t>FUNDING</t>
-        </is>
-      </c>
-      <c r="C142" s="1" t="n"/>
-      <c r="D142" s="1" t="n"/>
-      <c r="E142" s="1" t="n"/>
-      <c r="F142" s="1" t="n"/>
-      <c r="G142" s="1" t="n"/>
-      <c r="H142" s="1" t="n"/>
-      <c r="I142" s="1" t="n"/>
-      <c r="J142" s="1" t="n"/>
+      <c r="B142" s="21" t="n"/>
+      <c r="C142" s="21" t="n"/>
+      <c r="D142" s="22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E142" s="22" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F142" s="22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G142" s="21" t="n"/>
+      <c r="H142" s="21" t="n"/>
+      <c r="I142" s="21" t="n"/>
+      <c r="J142" s="21" t="n"/>
     </row>
     <row r="143">
-      <c r="B143" s="21" t="n"/>
-      <c r="C143" s="21" t="n"/>
-      <c r="D143" s="22" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E143" s="22" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F143" s="22" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G143" s="21" t="n"/>
-      <c r="H143" s="21" t="n"/>
-      <c r="I143" s="21" t="n"/>
-      <c r="J143" s="21" t="n"/>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>First round, money in</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D143" s="27" t="n">
+        <v>46143</v>
+      </c>
+      <c r="E143" s="27" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F143" s="28">
+        <f>IF(Assumptions!$E$5=2,E143,D143)</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>First round, money in</t>
+          <t>First round, amount</t>
         </is>
       </c>
       <c r="C144" s="18" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D144" s="27" t="n">
-        <v>46143</v>
-      </c>
-      <c r="E144" s="27" t="n">
-        <v>46143</v>
-      </c>
-      <c r="F144" s="28">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D144" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E144" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F144" s="24">
         <f>IF(Assumptions!$E$5=2,E144,D144)</f>
         <v/>
       </c>
@@ -4504,21 +4499,21 @@
     <row r="145">
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>First round, amount</t>
+          <t>Second round, money in</t>
         </is>
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D145" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E145" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F145" s="24">
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D145" s="27" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E145" s="27" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F145" s="28">
         <f>IF(Assumptions!$E$5=2,E145,D145)</f>
         <v/>
       </c>
@@ -4526,29 +4521,34 @@
     <row r="146">
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>Second round, money in</t>
+          <t>Second round, amount</t>
         </is>
       </c>
       <c r="C146" s="18" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D146" s="27" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E146" s="27" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F146" s="28">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D146" s="23" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E146" s="23" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F146" s="24">
         <f>IF(Assumptions!$E$5=2,E146,D146)</f>
         <v/>
+      </c>
+      <c r="J146" s="20" t="inlineStr">
+        <is>
+          <t>this is the raise the model is built to justify</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>Second round, amount</t>
+          <t>Convertible loan drawn</t>
         </is>
       </c>
       <c r="C147" s="18" t="inlineStr">
@@ -4557,62 +4557,35 @@
         </is>
       </c>
       <c r="D147" s="23" t="n">
-        <v>3000000</v>
+        <v>300000</v>
       </c>
       <c r="E147" s="23" t="n">
-        <v>10000000</v>
+        <v>300000</v>
       </c>
       <c r="F147" s="24">
         <f>IF(Assumptions!$E$5=2,E147,D147)</f>
         <v/>
-      </c>
-      <c r="J147" s="20" t="inlineStr">
-        <is>
-          <t>this is the raise the model is built to justify</t>
-        </is>
       </c>
     </row>
     <row r="148">
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>Convertible loan drawn</t>
+          <t>Loan drawn on</t>
         </is>
       </c>
       <c r="C148" s="18" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D148" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E148" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F148" s="24">
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D148" s="27" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E148" s="27" t="n">
+        <v>46204</v>
+      </c>
+      <c r="F148" s="28">
         <f>IF(Assumptions!$E$5=2,E148,D148)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="B149" s="9" t="inlineStr">
-        <is>
-          <t>Loan drawn on</t>
-        </is>
-      </c>
-      <c r="C149" s="18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D149" s="27" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E149" s="27" t="n">
-        <v>46204</v>
-      </c>
-      <c r="F149" s="28">
-        <f>IF(Assumptions!$E$5=2,E149,D149)</f>
         <v/>
       </c>
     </row>
@@ -11705,243 +11678,243 @@
         </is>
       </c>
       <c r="E35" s="43">
-        <f>IF(E$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(E$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(E$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(E$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="F35" s="43">
-        <f>IF(F$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(F$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(F$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(F$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="G35" s="43">
-        <f>IF(G$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(G$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(G$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(G$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="H35" s="43">
-        <f>IF(H$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(H$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(H$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(H$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="I35" s="43">
-        <f>IF(I$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(I$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(I$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(I$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="J35" s="43">
-        <f>IF(J$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(J$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(J$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(J$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="K35" s="43">
-        <f>IF(K$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(K$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(K$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(K$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="L35" s="43">
-        <f>IF(L$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(L$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(L$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(L$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="M35" s="43">
-        <f>IF(M$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(M$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(M$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(M$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="N35" s="43">
-        <f>IF(N$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(N$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(N$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(N$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="O35" s="43">
-        <f>IF(O$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(O$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(O$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(O$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="P35" s="43">
-        <f>IF(P$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(P$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(P$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(P$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="Q35" s="43">
-        <f>IF(Q$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(Q$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(Q$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(Q$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="R35" s="43">
-        <f>IF(R$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(R$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(R$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(R$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="S35" s="43">
-        <f>IF(S$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(S$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(S$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(S$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="T35" s="43">
-        <f>IF(T$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(T$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(T$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(T$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="U35" s="43">
-        <f>IF(U$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(U$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(U$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(U$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="V35" s="43">
-        <f>IF(V$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(V$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(V$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(V$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="W35" s="43">
-        <f>IF(W$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(W$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(W$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(W$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="X35" s="43">
-        <f>IF(X$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(X$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(X$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(X$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="Y35" s="43">
-        <f>IF(Y$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(Y$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(Y$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(Y$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="Z35" s="43">
-        <f>IF(Z$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(Z$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(Z$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(Z$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AA35" s="43">
-        <f>IF(AA$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AA$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AA$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AA$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AB35" s="43">
-        <f>IF(AB$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AB$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AB$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AB$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AC35" s="43">
-        <f>IF(AC$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AC$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AC$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AC$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AD35" s="43">
-        <f>IF(AD$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AD$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AD$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AD$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AE35" s="43">
-        <f>IF(AE$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AE$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AE$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AE$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AF35" s="43">
-        <f>IF(AF$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AF$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AF$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AF$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AG35" s="43">
-        <f>IF(AG$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AG$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AG$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AG$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AH35" s="43">
-        <f>IF(AH$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AH$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AH$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AH$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AI35" s="43">
-        <f>IF(AI$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AI$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AI$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AI$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AJ35" s="43">
-        <f>IF(AJ$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AJ$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AJ$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AJ$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AK35" s="43">
-        <f>IF(AK$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AK$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AK$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AK$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AL35" s="43">
-        <f>IF(AL$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AL$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AL$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AL$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AM35" s="43">
-        <f>IF(AM$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AM$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AM$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AM$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AN35" s="43">
-        <f>IF(AN$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AN$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AN$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AN$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AO35" s="43">
-        <f>IF(AO$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AO$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AO$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AO$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AP35" s="43">
-        <f>IF(AP$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AP$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AP$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AP$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AQ35" s="43">
-        <f>IF(AQ$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AQ$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AQ$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AQ$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AR35" s="43">
-        <f>IF(AR$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AR$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AR$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AR$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AS35" s="43">
-        <f>IF(AS$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AS$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AS$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AS$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AT35" s="43">
-        <f>IF(AT$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AT$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AT$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AT$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AU35" s="43">
-        <f>IF(AU$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AU$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AU$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AU$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AV35" s="43">
-        <f>IF(AV$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AV$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AV$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AV$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AW35" s="43">
-        <f>IF(AW$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AW$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AW$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AW$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AX35" s="43">
-        <f>IF(AX$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AX$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AX$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AX$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AY35" s="43">
-        <f>IF(AY$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AY$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AY$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AY$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AZ35" s="43">
-        <f>IF(AZ$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(AZ$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(AZ$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AZ$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BA35" s="43">
-        <f>IF(BA$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(BA$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(BA$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BA$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BB35" s="43">
-        <f>IF(BB$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(BB$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(BB$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BB$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BC35" s="43">
-        <f>IF(BC$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(BC$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(BC$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BC$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BD35" s="43">
-        <f>IF(BD$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(BD$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(BD$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BD$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BE35" s="43">
-        <f>IF(BE$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(BE$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(BE$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BE$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BF35" s="43">
-        <f>IF(BF$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(BF$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(BF$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BF$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BG35" s="43">
-        <f>IF(BG$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(BG$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(BG$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BG$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BH35" s="43">
-        <f>IF(BH$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(BH$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(BH$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BH$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BI35" s="43">
-        <f>IF(BI$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(BI$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(BI$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BI$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BJ35" s="43">
-        <f>IF(BJ$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(BJ$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(BJ$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BJ$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BK35" s="43">
-        <f>IF(BK$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(BK$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(BK$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BK$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BL35" s="43">
-        <f>IF(BL$3=Assumptions!$F$144,Assumptions!$F$145,0)+IF(BL$3=Assumptions!$F$146,Assumptions!$F$147,0)</f>
+        <f>IF(BL$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BL$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BN35" s="44">
@@ -11982,243 +11955,243 @@
         </is>
       </c>
       <c r="E36" s="43">
-        <f>IF(E$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(E$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="F36" s="43">
-        <f>IF(F$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(F$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="G36" s="43">
-        <f>IF(G$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(G$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="H36" s="43">
-        <f>IF(H$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(H$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="I36" s="43">
-        <f>IF(I$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(I$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="J36" s="43">
-        <f>IF(J$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(J$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="K36" s="43">
-        <f>IF(K$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(K$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="L36" s="43">
-        <f>IF(L$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(L$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="M36" s="43">
-        <f>IF(M$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(M$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="N36" s="43">
-        <f>IF(N$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(N$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="O36" s="43">
-        <f>IF(O$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(O$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="P36" s="43">
-        <f>IF(P$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(P$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="Q36" s="43">
-        <f>IF(Q$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(Q$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="R36" s="43">
-        <f>IF(R$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(R$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="S36" s="43">
-        <f>IF(S$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(S$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="T36" s="43">
-        <f>IF(T$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(T$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="U36" s="43">
-        <f>IF(U$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(U$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="V36" s="43">
-        <f>IF(V$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(V$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="W36" s="43">
-        <f>IF(W$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(W$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="X36" s="43">
-        <f>IF(X$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(X$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="Y36" s="43">
-        <f>IF(Y$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(Y$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="Z36" s="43">
-        <f>IF(Z$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(Z$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AA36" s="43">
-        <f>IF(AA$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AA$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AB36" s="43">
-        <f>IF(AB$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AB$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AC36" s="43">
-        <f>IF(AC$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AC$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AD36" s="43">
-        <f>IF(AD$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AD$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AE36" s="43">
-        <f>IF(AE$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AE$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AF36" s="43">
-        <f>IF(AF$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AF$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AG36" s="43">
-        <f>IF(AG$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AG$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AH36" s="43">
-        <f>IF(AH$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AH$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AI36" s="43">
-        <f>IF(AI$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AI$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AJ36" s="43">
-        <f>IF(AJ$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AJ$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AK36" s="43">
-        <f>IF(AK$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AK$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AL36" s="43">
-        <f>IF(AL$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AL$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AM36" s="43">
-        <f>IF(AM$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AM$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AN36" s="43">
-        <f>IF(AN$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AN$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AO36" s="43">
-        <f>IF(AO$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AO$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AP36" s="43">
-        <f>IF(AP$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AP$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AQ36" s="43">
-        <f>IF(AQ$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AQ$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AR36" s="43">
-        <f>IF(AR$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AR$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AS36" s="43">
-        <f>IF(AS$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AS$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AT36" s="43">
-        <f>IF(AT$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AT$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AU36" s="43">
-        <f>IF(AU$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AU$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AV36" s="43">
-        <f>IF(AV$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AV$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AW36" s="43">
-        <f>IF(AW$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AW$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AX36" s="43">
-        <f>IF(AX$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AX$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AY36" s="43">
-        <f>IF(AY$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AY$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AZ36" s="43">
-        <f>IF(AZ$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(AZ$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BA36" s="43">
-        <f>IF(BA$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(BA$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BB36" s="43">
-        <f>IF(BB$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(BB$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BC36" s="43">
-        <f>IF(BC$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(BC$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BD36" s="43">
-        <f>IF(BD$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(BD$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BE36" s="43">
-        <f>IF(BE$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(BE$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BF36" s="43">
-        <f>IF(BF$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(BF$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BG36" s="43">
-        <f>IF(BG$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(BG$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BH36" s="43">
-        <f>IF(BH$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(BH$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BI36" s="43">
-        <f>IF(BI$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(BI$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BJ36" s="43">
-        <f>IF(BJ$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(BJ$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BK36" s="43">
-        <f>IF(BK$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(BK$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BL36" s="43">
-        <f>IF(BL$3=Assumptions!$F$149,Assumptions!$F$148,0)</f>
+        <f>IF(BL$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BN36" s="44">
@@ -34552,243 +34525,243 @@
         </is>
       </c>
       <c r="E13" s="43">
-        <f>'Revenue Forecast'!E19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!E19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="F13" s="43">
-        <f>'Revenue Forecast'!F19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!F19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="G13" s="43">
-        <f>'Revenue Forecast'!G19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!G19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="H13" s="43">
-        <f>'Revenue Forecast'!H19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!H19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="I13" s="43">
-        <f>'Revenue Forecast'!I19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!I19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="J13" s="43">
-        <f>'Revenue Forecast'!J19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!J19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="K13" s="43">
-        <f>'Revenue Forecast'!K19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!K19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="L13" s="43">
-        <f>'Revenue Forecast'!L19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!L19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="M13" s="43">
-        <f>'Revenue Forecast'!M19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!M19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="N13" s="43">
-        <f>'Revenue Forecast'!N19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!N19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="O13" s="43">
-        <f>'Revenue Forecast'!O19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!O19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="P13" s="43">
-        <f>'Revenue Forecast'!P19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!P19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="Q13" s="43">
-        <f>'Revenue Forecast'!Q19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!Q19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="R13" s="43">
-        <f>'Revenue Forecast'!R19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!R19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="S13" s="43">
-        <f>'Revenue Forecast'!S19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!S19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="T13" s="43">
-        <f>'Revenue Forecast'!T19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!T19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="U13" s="43">
-        <f>'Revenue Forecast'!U19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!U19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="V13" s="43">
-        <f>'Revenue Forecast'!V19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!V19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="W13" s="43">
-        <f>'Revenue Forecast'!W19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!W19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="X13" s="43">
-        <f>'Revenue Forecast'!X19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!X19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="Y13" s="43">
-        <f>'Revenue Forecast'!Y19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!Y19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="Z13" s="43">
-        <f>'Revenue Forecast'!Z19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!Z19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AA13" s="43">
-        <f>'Revenue Forecast'!AA19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AA19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AB13" s="43">
-        <f>'Revenue Forecast'!AB19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AB19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AC13" s="43">
-        <f>'Revenue Forecast'!AC19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AC19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AD13" s="43">
-        <f>'Revenue Forecast'!AD19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AD19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AE13" s="43">
-        <f>'Revenue Forecast'!AE19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AE19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AF13" s="43">
-        <f>'Revenue Forecast'!AF19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AF19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AG13" s="43">
-        <f>'Revenue Forecast'!AG19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AG19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AH13" s="43">
-        <f>'Revenue Forecast'!AH19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AH19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AI13" s="43">
-        <f>'Revenue Forecast'!AI19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AI19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AJ13" s="43">
-        <f>'Revenue Forecast'!AJ19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AJ19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AK13" s="43">
-        <f>'Revenue Forecast'!AK19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AK19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AL13" s="43">
-        <f>'Revenue Forecast'!AL19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AL19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AM13" s="43">
-        <f>'Revenue Forecast'!AM19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AM19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AN13" s="43">
-        <f>'Revenue Forecast'!AN19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AN19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AO13" s="43">
-        <f>'Revenue Forecast'!AO19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AO19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AP13" s="43">
-        <f>'Revenue Forecast'!AP19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AP19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AQ13" s="43">
-        <f>'Revenue Forecast'!AQ19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AQ19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AR13" s="43">
-        <f>'Revenue Forecast'!AR19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AR19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AS13" s="43">
-        <f>'Revenue Forecast'!AS19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AS19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AT13" s="43">
-        <f>'Revenue Forecast'!AT19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AT19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AU13" s="43">
-        <f>'Revenue Forecast'!AU19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AU19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AV13" s="43">
-        <f>'Revenue Forecast'!AV19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AV19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AW13" s="43">
-        <f>'Revenue Forecast'!AW19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AW19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AX13" s="43">
-        <f>'Revenue Forecast'!AX19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AX19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AY13" s="43">
-        <f>'Revenue Forecast'!AY19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AY19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AZ13" s="43">
-        <f>'Revenue Forecast'!AZ19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!AZ19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BA13" s="43">
-        <f>'Revenue Forecast'!BA19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!BA19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BB13" s="43">
-        <f>'Revenue Forecast'!BB19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!BB19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BC13" s="43">
-        <f>'Revenue Forecast'!BC19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!BC19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BD13" s="43">
-        <f>'Revenue Forecast'!BD19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!BD19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BE13" s="43">
-        <f>'Revenue Forecast'!BE19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!BE19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BF13" s="43">
-        <f>'Revenue Forecast'!BF19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!BF19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BG13" s="43">
-        <f>'Revenue Forecast'!BG19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!BG19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BH13" s="43">
-        <f>'Revenue Forecast'!BH19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!BH19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BI13" s="43">
-        <f>'Revenue Forecast'!BI19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!BI19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BJ13" s="43">
-        <f>'Revenue Forecast'!BJ19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!BJ19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BK13" s="43">
-        <f>'Revenue Forecast'!BK19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!BK19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BL13" s="43">
-        <f>'Revenue Forecast'!BL19*Assumptions!$F$136</f>
+        <f>'Revenue Forecast'!BL19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BN13" s="44">
@@ -35172,243 +35145,243 @@
         </is>
       </c>
       <c r="E17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(E$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(F$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(G$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(H$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(I$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(J$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(K$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(L$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(M$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(N$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(O$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(P$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(Q$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(R$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(S$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(T$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(U$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(V$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(W$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(X$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(Y$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(Z$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AA$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AB$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AC$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AD$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AE$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AF$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AG$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AH$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AI$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AJ$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AK$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AL$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AM$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AN$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AO$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AP$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AQ$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AR$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AS$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AT$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AU$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AV$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AW$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AX$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AY$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(AZ$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(BA$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(BB$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(BC$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(BD$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(BE$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(BF$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(BG$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(BH$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(BI$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(BJ$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(BK$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL17" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$141)^(YEAR(BL$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN17" s="44">
@@ -35444,243 +35417,243 @@
         </is>
       </c>
       <c r="E18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(E$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(F$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(G$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(H$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(I$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(J$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(K$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(L$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(M$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(N$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(O$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(P$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(Q$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(R$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(S$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(T$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(U$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(V$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(W$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(X$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(Y$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(Z$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AA$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AB$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AC$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AD$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AE$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AF$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AG$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AH$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AI$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AJ$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AK$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AL$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AM$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AN$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AO$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AP$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AQ$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AR$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AS$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AT$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AU$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AV$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AW$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AX$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AY$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(AZ$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(BA$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(BB$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(BC$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(BD$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(BE$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(BF$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(BG$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(BH$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(BI$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(BJ$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(BK$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL18" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$141)^(YEAR(BL$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN18" s="44">
@@ -36064,243 +36037,243 @@
         </is>
       </c>
       <c r="E22" s="43">
-        <f>Personnel!E21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!E20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="F22" s="43">
-        <f>Personnel!F21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!F20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="G22" s="43">
-        <f>Personnel!G21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!G20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="H22" s="43">
-        <f>Personnel!H21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!H20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="I22" s="43">
-        <f>Personnel!I21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!I20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="J22" s="43">
-        <f>Personnel!J21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!J20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="K22" s="43">
-        <f>Personnel!K21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!K20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="L22" s="43">
-        <f>Personnel!L21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!L20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="M22" s="43">
-        <f>Personnel!M21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!M20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="N22" s="43">
-        <f>Personnel!N21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!N20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="O22" s="43">
-        <f>Personnel!O21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!O20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="P22" s="43">
-        <f>Personnel!P21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!P20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="Q22" s="43">
-        <f>Personnel!Q21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!Q20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="R22" s="43">
-        <f>Personnel!R21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!R20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="S22" s="43">
-        <f>Personnel!S21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!S20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="T22" s="43">
-        <f>Personnel!T21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!T20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="U22" s="43">
-        <f>Personnel!U21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!U20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="V22" s="43">
-        <f>Personnel!V21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!V20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="W22" s="43">
-        <f>Personnel!W21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!W20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="X22" s="43">
-        <f>Personnel!X21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!X20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="Y22" s="43">
-        <f>Personnel!Y21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!Y20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="Z22" s="43">
-        <f>Personnel!Z21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!Z20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AA22" s="43">
-        <f>Personnel!AA21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AA20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AB22" s="43">
-        <f>Personnel!AB21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AB20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AC22" s="43">
-        <f>Personnel!AC21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AC20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AD22" s="43">
-        <f>Personnel!AD21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AD20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AE22" s="43">
-        <f>Personnel!AE21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AE20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AF22" s="43">
-        <f>Personnel!AF21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AF20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AG22" s="43">
-        <f>Personnel!AG21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AG20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AH22" s="43">
-        <f>Personnel!AH21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AH20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AI22" s="43">
-        <f>Personnel!AI21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AI20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AJ22" s="43">
-        <f>Personnel!AJ21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AJ20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AK22" s="43">
-        <f>Personnel!AK21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AK20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AL22" s="43">
-        <f>Personnel!AL21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AL20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AM22" s="43">
-        <f>Personnel!AM21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AM20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AN22" s="43">
-        <f>Personnel!AN21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AN20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AO22" s="43">
-        <f>Personnel!AO21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AO20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AP22" s="43">
-        <f>Personnel!AP21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AP20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AQ22" s="43">
-        <f>Personnel!AQ21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AQ20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AR22" s="43">
-        <f>Personnel!AR21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AR20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AS22" s="43">
-        <f>Personnel!AS21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AS20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AT22" s="43">
-        <f>Personnel!AT21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AT20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AU22" s="43">
-        <f>Personnel!AU21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AU20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AV22" s="43">
-        <f>Personnel!AV21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AV20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AW22" s="43">
-        <f>Personnel!AW21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AW20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AX22" s="43">
-        <f>Personnel!AX21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AX20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AY22" s="43">
-        <f>Personnel!AY21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AY20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AZ22" s="43">
-        <f>Personnel!AZ21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!AZ20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BA22" s="43">
-        <f>Personnel!BA21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!BA20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BB22" s="43">
-        <f>Personnel!BB21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!BB20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BC22" s="43">
-        <f>Personnel!BC21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!BC20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BD22" s="43">
-        <f>Personnel!BD21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!BD20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BE22" s="43">
-        <f>Personnel!BE21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!BE20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BF22" s="43">
-        <f>Personnel!BF21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!BF20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BG22" s="43">
-        <f>Personnel!BG21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!BG20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BH22" s="43">
-        <f>Personnel!BH21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!BH20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BI22" s="43">
-        <f>Personnel!BI21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!BI20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BJ22" s="43">
-        <f>Personnel!BJ21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!BJ20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BK22" s="43">
-        <f>Personnel!BK21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!BK20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BL22" s="43">
-        <f>Personnel!BL21*(Assumptions!$F$132+Assumptions!$F$133+Assumptions!$F$134)</f>
+        <f>Personnel!BL20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BN22" s="44">
@@ -36345,239 +36318,239 @@
         <v/>
       </c>
       <c r="F23" s="43">
-        <f>MAX(0,Personnel!F21-Personnel!E21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!F20-Personnel!E20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="G23" s="43">
-        <f>MAX(0,Personnel!G21-Personnel!F21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!G20-Personnel!F20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="H23" s="43">
-        <f>MAX(0,Personnel!H21-Personnel!G21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!H20-Personnel!G20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="I23" s="43">
-        <f>MAX(0,Personnel!I21-Personnel!H21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!I20-Personnel!H20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="J23" s="43">
-        <f>MAX(0,Personnel!J21-Personnel!I21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!J20-Personnel!I20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="K23" s="43">
-        <f>MAX(0,Personnel!K21-Personnel!J21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!K20-Personnel!J20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="L23" s="43">
-        <f>MAX(0,Personnel!L21-Personnel!K21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!L20-Personnel!K20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="M23" s="43">
-        <f>MAX(0,Personnel!M21-Personnel!L21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!M20-Personnel!L20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="N23" s="43">
-        <f>MAX(0,Personnel!N21-Personnel!M21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!N20-Personnel!M20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="O23" s="43">
-        <f>MAX(0,Personnel!O21-Personnel!N21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!O20-Personnel!N20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="P23" s="43">
-        <f>MAX(0,Personnel!P21-Personnel!O21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!P20-Personnel!O20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="Q23" s="43">
-        <f>MAX(0,Personnel!Q21-Personnel!P21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!Q20-Personnel!P20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="R23" s="43">
-        <f>MAX(0,Personnel!R21-Personnel!Q21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!R20-Personnel!Q20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="S23" s="43">
-        <f>MAX(0,Personnel!S21-Personnel!R21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!S20-Personnel!R20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="T23" s="43">
-        <f>MAX(0,Personnel!T21-Personnel!S21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!T20-Personnel!S20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="U23" s="43">
-        <f>MAX(0,Personnel!U21-Personnel!T21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!U20-Personnel!T20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="V23" s="43">
-        <f>MAX(0,Personnel!V21-Personnel!U21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!V20-Personnel!U20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="W23" s="43">
-        <f>MAX(0,Personnel!W21-Personnel!V21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!W20-Personnel!V20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="X23" s="43">
-        <f>MAX(0,Personnel!X21-Personnel!W21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!X20-Personnel!W20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="Y23" s="43">
-        <f>MAX(0,Personnel!Y21-Personnel!X21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!Y20-Personnel!X20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="Z23" s="43">
-        <f>MAX(0,Personnel!Z21-Personnel!Y21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!Z20-Personnel!Y20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AA23" s="43">
-        <f>MAX(0,Personnel!AA21-Personnel!Z21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AA20-Personnel!Z20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AB23" s="43">
-        <f>MAX(0,Personnel!AB21-Personnel!AA21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AB20-Personnel!AA20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AC23" s="43">
-        <f>MAX(0,Personnel!AC21-Personnel!AB21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AC20-Personnel!AB20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AD23" s="43">
-        <f>MAX(0,Personnel!AD21-Personnel!AC21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AD20-Personnel!AC20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AE23" s="43">
-        <f>MAX(0,Personnel!AE21-Personnel!AD21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AE20-Personnel!AD20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AF23" s="43">
-        <f>MAX(0,Personnel!AF21-Personnel!AE21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AF20-Personnel!AE20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AG23" s="43">
-        <f>MAX(0,Personnel!AG21-Personnel!AF21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AG20-Personnel!AF20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AH23" s="43">
-        <f>MAX(0,Personnel!AH21-Personnel!AG21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AH20-Personnel!AG20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AI23" s="43">
-        <f>MAX(0,Personnel!AI21-Personnel!AH21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AI20-Personnel!AH20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AJ23" s="43">
-        <f>MAX(0,Personnel!AJ21-Personnel!AI21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AJ20-Personnel!AI20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AK23" s="43">
-        <f>MAX(0,Personnel!AK21-Personnel!AJ21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AK20-Personnel!AJ20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AL23" s="43">
-        <f>MAX(0,Personnel!AL21-Personnel!AK21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AL20-Personnel!AK20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AM23" s="43">
-        <f>MAX(0,Personnel!AM21-Personnel!AL21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AM20-Personnel!AL20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AN23" s="43">
-        <f>MAX(0,Personnel!AN21-Personnel!AM21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AN20-Personnel!AM20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AO23" s="43">
-        <f>MAX(0,Personnel!AO21-Personnel!AN21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AO20-Personnel!AN20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AP23" s="43">
-        <f>MAX(0,Personnel!AP21-Personnel!AO21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AP20-Personnel!AO20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AQ23" s="43">
-        <f>MAX(0,Personnel!AQ21-Personnel!AP21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AQ20-Personnel!AP20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AR23" s="43">
-        <f>MAX(0,Personnel!AR21-Personnel!AQ21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AR20-Personnel!AQ20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AS23" s="43">
-        <f>MAX(0,Personnel!AS21-Personnel!AR21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AS20-Personnel!AR20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AT23" s="43">
-        <f>MAX(0,Personnel!AT21-Personnel!AS21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AT20-Personnel!AS20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AU23" s="43">
-        <f>MAX(0,Personnel!AU21-Personnel!AT21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AU20-Personnel!AT20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AV23" s="43">
-        <f>MAX(0,Personnel!AV21-Personnel!AU21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AV20-Personnel!AU20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AW23" s="43">
-        <f>MAX(0,Personnel!AW21-Personnel!AV21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AW20-Personnel!AV20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AX23" s="43">
-        <f>MAX(0,Personnel!AX21-Personnel!AW21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AX20-Personnel!AW20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AY23" s="43">
-        <f>MAX(0,Personnel!AY21-Personnel!AX21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AY20-Personnel!AX20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AZ23" s="43">
-        <f>MAX(0,Personnel!AZ21-Personnel!AY21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!AZ20-Personnel!AY20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BA23" s="43">
-        <f>MAX(0,Personnel!BA21-Personnel!AZ21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!BA20-Personnel!AZ20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BB23" s="43">
-        <f>MAX(0,Personnel!BB21-Personnel!BA21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!BB20-Personnel!BA20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BC23" s="43">
-        <f>MAX(0,Personnel!BC21-Personnel!BB21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!BC20-Personnel!BB20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BD23" s="43">
-        <f>MAX(0,Personnel!BD21-Personnel!BC21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!BD20-Personnel!BC20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BE23" s="43">
-        <f>MAX(0,Personnel!BE21-Personnel!BD21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!BE20-Personnel!BD20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BF23" s="43">
-        <f>MAX(0,Personnel!BF21-Personnel!BE21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!BF20-Personnel!BE20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BG23" s="43">
-        <f>MAX(0,Personnel!BG21-Personnel!BF21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!BG20-Personnel!BF20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BH23" s="43">
-        <f>MAX(0,Personnel!BH21-Personnel!BG21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!BH20-Personnel!BG20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BI23" s="43">
-        <f>MAX(0,Personnel!BI21-Personnel!BH21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!BI20-Personnel!BH20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BJ23" s="43">
-        <f>MAX(0,Personnel!BJ21-Personnel!BI21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!BJ20-Personnel!BI20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BK23" s="43">
-        <f>MAX(0,Personnel!BK21-Personnel!BJ21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!BK20-Personnel!BJ20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BL23" s="43">
-        <f>MAX(0,Personnel!BL21-Personnel!BK21)*Assumptions!$F$135</f>
+        <f>MAX(0,Personnel!BL20-Personnel!BK20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BN23" s="44">
@@ -36890,243 +36863,243 @@
         </is>
       </c>
       <c r="E25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(E$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(F$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(G$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(H$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(I$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(J$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(K$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(L$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(M$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(N$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(O$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(P$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(Q$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(R$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(S$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(T$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(U$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(V$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(W$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(X$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(Y$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(Z$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AA$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AB$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AC$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AD$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AE$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AF$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AG$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AH$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AI$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AJ$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AK$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AL$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AM$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AN$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AO$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AP$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AQ$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AR$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AS$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AT$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AU$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AV$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AW$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AX$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AY$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(AZ$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(BA$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(BB$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(BC$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(BD$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(BE$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(BF$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(BG$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(BH$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(BI$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(BJ$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(BK$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL25" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$141)^(YEAR(BL$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN25" s="44">
@@ -37162,243 +37135,243 @@
         </is>
       </c>
       <c r="E26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(E$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(F$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(G$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(H$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(I$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(J$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(K$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(L$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(M$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(N$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(O$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(P$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(Q$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(R$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(S$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(T$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(U$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(V$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(W$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(X$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(Y$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(Z$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AA$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AB$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AC$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AD$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AE$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AF$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AG$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AH$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AI$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AJ$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AK$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AL$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AM$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AN$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AO$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AP$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AQ$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AR$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AS$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AT$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AU$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AV$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AW$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AX$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AY$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(AZ$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(BA$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(BB$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(BC$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(BD$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(BE$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(BF$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(BG$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(BH$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(BI$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(BJ$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(BK$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL26" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$141)^(YEAR(BL$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN26" s="44">
@@ -44234,7 +44207,7 @@
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Leadership and administration</t>
+          <t>Leadership, finance, HR, IT and legal</t>
         </is>
       </c>
       <c r="C18" s="42" t="inlineStr">
@@ -44504,278 +44477,278 @@
       </c>
       <c r="BT18" s="20" t="inlineStr">
         <is>
-          <t>a part-time finance lead in 2026, then the full leadership team once funded</t>
+          <t>the whole back office, typed per year on Assumptions</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Finance, HR, IT and legal</t>
-        </is>
-      </c>
-      <c r="C19" s="42" t="inlineStr">
+      <c r="B19" s="50" t="inlineStr">
+        <is>
+          <t>Operations, support and administration</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
       </c>
-      <c r="E19" s="54">
-        <f>ROUND((E11+SUM(E12:E18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="54">
-        <f>ROUND((F11+SUM(F12:F18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="54">
-        <f>ROUND((G11+SUM(G12:G18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="H19" s="54">
-        <f>ROUND((H11+SUM(H12:H18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="I19" s="54">
-        <f>ROUND((I11+SUM(I12:I18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="J19" s="54">
-        <f>ROUND((J11+SUM(J12:J18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="K19" s="54">
-        <f>ROUND((K11+SUM(K12:K18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="L19" s="54">
-        <f>ROUND((L11+SUM(L12:L18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="M19" s="54">
-        <f>ROUND((M11+SUM(M12:M18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="N19" s="54">
-        <f>ROUND((N11+SUM(N12:N18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="O19" s="54">
-        <f>ROUND((O11+SUM(O12:O18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="P19" s="54">
-        <f>ROUND((P11+SUM(P12:P18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="54">
-        <f>ROUND((Q11+SUM(Q12:Q18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="R19" s="54">
-        <f>ROUND((R11+SUM(R12:R18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="S19" s="54">
-        <f>ROUND((S11+SUM(S12:S18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="T19" s="54">
-        <f>ROUND((T11+SUM(T12:T18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="U19" s="54">
-        <f>ROUND((U11+SUM(U12:U18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="V19" s="54">
-        <f>ROUND((V11+SUM(V12:V18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="W19" s="54">
-        <f>ROUND((W11+SUM(W12:W18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="X19" s="54">
-        <f>ROUND((X11+SUM(X12:X18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="Y19" s="54">
-        <f>ROUND((Y11+SUM(Y12:Y18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="Z19" s="54">
-        <f>ROUND((Z11+SUM(Z12:Z18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AA19" s="54">
-        <f>ROUND((AA11+SUM(AA12:AA18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AB19" s="54">
-        <f>ROUND((AB11+SUM(AB12:AB18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AC19" s="54">
-        <f>ROUND((AC11+SUM(AC12:AC18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AD19" s="54">
-        <f>ROUND((AD11+SUM(AD12:AD18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AE19" s="54">
-        <f>ROUND((AE11+SUM(AE12:AE18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AF19" s="54">
-        <f>ROUND((AF11+SUM(AF12:AF18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AG19" s="54">
-        <f>ROUND((AG11+SUM(AG12:AG18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AH19" s="54">
-        <f>ROUND((AH11+SUM(AH12:AH18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AI19" s="54">
-        <f>ROUND((AI11+SUM(AI12:AI18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AJ19" s="54">
-        <f>ROUND((AJ11+SUM(AJ12:AJ18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AK19" s="54">
-        <f>ROUND((AK11+SUM(AK12:AK18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AL19" s="54">
-        <f>ROUND((AL11+SUM(AL12:AL18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AM19" s="54">
-        <f>ROUND((AM11+SUM(AM12:AM18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AN19" s="54">
-        <f>ROUND((AN11+SUM(AN12:AN18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AO19" s="54">
-        <f>ROUND((AO11+SUM(AO12:AO18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AP19" s="54">
-        <f>ROUND((AP11+SUM(AP12:AP18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AQ19" s="54">
-        <f>ROUND((AQ11+SUM(AQ12:AQ18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AR19" s="54">
-        <f>ROUND((AR11+SUM(AR12:AR18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AS19" s="54">
-        <f>ROUND((AS11+SUM(AS12:AS18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AT19" s="54">
-        <f>ROUND((AT11+SUM(AT12:AT18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AU19" s="54">
-        <f>ROUND((AU11+SUM(AU12:AU18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AV19" s="54">
-        <f>ROUND((AV11+SUM(AV12:AV18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AW19" s="54">
-        <f>ROUND((AW11+SUM(AW12:AW18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AX19" s="54">
-        <f>ROUND((AX11+SUM(AX12:AX18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AY19" s="54">
-        <f>ROUND((AY11+SUM(AY12:AY18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="AZ19" s="54">
-        <f>ROUND((AZ11+SUM(AZ12:AZ18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BA19" s="54">
-        <f>ROUND((BA11+SUM(BA12:BA18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BB19" s="54">
-        <f>ROUND((BB11+SUM(BB12:BB18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BC19" s="54">
-        <f>ROUND((BC11+SUM(BC12:BC18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BD19" s="54">
-        <f>ROUND((BD11+SUM(BD12:BD18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BE19" s="54">
-        <f>ROUND((BE11+SUM(BE12:BE18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BF19" s="54">
-        <f>ROUND((BF11+SUM(BF12:BF18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BG19" s="54">
-        <f>ROUND((BG11+SUM(BG12:BG18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BH19" s="54">
-        <f>ROUND((BH11+SUM(BH12:BH18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BI19" s="54">
-        <f>ROUND((BI11+SUM(BI12:BI18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BJ19" s="54">
-        <f>ROUND((BJ11+SUM(BJ12:BJ18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BK19" s="54">
-        <f>ROUND((BK11+SUM(BK12:BK18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BL19" s="54">
-        <f>ROUND((BL11+SUM(BL12:BL18))/Assumptions!$F$118,0)</f>
-        <v/>
-      </c>
-      <c r="BN19" s="55">
+      <c r="E19" s="38">
+        <f>SUM(E12:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="38">
+        <f>SUM(F12:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="38">
+        <f>SUM(G12:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="38">
+        <f>SUM(H12:H18)</f>
+        <v/>
+      </c>
+      <c r="I19" s="38">
+        <f>SUM(I12:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="38">
+        <f>SUM(J12:J18)</f>
+        <v/>
+      </c>
+      <c r="K19" s="38">
+        <f>SUM(K12:K18)</f>
+        <v/>
+      </c>
+      <c r="L19" s="38">
+        <f>SUM(L12:L18)</f>
+        <v/>
+      </c>
+      <c r="M19" s="38">
+        <f>SUM(M12:M18)</f>
+        <v/>
+      </c>
+      <c r="N19" s="38">
+        <f>SUM(N12:N18)</f>
+        <v/>
+      </c>
+      <c r="O19" s="38">
+        <f>SUM(O12:O18)</f>
+        <v/>
+      </c>
+      <c r="P19" s="38">
+        <f>SUM(P12:P18)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="38">
+        <f>SUM(Q12:Q18)</f>
+        <v/>
+      </c>
+      <c r="R19" s="38">
+        <f>SUM(R12:R18)</f>
+        <v/>
+      </c>
+      <c r="S19" s="38">
+        <f>SUM(S12:S18)</f>
+        <v/>
+      </c>
+      <c r="T19" s="38">
+        <f>SUM(T12:T18)</f>
+        <v/>
+      </c>
+      <c r="U19" s="38">
+        <f>SUM(U12:U18)</f>
+        <v/>
+      </c>
+      <c r="V19" s="38">
+        <f>SUM(V12:V18)</f>
+        <v/>
+      </c>
+      <c r="W19" s="38">
+        <f>SUM(W12:W18)</f>
+        <v/>
+      </c>
+      <c r="X19" s="38">
+        <f>SUM(X12:X18)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="38">
+        <f>SUM(Y12:Y18)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="38">
+        <f>SUM(Z12:Z18)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="38">
+        <f>SUM(AA12:AA18)</f>
+        <v/>
+      </c>
+      <c r="AB19" s="38">
+        <f>SUM(AB12:AB18)</f>
+        <v/>
+      </c>
+      <c r="AC19" s="38">
+        <f>SUM(AC12:AC18)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="38">
+        <f>SUM(AD12:AD18)</f>
+        <v/>
+      </c>
+      <c r="AE19" s="38">
+        <f>SUM(AE12:AE18)</f>
+        <v/>
+      </c>
+      <c r="AF19" s="38">
+        <f>SUM(AF12:AF18)</f>
+        <v/>
+      </c>
+      <c r="AG19" s="38">
+        <f>SUM(AG12:AG18)</f>
+        <v/>
+      </c>
+      <c r="AH19" s="38">
+        <f>SUM(AH12:AH18)</f>
+        <v/>
+      </c>
+      <c r="AI19" s="38">
+        <f>SUM(AI12:AI18)</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="38">
+        <f>SUM(AJ12:AJ18)</f>
+        <v/>
+      </c>
+      <c r="AK19" s="38">
+        <f>SUM(AK12:AK18)</f>
+        <v/>
+      </c>
+      <c r="AL19" s="38">
+        <f>SUM(AL12:AL18)</f>
+        <v/>
+      </c>
+      <c r="AM19" s="38">
+        <f>SUM(AM12:AM18)</f>
+        <v/>
+      </c>
+      <c r="AN19" s="38">
+        <f>SUM(AN12:AN18)</f>
+        <v/>
+      </c>
+      <c r="AO19" s="38">
+        <f>SUM(AO12:AO18)</f>
+        <v/>
+      </c>
+      <c r="AP19" s="38">
+        <f>SUM(AP12:AP18)</f>
+        <v/>
+      </c>
+      <c r="AQ19" s="38">
+        <f>SUM(AQ12:AQ18)</f>
+        <v/>
+      </c>
+      <c r="AR19" s="38">
+        <f>SUM(AR12:AR18)</f>
+        <v/>
+      </c>
+      <c r="AS19" s="38">
+        <f>SUM(AS12:AS18)</f>
+        <v/>
+      </c>
+      <c r="AT19" s="38">
+        <f>SUM(AT12:AT18)</f>
+        <v/>
+      </c>
+      <c r="AU19" s="38">
+        <f>SUM(AU12:AU18)</f>
+        <v/>
+      </c>
+      <c r="AV19" s="38">
+        <f>SUM(AV12:AV18)</f>
+        <v/>
+      </c>
+      <c r="AW19" s="38">
+        <f>SUM(AW12:AW18)</f>
+        <v/>
+      </c>
+      <c r="AX19" s="38">
+        <f>SUM(AX12:AX18)</f>
+        <v/>
+      </c>
+      <c r="AY19" s="38">
+        <f>SUM(AY12:AY18)</f>
+        <v/>
+      </c>
+      <c r="AZ19" s="38">
+        <f>SUM(AZ12:AZ18)</f>
+        <v/>
+      </c>
+      <c r="BA19" s="38">
+        <f>SUM(BA12:BA18)</f>
+        <v/>
+      </c>
+      <c r="BB19" s="38">
+        <f>SUM(BB12:BB18)</f>
+        <v/>
+      </c>
+      <c r="BC19" s="38">
+        <f>SUM(BC12:BC18)</f>
+        <v/>
+      </c>
+      <c r="BD19" s="38">
+        <f>SUM(BD12:BD18)</f>
+        <v/>
+      </c>
+      <c r="BE19" s="38">
+        <f>SUM(BE12:BE18)</f>
+        <v/>
+      </c>
+      <c r="BF19" s="38">
+        <f>SUM(BF12:BF18)</f>
+        <v/>
+      </c>
+      <c r="BG19" s="38">
+        <f>SUM(BG12:BG18)</f>
+        <v/>
+      </c>
+      <c r="BH19" s="38">
+        <f>SUM(BH12:BH18)</f>
+        <v/>
+      </c>
+      <c r="BI19" s="38">
+        <f>SUM(BI12:BI18)</f>
+        <v/>
+      </c>
+      <c r="BJ19" s="38">
+        <f>SUM(BJ12:BJ18)</f>
+        <v/>
+      </c>
+      <c r="BK19" s="38">
+        <f>SUM(BK12:BK18)</f>
+        <v/>
+      </c>
+      <c r="BL19" s="38">
+        <f>SUM(BL12:BL18)</f>
+        <v/>
+      </c>
+      <c r="BN19" s="38">
         <f>P19</f>
         <v/>
       </c>
-      <c r="BO19" s="55">
+      <c r="BO19" s="38">
         <f>AB19</f>
         <v/>
       </c>
-      <c r="BP19" s="55">
+      <c r="BP19" s="38">
         <f>AN19</f>
         <v/>
       </c>
-      <c r="BQ19" s="55">
+      <c r="BQ19" s="38">
         <f>AZ19</f>
         <v/>
       </c>
-      <c r="BR19" s="55">
+      <c r="BR19" s="38">
         <f>BL19</f>
         <v/>
       </c>
@@ -44783,7 +44756,7 @@
     <row r="20">
       <c r="B20" s="50" t="inlineStr">
         <is>
-          <t>Operations, support and administration</t>
+          <t>Total on payroll</t>
         </is>
       </c>
       <c r="C20" s="51" t="inlineStr">
@@ -44792,243 +44765,243 @@
         </is>
       </c>
       <c r="E20" s="38">
-        <f>SUM(E12:E19)</f>
+        <f>E11+E19</f>
         <v/>
       </c>
       <c r="F20" s="38">
-        <f>SUM(F12:F19)</f>
+        <f>F11+F19</f>
         <v/>
       </c>
       <c r="G20" s="38">
-        <f>SUM(G12:G19)</f>
+        <f>G11+G19</f>
         <v/>
       </c>
       <c r="H20" s="38">
-        <f>SUM(H12:H19)</f>
+        <f>H11+H19</f>
         <v/>
       </c>
       <c r="I20" s="38">
-        <f>SUM(I12:I19)</f>
+        <f>I11+I19</f>
         <v/>
       </c>
       <c r="J20" s="38">
-        <f>SUM(J12:J19)</f>
+        <f>J11+J19</f>
         <v/>
       </c>
       <c r="K20" s="38">
-        <f>SUM(K12:K19)</f>
+        <f>K11+K19</f>
         <v/>
       </c>
       <c r="L20" s="38">
-        <f>SUM(L12:L19)</f>
+        <f>L11+L19</f>
         <v/>
       </c>
       <c r="M20" s="38">
-        <f>SUM(M12:M19)</f>
+        <f>M11+M19</f>
         <v/>
       </c>
       <c r="N20" s="38">
-        <f>SUM(N12:N19)</f>
+        <f>N11+N19</f>
         <v/>
       </c>
       <c r="O20" s="38">
-        <f>SUM(O12:O19)</f>
+        <f>O11+O19</f>
         <v/>
       </c>
       <c r="P20" s="38">
-        <f>SUM(P12:P19)</f>
+        <f>P11+P19</f>
         <v/>
       </c>
       <c r="Q20" s="38">
-        <f>SUM(Q12:Q19)</f>
+        <f>Q11+Q19</f>
         <v/>
       </c>
       <c r="R20" s="38">
-        <f>SUM(R12:R19)</f>
+        <f>R11+R19</f>
         <v/>
       </c>
       <c r="S20" s="38">
-        <f>SUM(S12:S19)</f>
+        <f>S11+S19</f>
         <v/>
       </c>
       <c r="T20" s="38">
-        <f>SUM(T12:T19)</f>
+        <f>T11+T19</f>
         <v/>
       </c>
       <c r="U20" s="38">
-        <f>SUM(U12:U19)</f>
+        <f>U11+U19</f>
         <v/>
       </c>
       <c r="V20" s="38">
-        <f>SUM(V12:V19)</f>
+        <f>V11+V19</f>
         <v/>
       </c>
       <c r="W20" s="38">
-        <f>SUM(W12:W19)</f>
+        <f>W11+W19</f>
         <v/>
       </c>
       <c r="X20" s="38">
-        <f>SUM(X12:X19)</f>
+        <f>X11+X19</f>
         <v/>
       </c>
       <c r="Y20" s="38">
-        <f>SUM(Y12:Y19)</f>
+        <f>Y11+Y19</f>
         <v/>
       </c>
       <c r="Z20" s="38">
-        <f>SUM(Z12:Z19)</f>
+        <f>Z11+Z19</f>
         <v/>
       </c>
       <c r="AA20" s="38">
-        <f>SUM(AA12:AA19)</f>
+        <f>AA11+AA19</f>
         <v/>
       </c>
       <c r="AB20" s="38">
-        <f>SUM(AB12:AB19)</f>
+        <f>AB11+AB19</f>
         <v/>
       </c>
       <c r="AC20" s="38">
-        <f>SUM(AC12:AC19)</f>
+        <f>AC11+AC19</f>
         <v/>
       </c>
       <c r="AD20" s="38">
-        <f>SUM(AD12:AD19)</f>
+        <f>AD11+AD19</f>
         <v/>
       </c>
       <c r="AE20" s="38">
-        <f>SUM(AE12:AE19)</f>
+        <f>AE11+AE19</f>
         <v/>
       </c>
       <c r="AF20" s="38">
-        <f>SUM(AF12:AF19)</f>
+        <f>AF11+AF19</f>
         <v/>
       </c>
       <c r="AG20" s="38">
-        <f>SUM(AG12:AG19)</f>
+        <f>AG11+AG19</f>
         <v/>
       </c>
       <c r="AH20" s="38">
-        <f>SUM(AH12:AH19)</f>
+        <f>AH11+AH19</f>
         <v/>
       </c>
       <c r="AI20" s="38">
-        <f>SUM(AI12:AI19)</f>
+        <f>AI11+AI19</f>
         <v/>
       </c>
       <c r="AJ20" s="38">
-        <f>SUM(AJ12:AJ19)</f>
+        <f>AJ11+AJ19</f>
         <v/>
       </c>
       <c r="AK20" s="38">
-        <f>SUM(AK12:AK19)</f>
+        <f>AK11+AK19</f>
         <v/>
       </c>
       <c r="AL20" s="38">
-        <f>SUM(AL12:AL19)</f>
+        <f>AL11+AL19</f>
         <v/>
       </c>
       <c r="AM20" s="38">
-        <f>SUM(AM12:AM19)</f>
+        <f>AM11+AM19</f>
         <v/>
       </c>
       <c r="AN20" s="38">
-        <f>SUM(AN12:AN19)</f>
+        <f>AN11+AN19</f>
         <v/>
       </c>
       <c r="AO20" s="38">
-        <f>SUM(AO12:AO19)</f>
+        <f>AO11+AO19</f>
         <v/>
       </c>
       <c r="AP20" s="38">
-        <f>SUM(AP12:AP19)</f>
+        <f>AP11+AP19</f>
         <v/>
       </c>
       <c r="AQ20" s="38">
-        <f>SUM(AQ12:AQ19)</f>
+        <f>AQ11+AQ19</f>
         <v/>
       </c>
       <c r="AR20" s="38">
-        <f>SUM(AR12:AR19)</f>
+        <f>AR11+AR19</f>
         <v/>
       </c>
       <c r="AS20" s="38">
-        <f>SUM(AS12:AS19)</f>
+        <f>AS11+AS19</f>
         <v/>
       </c>
       <c r="AT20" s="38">
-        <f>SUM(AT12:AT19)</f>
+        <f>AT11+AT19</f>
         <v/>
       </c>
       <c r="AU20" s="38">
-        <f>SUM(AU12:AU19)</f>
+        <f>AU11+AU19</f>
         <v/>
       </c>
       <c r="AV20" s="38">
-        <f>SUM(AV12:AV19)</f>
+        <f>AV11+AV19</f>
         <v/>
       </c>
       <c r="AW20" s="38">
-        <f>SUM(AW12:AW19)</f>
+        <f>AW11+AW19</f>
         <v/>
       </c>
       <c r="AX20" s="38">
-        <f>SUM(AX12:AX19)</f>
+        <f>AX11+AX19</f>
         <v/>
       </c>
       <c r="AY20" s="38">
-        <f>SUM(AY12:AY19)</f>
+        <f>AY11+AY19</f>
         <v/>
       </c>
       <c r="AZ20" s="38">
-        <f>SUM(AZ12:AZ19)</f>
+        <f>AZ11+AZ19</f>
         <v/>
       </c>
       <c r="BA20" s="38">
-        <f>SUM(BA12:BA19)</f>
+        <f>BA11+BA19</f>
         <v/>
       </c>
       <c r="BB20" s="38">
-        <f>SUM(BB12:BB19)</f>
+        <f>BB11+BB19</f>
         <v/>
       </c>
       <c r="BC20" s="38">
-        <f>SUM(BC12:BC19)</f>
+        <f>BC11+BC19</f>
         <v/>
       </c>
       <c r="BD20" s="38">
-        <f>SUM(BD12:BD19)</f>
+        <f>BD11+BD19</f>
         <v/>
       </c>
       <c r="BE20" s="38">
-        <f>SUM(BE12:BE19)</f>
+        <f>BE11+BE19</f>
         <v/>
       </c>
       <c r="BF20" s="38">
-        <f>SUM(BF12:BF19)</f>
+        <f>BF11+BF19</f>
         <v/>
       </c>
       <c r="BG20" s="38">
-        <f>SUM(BG12:BG19)</f>
+        <f>BG11+BG19</f>
         <v/>
       </c>
       <c r="BH20" s="38">
-        <f>SUM(BH12:BH19)</f>
+        <f>BH11+BH19</f>
         <v/>
       </c>
       <c r="BI20" s="38">
-        <f>SUM(BI12:BI19)</f>
+        <f>BI11+BI19</f>
         <v/>
       </c>
       <c r="BJ20" s="38">
-        <f>SUM(BJ12:BJ19)</f>
+        <f>BJ11+BJ19</f>
         <v/>
       </c>
       <c r="BK20" s="38">
-        <f>SUM(BK12:BK19)</f>
+        <f>BK11+BK19</f>
         <v/>
       </c>
       <c r="BL20" s="38">
-        <f>SUM(BL12:BL19)</f>
+        <f>BL11+BL19</f>
         <v/>
       </c>
       <c r="BN20" s="38">
@@ -45053,828 +45026,556 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="50" t="inlineStr">
-        <is>
-          <t>Total on payroll</t>
-        </is>
-      </c>
-      <c r="C21" s="51" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Field service engineers</t>
+        </is>
+      </c>
+      <c r="C21" s="42" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
       </c>
-      <c r="E21" s="38">
-        <f>E11+E20</f>
-        <v/>
-      </c>
-      <c r="F21" s="38">
-        <f>F11+F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="38">
-        <f>G11+G20</f>
-        <v/>
-      </c>
-      <c r="H21" s="38">
-        <f>H11+H20</f>
-        <v/>
-      </c>
-      <c r="I21" s="38">
-        <f>I11+I20</f>
-        <v/>
-      </c>
-      <c r="J21" s="38">
-        <f>J11+J20</f>
-        <v/>
-      </c>
-      <c r="K21" s="38">
-        <f>K11+K20</f>
-        <v/>
-      </c>
-      <c r="L21" s="38">
-        <f>L11+L20</f>
-        <v/>
-      </c>
-      <c r="M21" s="38">
-        <f>M11+M20</f>
-        <v/>
-      </c>
-      <c r="N21" s="38">
-        <f>N11+N20</f>
-        <v/>
-      </c>
-      <c r="O21" s="38">
-        <f>O11+O20</f>
-        <v/>
-      </c>
-      <c r="P21" s="38">
-        <f>P11+P20</f>
-        <v/>
-      </c>
-      <c r="Q21" s="38">
-        <f>Q11+Q20</f>
-        <v/>
-      </c>
-      <c r="R21" s="38">
-        <f>R11+R20</f>
-        <v/>
-      </c>
-      <c r="S21" s="38">
-        <f>S11+S20</f>
-        <v/>
-      </c>
-      <c r="T21" s="38">
-        <f>T11+T20</f>
-        <v/>
-      </c>
-      <c r="U21" s="38">
-        <f>U11+U20</f>
-        <v/>
-      </c>
-      <c r="V21" s="38">
-        <f>V11+V20</f>
-        <v/>
-      </c>
-      <c r="W21" s="38">
-        <f>W11+W20</f>
-        <v/>
-      </c>
-      <c r="X21" s="38">
-        <f>X11+X20</f>
-        <v/>
-      </c>
-      <c r="Y21" s="38">
-        <f>Y11+Y20</f>
-        <v/>
-      </c>
-      <c r="Z21" s="38">
-        <f>Z11+Z20</f>
-        <v/>
-      </c>
-      <c r="AA21" s="38">
-        <f>AA11+AA20</f>
-        <v/>
-      </c>
-      <c r="AB21" s="38">
-        <f>AB11+AB20</f>
-        <v/>
-      </c>
-      <c r="AC21" s="38">
-        <f>AC11+AC20</f>
-        <v/>
-      </c>
-      <c r="AD21" s="38">
-        <f>AD11+AD20</f>
-        <v/>
-      </c>
-      <c r="AE21" s="38">
-        <f>AE11+AE20</f>
-        <v/>
-      </c>
-      <c r="AF21" s="38">
-        <f>AF11+AF20</f>
-        <v/>
-      </c>
-      <c r="AG21" s="38">
-        <f>AG11+AG20</f>
-        <v/>
-      </c>
-      <c r="AH21" s="38">
-        <f>AH11+AH20</f>
-        <v/>
-      </c>
-      <c r="AI21" s="38">
-        <f>AI11+AI20</f>
-        <v/>
-      </c>
-      <c r="AJ21" s="38">
-        <f>AJ11+AJ20</f>
-        <v/>
-      </c>
-      <c r="AK21" s="38">
-        <f>AK11+AK20</f>
-        <v/>
-      </c>
-      <c r="AL21" s="38">
-        <f>AL11+AL20</f>
-        <v/>
-      </c>
-      <c r="AM21" s="38">
-        <f>AM11+AM20</f>
-        <v/>
-      </c>
-      <c r="AN21" s="38">
-        <f>AN11+AN20</f>
-        <v/>
-      </c>
-      <c r="AO21" s="38">
-        <f>AO11+AO20</f>
-        <v/>
-      </c>
-      <c r="AP21" s="38">
-        <f>AP11+AP20</f>
-        <v/>
-      </c>
-      <c r="AQ21" s="38">
-        <f>AQ11+AQ20</f>
-        <v/>
-      </c>
-      <c r="AR21" s="38">
-        <f>AR11+AR20</f>
-        <v/>
-      </c>
-      <c r="AS21" s="38">
-        <f>AS11+AS20</f>
-        <v/>
-      </c>
-      <c r="AT21" s="38">
-        <f>AT11+AT20</f>
-        <v/>
-      </c>
-      <c r="AU21" s="38">
-        <f>AU11+AU20</f>
-        <v/>
-      </c>
-      <c r="AV21" s="38">
-        <f>AV11+AV20</f>
-        <v/>
-      </c>
-      <c r="AW21" s="38">
-        <f>AW11+AW20</f>
-        <v/>
-      </c>
-      <c r="AX21" s="38">
-        <f>AX11+AX20</f>
-        <v/>
-      </c>
-      <c r="AY21" s="38">
-        <f>AY11+AY20</f>
-        <v/>
-      </c>
-      <c r="AZ21" s="38">
-        <f>AZ11+AZ20</f>
-        <v/>
-      </c>
-      <c r="BA21" s="38">
-        <f>BA11+BA20</f>
-        <v/>
-      </c>
-      <c r="BB21" s="38">
-        <f>BB11+BB20</f>
-        <v/>
-      </c>
-      <c r="BC21" s="38">
-        <f>BC11+BC20</f>
-        <v/>
-      </c>
-      <c r="BD21" s="38">
-        <f>BD11+BD20</f>
-        <v/>
-      </c>
-      <c r="BE21" s="38">
-        <f>BE11+BE20</f>
-        <v/>
-      </c>
-      <c r="BF21" s="38">
-        <f>BF11+BF20</f>
-        <v/>
-      </c>
-      <c r="BG21" s="38">
-        <f>BG11+BG20</f>
-        <v/>
-      </c>
-      <c r="BH21" s="38">
-        <f>BH11+BH20</f>
-        <v/>
-      </c>
-      <c r="BI21" s="38">
-        <f>BI11+BI20</f>
-        <v/>
-      </c>
-      <c r="BJ21" s="38">
-        <f>BJ11+BJ20</f>
-        <v/>
-      </c>
-      <c r="BK21" s="38">
-        <f>BK11+BK20</f>
-        <v/>
-      </c>
-      <c r="BL21" s="38">
-        <f>BL11+BL20</f>
-        <v/>
-      </c>
-      <c r="BN21" s="38">
+      <c r="E21" s="54">
+        <f>ROUND('Revenue Forecast'!E41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="54">
+        <f>ROUND('Revenue Forecast'!F41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="54">
+        <f>ROUND('Revenue Forecast'!G41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="54">
+        <f>ROUND('Revenue Forecast'!H41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="I21" s="54">
+        <f>ROUND('Revenue Forecast'!I41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="54">
+        <f>ROUND('Revenue Forecast'!J41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="54">
+        <f>ROUND('Revenue Forecast'!K41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="54">
+        <f>ROUND('Revenue Forecast'!L41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="54">
+        <f>ROUND('Revenue Forecast'!M41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="54">
+        <f>ROUND('Revenue Forecast'!N41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="54">
+        <f>ROUND('Revenue Forecast'!O41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="P21" s="54">
+        <f>ROUND('Revenue Forecast'!P41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="54">
+        <f>ROUND('Revenue Forecast'!Q41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="R21" s="54">
+        <f>ROUND('Revenue Forecast'!R41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="S21" s="54">
+        <f>ROUND('Revenue Forecast'!S41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="T21" s="54">
+        <f>ROUND('Revenue Forecast'!T41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="U21" s="54">
+        <f>ROUND('Revenue Forecast'!U41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="V21" s="54">
+        <f>ROUND('Revenue Forecast'!V41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="W21" s="54">
+        <f>ROUND('Revenue Forecast'!W41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="X21" s="54">
+        <f>ROUND('Revenue Forecast'!X41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="54">
+        <f>ROUND('Revenue Forecast'!Y41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="54">
+        <f>ROUND('Revenue Forecast'!Z41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="54">
+        <f>ROUND('Revenue Forecast'!AA41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AB21" s="54">
+        <f>ROUND('Revenue Forecast'!AB41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AC21" s="54">
+        <f>ROUND('Revenue Forecast'!AC41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="54">
+        <f>ROUND('Revenue Forecast'!AD41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AE21" s="54">
+        <f>ROUND('Revenue Forecast'!AE41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AF21" s="54">
+        <f>ROUND('Revenue Forecast'!AF41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AG21" s="54">
+        <f>ROUND('Revenue Forecast'!AG41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AH21" s="54">
+        <f>ROUND('Revenue Forecast'!AH41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AI21" s="54">
+        <f>ROUND('Revenue Forecast'!AI41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="54">
+        <f>ROUND('Revenue Forecast'!AJ41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AK21" s="54">
+        <f>ROUND('Revenue Forecast'!AK41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AL21" s="54">
+        <f>ROUND('Revenue Forecast'!AL41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AM21" s="54">
+        <f>ROUND('Revenue Forecast'!AM41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AN21" s="54">
+        <f>ROUND('Revenue Forecast'!AN41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AO21" s="54">
+        <f>ROUND('Revenue Forecast'!AO41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AP21" s="54">
+        <f>ROUND('Revenue Forecast'!AP41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AQ21" s="54">
+        <f>ROUND('Revenue Forecast'!AQ41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AR21" s="54">
+        <f>ROUND('Revenue Forecast'!AR41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AS21" s="54">
+        <f>ROUND('Revenue Forecast'!AS41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AT21" s="54">
+        <f>ROUND('Revenue Forecast'!AT41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AU21" s="54">
+        <f>ROUND('Revenue Forecast'!AU41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AV21" s="54">
+        <f>ROUND('Revenue Forecast'!AV41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AW21" s="54">
+        <f>ROUND('Revenue Forecast'!AW41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AX21" s="54">
+        <f>ROUND('Revenue Forecast'!AX41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AY21" s="54">
+        <f>ROUND('Revenue Forecast'!AY41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="AZ21" s="54">
+        <f>ROUND('Revenue Forecast'!AZ41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BA21" s="54">
+        <f>ROUND('Revenue Forecast'!BA41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BB21" s="54">
+        <f>ROUND('Revenue Forecast'!BB41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BC21" s="54">
+        <f>ROUND('Revenue Forecast'!BC41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BD21" s="54">
+        <f>ROUND('Revenue Forecast'!BD41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BE21" s="54">
+        <f>ROUND('Revenue Forecast'!BE41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BF21" s="54">
+        <f>ROUND('Revenue Forecast'!BF41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BG21" s="54">
+        <f>ROUND('Revenue Forecast'!BG41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BH21" s="54">
+        <f>ROUND('Revenue Forecast'!BH41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BI21" s="54">
+        <f>ROUND('Revenue Forecast'!BI41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BJ21" s="54">
+        <f>ROUND('Revenue Forecast'!BJ41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BK21" s="54">
+        <f>ROUND('Revenue Forecast'!BK41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BL21" s="54">
+        <f>ROUND('Revenue Forecast'!BL41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <v/>
+      </c>
+      <c r="BN21" s="55">
         <f>P21</f>
         <v/>
       </c>
-      <c r="BO21" s="38">
+      <c r="BO21" s="55">
         <f>AB21</f>
         <v/>
       </c>
-      <c r="BP21" s="38">
+      <c r="BP21" s="55">
         <f>AN21</f>
         <v/>
       </c>
-      <c r="BQ21" s="38">
+      <c r="BQ21" s="55">
         <f>AZ21</f>
         <v/>
       </c>
-      <c r="BR21" s="38">
+      <c r="BR21" s="55">
         <f>BL21</f>
         <v/>
+      </c>
+      <c r="BT21" s="20" t="inlineStr">
+        <is>
+          <t>counted here but paid for in service COGS, so they are not charged twice</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Field service engineers</t>
-        </is>
-      </c>
-      <c r="C22" s="42" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>Total headcount</t>
+        </is>
+      </c>
+      <c r="C22" s="45" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
       </c>
-      <c r="E22" s="54">
-        <f>ROUND('Revenue Forecast'!E41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="F22" s="54">
-        <f>ROUND('Revenue Forecast'!F41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="G22" s="54">
-        <f>ROUND('Revenue Forecast'!G41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="H22" s="54">
-        <f>ROUND('Revenue Forecast'!H41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="I22" s="54">
-        <f>ROUND('Revenue Forecast'!I41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="J22" s="54">
-        <f>ROUND('Revenue Forecast'!J41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="K22" s="54">
-        <f>ROUND('Revenue Forecast'!K41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="L22" s="54">
-        <f>ROUND('Revenue Forecast'!L41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="M22" s="54">
-        <f>ROUND('Revenue Forecast'!M41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="N22" s="54">
-        <f>ROUND('Revenue Forecast'!N41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="O22" s="54">
-        <f>ROUND('Revenue Forecast'!O41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="P22" s="54">
-        <f>ROUND('Revenue Forecast'!P41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="54">
-        <f>ROUND('Revenue Forecast'!Q41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="R22" s="54">
-        <f>ROUND('Revenue Forecast'!R41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="S22" s="54">
-        <f>ROUND('Revenue Forecast'!S41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="T22" s="54">
-        <f>ROUND('Revenue Forecast'!T41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="U22" s="54">
-        <f>ROUND('Revenue Forecast'!U41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="V22" s="54">
-        <f>ROUND('Revenue Forecast'!V41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="W22" s="54">
-        <f>ROUND('Revenue Forecast'!W41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="X22" s="54">
-        <f>ROUND('Revenue Forecast'!X41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="Y22" s="54">
-        <f>ROUND('Revenue Forecast'!Y41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="Z22" s="54">
-        <f>ROUND('Revenue Forecast'!Z41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AA22" s="54">
-        <f>ROUND('Revenue Forecast'!AA41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AB22" s="54">
-        <f>ROUND('Revenue Forecast'!AB41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AC22" s="54">
-        <f>ROUND('Revenue Forecast'!AC41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AD22" s="54">
-        <f>ROUND('Revenue Forecast'!AD41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AE22" s="54">
-        <f>ROUND('Revenue Forecast'!AE41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AF22" s="54">
-        <f>ROUND('Revenue Forecast'!AF41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AG22" s="54">
-        <f>ROUND('Revenue Forecast'!AG41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AH22" s="54">
-        <f>ROUND('Revenue Forecast'!AH41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AI22" s="54">
-        <f>ROUND('Revenue Forecast'!AI41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AJ22" s="54">
-        <f>ROUND('Revenue Forecast'!AJ41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AK22" s="54">
-        <f>ROUND('Revenue Forecast'!AK41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AL22" s="54">
-        <f>ROUND('Revenue Forecast'!AL41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AM22" s="54">
-        <f>ROUND('Revenue Forecast'!AM41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AN22" s="54">
-        <f>ROUND('Revenue Forecast'!AN41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AO22" s="54">
-        <f>ROUND('Revenue Forecast'!AO41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AP22" s="54">
-        <f>ROUND('Revenue Forecast'!AP41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AQ22" s="54">
-        <f>ROUND('Revenue Forecast'!AQ41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AR22" s="54">
-        <f>ROUND('Revenue Forecast'!AR41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AS22" s="54">
-        <f>ROUND('Revenue Forecast'!AS41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AT22" s="54">
-        <f>ROUND('Revenue Forecast'!AT41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AU22" s="54">
-        <f>ROUND('Revenue Forecast'!AU41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AV22" s="54">
-        <f>ROUND('Revenue Forecast'!AV41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AW22" s="54">
-        <f>ROUND('Revenue Forecast'!AW41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AX22" s="54">
-        <f>ROUND('Revenue Forecast'!AX41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AY22" s="54">
-        <f>ROUND('Revenue Forecast'!AY41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="AZ22" s="54">
-        <f>ROUND('Revenue Forecast'!AZ41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BA22" s="54">
-        <f>ROUND('Revenue Forecast'!BA41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BB22" s="54">
-        <f>ROUND('Revenue Forecast'!BB41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BC22" s="54">
-        <f>ROUND('Revenue Forecast'!BC41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BD22" s="54">
-        <f>ROUND('Revenue Forecast'!BD41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BE22" s="54">
-        <f>ROUND('Revenue Forecast'!BE41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BF22" s="54">
-        <f>ROUND('Revenue Forecast'!BF41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BG22" s="54">
-        <f>ROUND('Revenue Forecast'!BG41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BH22" s="54">
-        <f>ROUND('Revenue Forecast'!BH41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BI22" s="54">
-        <f>ROUND('Revenue Forecast'!BI41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BJ22" s="54">
-        <f>ROUND('Revenue Forecast'!BJ41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BK22" s="54">
-        <f>ROUND('Revenue Forecast'!BK41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BL22" s="54">
-        <f>ROUND('Revenue Forecast'!BL41*Assumptions!$F$45/Assumptions!$F$119,0)</f>
-        <v/>
-      </c>
-      <c r="BN22" s="55">
+      <c r="D22" s="1" t="n"/>
+      <c r="E22" s="69">
+        <f>E20+E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="69">
+        <f>F20+F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="69">
+        <f>G20+G21</f>
+        <v/>
+      </c>
+      <c r="H22" s="69">
+        <f>H20+H21</f>
+        <v/>
+      </c>
+      <c r="I22" s="69">
+        <f>I20+I21</f>
+        <v/>
+      </c>
+      <c r="J22" s="69">
+        <f>J20+J21</f>
+        <v/>
+      </c>
+      <c r="K22" s="69">
+        <f>K20+K21</f>
+        <v/>
+      </c>
+      <c r="L22" s="69">
+        <f>L20+L21</f>
+        <v/>
+      </c>
+      <c r="M22" s="69">
+        <f>M20+M21</f>
+        <v/>
+      </c>
+      <c r="N22" s="69">
+        <f>N20+N21</f>
+        <v/>
+      </c>
+      <c r="O22" s="69">
+        <f>O20+O21</f>
+        <v/>
+      </c>
+      <c r="P22" s="69">
+        <f>P20+P21</f>
+        <v/>
+      </c>
+      <c r="Q22" s="69">
+        <f>Q20+Q21</f>
+        <v/>
+      </c>
+      <c r="R22" s="69">
+        <f>R20+R21</f>
+        <v/>
+      </c>
+      <c r="S22" s="69">
+        <f>S20+S21</f>
+        <v/>
+      </c>
+      <c r="T22" s="69">
+        <f>T20+T21</f>
+        <v/>
+      </c>
+      <c r="U22" s="69">
+        <f>U20+U21</f>
+        <v/>
+      </c>
+      <c r="V22" s="69">
+        <f>V20+V21</f>
+        <v/>
+      </c>
+      <c r="W22" s="69">
+        <f>W20+W21</f>
+        <v/>
+      </c>
+      <c r="X22" s="69">
+        <f>X20+X21</f>
+        <v/>
+      </c>
+      <c r="Y22" s="69">
+        <f>Y20+Y21</f>
+        <v/>
+      </c>
+      <c r="Z22" s="69">
+        <f>Z20+Z21</f>
+        <v/>
+      </c>
+      <c r="AA22" s="69">
+        <f>AA20+AA21</f>
+        <v/>
+      </c>
+      <c r="AB22" s="69">
+        <f>AB20+AB21</f>
+        <v/>
+      </c>
+      <c r="AC22" s="69">
+        <f>AC20+AC21</f>
+        <v/>
+      </c>
+      <c r="AD22" s="69">
+        <f>AD20+AD21</f>
+        <v/>
+      </c>
+      <c r="AE22" s="69">
+        <f>AE20+AE21</f>
+        <v/>
+      </c>
+      <c r="AF22" s="69">
+        <f>AF20+AF21</f>
+        <v/>
+      </c>
+      <c r="AG22" s="69">
+        <f>AG20+AG21</f>
+        <v/>
+      </c>
+      <c r="AH22" s="69">
+        <f>AH20+AH21</f>
+        <v/>
+      </c>
+      <c r="AI22" s="69">
+        <f>AI20+AI21</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="69">
+        <f>AJ20+AJ21</f>
+        <v/>
+      </c>
+      <c r="AK22" s="69">
+        <f>AK20+AK21</f>
+        <v/>
+      </c>
+      <c r="AL22" s="69">
+        <f>AL20+AL21</f>
+        <v/>
+      </c>
+      <c r="AM22" s="69">
+        <f>AM20+AM21</f>
+        <v/>
+      </c>
+      <c r="AN22" s="69">
+        <f>AN20+AN21</f>
+        <v/>
+      </c>
+      <c r="AO22" s="69">
+        <f>AO20+AO21</f>
+        <v/>
+      </c>
+      <c r="AP22" s="69">
+        <f>AP20+AP21</f>
+        <v/>
+      </c>
+      <c r="AQ22" s="69">
+        <f>AQ20+AQ21</f>
+        <v/>
+      </c>
+      <c r="AR22" s="69">
+        <f>AR20+AR21</f>
+        <v/>
+      </c>
+      <c r="AS22" s="69">
+        <f>AS20+AS21</f>
+        <v/>
+      </c>
+      <c r="AT22" s="69">
+        <f>AT20+AT21</f>
+        <v/>
+      </c>
+      <c r="AU22" s="69">
+        <f>AU20+AU21</f>
+        <v/>
+      </c>
+      <c r="AV22" s="69">
+        <f>AV20+AV21</f>
+        <v/>
+      </c>
+      <c r="AW22" s="69">
+        <f>AW20+AW21</f>
+        <v/>
+      </c>
+      <c r="AX22" s="69">
+        <f>AX20+AX21</f>
+        <v/>
+      </c>
+      <c r="AY22" s="69">
+        <f>AY20+AY21</f>
+        <v/>
+      </c>
+      <c r="AZ22" s="69">
+        <f>AZ20+AZ21</f>
+        <v/>
+      </c>
+      <c r="BA22" s="69">
+        <f>BA20+BA21</f>
+        <v/>
+      </c>
+      <c r="BB22" s="69">
+        <f>BB20+BB21</f>
+        <v/>
+      </c>
+      <c r="BC22" s="69">
+        <f>BC20+BC21</f>
+        <v/>
+      </c>
+      <c r="BD22" s="69">
+        <f>BD20+BD21</f>
+        <v/>
+      </c>
+      <c r="BE22" s="69">
+        <f>BE20+BE21</f>
+        <v/>
+      </c>
+      <c r="BF22" s="69">
+        <f>BF20+BF21</f>
+        <v/>
+      </c>
+      <c r="BG22" s="69">
+        <f>BG20+BG21</f>
+        <v/>
+      </c>
+      <c r="BH22" s="69">
+        <f>BH20+BH21</f>
+        <v/>
+      </c>
+      <c r="BI22" s="69">
+        <f>BI20+BI21</f>
+        <v/>
+      </c>
+      <c r="BJ22" s="69">
+        <f>BJ20+BJ21</f>
+        <v/>
+      </c>
+      <c r="BK22" s="69">
+        <f>BK20+BK21</f>
+        <v/>
+      </c>
+      <c r="BL22" s="69">
+        <f>BL20+BL21</f>
+        <v/>
+      </c>
+      <c r="BM22" s="1" t="n"/>
+      <c r="BN22" s="69">
         <f>P22</f>
         <v/>
       </c>
-      <c r="BO22" s="55">
+      <c r="BO22" s="69">
         <f>AB22</f>
         <v/>
       </c>
-      <c r="BP22" s="55">
+      <c r="BP22" s="69">
         <f>AN22</f>
         <v/>
       </c>
-      <c r="BQ22" s="55">
+      <c r="BQ22" s="69">
         <f>AZ22</f>
         <v/>
       </c>
-      <c r="BR22" s="55">
+      <c r="BR22" s="69">
         <f>BL22</f>
         <v/>
       </c>
-      <c r="BT22" s="20" t="inlineStr">
-        <is>
-          <t>counted here but paid for in service COGS, so they are not charged twice</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t>Total headcount</t>
-        </is>
-      </c>
-      <c r="C23" s="45" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n"/>
-      <c r="E23" s="69">
-        <f>E21+E22</f>
-        <v/>
-      </c>
-      <c r="F23" s="69">
-        <f>F21+F22</f>
-        <v/>
-      </c>
-      <c r="G23" s="69">
-        <f>G21+G22</f>
-        <v/>
-      </c>
-      <c r="H23" s="69">
-        <f>H21+H22</f>
-        <v/>
-      </c>
-      <c r="I23" s="69">
-        <f>I21+I22</f>
-        <v/>
-      </c>
-      <c r="J23" s="69">
-        <f>J21+J22</f>
-        <v/>
-      </c>
-      <c r="K23" s="69">
-        <f>K21+K22</f>
-        <v/>
-      </c>
-      <c r="L23" s="69">
-        <f>L21+L22</f>
-        <v/>
-      </c>
-      <c r="M23" s="69">
-        <f>M21+M22</f>
-        <v/>
-      </c>
-      <c r="N23" s="69">
-        <f>N21+N22</f>
-        <v/>
-      </c>
-      <c r="O23" s="69">
-        <f>O21+O22</f>
-        <v/>
-      </c>
-      <c r="P23" s="69">
-        <f>P21+P22</f>
-        <v/>
-      </c>
-      <c r="Q23" s="69">
-        <f>Q21+Q22</f>
-        <v/>
-      </c>
-      <c r="R23" s="69">
-        <f>R21+R22</f>
-        <v/>
-      </c>
-      <c r="S23" s="69">
-        <f>S21+S22</f>
-        <v/>
-      </c>
-      <c r="T23" s="69">
-        <f>T21+T22</f>
-        <v/>
-      </c>
-      <c r="U23" s="69">
-        <f>U21+U22</f>
-        <v/>
-      </c>
-      <c r="V23" s="69">
-        <f>V21+V22</f>
-        <v/>
-      </c>
-      <c r="W23" s="69">
-        <f>W21+W22</f>
-        <v/>
-      </c>
-      <c r="X23" s="69">
-        <f>X21+X22</f>
-        <v/>
-      </c>
-      <c r="Y23" s="69">
-        <f>Y21+Y22</f>
-        <v/>
-      </c>
-      <c r="Z23" s="69">
-        <f>Z21+Z22</f>
-        <v/>
-      </c>
-      <c r="AA23" s="69">
-        <f>AA21+AA22</f>
-        <v/>
-      </c>
-      <c r="AB23" s="69">
-        <f>AB21+AB22</f>
-        <v/>
-      </c>
-      <c r="AC23" s="69">
-        <f>AC21+AC22</f>
-        <v/>
-      </c>
-      <c r="AD23" s="69">
-        <f>AD21+AD22</f>
-        <v/>
-      </c>
-      <c r="AE23" s="69">
-        <f>AE21+AE22</f>
-        <v/>
-      </c>
-      <c r="AF23" s="69">
-        <f>AF21+AF22</f>
-        <v/>
-      </c>
-      <c r="AG23" s="69">
-        <f>AG21+AG22</f>
-        <v/>
-      </c>
-      <c r="AH23" s="69">
-        <f>AH21+AH22</f>
-        <v/>
-      </c>
-      <c r="AI23" s="69">
-        <f>AI21+AI22</f>
-        <v/>
-      </c>
-      <c r="AJ23" s="69">
-        <f>AJ21+AJ22</f>
-        <v/>
-      </c>
-      <c r="AK23" s="69">
-        <f>AK21+AK22</f>
-        <v/>
-      </c>
-      <c r="AL23" s="69">
-        <f>AL21+AL22</f>
-        <v/>
-      </c>
-      <c r="AM23" s="69">
-        <f>AM21+AM22</f>
-        <v/>
-      </c>
-      <c r="AN23" s="69">
-        <f>AN21+AN22</f>
-        <v/>
-      </c>
-      <c r="AO23" s="69">
-        <f>AO21+AO22</f>
-        <v/>
-      </c>
-      <c r="AP23" s="69">
-        <f>AP21+AP22</f>
-        <v/>
-      </c>
-      <c r="AQ23" s="69">
-        <f>AQ21+AQ22</f>
-        <v/>
-      </c>
-      <c r="AR23" s="69">
-        <f>AR21+AR22</f>
-        <v/>
-      </c>
-      <c r="AS23" s="69">
-        <f>AS21+AS22</f>
-        <v/>
-      </c>
-      <c r="AT23" s="69">
-        <f>AT21+AT22</f>
-        <v/>
-      </c>
-      <c r="AU23" s="69">
-        <f>AU21+AU22</f>
-        <v/>
-      </c>
-      <c r="AV23" s="69">
-        <f>AV21+AV22</f>
-        <v/>
-      </c>
-      <c r="AW23" s="69">
-        <f>AW21+AW22</f>
-        <v/>
-      </c>
-      <c r="AX23" s="69">
-        <f>AX21+AX22</f>
-        <v/>
-      </c>
-      <c r="AY23" s="69">
-        <f>AY21+AY22</f>
-        <v/>
-      </c>
-      <c r="AZ23" s="69">
-        <f>AZ21+AZ22</f>
-        <v/>
-      </c>
-      <c r="BA23" s="69">
-        <f>BA21+BA22</f>
-        <v/>
-      </c>
-      <c r="BB23" s="69">
-        <f>BB21+BB22</f>
-        <v/>
-      </c>
-      <c r="BC23" s="69">
-        <f>BC21+BC22</f>
-        <v/>
-      </c>
-      <c r="BD23" s="69">
-        <f>BD21+BD22</f>
-        <v/>
-      </c>
-      <c r="BE23" s="69">
-        <f>BE21+BE22</f>
-        <v/>
-      </c>
-      <c r="BF23" s="69">
-        <f>BF21+BF22</f>
-        <v/>
-      </c>
-      <c r="BG23" s="69">
-        <f>BG21+BG22</f>
-        <v/>
-      </c>
-      <c r="BH23" s="69">
-        <f>BH21+BH22</f>
-        <v/>
-      </c>
-      <c r="BI23" s="69">
-        <f>BI21+BI22</f>
-        <v/>
-      </c>
-      <c r="BJ23" s="69">
-        <f>BJ21+BJ22</f>
-        <v/>
-      </c>
-      <c r="BK23" s="69">
-        <f>BK21+BK22</f>
-        <v/>
-      </c>
-      <c r="BL23" s="69">
-        <f>BL21+BL22</f>
-        <v/>
-      </c>
-      <c r="BM23" s="1" t="n"/>
-      <c r="BN23" s="69">
-        <f>P23</f>
-        <v/>
-      </c>
-      <c r="BO23" s="69">
-        <f>AB23</f>
-        <v/>
-      </c>
-      <c r="BP23" s="69">
-        <f>AN23</f>
-        <v/>
-      </c>
-      <c r="BQ23" s="69">
-        <f>AZ23</f>
-        <v/>
-      </c>
-      <c r="BR23" s="69">
-        <f>BL23</f>
-        <v/>
-      </c>
-      <c r="BS23" s="1" t="n"/>
+      <c r="BS22" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="39" t="inlineStr">
@@ -45964,243 +45665,243 @@
         </is>
       </c>
       <c r="E26" s="43">
-        <f>E17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
+        <f>E17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F26" s="43">
-        <f>F17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
+        <f>F17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G26" s="43">
-        <f>G17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
+        <f>G17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H26" s="43">
-        <f>H17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
+        <f>H17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I26" s="43">
-        <f>I17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
+        <f>I17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J26" s="43">
-        <f>J17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
+        <f>J17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K26" s="43">
-        <f>K17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
+        <f>K17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L26" s="43">
-        <f>L17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
+        <f>L17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M26" s="43">
-        <f>M17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
+        <f>M17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N26" s="43">
-        <f>N17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
+        <f>N17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O26" s="43">
-        <f>O17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
+        <f>O17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P26" s="43">
-        <f>P17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
+        <f>P17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q26" s="43">
-        <f>Q17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
+        <f>Q17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R26" s="43">
-        <f>R17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
+        <f>R17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S26" s="43">
-        <f>S17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
+        <f>S17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T26" s="43">
-        <f>T17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
+        <f>T17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U26" s="43">
-        <f>U17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
+        <f>U17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V26" s="43">
-        <f>V17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
+        <f>V17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W26" s="43">
-        <f>W17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
+        <f>W17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X26" s="43">
-        <f>X17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
+        <f>X17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y26" s="43">
-        <f>Y17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
+        <f>Y17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z26" s="43">
-        <f>Z17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
+        <f>Z17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA26" s="43">
-        <f>AA17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
+        <f>AA17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB26" s="43">
-        <f>AB17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
+        <f>AB17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC26" s="43">
-        <f>AC17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
+        <f>AC17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD26" s="43">
-        <f>AD17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
+        <f>AD17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE26" s="43">
-        <f>AE17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
+        <f>AE17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF26" s="43">
-        <f>AF17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
+        <f>AF17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG26" s="43">
-        <f>AG17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
+        <f>AG17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH26" s="43">
-        <f>AH17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
+        <f>AH17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI26" s="43">
-        <f>AI17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
+        <f>AI17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ26" s="43">
-        <f>AJ17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
+        <f>AJ17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK26" s="43">
-        <f>AK17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
+        <f>AK17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL26" s="43">
-        <f>AL17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
+        <f>AL17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM26" s="43">
-        <f>AM17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
+        <f>AM17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN26" s="43">
-        <f>AN17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
+        <f>AN17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO26" s="43">
-        <f>AO17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
+        <f>AO17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP26" s="43">
-        <f>AP17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
+        <f>AP17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ26" s="43">
-        <f>AQ17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
+        <f>AQ17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR26" s="43">
-        <f>AR17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
+        <f>AR17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS26" s="43">
-        <f>AS17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
+        <f>AS17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT26" s="43">
-        <f>AT17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
+        <f>AT17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU26" s="43">
-        <f>AU17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
+        <f>AU17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV26" s="43">
-        <f>AV17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
+        <f>AV17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW26" s="43">
-        <f>AW17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
+        <f>AW17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX26" s="43">
-        <f>AX17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
+        <f>AX17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY26" s="43">
-        <f>AY17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
+        <f>AY17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ26" s="43">
-        <f>AZ17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
+        <f>AZ17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA26" s="43">
-        <f>BA17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
+        <f>BA17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB26" s="43">
-        <f>BB17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
+        <f>BB17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC26" s="43">
-        <f>BC17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
+        <f>BC17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD26" s="43">
-        <f>BD17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
+        <f>BD17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE26" s="43">
-        <f>BE17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
+        <f>BE17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF26" s="43">
-        <f>BF17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
+        <f>BF17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG26" s="43">
-        <f>BG17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
+        <f>BG17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH26" s="43">
-        <f>BH17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
+        <f>BH17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI26" s="43">
-        <f>BI17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
+        <f>BI17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ26" s="43">
-        <f>BJ17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
+        <f>BJ17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK26" s="43">
-        <f>BK17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
+        <f>BK17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL26" s="43">
-        <f>BL17*Assumptions!$F$128*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
+        <f>BL17*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN26" s="44">
@@ -46236,243 +45937,243 @@
         </is>
       </c>
       <c r="E27" s="43">
-        <f>(E6*Assumptions!$F$122+E7*Assumptions!$F$123+(E8+E9+E10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
+        <f>(E6*Assumptions!$F$121+E7*Assumptions!$F$122+(E8+E9+E10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F27" s="43">
-        <f>(F6*Assumptions!$F$122+F7*Assumptions!$F$123+(F8+F9+F10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
+        <f>(F6*Assumptions!$F$121+F7*Assumptions!$F$122+(F8+F9+F10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G27" s="43">
-        <f>(G6*Assumptions!$F$122+G7*Assumptions!$F$123+(G8+G9+G10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
+        <f>(G6*Assumptions!$F$121+G7*Assumptions!$F$122+(G8+G9+G10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H27" s="43">
-        <f>(H6*Assumptions!$F$122+H7*Assumptions!$F$123+(H8+H9+H10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
+        <f>(H6*Assumptions!$F$121+H7*Assumptions!$F$122+(H8+H9+H10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I27" s="43">
-        <f>(I6*Assumptions!$F$122+I7*Assumptions!$F$123+(I8+I9+I10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
+        <f>(I6*Assumptions!$F$121+I7*Assumptions!$F$122+(I8+I9+I10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J27" s="43">
-        <f>(J6*Assumptions!$F$122+J7*Assumptions!$F$123+(J8+J9+J10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
+        <f>(J6*Assumptions!$F$121+J7*Assumptions!$F$122+(J8+J9+J10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K27" s="43">
-        <f>(K6*Assumptions!$F$122+K7*Assumptions!$F$123+(K8+K9+K10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
+        <f>(K6*Assumptions!$F$121+K7*Assumptions!$F$122+(K8+K9+K10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L27" s="43">
-        <f>(L6*Assumptions!$F$122+L7*Assumptions!$F$123+(L8+L9+L10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
+        <f>(L6*Assumptions!$F$121+L7*Assumptions!$F$122+(L8+L9+L10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M27" s="43">
-        <f>(M6*Assumptions!$F$122+M7*Assumptions!$F$123+(M8+M9+M10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
+        <f>(M6*Assumptions!$F$121+M7*Assumptions!$F$122+(M8+M9+M10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N27" s="43">
-        <f>(N6*Assumptions!$F$122+N7*Assumptions!$F$123+(N8+N9+N10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
+        <f>(N6*Assumptions!$F$121+N7*Assumptions!$F$122+(N8+N9+N10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O27" s="43">
-        <f>(O6*Assumptions!$F$122+O7*Assumptions!$F$123+(O8+O9+O10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
+        <f>(O6*Assumptions!$F$121+O7*Assumptions!$F$122+(O8+O9+O10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P27" s="43">
-        <f>(P6*Assumptions!$F$122+P7*Assumptions!$F$123+(P8+P9+P10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
+        <f>(P6*Assumptions!$F$121+P7*Assumptions!$F$122+(P8+P9+P10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q27" s="43">
-        <f>(Q6*Assumptions!$F$122+Q7*Assumptions!$F$123+(Q8+Q9+Q10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
+        <f>(Q6*Assumptions!$F$121+Q7*Assumptions!$F$122+(Q8+Q9+Q10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R27" s="43">
-        <f>(R6*Assumptions!$F$122+R7*Assumptions!$F$123+(R8+R9+R10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
+        <f>(R6*Assumptions!$F$121+R7*Assumptions!$F$122+(R8+R9+R10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S27" s="43">
-        <f>(S6*Assumptions!$F$122+S7*Assumptions!$F$123+(S8+S9+S10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
+        <f>(S6*Assumptions!$F$121+S7*Assumptions!$F$122+(S8+S9+S10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T27" s="43">
-        <f>(T6*Assumptions!$F$122+T7*Assumptions!$F$123+(T8+T9+T10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
+        <f>(T6*Assumptions!$F$121+T7*Assumptions!$F$122+(T8+T9+T10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U27" s="43">
-        <f>(U6*Assumptions!$F$122+U7*Assumptions!$F$123+(U8+U9+U10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
+        <f>(U6*Assumptions!$F$121+U7*Assumptions!$F$122+(U8+U9+U10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V27" s="43">
-        <f>(V6*Assumptions!$F$122+V7*Assumptions!$F$123+(V8+V9+V10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
+        <f>(V6*Assumptions!$F$121+V7*Assumptions!$F$122+(V8+V9+V10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W27" s="43">
-        <f>(W6*Assumptions!$F$122+W7*Assumptions!$F$123+(W8+W9+W10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
+        <f>(W6*Assumptions!$F$121+W7*Assumptions!$F$122+(W8+W9+W10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X27" s="43">
-        <f>(X6*Assumptions!$F$122+X7*Assumptions!$F$123+(X8+X9+X10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
+        <f>(X6*Assumptions!$F$121+X7*Assumptions!$F$122+(X8+X9+X10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y27" s="43">
-        <f>(Y6*Assumptions!$F$122+Y7*Assumptions!$F$123+(Y8+Y9+Y10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
+        <f>(Y6*Assumptions!$F$121+Y7*Assumptions!$F$122+(Y8+Y9+Y10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z27" s="43">
-        <f>(Z6*Assumptions!$F$122+Z7*Assumptions!$F$123+(Z8+Z9+Z10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
+        <f>(Z6*Assumptions!$F$121+Z7*Assumptions!$F$122+(Z8+Z9+Z10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA27" s="43">
-        <f>(AA6*Assumptions!$F$122+AA7*Assumptions!$F$123+(AA8+AA9+AA10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
+        <f>(AA6*Assumptions!$F$121+AA7*Assumptions!$F$122+(AA8+AA9+AA10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB27" s="43">
-        <f>(AB6*Assumptions!$F$122+AB7*Assumptions!$F$123+(AB8+AB9+AB10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
+        <f>(AB6*Assumptions!$F$121+AB7*Assumptions!$F$122+(AB8+AB9+AB10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC27" s="43">
-        <f>(AC6*Assumptions!$F$122+AC7*Assumptions!$F$123+(AC8+AC9+AC10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
+        <f>(AC6*Assumptions!$F$121+AC7*Assumptions!$F$122+(AC8+AC9+AC10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD27" s="43">
-        <f>(AD6*Assumptions!$F$122+AD7*Assumptions!$F$123+(AD8+AD9+AD10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
+        <f>(AD6*Assumptions!$F$121+AD7*Assumptions!$F$122+(AD8+AD9+AD10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE27" s="43">
-        <f>(AE6*Assumptions!$F$122+AE7*Assumptions!$F$123+(AE8+AE9+AE10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
+        <f>(AE6*Assumptions!$F$121+AE7*Assumptions!$F$122+(AE8+AE9+AE10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF27" s="43">
-        <f>(AF6*Assumptions!$F$122+AF7*Assumptions!$F$123+(AF8+AF9+AF10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
+        <f>(AF6*Assumptions!$F$121+AF7*Assumptions!$F$122+(AF8+AF9+AF10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG27" s="43">
-        <f>(AG6*Assumptions!$F$122+AG7*Assumptions!$F$123+(AG8+AG9+AG10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
+        <f>(AG6*Assumptions!$F$121+AG7*Assumptions!$F$122+(AG8+AG9+AG10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH27" s="43">
-        <f>(AH6*Assumptions!$F$122+AH7*Assumptions!$F$123+(AH8+AH9+AH10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
+        <f>(AH6*Assumptions!$F$121+AH7*Assumptions!$F$122+(AH8+AH9+AH10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI27" s="43">
-        <f>(AI6*Assumptions!$F$122+AI7*Assumptions!$F$123+(AI8+AI9+AI10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
+        <f>(AI6*Assumptions!$F$121+AI7*Assumptions!$F$122+(AI8+AI9+AI10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ27" s="43">
-        <f>(AJ6*Assumptions!$F$122+AJ7*Assumptions!$F$123+(AJ8+AJ9+AJ10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
+        <f>(AJ6*Assumptions!$F$121+AJ7*Assumptions!$F$122+(AJ8+AJ9+AJ10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK27" s="43">
-        <f>(AK6*Assumptions!$F$122+AK7*Assumptions!$F$123+(AK8+AK9+AK10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
+        <f>(AK6*Assumptions!$F$121+AK7*Assumptions!$F$122+(AK8+AK9+AK10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL27" s="43">
-        <f>(AL6*Assumptions!$F$122+AL7*Assumptions!$F$123+(AL8+AL9+AL10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
+        <f>(AL6*Assumptions!$F$121+AL7*Assumptions!$F$122+(AL8+AL9+AL10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM27" s="43">
-        <f>(AM6*Assumptions!$F$122+AM7*Assumptions!$F$123+(AM8+AM9+AM10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
+        <f>(AM6*Assumptions!$F$121+AM7*Assumptions!$F$122+(AM8+AM9+AM10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN27" s="43">
-        <f>(AN6*Assumptions!$F$122+AN7*Assumptions!$F$123+(AN8+AN9+AN10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
+        <f>(AN6*Assumptions!$F$121+AN7*Assumptions!$F$122+(AN8+AN9+AN10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO27" s="43">
-        <f>(AO6*Assumptions!$F$122+AO7*Assumptions!$F$123+(AO8+AO9+AO10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
+        <f>(AO6*Assumptions!$F$121+AO7*Assumptions!$F$122+(AO8+AO9+AO10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP27" s="43">
-        <f>(AP6*Assumptions!$F$122+AP7*Assumptions!$F$123+(AP8+AP9+AP10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
+        <f>(AP6*Assumptions!$F$121+AP7*Assumptions!$F$122+(AP8+AP9+AP10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ27" s="43">
-        <f>(AQ6*Assumptions!$F$122+AQ7*Assumptions!$F$123+(AQ8+AQ9+AQ10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
+        <f>(AQ6*Assumptions!$F$121+AQ7*Assumptions!$F$122+(AQ8+AQ9+AQ10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR27" s="43">
-        <f>(AR6*Assumptions!$F$122+AR7*Assumptions!$F$123+(AR8+AR9+AR10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
+        <f>(AR6*Assumptions!$F$121+AR7*Assumptions!$F$122+(AR8+AR9+AR10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS27" s="43">
-        <f>(AS6*Assumptions!$F$122+AS7*Assumptions!$F$123+(AS8+AS9+AS10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
+        <f>(AS6*Assumptions!$F$121+AS7*Assumptions!$F$122+(AS8+AS9+AS10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT27" s="43">
-        <f>(AT6*Assumptions!$F$122+AT7*Assumptions!$F$123+(AT8+AT9+AT10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
+        <f>(AT6*Assumptions!$F$121+AT7*Assumptions!$F$122+(AT8+AT9+AT10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU27" s="43">
-        <f>(AU6*Assumptions!$F$122+AU7*Assumptions!$F$123+(AU8+AU9+AU10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
+        <f>(AU6*Assumptions!$F$121+AU7*Assumptions!$F$122+(AU8+AU9+AU10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV27" s="43">
-        <f>(AV6*Assumptions!$F$122+AV7*Assumptions!$F$123+(AV8+AV9+AV10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
+        <f>(AV6*Assumptions!$F$121+AV7*Assumptions!$F$122+(AV8+AV9+AV10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW27" s="43">
-        <f>(AW6*Assumptions!$F$122+AW7*Assumptions!$F$123+(AW8+AW9+AW10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
+        <f>(AW6*Assumptions!$F$121+AW7*Assumptions!$F$122+(AW8+AW9+AW10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX27" s="43">
-        <f>(AX6*Assumptions!$F$122+AX7*Assumptions!$F$123+(AX8+AX9+AX10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
+        <f>(AX6*Assumptions!$F$121+AX7*Assumptions!$F$122+(AX8+AX9+AX10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY27" s="43">
-        <f>(AY6*Assumptions!$F$122+AY7*Assumptions!$F$123+(AY8+AY9+AY10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
+        <f>(AY6*Assumptions!$F$121+AY7*Assumptions!$F$122+(AY8+AY9+AY10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ27" s="43">
-        <f>(AZ6*Assumptions!$F$122+AZ7*Assumptions!$F$123+(AZ8+AZ9+AZ10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
+        <f>(AZ6*Assumptions!$F$121+AZ7*Assumptions!$F$122+(AZ8+AZ9+AZ10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA27" s="43">
-        <f>(BA6*Assumptions!$F$122+BA7*Assumptions!$F$123+(BA8+BA9+BA10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
+        <f>(BA6*Assumptions!$F$121+BA7*Assumptions!$F$122+(BA8+BA9+BA10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB27" s="43">
-        <f>(BB6*Assumptions!$F$122+BB7*Assumptions!$F$123+(BB8+BB9+BB10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
+        <f>(BB6*Assumptions!$F$121+BB7*Assumptions!$F$122+(BB8+BB9+BB10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC27" s="43">
-        <f>(BC6*Assumptions!$F$122+BC7*Assumptions!$F$123+(BC8+BC9+BC10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
+        <f>(BC6*Assumptions!$F$121+BC7*Assumptions!$F$122+(BC8+BC9+BC10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD27" s="43">
-        <f>(BD6*Assumptions!$F$122+BD7*Assumptions!$F$123+(BD8+BD9+BD10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
+        <f>(BD6*Assumptions!$F$121+BD7*Assumptions!$F$122+(BD8+BD9+BD10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE27" s="43">
-        <f>(BE6*Assumptions!$F$122+BE7*Assumptions!$F$123+(BE8+BE9+BE10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
+        <f>(BE6*Assumptions!$F$121+BE7*Assumptions!$F$122+(BE8+BE9+BE10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF27" s="43">
-        <f>(BF6*Assumptions!$F$122+BF7*Assumptions!$F$123+(BF8+BF9+BF10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
+        <f>(BF6*Assumptions!$F$121+BF7*Assumptions!$F$122+(BF8+BF9+BF10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG27" s="43">
-        <f>(BG6*Assumptions!$F$122+BG7*Assumptions!$F$123+(BG8+BG9+BG10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
+        <f>(BG6*Assumptions!$F$121+BG7*Assumptions!$F$122+(BG8+BG9+BG10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH27" s="43">
-        <f>(BH6*Assumptions!$F$122+BH7*Assumptions!$F$123+(BH8+BH9+BH10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
+        <f>(BH6*Assumptions!$F$121+BH7*Assumptions!$F$122+(BH8+BH9+BH10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI27" s="43">
-        <f>(BI6*Assumptions!$F$122+BI7*Assumptions!$F$123+(BI8+BI9+BI10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
+        <f>(BI6*Assumptions!$F$121+BI7*Assumptions!$F$122+(BI8+BI9+BI10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ27" s="43">
-        <f>(BJ6*Assumptions!$F$122+BJ7*Assumptions!$F$123+(BJ8+BJ9+BJ10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
+        <f>(BJ6*Assumptions!$F$121+BJ7*Assumptions!$F$122+(BJ8+BJ9+BJ10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK27" s="43">
-        <f>(BK6*Assumptions!$F$122+BK7*Assumptions!$F$123+(BK8+BK9+BK10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
+        <f>(BK6*Assumptions!$F$121+BK7*Assumptions!$F$122+(BK8+BK9+BK10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL27" s="43">
-        <f>(BL6*Assumptions!$F$122+BL7*Assumptions!$F$123+(BL8+BL9+BL10)*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
+        <f>(BL6*Assumptions!$F$121+BL7*Assumptions!$F$122+(BL8+BL9+BL10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN27" s="44">
@@ -46508,243 +46209,243 @@
         </is>
       </c>
       <c r="E28" s="43">
-        <f>((E12+E13)*Assumptions!$F$125+(E14+E15)*Assumptions!$F$126+(E16+E18+E19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
+        <f>((E12+E13)*Assumptions!$F$124+(E14+E15)*Assumptions!$F$125+(E16+E18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F28" s="43">
-        <f>((F12+F13)*Assumptions!$F$125+(F14+F15)*Assumptions!$F$126+(F16+F18+F19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
+        <f>((F12+F13)*Assumptions!$F$124+(F14+F15)*Assumptions!$F$125+(F16+F18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G28" s="43">
-        <f>((G12+G13)*Assumptions!$F$125+(G14+G15)*Assumptions!$F$126+(G16+G18+G19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
+        <f>((G12+G13)*Assumptions!$F$124+(G14+G15)*Assumptions!$F$125+(G16+G18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H28" s="43">
-        <f>((H12+H13)*Assumptions!$F$125+(H14+H15)*Assumptions!$F$126+(H16+H18+H19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
+        <f>((H12+H13)*Assumptions!$F$124+(H14+H15)*Assumptions!$F$125+(H16+H18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I28" s="43">
-        <f>((I12+I13)*Assumptions!$F$125+(I14+I15)*Assumptions!$F$126+(I16+I18+I19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
+        <f>((I12+I13)*Assumptions!$F$124+(I14+I15)*Assumptions!$F$125+(I16+I18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J28" s="43">
-        <f>((J12+J13)*Assumptions!$F$125+(J14+J15)*Assumptions!$F$126+(J16+J18+J19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
+        <f>((J12+J13)*Assumptions!$F$124+(J14+J15)*Assumptions!$F$125+(J16+J18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K28" s="43">
-        <f>((K12+K13)*Assumptions!$F$125+(K14+K15)*Assumptions!$F$126+(K16+K18+K19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
+        <f>((K12+K13)*Assumptions!$F$124+(K14+K15)*Assumptions!$F$125+(K16+K18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L28" s="43">
-        <f>((L12+L13)*Assumptions!$F$125+(L14+L15)*Assumptions!$F$126+(L16+L18+L19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
+        <f>((L12+L13)*Assumptions!$F$124+(L14+L15)*Assumptions!$F$125+(L16+L18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M28" s="43">
-        <f>((M12+M13)*Assumptions!$F$125+(M14+M15)*Assumptions!$F$126+(M16+M18+M19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
+        <f>((M12+M13)*Assumptions!$F$124+(M14+M15)*Assumptions!$F$125+(M16+M18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N28" s="43">
-        <f>((N12+N13)*Assumptions!$F$125+(N14+N15)*Assumptions!$F$126+(N16+N18+N19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
+        <f>((N12+N13)*Assumptions!$F$124+(N14+N15)*Assumptions!$F$125+(N16+N18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O28" s="43">
-        <f>((O12+O13)*Assumptions!$F$125+(O14+O15)*Assumptions!$F$126+(O16+O18+O19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
+        <f>((O12+O13)*Assumptions!$F$124+(O14+O15)*Assumptions!$F$125+(O16+O18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P28" s="43">
-        <f>((P12+P13)*Assumptions!$F$125+(P14+P15)*Assumptions!$F$126+(P16+P18+P19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
+        <f>((P12+P13)*Assumptions!$F$124+(P14+P15)*Assumptions!$F$125+(P16+P18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q28" s="43">
-        <f>((Q12+Q13)*Assumptions!$F$125+(Q14+Q15)*Assumptions!$F$126+(Q16+Q18+Q19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
+        <f>((Q12+Q13)*Assumptions!$F$124+(Q14+Q15)*Assumptions!$F$125+(Q16+Q18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R28" s="43">
-        <f>((R12+R13)*Assumptions!$F$125+(R14+R15)*Assumptions!$F$126+(R16+R18+R19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
+        <f>((R12+R13)*Assumptions!$F$124+(R14+R15)*Assumptions!$F$125+(R16+R18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S28" s="43">
-        <f>((S12+S13)*Assumptions!$F$125+(S14+S15)*Assumptions!$F$126+(S16+S18+S19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
+        <f>((S12+S13)*Assumptions!$F$124+(S14+S15)*Assumptions!$F$125+(S16+S18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T28" s="43">
-        <f>((T12+T13)*Assumptions!$F$125+(T14+T15)*Assumptions!$F$126+(T16+T18+T19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
+        <f>((T12+T13)*Assumptions!$F$124+(T14+T15)*Assumptions!$F$125+(T16+T18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U28" s="43">
-        <f>((U12+U13)*Assumptions!$F$125+(U14+U15)*Assumptions!$F$126+(U16+U18+U19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
+        <f>((U12+U13)*Assumptions!$F$124+(U14+U15)*Assumptions!$F$125+(U16+U18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V28" s="43">
-        <f>((V12+V13)*Assumptions!$F$125+(V14+V15)*Assumptions!$F$126+(V16+V18+V19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
+        <f>((V12+V13)*Assumptions!$F$124+(V14+V15)*Assumptions!$F$125+(V16+V18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W28" s="43">
-        <f>((W12+W13)*Assumptions!$F$125+(W14+W15)*Assumptions!$F$126+(W16+W18+W19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
+        <f>((W12+W13)*Assumptions!$F$124+(W14+W15)*Assumptions!$F$125+(W16+W18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X28" s="43">
-        <f>((X12+X13)*Assumptions!$F$125+(X14+X15)*Assumptions!$F$126+(X16+X18+X19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
+        <f>((X12+X13)*Assumptions!$F$124+(X14+X15)*Assumptions!$F$125+(X16+X18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y28" s="43">
-        <f>((Y12+Y13)*Assumptions!$F$125+(Y14+Y15)*Assumptions!$F$126+(Y16+Y18+Y19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
+        <f>((Y12+Y13)*Assumptions!$F$124+(Y14+Y15)*Assumptions!$F$125+(Y16+Y18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z28" s="43">
-        <f>((Z12+Z13)*Assumptions!$F$125+(Z14+Z15)*Assumptions!$F$126+(Z16+Z18+Z19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
+        <f>((Z12+Z13)*Assumptions!$F$124+(Z14+Z15)*Assumptions!$F$125+(Z16+Z18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA28" s="43">
-        <f>((AA12+AA13)*Assumptions!$F$125+(AA14+AA15)*Assumptions!$F$126+(AA16+AA18+AA19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
+        <f>((AA12+AA13)*Assumptions!$F$124+(AA14+AA15)*Assumptions!$F$125+(AA16+AA18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB28" s="43">
-        <f>((AB12+AB13)*Assumptions!$F$125+(AB14+AB15)*Assumptions!$F$126+(AB16+AB18+AB19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
+        <f>((AB12+AB13)*Assumptions!$F$124+(AB14+AB15)*Assumptions!$F$125+(AB16+AB18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC28" s="43">
-        <f>((AC12+AC13)*Assumptions!$F$125+(AC14+AC15)*Assumptions!$F$126+(AC16+AC18+AC19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
+        <f>((AC12+AC13)*Assumptions!$F$124+(AC14+AC15)*Assumptions!$F$125+(AC16+AC18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD28" s="43">
-        <f>((AD12+AD13)*Assumptions!$F$125+(AD14+AD15)*Assumptions!$F$126+(AD16+AD18+AD19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
+        <f>((AD12+AD13)*Assumptions!$F$124+(AD14+AD15)*Assumptions!$F$125+(AD16+AD18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE28" s="43">
-        <f>((AE12+AE13)*Assumptions!$F$125+(AE14+AE15)*Assumptions!$F$126+(AE16+AE18+AE19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
+        <f>((AE12+AE13)*Assumptions!$F$124+(AE14+AE15)*Assumptions!$F$125+(AE16+AE18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF28" s="43">
-        <f>((AF12+AF13)*Assumptions!$F$125+(AF14+AF15)*Assumptions!$F$126+(AF16+AF18+AF19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
+        <f>((AF12+AF13)*Assumptions!$F$124+(AF14+AF15)*Assumptions!$F$125+(AF16+AF18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG28" s="43">
-        <f>((AG12+AG13)*Assumptions!$F$125+(AG14+AG15)*Assumptions!$F$126+(AG16+AG18+AG19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
+        <f>((AG12+AG13)*Assumptions!$F$124+(AG14+AG15)*Assumptions!$F$125+(AG16+AG18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH28" s="43">
-        <f>((AH12+AH13)*Assumptions!$F$125+(AH14+AH15)*Assumptions!$F$126+(AH16+AH18+AH19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
+        <f>((AH12+AH13)*Assumptions!$F$124+(AH14+AH15)*Assumptions!$F$125+(AH16+AH18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI28" s="43">
-        <f>((AI12+AI13)*Assumptions!$F$125+(AI14+AI15)*Assumptions!$F$126+(AI16+AI18+AI19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
+        <f>((AI12+AI13)*Assumptions!$F$124+(AI14+AI15)*Assumptions!$F$125+(AI16+AI18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ28" s="43">
-        <f>((AJ12+AJ13)*Assumptions!$F$125+(AJ14+AJ15)*Assumptions!$F$126+(AJ16+AJ18+AJ19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
+        <f>((AJ12+AJ13)*Assumptions!$F$124+(AJ14+AJ15)*Assumptions!$F$125+(AJ16+AJ18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK28" s="43">
-        <f>((AK12+AK13)*Assumptions!$F$125+(AK14+AK15)*Assumptions!$F$126+(AK16+AK18+AK19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
+        <f>((AK12+AK13)*Assumptions!$F$124+(AK14+AK15)*Assumptions!$F$125+(AK16+AK18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL28" s="43">
-        <f>((AL12+AL13)*Assumptions!$F$125+(AL14+AL15)*Assumptions!$F$126+(AL16+AL18+AL19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
+        <f>((AL12+AL13)*Assumptions!$F$124+(AL14+AL15)*Assumptions!$F$125+(AL16+AL18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM28" s="43">
-        <f>((AM12+AM13)*Assumptions!$F$125+(AM14+AM15)*Assumptions!$F$126+(AM16+AM18+AM19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
+        <f>((AM12+AM13)*Assumptions!$F$124+(AM14+AM15)*Assumptions!$F$125+(AM16+AM18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN28" s="43">
-        <f>((AN12+AN13)*Assumptions!$F$125+(AN14+AN15)*Assumptions!$F$126+(AN16+AN18+AN19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
+        <f>((AN12+AN13)*Assumptions!$F$124+(AN14+AN15)*Assumptions!$F$125+(AN16+AN18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO28" s="43">
-        <f>((AO12+AO13)*Assumptions!$F$125+(AO14+AO15)*Assumptions!$F$126+(AO16+AO18+AO19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
+        <f>((AO12+AO13)*Assumptions!$F$124+(AO14+AO15)*Assumptions!$F$125+(AO16+AO18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP28" s="43">
-        <f>((AP12+AP13)*Assumptions!$F$125+(AP14+AP15)*Assumptions!$F$126+(AP16+AP18+AP19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
+        <f>((AP12+AP13)*Assumptions!$F$124+(AP14+AP15)*Assumptions!$F$125+(AP16+AP18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ28" s="43">
-        <f>((AQ12+AQ13)*Assumptions!$F$125+(AQ14+AQ15)*Assumptions!$F$126+(AQ16+AQ18+AQ19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
+        <f>((AQ12+AQ13)*Assumptions!$F$124+(AQ14+AQ15)*Assumptions!$F$125+(AQ16+AQ18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR28" s="43">
-        <f>((AR12+AR13)*Assumptions!$F$125+(AR14+AR15)*Assumptions!$F$126+(AR16+AR18+AR19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
+        <f>((AR12+AR13)*Assumptions!$F$124+(AR14+AR15)*Assumptions!$F$125+(AR16+AR18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS28" s="43">
-        <f>((AS12+AS13)*Assumptions!$F$125+(AS14+AS15)*Assumptions!$F$126+(AS16+AS18+AS19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
+        <f>((AS12+AS13)*Assumptions!$F$124+(AS14+AS15)*Assumptions!$F$125+(AS16+AS18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT28" s="43">
-        <f>((AT12+AT13)*Assumptions!$F$125+(AT14+AT15)*Assumptions!$F$126+(AT16+AT18+AT19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
+        <f>((AT12+AT13)*Assumptions!$F$124+(AT14+AT15)*Assumptions!$F$125+(AT16+AT18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU28" s="43">
-        <f>((AU12+AU13)*Assumptions!$F$125+(AU14+AU15)*Assumptions!$F$126+(AU16+AU18+AU19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
+        <f>((AU12+AU13)*Assumptions!$F$124+(AU14+AU15)*Assumptions!$F$125+(AU16+AU18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV28" s="43">
-        <f>((AV12+AV13)*Assumptions!$F$125+(AV14+AV15)*Assumptions!$F$126+(AV16+AV18+AV19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
+        <f>((AV12+AV13)*Assumptions!$F$124+(AV14+AV15)*Assumptions!$F$125+(AV16+AV18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW28" s="43">
-        <f>((AW12+AW13)*Assumptions!$F$125+(AW14+AW15)*Assumptions!$F$126+(AW16+AW18+AW19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
+        <f>((AW12+AW13)*Assumptions!$F$124+(AW14+AW15)*Assumptions!$F$125+(AW16+AW18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX28" s="43">
-        <f>((AX12+AX13)*Assumptions!$F$125+(AX14+AX15)*Assumptions!$F$126+(AX16+AX18+AX19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
+        <f>((AX12+AX13)*Assumptions!$F$124+(AX14+AX15)*Assumptions!$F$125+(AX16+AX18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY28" s="43">
-        <f>((AY12+AY13)*Assumptions!$F$125+(AY14+AY15)*Assumptions!$F$126+(AY16+AY18+AY19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
+        <f>((AY12+AY13)*Assumptions!$F$124+(AY14+AY15)*Assumptions!$F$125+(AY16+AY18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ28" s="43">
-        <f>((AZ12+AZ13)*Assumptions!$F$125+(AZ14+AZ15)*Assumptions!$F$126+(AZ16+AZ18+AZ19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
+        <f>((AZ12+AZ13)*Assumptions!$F$124+(AZ14+AZ15)*Assumptions!$F$125+(AZ16+AZ18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA28" s="43">
-        <f>((BA12+BA13)*Assumptions!$F$125+(BA14+BA15)*Assumptions!$F$126+(BA16+BA18+BA19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
+        <f>((BA12+BA13)*Assumptions!$F$124+(BA14+BA15)*Assumptions!$F$125+(BA16+BA18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB28" s="43">
-        <f>((BB12+BB13)*Assumptions!$F$125+(BB14+BB15)*Assumptions!$F$126+(BB16+BB18+BB19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
+        <f>((BB12+BB13)*Assumptions!$F$124+(BB14+BB15)*Assumptions!$F$125+(BB16+BB18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC28" s="43">
-        <f>((BC12+BC13)*Assumptions!$F$125+(BC14+BC15)*Assumptions!$F$126+(BC16+BC18+BC19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
+        <f>((BC12+BC13)*Assumptions!$F$124+(BC14+BC15)*Assumptions!$F$125+(BC16+BC18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD28" s="43">
-        <f>((BD12+BD13)*Assumptions!$F$125+(BD14+BD15)*Assumptions!$F$126+(BD16+BD18+BD19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
+        <f>((BD12+BD13)*Assumptions!$F$124+(BD14+BD15)*Assumptions!$F$125+(BD16+BD18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE28" s="43">
-        <f>((BE12+BE13)*Assumptions!$F$125+(BE14+BE15)*Assumptions!$F$126+(BE16+BE18+BE19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
+        <f>((BE12+BE13)*Assumptions!$F$124+(BE14+BE15)*Assumptions!$F$125+(BE16+BE18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF28" s="43">
-        <f>((BF12+BF13)*Assumptions!$F$125+(BF14+BF15)*Assumptions!$F$126+(BF16+BF18+BF19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
+        <f>((BF12+BF13)*Assumptions!$F$124+(BF14+BF15)*Assumptions!$F$125+(BF16+BF18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG28" s="43">
-        <f>((BG12+BG13)*Assumptions!$F$125+(BG14+BG15)*Assumptions!$F$126+(BG16+BG18+BG19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
+        <f>((BG12+BG13)*Assumptions!$F$124+(BG14+BG15)*Assumptions!$F$125+(BG16+BG18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH28" s="43">
-        <f>((BH12+BH13)*Assumptions!$F$125+(BH14+BH15)*Assumptions!$F$126+(BH16+BH18+BH19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
+        <f>((BH12+BH13)*Assumptions!$F$124+(BH14+BH15)*Assumptions!$F$125+(BH16+BH18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI28" s="43">
-        <f>((BI12+BI13)*Assumptions!$F$125+(BI14+BI15)*Assumptions!$F$126+(BI16+BI18+BI19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
+        <f>((BI12+BI13)*Assumptions!$F$124+(BI14+BI15)*Assumptions!$F$125+(BI16+BI18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ28" s="43">
-        <f>((BJ12+BJ13)*Assumptions!$F$125+(BJ14+BJ15)*Assumptions!$F$126+(BJ16+BJ18+BJ19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
+        <f>((BJ12+BJ13)*Assumptions!$F$124+(BJ14+BJ15)*Assumptions!$F$125+(BJ16+BJ18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK28" s="43">
-        <f>((BK12+BK13)*Assumptions!$F$125+(BK14+BK15)*Assumptions!$F$126+(BK16+BK18+BK19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
+        <f>((BK12+BK13)*Assumptions!$F$124+(BK14+BK15)*Assumptions!$F$125+(BK16+BK18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL28" s="43">
-        <f>((BL12+BL13)*Assumptions!$F$125+(BL14+BL15)*Assumptions!$F$126+(BL16+BL18+BL19)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
+        <f>((BL12+BL13)*Assumptions!$F$124+(BL14+BL15)*Assumptions!$F$125+(BL16+BL18)*Assumptions!$F$126)*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN28" s="44">
@@ -47052,243 +46753,243 @@
         </is>
       </c>
       <c r="E31" s="56">
-        <f>IFERROR(E29/E21,0)</f>
+        <f>IFERROR(E29/E20,0)</f>
         <v/>
       </c>
       <c r="F31" s="56">
-        <f>IFERROR(F29/F21,0)</f>
+        <f>IFERROR(F29/F20,0)</f>
         <v/>
       </c>
       <c r="G31" s="56">
-        <f>IFERROR(G29/G21,0)</f>
+        <f>IFERROR(G29/G20,0)</f>
         <v/>
       </c>
       <c r="H31" s="56">
-        <f>IFERROR(H29/H21,0)</f>
+        <f>IFERROR(H29/H20,0)</f>
         <v/>
       </c>
       <c r="I31" s="56">
-        <f>IFERROR(I29/I21,0)</f>
+        <f>IFERROR(I29/I20,0)</f>
         <v/>
       </c>
       <c r="J31" s="56">
-        <f>IFERROR(J29/J21,0)</f>
+        <f>IFERROR(J29/J20,0)</f>
         <v/>
       </c>
       <c r="K31" s="56">
-        <f>IFERROR(K29/K21,0)</f>
+        <f>IFERROR(K29/K20,0)</f>
         <v/>
       </c>
       <c r="L31" s="56">
-        <f>IFERROR(L29/L21,0)</f>
+        <f>IFERROR(L29/L20,0)</f>
         <v/>
       </c>
       <c r="M31" s="56">
-        <f>IFERROR(M29/M21,0)</f>
+        <f>IFERROR(M29/M20,0)</f>
         <v/>
       </c>
       <c r="N31" s="56">
-        <f>IFERROR(N29/N21,0)</f>
+        <f>IFERROR(N29/N20,0)</f>
         <v/>
       </c>
       <c r="O31" s="56">
-        <f>IFERROR(O29/O21,0)</f>
+        <f>IFERROR(O29/O20,0)</f>
         <v/>
       </c>
       <c r="P31" s="56">
-        <f>IFERROR(P29/P21,0)</f>
+        <f>IFERROR(P29/P20,0)</f>
         <v/>
       </c>
       <c r="Q31" s="56">
-        <f>IFERROR(Q29/Q21,0)</f>
+        <f>IFERROR(Q29/Q20,0)</f>
         <v/>
       </c>
       <c r="R31" s="56">
-        <f>IFERROR(R29/R21,0)</f>
+        <f>IFERROR(R29/R20,0)</f>
         <v/>
       </c>
       <c r="S31" s="56">
-        <f>IFERROR(S29/S21,0)</f>
+        <f>IFERROR(S29/S20,0)</f>
         <v/>
       </c>
       <c r="T31" s="56">
-        <f>IFERROR(T29/T21,0)</f>
+        <f>IFERROR(T29/T20,0)</f>
         <v/>
       </c>
       <c r="U31" s="56">
-        <f>IFERROR(U29/U21,0)</f>
+        <f>IFERROR(U29/U20,0)</f>
         <v/>
       </c>
       <c r="V31" s="56">
-        <f>IFERROR(V29/V21,0)</f>
+        <f>IFERROR(V29/V20,0)</f>
         <v/>
       </c>
       <c r="W31" s="56">
-        <f>IFERROR(W29/W21,0)</f>
+        <f>IFERROR(W29/W20,0)</f>
         <v/>
       </c>
       <c r="X31" s="56">
-        <f>IFERROR(X29/X21,0)</f>
+        <f>IFERROR(X29/X20,0)</f>
         <v/>
       </c>
       <c r="Y31" s="56">
-        <f>IFERROR(Y29/Y21,0)</f>
+        <f>IFERROR(Y29/Y20,0)</f>
         <v/>
       </c>
       <c r="Z31" s="56">
-        <f>IFERROR(Z29/Z21,0)</f>
+        <f>IFERROR(Z29/Z20,0)</f>
         <v/>
       </c>
       <c r="AA31" s="56">
-        <f>IFERROR(AA29/AA21,0)</f>
+        <f>IFERROR(AA29/AA20,0)</f>
         <v/>
       </c>
       <c r="AB31" s="56">
-        <f>IFERROR(AB29/AB21,0)</f>
+        <f>IFERROR(AB29/AB20,0)</f>
         <v/>
       </c>
       <c r="AC31" s="56">
-        <f>IFERROR(AC29/AC21,0)</f>
+        <f>IFERROR(AC29/AC20,0)</f>
         <v/>
       </c>
       <c r="AD31" s="56">
-        <f>IFERROR(AD29/AD21,0)</f>
+        <f>IFERROR(AD29/AD20,0)</f>
         <v/>
       </c>
       <c r="AE31" s="56">
-        <f>IFERROR(AE29/AE21,0)</f>
+        <f>IFERROR(AE29/AE20,0)</f>
         <v/>
       </c>
       <c r="AF31" s="56">
-        <f>IFERROR(AF29/AF21,0)</f>
+        <f>IFERROR(AF29/AF20,0)</f>
         <v/>
       </c>
       <c r="AG31" s="56">
-        <f>IFERROR(AG29/AG21,0)</f>
+        <f>IFERROR(AG29/AG20,0)</f>
         <v/>
       </c>
       <c r="AH31" s="56">
-        <f>IFERROR(AH29/AH21,0)</f>
+        <f>IFERROR(AH29/AH20,0)</f>
         <v/>
       </c>
       <c r="AI31" s="56">
-        <f>IFERROR(AI29/AI21,0)</f>
+        <f>IFERROR(AI29/AI20,0)</f>
         <v/>
       </c>
       <c r="AJ31" s="56">
-        <f>IFERROR(AJ29/AJ21,0)</f>
+        <f>IFERROR(AJ29/AJ20,0)</f>
         <v/>
       </c>
       <c r="AK31" s="56">
-        <f>IFERROR(AK29/AK21,0)</f>
+        <f>IFERROR(AK29/AK20,0)</f>
         <v/>
       </c>
       <c r="AL31" s="56">
-        <f>IFERROR(AL29/AL21,0)</f>
+        <f>IFERROR(AL29/AL20,0)</f>
         <v/>
       </c>
       <c r="AM31" s="56">
-        <f>IFERROR(AM29/AM21,0)</f>
+        <f>IFERROR(AM29/AM20,0)</f>
         <v/>
       </c>
       <c r="AN31" s="56">
-        <f>IFERROR(AN29/AN21,0)</f>
+        <f>IFERROR(AN29/AN20,0)</f>
         <v/>
       </c>
       <c r="AO31" s="56">
-        <f>IFERROR(AO29/AO21,0)</f>
+        <f>IFERROR(AO29/AO20,0)</f>
         <v/>
       </c>
       <c r="AP31" s="56">
-        <f>IFERROR(AP29/AP21,0)</f>
+        <f>IFERROR(AP29/AP20,0)</f>
         <v/>
       </c>
       <c r="AQ31" s="56">
-        <f>IFERROR(AQ29/AQ21,0)</f>
+        <f>IFERROR(AQ29/AQ20,0)</f>
         <v/>
       </c>
       <c r="AR31" s="56">
-        <f>IFERROR(AR29/AR21,0)</f>
+        <f>IFERROR(AR29/AR20,0)</f>
         <v/>
       </c>
       <c r="AS31" s="56">
-        <f>IFERROR(AS29/AS21,0)</f>
+        <f>IFERROR(AS29/AS20,0)</f>
         <v/>
       </c>
       <c r="AT31" s="56">
-        <f>IFERROR(AT29/AT21,0)</f>
+        <f>IFERROR(AT29/AT20,0)</f>
         <v/>
       </c>
       <c r="AU31" s="56">
-        <f>IFERROR(AU29/AU21,0)</f>
+        <f>IFERROR(AU29/AU20,0)</f>
         <v/>
       </c>
       <c r="AV31" s="56">
-        <f>IFERROR(AV29/AV21,0)</f>
+        <f>IFERROR(AV29/AV20,0)</f>
         <v/>
       </c>
       <c r="AW31" s="56">
-        <f>IFERROR(AW29/AW21,0)</f>
+        <f>IFERROR(AW29/AW20,0)</f>
         <v/>
       </c>
       <c r="AX31" s="56">
-        <f>IFERROR(AX29/AX21,0)</f>
+        <f>IFERROR(AX29/AX20,0)</f>
         <v/>
       </c>
       <c r="AY31" s="56">
-        <f>IFERROR(AY29/AY21,0)</f>
+        <f>IFERROR(AY29/AY20,0)</f>
         <v/>
       </c>
       <c r="AZ31" s="56">
-        <f>IFERROR(AZ29/AZ21,0)</f>
+        <f>IFERROR(AZ29/AZ20,0)</f>
         <v/>
       </c>
       <c r="BA31" s="56">
-        <f>IFERROR(BA29/BA21,0)</f>
+        <f>IFERROR(BA29/BA20,0)</f>
         <v/>
       </c>
       <c r="BB31" s="56">
-        <f>IFERROR(BB29/BB21,0)</f>
+        <f>IFERROR(BB29/BB20,0)</f>
         <v/>
       </c>
       <c r="BC31" s="56">
-        <f>IFERROR(BC29/BC21,0)</f>
+        <f>IFERROR(BC29/BC20,0)</f>
         <v/>
       </c>
       <c r="BD31" s="56">
-        <f>IFERROR(BD29/BD21,0)</f>
+        <f>IFERROR(BD29/BD20,0)</f>
         <v/>
       </c>
       <c r="BE31" s="56">
-        <f>IFERROR(BE29/BE21,0)</f>
+        <f>IFERROR(BE29/BE20,0)</f>
         <v/>
       </c>
       <c r="BF31" s="56">
-        <f>IFERROR(BF29/BF21,0)</f>
+        <f>IFERROR(BF29/BF20,0)</f>
         <v/>
       </c>
       <c r="BG31" s="56">
-        <f>IFERROR(BG29/BG21,0)</f>
+        <f>IFERROR(BG29/BG20,0)</f>
         <v/>
       </c>
       <c r="BH31" s="56">
-        <f>IFERROR(BH29/BH21,0)</f>
+        <f>IFERROR(BH29/BH20,0)</f>
         <v/>
       </c>
       <c r="BI31" s="56">
-        <f>IFERROR(BI29/BI21,0)</f>
+        <f>IFERROR(BI29/BI20,0)</f>
         <v/>
       </c>
       <c r="BJ31" s="56">
-        <f>IFERROR(BJ29/BJ21,0)</f>
+        <f>IFERROR(BJ29/BJ20,0)</f>
         <v/>
       </c>
       <c r="BK31" s="56">
-        <f>IFERROR(BK29/BK21,0)</f>
+        <f>IFERROR(BK29/BK20,0)</f>
         <v/>
       </c>
       <c r="BL31" s="56">
-        <f>IFERROR(BL29/BL21,0)</f>
+        <f>IFERROR(BL29/BL20,0)</f>
         <v/>
       </c>
       <c r="BN31" s="57">
@@ -47757,23 +47458,23 @@
         </is>
       </c>
       <c r="D23" s="62">
-        <f>Personnel!BN21</f>
+        <f>Personnel!BN20</f>
         <v/>
       </c>
       <c r="E23" s="62">
-        <f>Personnel!BO21</f>
+        <f>Personnel!BO20</f>
         <v/>
       </c>
       <c r="F23" s="62">
-        <f>Personnel!BP21</f>
+        <f>Personnel!BP20</f>
         <v/>
       </c>
       <c r="G23" s="62">
-        <f>Personnel!BQ21</f>
+        <f>Personnel!BQ20</f>
         <v/>
       </c>
       <c r="H23" s="62">
-        <f>Personnel!BR21</f>
+        <f>Personnel!BR20</f>
         <v/>
       </c>
     </row>
@@ -47784,23 +47485,23 @@
         </is>
       </c>
       <c r="D24" s="54">
-        <f>Personnel!BN22</f>
+        <f>Personnel!BN21</f>
         <v/>
       </c>
       <c r="E24" s="54">
-        <f>Personnel!BO22</f>
+        <f>Personnel!BO21</f>
         <v/>
       </c>
       <c r="F24" s="54">
-        <f>Personnel!BP22</f>
+        <f>Personnel!BP21</f>
         <v/>
       </c>
       <c r="G24" s="54">
-        <f>Personnel!BQ22</f>
+        <f>Personnel!BQ21</f>
         <v/>
       </c>
       <c r="H24" s="54">
-        <f>Personnel!BR22</f>
+        <f>Personnel!BR21</f>
         <v/>
       </c>
     </row>
@@ -47811,23 +47512,23 @@
         </is>
       </c>
       <c r="D25" s="38">
-        <f>Personnel!BN23</f>
+        <f>Personnel!BN22</f>
         <v/>
       </c>
       <c r="E25" s="38">
-        <f>Personnel!BO23</f>
+        <f>Personnel!BO22</f>
         <v/>
       </c>
       <c r="F25" s="38">
-        <f>Personnel!BP23</f>
+        <f>Personnel!BP22</f>
         <v/>
       </c>
       <c r="G25" s="38">
-        <f>Personnel!BQ23</f>
+        <f>Personnel!BQ22</f>
         <v/>
       </c>
       <c r="H25" s="38">
-        <f>Personnel!BR23</f>
+        <f>Personnel!BR22</f>
         <v/>
       </c>
     </row>

--- a/models/Tarnoc_v2_2026-09-01.xlsx
+++ b/models/Tarnoc_v2_2026-09-01.xlsx
@@ -29366,243 +29366,243 @@
         </is>
       </c>
       <c r="E7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(E$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(E$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),E6)</f>
         <v/>
       </c>
       <c r="F7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(F$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(F$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),F6)</f>
         <v/>
       </c>
       <c r="G7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(G$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(G$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),G6)</f>
         <v/>
       </c>
       <c r="H7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(H$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(H$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),H6)</f>
         <v/>
       </c>
       <c r="I7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(I$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(I$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),I6)</f>
         <v/>
       </c>
       <c r="J7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(J$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(J$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),J6)</f>
         <v/>
       </c>
       <c r="K7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(K$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(K$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),K6)</f>
         <v/>
       </c>
       <c r="L7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(L$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(L$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),L6)</f>
         <v/>
       </c>
       <c r="M7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(M$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(M$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),M6)</f>
         <v/>
       </c>
       <c r="N7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(N$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(N$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),N6)</f>
         <v/>
       </c>
       <c r="O7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(O$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(O$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),O6)</f>
         <v/>
       </c>
       <c r="P7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(P$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(P$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),P6)</f>
         <v/>
       </c>
       <c r="Q7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(Q$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(Q$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),Q6)</f>
         <v/>
       </c>
       <c r="R7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(R$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(R$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),R6)</f>
         <v/>
       </c>
       <c r="S7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(S$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(S$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),S6)</f>
         <v/>
       </c>
       <c r="T7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(T$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(T$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),T6)</f>
         <v/>
       </c>
       <c r="U7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(U$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(U$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),U6)</f>
         <v/>
       </c>
       <c r="V7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(V$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(V$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),V6)</f>
         <v/>
       </c>
       <c r="W7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(W$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(W$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),W6)</f>
         <v/>
       </c>
       <c r="X7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(X$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(X$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),X6)</f>
         <v/>
       </c>
       <c r="Y7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(Y$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(Y$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),Y6)</f>
         <v/>
       </c>
       <c r="Z7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(Z$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(Z$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),Z6)</f>
         <v/>
       </c>
       <c r="AA7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AA$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AA$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AA6)</f>
         <v/>
       </c>
       <c r="AB7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AB$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AB$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AB6)</f>
         <v/>
       </c>
       <c r="AC7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AC$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AC$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AC6)</f>
         <v/>
       </c>
       <c r="AD7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AD$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AD$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AD6)</f>
         <v/>
       </c>
       <c r="AE7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AE$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AE$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AE6)</f>
         <v/>
       </c>
       <c r="AF7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AF$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AF$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AF6)</f>
         <v/>
       </c>
       <c r="AG7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AG$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AG$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AG6)</f>
         <v/>
       </c>
       <c r="AH7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AH$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AH$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AH6)</f>
         <v/>
       </c>
       <c r="AI7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AI$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AI$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AI6)</f>
         <v/>
       </c>
       <c r="AJ7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AJ$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AJ$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AJ6)</f>
         <v/>
       </c>
       <c r="AK7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AK$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AK$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AK6)</f>
         <v/>
       </c>
       <c r="AL7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AL$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AL$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AL6)</f>
         <v/>
       </c>
       <c r="AM7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AM$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AM$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AM6)</f>
         <v/>
       </c>
       <c r="AN7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AN$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AN$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AN6)</f>
         <v/>
       </c>
       <c r="AO7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AO$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AO$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AO6)</f>
         <v/>
       </c>
       <c r="AP7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AP$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AP$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AP6)</f>
         <v/>
       </c>
       <c r="AQ7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AQ$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AQ$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AQ6)</f>
         <v/>
       </c>
       <c r="AR7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AR$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AR$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AR6)</f>
         <v/>
       </c>
       <c r="AS7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AS$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AS$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AS6)</f>
         <v/>
       </c>
       <c r="AT7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AT$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AT$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AT6)</f>
         <v/>
       </c>
       <c r="AU7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AU$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AU$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AU6)</f>
         <v/>
       </c>
       <c r="AV7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AV$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AV$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AV6)</f>
         <v/>
       </c>
       <c r="AW7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AW$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AW$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AW6)</f>
         <v/>
       </c>
       <c r="AX7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AX$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AX$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AX6)</f>
         <v/>
       </c>
       <c r="AY7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AY$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AY$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AY6)</f>
         <v/>
       </c>
       <c r="AZ7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(AZ$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(AZ$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),AZ6)</f>
         <v/>
       </c>
       <c r="BA7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(BA$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(BA$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),BA6)</f>
         <v/>
       </c>
       <c r="BB7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(BB$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(BB$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),BB6)</f>
         <v/>
       </c>
       <c r="BC7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(BC$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(BC$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),BC6)</f>
         <v/>
       </c>
       <c r="BD7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(BD$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(BD$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),BD6)</f>
         <v/>
       </c>
       <c r="BE7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(BE$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(BE$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),BE6)</f>
         <v/>
       </c>
       <c r="BF7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(BF$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(BF$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),BF6)</f>
         <v/>
       </c>
       <c r="BG7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(BG$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(BG$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),BG6)</f>
         <v/>
       </c>
       <c r="BH7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(BH$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(BH$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),BH6)</f>
         <v/>
       </c>
       <c r="BI7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(BI$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(BI$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),BI6)</f>
         <v/>
       </c>
       <c r="BJ7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(BJ$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(BJ$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),BJ6)</f>
         <v/>
       </c>
       <c r="BK7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(BK$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(BK$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),BK6)</f>
         <v/>
       </c>
       <c r="BL7" s="54">
-        <f>IFERROR(HLOOKUP(YEAR(BL$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),0)</f>
+        <f>IFERROR(HLOOKUP(YEAR(BL$3)+1,'Revenue Forecast'!$BN$3:$BR$34,32,FALSE),BL6)</f>
         <v/>
       </c>
       <c r="BN7" s="55">
@@ -29627,7 +29627,7 @@
       </c>
       <c r="BT7" s="20" t="inlineStr">
         <is>
-          <t>only used when the tier basis switch is set to 2</t>
+          <t>only used when the tier basis switch is set to 2; beyond the horizon, next year is taken as at least this year</t>
         </is>
       </c>
     </row>

--- a/models/Tarnoc_v2_2026-09-01.xlsx
+++ b/models/Tarnoc_v2_2026-09-01.xlsx
@@ -4017,12 +4017,12 @@
     <row r="122">
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Units on a service contract per field engineer</t>
+          <t>Boilers one field engineer can look after</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>units</t>
+          <t>boilers</t>
         </is>
       </c>
       <c r="D122" s="29" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="J122" s="20" t="inlineStr">
         <is>
-          <t>one visit per contract per year, so about three and a half visits per engineer per working day</t>
+          <t>sizes the field service team: boilers on a service contract divided by this number = engineers to hire. Each boiler gets one visit a year, an engineer does three to four a day</t>
         </is>
       </c>
     </row>
@@ -44863,7 +44863,7 @@
       </c>
       <c r="BT19" s="20" t="inlineStr">
         <is>
-          <t>salaried staff: one engineer per 750 units on a service contract</t>
+          <t>salaried staff: boilers on a service contract divided by the boilers one engineer can look after</t>
         </is>
       </c>
     </row>

--- a/models/Tarnoc_v2_2026-09-01.xlsx
+++ b/models/Tarnoc_v2_2026-09-01.xlsx
@@ -1315,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J152"/>
+  <dimension ref="B1:J148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3790,7 +3790,7 @@
     <row r="113">
       <c r="B113" s="31" t="inlineStr">
         <is>
-          <t>Quality and certification team</t>
+          <t>Leadership, finance, HR, IT and legal</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -3814,7 +3814,11 @@
         <v>2030</v>
       </c>
       <c r="I113" s="21" t="n"/>
-      <c r="J113" s="21" t="n"/>
+      <c r="J113" s="34" t="inlineStr">
+        <is>
+          <t>the whole back office, typed per year: leadership in post by end 2026, then finance, HR, IT and legal as the company grows</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="B114" s="14" t="inlineStr">
@@ -3823,19 +3827,19 @@
         </is>
       </c>
       <c r="D114" s="29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E114" s="29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F114" s="29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G114" s="29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H114" s="29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115">
@@ -3845,19 +3849,19 @@
         </is>
       </c>
       <c r="D115" s="29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E115" s="29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F115" s="29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G115" s="29" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H115" s="29" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116">
@@ -3888,201 +3892,185 @@
       </c>
     </row>
     <row r="117">
-      <c r="B117" s="31" t="inlineStr">
-        <is>
-          <t>Leadership, finance, HR, IT and legal</t>
-        </is>
-      </c>
-      <c r="C117" s="32" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="D117" s="33" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E117" s="33" t="n">
-        <v>2027</v>
-      </c>
-      <c r="F117" s="33" t="n">
-        <v>2028</v>
-      </c>
-      <c r="G117" s="33" t="n">
-        <v>2029</v>
-      </c>
-      <c r="H117" s="33" t="n">
-        <v>2030</v>
-      </c>
+      <c r="B117" s="21" t="n"/>
+      <c r="C117" s="21" t="n"/>
+      <c r="D117" s="22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E117" s="22" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F117" s="22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G117" s="21" t="n"/>
+      <c r="H117" s="21" t="n"/>
       <c r="I117" s="21" t="n"/>
-      <c r="J117" s="34" t="inlineStr">
-        <is>
-          <t>the whole back office, typed per year: leadership in post by end 2026, then finance, HR, IT and legal as the company grows</t>
-        </is>
-      </c>
+      <c r="J117" s="21" t="n"/>
     </row>
     <row r="118">
-      <c r="B118" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Base</t>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>Boilers one field engineer can look after</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>boilers</t>
         </is>
       </c>
       <c r="D118" s="29" t="n">
-        <v>3</v>
+        <v>750</v>
       </c>
       <c r="E118" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="F118" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="G118" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H118" s="29" t="n">
-        <v>8</v>
+        <v>750</v>
+      </c>
+      <c r="F118" s="30">
+        <f>IF(Assumptions!$E$5=2,E118,D118)</f>
+        <v/>
+      </c>
+      <c r="J118" s="20" t="inlineStr">
+        <is>
+          <t>sizes the field service team: boilers on a service contract divided by this number = engineers to hire. Each boiler gets one visit a year, an engineer does three to four a day</t>
+        </is>
       </c>
     </row>
     <row r="119">
-      <c r="B119" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Aggressive</t>
-        </is>
-      </c>
-      <c r="D119" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E119" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="F119" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G119" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="H119" s="29" t="n">
-        <v>18</v>
-      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>LOADED COST PER PERSON  (employer cost, including taxes)</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n"/>
+      <c r="D119" s="1" t="n"/>
+      <c r="E119" s="1" t="n"/>
+      <c r="F119" s="1" t="n"/>
+      <c r="G119" s="1" t="n"/>
+      <c r="H119" s="1" t="n"/>
+      <c r="I119" s="1" t="n"/>
+      <c r="J119" s="1" t="n"/>
     </row>
     <row r="120">
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Live (per case)</t>
-        </is>
-      </c>
-      <c r="D120" s="30">
-        <f>IF(Assumptions!$E$5=2,D119,D118)</f>
-        <v/>
-      </c>
-      <c r="E120" s="30">
-        <f>IF(Assumptions!$E$5=2,E119,E118)</f>
-        <v/>
-      </c>
-      <c r="F120" s="30">
-        <f>IF(Assumptions!$E$5=2,F119,F118)</f>
-        <v/>
-      </c>
-      <c r="G120" s="30">
-        <f>IF(Assumptions!$E$5=2,G119,G118)</f>
-        <v/>
-      </c>
-      <c r="H120" s="30">
-        <f>IF(Assumptions!$E$5=2,H119,H118)</f>
-        <v/>
-      </c>
+      <c r="B120" s="21" t="n"/>
+      <c r="C120" s="21" t="n"/>
+      <c r="D120" s="22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E120" s="22" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G120" s="21" t="n"/>
+      <c r="H120" s="21" t="n"/>
+      <c r="I120" s="21" t="n"/>
+      <c r="J120" s="21" t="n"/>
     </row>
     <row r="121">
-      <c r="B121" s="21" t="n"/>
-      <c r="C121" s="21" t="n"/>
-      <c r="D121" s="22" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E121" s="22" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F121" s="22" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G121" s="21" t="n"/>
-      <c r="H121" s="21" t="n"/>
-      <c r="I121" s="21" t="n"/>
-      <c r="J121" s="21" t="n"/>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>Sales rep</t>
+        </is>
+      </c>
+      <c r="C121" s="18" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D121" s="23" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E121" s="23" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F121" s="24">
+        <f>IF(Assumptions!$E$5=2,E121,D121)</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Boilers one field engineer can look after</t>
+          <t>Partner manager</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>boilers</t>
-        </is>
-      </c>
-      <c r="D122" s="29" t="n">
-        <v>750</v>
-      </c>
-      <c r="E122" s="29" t="n">
-        <v>750</v>
-      </c>
-      <c r="F122" s="30">
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D122" s="23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E122" s="23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F122" s="24">
         <f>IF(Assumptions!$E$5=2,E122,D122)</f>
         <v/>
-      </c>
-      <c r="J122" s="20" t="inlineStr">
-        <is>
-          <t>sizes the field service team: boilers on a service contract divided by this number = engineers to hire. Each boiler gets one visit a year, an engineer does three to four a day</t>
-        </is>
       </c>
     </row>
     <row r="123">
-      <c r="B123" s="7" t="inlineStr">
-        <is>
-          <t>LOADED COST PER PERSON  (employer cost, including taxes)</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="n"/>
-      <c r="D123" s="1" t="n"/>
-      <c r="E123" s="1" t="n"/>
-      <c r="F123" s="1" t="n"/>
-      <c r="G123" s="1" t="n"/>
-      <c r="H123" s="1" t="n"/>
-      <c r="I123" s="1" t="n"/>
-      <c r="J123" s="1" t="n"/>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>Trainer, order desk, marketing</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D123" s="23" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E123" s="23" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F123" s="24">
+        <f>IF(Assumptions!$E$5=2,E123,D123)</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
-      <c r="B124" s="21" t="n"/>
-      <c r="C124" s="21" t="n"/>
-      <c r="D124" s="22" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E124" s="22" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F124" s="22" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G124" s="21" t="n"/>
-      <c r="H124" s="21" t="n"/>
-      <c r="I124" s="21" t="n"/>
-      <c r="J124" s="21" t="n"/>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>Supply chain and production</t>
+        </is>
+      </c>
+      <c r="C124" s="18" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D124" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E124" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F124" s="24">
+        <f>IF(Assumptions!$E$5=2,E124,D124)</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Sales rep</t>
+          <t>Support and escalation</t>
         </is>
       </c>
       <c r="C125" s="18" t="inlineStr">
@@ -4091,10 +4079,10 @@
         </is>
       </c>
       <c r="D125" s="23" t="n">
-        <v>7500</v>
+        <v>4800</v>
       </c>
       <c r="E125" s="23" t="n">
-        <v>7500</v>
+        <v>4800</v>
       </c>
       <c r="F125" s="24">
         <f>IF(Assumptions!$E$5=2,E125,D125)</f>
@@ -4104,7 +4092,7 @@
     <row r="126">
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Partner manager</t>
+          <t>Leadership, finance, HR, IT and legal</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
@@ -4113,10 +4101,10 @@
         </is>
       </c>
       <c r="D126" s="23" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="E126" s="23" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="F126" s="24">
         <f>IF(Assumptions!$E$5=2,E126,D126)</f>
@@ -4126,7 +4114,7 @@
     <row r="127">
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Trainer, order desk, marketing</t>
+          <t>R&amp;D engineer</t>
         </is>
       </c>
       <c r="C127" s="18" t="inlineStr">
@@ -4135,20 +4123,25 @@
         </is>
       </c>
       <c r="D127" s="23" t="n">
-        <v>7000</v>
+        <v>5700</v>
       </c>
       <c r="E127" s="23" t="n">
-        <v>7000</v>
+        <v>5700</v>
       </c>
       <c r="F127" s="24">
         <f>IF(Assumptions!$E$5=2,E127,D127)</f>
         <v/>
+      </c>
+      <c r="J127" s="20" t="inlineStr">
+        <is>
+          <t>the blended cost of the seven engineers already in post</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Supply chain and production</t>
+          <t>Field service engineer</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
@@ -4157,10 +4150,10 @@
         </is>
       </c>
       <c r="D128" s="23" t="n">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="E128" s="23" t="n">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="F128" s="24">
         <f>IF(Assumptions!$E$5=2,E128,D128)</f>
@@ -4168,53 +4161,47 @@
       </c>
     </row>
     <row r="129">
-      <c r="B129" s="9" t="inlineStr">
-        <is>
-          <t>Support and escalation</t>
-        </is>
-      </c>
-      <c r="C129" s="18" t="inlineStr">
-        <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D129" s="23" t="n">
-        <v>4800</v>
-      </c>
-      <c r="E129" s="23" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F129" s="24">
-        <f>IF(Assumptions!$E$5=2,E129,D129)</f>
-        <v/>
-      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>OVERHEADS AND OTHER OPERATING COSTS</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n"/>
+      <c r="D129" s="1" t="n"/>
+      <c r="E129" s="1" t="n"/>
+      <c r="F129" s="1" t="n"/>
+      <c r="G129" s="1" t="n"/>
+      <c r="H129" s="1" t="n"/>
+      <c r="I129" s="1" t="n"/>
+      <c r="J129" s="1" t="n"/>
     </row>
     <row r="130">
-      <c r="B130" s="9" t="inlineStr">
-        <is>
-          <t>Quality, certification and G&amp;A</t>
-        </is>
-      </c>
-      <c r="C130" s="18" t="inlineStr">
-        <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D130" s="23" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E130" s="23" t="n">
-        <v>7000</v>
-      </c>
-      <c r="F130" s="24">
-        <f>IF(Assumptions!$E$5=2,E130,D130)</f>
-        <v/>
-      </c>
+      <c r="B130" s="21" t="n"/>
+      <c r="C130" s="21" t="n"/>
+      <c r="D130" s="22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E130" s="22" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F130" s="22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G130" s="21" t="n"/>
+      <c r="H130" s="21" t="n"/>
+      <c r="I130" s="21" t="n"/>
+      <c r="J130" s="21" t="n"/>
     </row>
     <row r="131">
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>R&amp;D engineer</t>
+          <t>Offices and facilities per person</t>
         </is>
       </c>
       <c r="C131" s="18" t="inlineStr">
@@ -4223,25 +4210,20 @@
         </is>
       </c>
       <c r="D131" s="23" t="n">
-        <v>5700</v>
+        <v>700</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>5700</v>
+        <v>700</v>
       </c>
       <c r="F131" s="24">
         <f>IF(Assumptions!$E$5=2,E131,D131)</f>
         <v/>
-      </c>
-      <c r="J131" s="20" t="inlineStr">
-        <is>
-          <t>the blended cost of the seven engineers already in post</t>
-        </is>
       </c>
     </row>
     <row r="132">
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Field service engineer</t>
+          <t>IT and software per person</t>
         </is>
       </c>
       <c r="C132" s="18" t="inlineStr">
@@ -4250,10 +4232,10 @@
         </is>
       </c>
       <c r="D132" s="23" t="n">
-        <v>6500</v>
+        <v>250</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>6500</v>
+        <v>250</v>
       </c>
       <c r="F132" s="24">
         <f>IF(Assumptions!$E$5=2,E132,D132)</f>
@@ -4261,59 +4243,65 @@
       </c>
     </row>
     <row r="133">
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>OVERHEADS AND OTHER OPERATING COSTS</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="n"/>
-      <c r="D133" s="1" t="n"/>
-      <c r="E133" s="1" t="n"/>
-      <c r="F133" s="1" t="n"/>
-      <c r="G133" s="1" t="n"/>
-      <c r="H133" s="1" t="n"/>
-      <c r="I133" s="1" t="n"/>
-      <c r="J133" s="1" t="n"/>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>Travel per person</t>
+        </is>
+      </c>
+      <c r="C133" s="18" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D133" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="E133" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="F133" s="24">
+        <f>IF(Assumptions!$E$5=2,E133,D133)</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
-      <c r="B134" s="21" t="n"/>
-      <c r="C134" s="21" t="n"/>
-      <c r="D134" s="22" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E134" s="22" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F134" s="22" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G134" s="21" t="n"/>
-      <c r="H134" s="21" t="n"/>
-      <c r="I134" s="21" t="n"/>
-      <c r="J134" s="21" t="n"/>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>Recruitment per net new hire</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D134" s="23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E134" s="23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F134" s="24">
+        <f>IF(Assumptions!$E$5=2,E134,D134)</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Offices and facilities per person</t>
+          <t>Installer training and demo unit per new partner</t>
         </is>
       </c>
       <c r="C135" s="18" t="inlineStr">
         <is>
-          <t>EUR/month</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D135" s="23" t="n">
-        <v>700</v>
+        <v>3500</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>700</v>
+        <v>3500</v>
       </c>
       <c r="F135" s="24">
         <f>IF(Assumptions!$E$5=2,E135,D135)</f>
@@ -4323,7 +4311,7 @@
     <row r="136">
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>IT and software per person</t>
+          <t>Finance and legal</t>
         </is>
       </c>
       <c r="C136" s="18" t="inlineStr">
@@ -4332,10 +4320,10 @@
         </is>
       </c>
       <c r="D136" s="23" t="n">
-        <v>250</v>
+        <v>7000</v>
       </c>
       <c r="E136" s="23" t="n">
-        <v>250</v>
+        <v>7000</v>
       </c>
       <c r="F136" s="24">
         <f>IF(Assumptions!$E$5=2,E136,D136)</f>
@@ -4345,7 +4333,7 @@
     <row r="137">
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>Travel per person</t>
+          <t>Other general</t>
         </is>
       </c>
       <c r="C137" s="18" t="inlineStr">
@@ -4354,10 +4342,10 @@
         </is>
       </c>
       <c r="D137" s="23" t="n">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="E137" s="23" t="n">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="F137" s="24">
         <f>IF(Assumptions!$E$5=2,E137,D137)</f>
@@ -4367,12 +4355,12 @@
     <row r="138">
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>Recruitment per net new hire</t>
+          <t>Ongoing development</t>
         </is>
       </c>
       <c r="C138" s="18" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>EUR/month</t>
         </is>
       </c>
       <c r="D138" s="23" t="n">
@@ -4389,19 +4377,19 @@
     <row r="139">
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>Installer training and demo unit per new partner</t>
+          <t>Third party product development</t>
         </is>
       </c>
       <c r="C139" s="18" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>EUR/month</t>
         </is>
       </c>
       <c r="D139" s="23" t="n">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="E139" s="23" t="n">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="F139" s="24">
         <f>IF(Assumptions!$E$5=2,E139,D139)</f>
@@ -4411,87 +4399,81 @@
     <row r="140">
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>Finance and legal</t>
+          <t>Annual increase on the costs above</t>
         </is>
       </c>
       <c r="C140" s="18" t="inlineStr">
         <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D140" s="23" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E140" s="23" t="n">
-        <v>7000</v>
-      </c>
-      <c r="F140" s="24">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D140" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E140" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F140" s="26">
         <f>IF(Assumptions!$E$5=2,E140,D140)</f>
         <v/>
       </c>
     </row>
     <row r="141">
-      <c r="B141" s="9" t="inlineStr">
-        <is>
-          <t>Other general</t>
-        </is>
-      </c>
-      <c r="C141" s="18" t="inlineStr">
-        <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D141" s="23" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E141" s="23" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F141" s="24">
-        <f>IF(Assumptions!$E$5=2,E141,D141)</f>
-        <v/>
-      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>FUNDING</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="n"/>
+      <c r="D141" s="1" t="n"/>
+      <c r="E141" s="1" t="n"/>
+      <c r="F141" s="1" t="n"/>
+      <c r="G141" s="1" t="n"/>
+      <c r="H141" s="1" t="n"/>
+      <c r="I141" s="1" t="n"/>
+      <c r="J141" s="1" t="n"/>
     </row>
     <row r="142">
-      <c r="B142" s="9" t="inlineStr">
-        <is>
-          <t>Ongoing development</t>
-        </is>
-      </c>
-      <c r="C142" s="18" t="inlineStr">
-        <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D142" s="23" t="n">
-        <v>8000</v>
-      </c>
-      <c r="E142" s="23" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F142" s="24">
-        <f>IF(Assumptions!$E$5=2,E142,D142)</f>
-        <v/>
-      </c>
+      <c r="B142" s="21" t="n"/>
+      <c r="C142" s="21" t="n"/>
+      <c r="D142" s="22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E142" s="22" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F142" s="22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G142" s="21" t="n"/>
+      <c r="H142" s="21" t="n"/>
+      <c r="I142" s="21" t="n"/>
+      <c r="J142" s="21" t="n"/>
     </row>
     <row r="143">
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>Third party product development</t>
+          <t>First round, money in</t>
         </is>
       </c>
       <c r="C143" s="18" t="inlineStr">
         <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D143" s="23" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E143" s="23" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F143" s="24">
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D143" s="27" t="n">
+        <v>46143</v>
+      </c>
+      <c r="E143" s="27" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F143" s="28">
         <f>IF(Assumptions!$E$5=2,E143,D143)</f>
         <v/>
       </c>
@@ -4499,81 +4481,92 @@
     <row r="144">
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>Annual increase on the costs above</t>
+          <t>First round, amount</t>
         </is>
       </c>
       <c r="C144" s="18" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D144" s="25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E144" s="25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F144" s="26">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D144" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E144" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F144" s="24">
         <f>IF(Assumptions!$E$5=2,E144,D144)</f>
         <v/>
       </c>
     </row>
     <row r="145">
-      <c r="B145" s="7" t="inlineStr">
-        <is>
-          <t>FUNDING</t>
-        </is>
-      </c>
-      <c r="C145" s="1" t="n"/>
-      <c r="D145" s="1" t="n"/>
-      <c r="E145" s="1" t="n"/>
-      <c r="F145" s="1" t="n"/>
-      <c r="G145" s="1" t="n"/>
-      <c r="H145" s="1" t="n"/>
-      <c r="I145" s="1" t="n"/>
-      <c r="J145" s="1" t="n"/>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>Second round, money in</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D145" s="27" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E145" s="27" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F145" s="28">
+        <f>IF(Assumptions!$E$5=2,E145,D145)</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
-      <c r="B146" s="21" t="n"/>
-      <c r="C146" s="21" t="n"/>
-      <c r="D146" s="22" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E146" s="22" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F146" s="22" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G146" s="21" t="n"/>
-      <c r="H146" s="21" t="n"/>
-      <c r="I146" s="21" t="n"/>
-      <c r="J146" s="21" t="n"/>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>Second round, amount</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D146" s="23" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E146" s="23" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F146" s="24">
+        <f>IF(Assumptions!$E$5=2,E146,D146)</f>
+        <v/>
+      </c>
+      <c r="J146" s="20" t="inlineStr">
+        <is>
+          <t>this is the raise the model is built to justify</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>First round, money in</t>
+          <t>Convertible loan drawn</t>
         </is>
       </c>
       <c r="C147" s="18" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D147" s="27" t="n">
-        <v>46143</v>
-      </c>
-      <c r="E147" s="27" t="n">
-        <v>46143</v>
-      </c>
-      <c r="F147" s="28">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D147" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E147" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F147" s="24">
         <f>IF(Assumptions!$E$5=2,E147,D147)</f>
         <v/>
       </c>
@@ -4581,115 +4574,22 @@
     <row r="148">
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>First round, amount</t>
+          <t>Loan drawn on</t>
         </is>
       </c>
       <c r="C148" s="18" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D148" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E148" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F148" s="24">
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D148" s="27" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E148" s="27" t="n">
+        <v>46204</v>
+      </c>
+      <c r="F148" s="28">
         <f>IF(Assumptions!$E$5=2,E148,D148)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="B149" s="9" t="inlineStr">
-        <is>
-          <t>Second round, money in</t>
-        </is>
-      </c>
-      <c r="C149" s="18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D149" s="27" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E149" s="27" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F149" s="28">
-        <f>IF(Assumptions!$E$5=2,E149,D149)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="B150" s="9" t="inlineStr">
-        <is>
-          <t>Second round, amount</t>
-        </is>
-      </c>
-      <c r="C150" s="18" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D150" s="23" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="E150" s="23" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="F150" s="24">
-        <f>IF(Assumptions!$E$5=2,E150,D150)</f>
-        <v/>
-      </c>
-      <c r="J150" s="20" t="inlineStr">
-        <is>
-          <t>this is the raise the model is built to justify</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="B151" s="9" t="inlineStr">
-        <is>
-          <t>Convertible loan drawn</t>
-        </is>
-      </c>
-      <c r="C151" s="18" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D151" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E151" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F151" s="24">
-        <f>IF(Assumptions!$E$5=2,E151,D151)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="B152" s="9" t="inlineStr">
-        <is>
-          <t>Loan drawn on</t>
-        </is>
-      </c>
-      <c r="C152" s="18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D152" s="27" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E152" s="27" t="n">
-        <v>46204</v>
-      </c>
-      <c r="F152" s="28">
-        <f>IF(Assumptions!$E$5=2,E152,D152)</f>
         <v/>
       </c>
     </row>
@@ -11782,243 +11682,243 @@
         </is>
       </c>
       <c r="E35" s="43">
-        <f>IF(E$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(E$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(E$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(E$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="F35" s="43">
-        <f>IF(F$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(F$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(F$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(F$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="G35" s="43">
-        <f>IF(G$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(G$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(G$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(G$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="H35" s="43">
-        <f>IF(H$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(H$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(H$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(H$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="I35" s="43">
-        <f>IF(I$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(I$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(I$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(I$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="J35" s="43">
-        <f>IF(J$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(J$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(J$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(J$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="K35" s="43">
-        <f>IF(K$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(K$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(K$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(K$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="L35" s="43">
-        <f>IF(L$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(L$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(L$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(L$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="M35" s="43">
-        <f>IF(M$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(M$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(M$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(M$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="N35" s="43">
-        <f>IF(N$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(N$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(N$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(N$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="O35" s="43">
-        <f>IF(O$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(O$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(O$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(O$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="P35" s="43">
-        <f>IF(P$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(P$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(P$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(P$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="Q35" s="43">
-        <f>IF(Q$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(Q$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(Q$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(Q$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="R35" s="43">
-        <f>IF(R$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(R$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(R$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(R$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="S35" s="43">
-        <f>IF(S$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(S$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(S$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(S$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="T35" s="43">
-        <f>IF(T$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(T$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(T$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(T$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="U35" s="43">
-        <f>IF(U$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(U$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(U$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(U$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="V35" s="43">
-        <f>IF(V$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(V$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(V$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(V$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="W35" s="43">
-        <f>IF(W$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(W$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(W$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(W$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="X35" s="43">
-        <f>IF(X$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(X$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(X$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(X$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="Y35" s="43">
-        <f>IF(Y$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(Y$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(Y$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(Y$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="Z35" s="43">
-        <f>IF(Z$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(Z$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(Z$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(Z$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AA35" s="43">
-        <f>IF(AA$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AA$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AA$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AA$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AB35" s="43">
-        <f>IF(AB$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AB$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AB$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AB$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AC35" s="43">
-        <f>IF(AC$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AC$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AC$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AC$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AD35" s="43">
-        <f>IF(AD$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AD$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AD$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AD$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AE35" s="43">
-        <f>IF(AE$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AE$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AE$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AE$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AF35" s="43">
-        <f>IF(AF$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AF$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AF$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AF$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AG35" s="43">
-        <f>IF(AG$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AG$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AG$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AG$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AH35" s="43">
-        <f>IF(AH$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AH$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AH$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AH$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AI35" s="43">
-        <f>IF(AI$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AI$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AI$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AI$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AJ35" s="43">
-        <f>IF(AJ$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AJ$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AJ$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AJ$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AK35" s="43">
-        <f>IF(AK$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AK$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AK$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AK$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AL35" s="43">
-        <f>IF(AL$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AL$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AL$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AL$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AM35" s="43">
-        <f>IF(AM$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AM$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AM$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AM$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AN35" s="43">
-        <f>IF(AN$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AN$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AN$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AN$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AO35" s="43">
-        <f>IF(AO$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AO$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AO$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AO$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AP35" s="43">
-        <f>IF(AP$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AP$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AP$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AP$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AQ35" s="43">
-        <f>IF(AQ$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AQ$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AQ$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AQ$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AR35" s="43">
-        <f>IF(AR$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AR$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AR$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AR$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AS35" s="43">
-        <f>IF(AS$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AS$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AS$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AS$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AT35" s="43">
-        <f>IF(AT$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AT$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AT$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AT$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AU35" s="43">
-        <f>IF(AU$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AU$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AU$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AU$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AV35" s="43">
-        <f>IF(AV$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AV$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AV$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AV$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AW35" s="43">
-        <f>IF(AW$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AW$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AW$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AW$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AX35" s="43">
-        <f>IF(AX$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AX$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AX$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AX$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AY35" s="43">
-        <f>IF(AY$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AY$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AY$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AY$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="AZ35" s="43">
-        <f>IF(AZ$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(AZ$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(AZ$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AZ$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BA35" s="43">
-        <f>IF(BA$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(BA$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(BA$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BA$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BB35" s="43">
-        <f>IF(BB$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(BB$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(BB$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BB$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BC35" s="43">
-        <f>IF(BC$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(BC$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(BC$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BC$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BD35" s="43">
-        <f>IF(BD$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(BD$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(BD$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BD$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BE35" s="43">
-        <f>IF(BE$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(BE$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(BE$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BE$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BF35" s="43">
-        <f>IF(BF$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(BF$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(BF$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BF$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BG35" s="43">
-        <f>IF(BG$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(BG$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(BG$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BG$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BH35" s="43">
-        <f>IF(BH$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(BH$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(BH$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BH$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BI35" s="43">
-        <f>IF(BI$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(BI$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(BI$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BI$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BJ35" s="43">
-        <f>IF(BJ$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(BJ$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(BJ$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BJ$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BK35" s="43">
-        <f>IF(BK$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(BK$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(BK$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BK$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BL35" s="43">
-        <f>IF(BL$3=Assumptions!$F$147,Assumptions!$F$148,0)+IF(BL$3=Assumptions!$F$149,Assumptions!$F$150,0)</f>
+        <f>IF(BL$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BL$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
         <v/>
       </c>
       <c r="BN35" s="44">
@@ -12059,243 +11959,243 @@
         </is>
       </c>
       <c r="E36" s="43">
-        <f>IF(E$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(E$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="F36" s="43">
-        <f>IF(F$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(F$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="G36" s="43">
-        <f>IF(G$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(G$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="H36" s="43">
-        <f>IF(H$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(H$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="I36" s="43">
-        <f>IF(I$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(I$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="J36" s="43">
-        <f>IF(J$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(J$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="K36" s="43">
-        <f>IF(K$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(K$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="L36" s="43">
-        <f>IF(L$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(L$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="M36" s="43">
-        <f>IF(M$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(M$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="N36" s="43">
-        <f>IF(N$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(N$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="O36" s="43">
-        <f>IF(O$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(O$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="P36" s="43">
-        <f>IF(P$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(P$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="Q36" s="43">
-        <f>IF(Q$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(Q$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="R36" s="43">
-        <f>IF(R$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(R$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="S36" s="43">
-        <f>IF(S$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(S$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="T36" s="43">
-        <f>IF(T$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(T$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="U36" s="43">
-        <f>IF(U$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(U$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="V36" s="43">
-        <f>IF(V$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(V$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="W36" s="43">
-        <f>IF(W$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(W$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="X36" s="43">
-        <f>IF(X$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(X$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="Y36" s="43">
-        <f>IF(Y$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(Y$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="Z36" s="43">
-        <f>IF(Z$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(Z$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AA36" s="43">
-        <f>IF(AA$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AA$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AB36" s="43">
-        <f>IF(AB$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AB$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AC36" s="43">
-        <f>IF(AC$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AC$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AD36" s="43">
-        <f>IF(AD$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AD$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AE36" s="43">
-        <f>IF(AE$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AE$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AF36" s="43">
-        <f>IF(AF$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AF$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AG36" s="43">
-        <f>IF(AG$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AG$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AH36" s="43">
-        <f>IF(AH$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AH$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AI36" s="43">
-        <f>IF(AI$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AI$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AJ36" s="43">
-        <f>IF(AJ$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AJ$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AK36" s="43">
-        <f>IF(AK$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AK$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AL36" s="43">
-        <f>IF(AL$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AL$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AM36" s="43">
-        <f>IF(AM$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AM$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AN36" s="43">
-        <f>IF(AN$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AN$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AO36" s="43">
-        <f>IF(AO$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AO$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AP36" s="43">
-        <f>IF(AP$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AP$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AQ36" s="43">
-        <f>IF(AQ$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AQ$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AR36" s="43">
-        <f>IF(AR$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AR$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AS36" s="43">
-        <f>IF(AS$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AS$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AT36" s="43">
-        <f>IF(AT$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AT$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AU36" s="43">
-        <f>IF(AU$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AU$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AV36" s="43">
-        <f>IF(AV$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AV$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AW36" s="43">
-        <f>IF(AW$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AW$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AX36" s="43">
-        <f>IF(AX$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AX$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AY36" s="43">
-        <f>IF(AY$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AY$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="AZ36" s="43">
-        <f>IF(AZ$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(AZ$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BA36" s="43">
-        <f>IF(BA$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(BA$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BB36" s="43">
-        <f>IF(BB$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(BB$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BC36" s="43">
-        <f>IF(BC$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(BC$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BD36" s="43">
-        <f>IF(BD$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(BD$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BE36" s="43">
-        <f>IF(BE$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(BE$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BF36" s="43">
-        <f>IF(BF$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(BF$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BG36" s="43">
-        <f>IF(BG$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(BG$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BH36" s="43">
-        <f>IF(BH$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(BH$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BI36" s="43">
-        <f>IF(BI$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(BI$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BJ36" s="43">
-        <f>IF(BJ$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(BJ$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BK36" s="43">
-        <f>IF(BK$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(BK$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BL36" s="43">
-        <f>IF(BL$3=Assumptions!$F$152,Assumptions!$F$151,0)</f>
+        <f>IF(BL$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
         <v/>
       </c>
       <c r="BN36" s="44">
@@ -34634,243 +34534,243 @@
         </is>
       </c>
       <c r="E13" s="43">
-        <f>'Revenue Forecast'!E19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!E19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="F13" s="43">
-        <f>'Revenue Forecast'!F19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!F19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="G13" s="43">
-        <f>'Revenue Forecast'!G19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!G19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="H13" s="43">
-        <f>'Revenue Forecast'!H19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!H19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="I13" s="43">
-        <f>'Revenue Forecast'!I19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!I19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="J13" s="43">
-        <f>'Revenue Forecast'!J19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!J19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="K13" s="43">
-        <f>'Revenue Forecast'!K19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!K19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="L13" s="43">
-        <f>'Revenue Forecast'!L19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!L19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="M13" s="43">
-        <f>'Revenue Forecast'!M19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!M19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="N13" s="43">
-        <f>'Revenue Forecast'!N19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!N19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="O13" s="43">
-        <f>'Revenue Forecast'!O19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!O19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="P13" s="43">
-        <f>'Revenue Forecast'!P19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!P19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="Q13" s="43">
-        <f>'Revenue Forecast'!Q19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!Q19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="R13" s="43">
-        <f>'Revenue Forecast'!R19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!R19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="S13" s="43">
-        <f>'Revenue Forecast'!S19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!S19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="T13" s="43">
-        <f>'Revenue Forecast'!T19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!T19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="U13" s="43">
-        <f>'Revenue Forecast'!U19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!U19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="V13" s="43">
-        <f>'Revenue Forecast'!V19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!V19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="W13" s="43">
-        <f>'Revenue Forecast'!W19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!W19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="X13" s="43">
-        <f>'Revenue Forecast'!X19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!X19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="Y13" s="43">
-        <f>'Revenue Forecast'!Y19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!Y19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="Z13" s="43">
-        <f>'Revenue Forecast'!Z19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!Z19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AA13" s="43">
-        <f>'Revenue Forecast'!AA19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AA19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AB13" s="43">
-        <f>'Revenue Forecast'!AB19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AB19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AC13" s="43">
-        <f>'Revenue Forecast'!AC19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AC19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AD13" s="43">
-        <f>'Revenue Forecast'!AD19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AD19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AE13" s="43">
-        <f>'Revenue Forecast'!AE19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AE19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AF13" s="43">
-        <f>'Revenue Forecast'!AF19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AF19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AG13" s="43">
-        <f>'Revenue Forecast'!AG19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AG19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AH13" s="43">
-        <f>'Revenue Forecast'!AH19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AH19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AI13" s="43">
-        <f>'Revenue Forecast'!AI19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AI19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AJ13" s="43">
-        <f>'Revenue Forecast'!AJ19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AJ19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AK13" s="43">
-        <f>'Revenue Forecast'!AK19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AK19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AL13" s="43">
-        <f>'Revenue Forecast'!AL19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AL19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AM13" s="43">
-        <f>'Revenue Forecast'!AM19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AM19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AN13" s="43">
-        <f>'Revenue Forecast'!AN19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AN19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AO13" s="43">
-        <f>'Revenue Forecast'!AO19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AO19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AP13" s="43">
-        <f>'Revenue Forecast'!AP19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AP19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AQ13" s="43">
-        <f>'Revenue Forecast'!AQ19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AQ19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AR13" s="43">
-        <f>'Revenue Forecast'!AR19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AR19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AS13" s="43">
-        <f>'Revenue Forecast'!AS19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AS19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AT13" s="43">
-        <f>'Revenue Forecast'!AT19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AT19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AU13" s="43">
-        <f>'Revenue Forecast'!AU19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AU19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AV13" s="43">
-        <f>'Revenue Forecast'!AV19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AV19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AW13" s="43">
-        <f>'Revenue Forecast'!AW19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AW19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AX13" s="43">
-        <f>'Revenue Forecast'!AX19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AX19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AY13" s="43">
-        <f>'Revenue Forecast'!AY19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AY19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="AZ13" s="43">
-        <f>'Revenue Forecast'!AZ19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!AZ19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BA13" s="43">
-        <f>'Revenue Forecast'!BA19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!BA19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BB13" s="43">
-        <f>'Revenue Forecast'!BB19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!BB19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BC13" s="43">
-        <f>'Revenue Forecast'!BC19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!BC19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BD13" s="43">
-        <f>'Revenue Forecast'!BD19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!BD19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BE13" s="43">
-        <f>'Revenue Forecast'!BE19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!BE19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BF13" s="43">
-        <f>'Revenue Forecast'!BF19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!BF19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BG13" s="43">
-        <f>'Revenue Forecast'!BG19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!BG19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BH13" s="43">
-        <f>'Revenue Forecast'!BH19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!BH19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BI13" s="43">
-        <f>'Revenue Forecast'!BI19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!BI19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BJ13" s="43">
-        <f>'Revenue Forecast'!BJ19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!BJ19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BK13" s="43">
-        <f>'Revenue Forecast'!BK19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!BK19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BL13" s="43">
-        <f>'Revenue Forecast'!BL19*Assumptions!$F$139</f>
+        <f>'Revenue Forecast'!BL19*Assumptions!$F$135</f>
         <v/>
       </c>
       <c r="BN13" s="44">
@@ -35254,243 +35154,243 @@
         </is>
       </c>
       <c r="E17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(E$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(F$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(G$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(H$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(I$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(J$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(K$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(L$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(M$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(N$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(O$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(P$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(Q$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(R$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(S$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(T$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(U$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(V$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(W$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(X$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(Y$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(Z$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AA$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AB$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AC$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AD$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AE$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AF$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AG$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AH$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AI$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AJ$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AK$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AL$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AM$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AN$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AO$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AP$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AQ$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AR$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AS$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AT$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AU$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AV$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AW$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AX$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AY$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(AZ$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(BA$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(BB$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(BC$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(BD$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(BE$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(BF$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(BG$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(BH$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(BI$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(BJ$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(BK$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL17" s="43">
-        <f>Assumptions!$F$142*(1+Assumptions!$F$144)^(YEAR(BL$3)-2026)</f>
+        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN17" s="44">
@@ -35526,243 +35426,243 @@
         </is>
       </c>
       <c r="E18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(E$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(F$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(G$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(H$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(I$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(J$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(K$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(L$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(M$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(N$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(O$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(P$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(Q$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(R$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(S$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(T$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(U$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(V$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(W$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(X$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(Y$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(Z$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AA$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AB$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AC$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AD$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AE$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AF$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AG$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AH$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AI$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AJ$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AK$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AL$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AM$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AN$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AO$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AP$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AQ$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AR$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AS$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AT$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AU$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AV$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AW$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AX$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AY$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(AZ$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(BA$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(BB$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(BC$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(BD$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(BE$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(BF$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(BG$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(BH$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(BI$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(BJ$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(BK$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL18" s="43">
-        <f>Assumptions!$F$143*(1+Assumptions!$F$144)^(YEAR(BL$3)-2026)</f>
+        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN18" s="44">
@@ -36146,243 +36046,243 @@
         </is>
       </c>
       <c r="E22" s="43">
-        <f>Personnel!E21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!E20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="F22" s="43">
-        <f>Personnel!F21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!F20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="G22" s="43">
-        <f>Personnel!G21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!G20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="H22" s="43">
-        <f>Personnel!H21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!H20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="I22" s="43">
-        <f>Personnel!I21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!I20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="J22" s="43">
-        <f>Personnel!J21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!J20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="K22" s="43">
-        <f>Personnel!K21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!K20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="L22" s="43">
-        <f>Personnel!L21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!L20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="M22" s="43">
-        <f>Personnel!M21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!M20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="N22" s="43">
-        <f>Personnel!N21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!N20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="O22" s="43">
-        <f>Personnel!O21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!O20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="P22" s="43">
-        <f>Personnel!P21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!P20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="Q22" s="43">
-        <f>Personnel!Q21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!Q20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="R22" s="43">
-        <f>Personnel!R21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!R20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="S22" s="43">
-        <f>Personnel!S21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!S20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="T22" s="43">
-        <f>Personnel!T21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!T20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="U22" s="43">
-        <f>Personnel!U21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!U20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="V22" s="43">
-        <f>Personnel!V21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!V20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="W22" s="43">
-        <f>Personnel!W21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!W20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="X22" s="43">
-        <f>Personnel!X21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!X20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="Y22" s="43">
-        <f>Personnel!Y21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!Y20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="Z22" s="43">
-        <f>Personnel!Z21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!Z20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AA22" s="43">
-        <f>Personnel!AA21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AA20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AB22" s="43">
-        <f>Personnel!AB21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AB20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AC22" s="43">
-        <f>Personnel!AC21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AC20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AD22" s="43">
-        <f>Personnel!AD21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AD20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AE22" s="43">
-        <f>Personnel!AE21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AE20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AF22" s="43">
-        <f>Personnel!AF21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AF20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AG22" s="43">
-        <f>Personnel!AG21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AG20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AH22" s="43">
-        <f>Personnel!AH21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AH20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AI22" s="43">
-        <f>Personnel!AI21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AI20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AJ22" s="43">
-        <f>Personnel!AJ21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AJ20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AK22" s="43">
-        <f>Personnel!AK21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AK20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AL22" s="43">
-        <f>Personnel!AL21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AL20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AM22" s="43">
-        <f>Personnel!AM21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AM20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AN22" s="43">
-        <f>Personnel!AN21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AN20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AO22" s="43">
-        <f>Personnel!AO21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AO20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AP22" s="43">
-        <f>Personnel!AP21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AP20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AQ22" s="43">
-        <f>Personnel!AQ21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AQ20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AR22" s="43">
-        <f>Personnel!AR21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AR20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AS22" s="43">
-        <f>Personnel!AS21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AS20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AT22" s="43">
-        <f>Personnel!AT21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AT20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AU22" s="43">
-        <f>Personnel!AU21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AU20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AV22" s="43">
-        <f>Personnel!AV21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AV20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AW22" s="43">
-        <f>Personnel!AW21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AW20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AX22" s="43">
-        <f>Personnel!AX21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AX20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AY22" s="43">
-        <f>Personnel!AY21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AY20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="AZ22" s="43">
-        <f>Personnel!AZ21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!AZ20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BA22" s="43">
-        <f>Personnel!BA21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!BA20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BB22" s="43">
-        <f>Personnel!BB21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!BB20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BC22" s="43">
-        <f>Personnel!BC21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!BC20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BD22" s="43">
-        <f>Personnel!BD21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!BD20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BE22" s="43">
-        <f>Personnel!BE21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!BE20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BF22" s="43">
-        <f>Personnel!BF21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!BF20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BG22" s="43">
-        <f>Personnel!BG21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!BG20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BH22" s="43">
-        <f>Personnel!BH21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!BH20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BI22" s="43">
-        <f>Personnel!BI21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!BI20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BJ22" s="43">
-        <f>Personnel!BJ21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!BJ20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BK22" s="43">
-        <f>Personnel!BK21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!BK20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BL22" s="43">
-        <f>Personnel!BL21*(Assumptions!$F$135+Assumptions!$F$136+Assumptions!$F$137)</f>
+        <f>Personnel!BL20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
         <v/>
       </c>
       <c r="BN22" s="44">
@@ -36427,239 +36327,239 @@
         <v/>
       </c>
       <c r="F23" s="43">
-        <f>MAX(0,Personnel!F21-Personnel!E21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!F20-Personnel!E20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="G23" s="43">
-        <f>MAX(0,Personnel!G21-Personnel!F21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!G20-Personnel!F20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="H23" s="43">
-        <f>MAX(0,Personnel!H21-Personnel!G21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!H20-Personnel!G20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="I23" s="43">
-        <f>MAX(0,Personnel!I21-Personnel!H21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!I20-Personnel!H20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="J23" s="43">
-        <f>MAX(0,Personnel!J21-Personnel!I21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!J20-Personnel!I20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="K23" s="43">
-        <f>MAX(0,Personnel!K21-Personnel!J21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!K20-Personnel!J20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="L23" s="43">
-        <f>MAX(0,Personnel!L21-Personnel!K21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!L20-Personnel!K20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="M23" s="43">
-        <f>MAX(0,Personnel!M21-Personnel!L21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!M20-Personnel!L20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="N23" s="43">
-        <f>MAX(0,Personnel!N21-Personnel!M21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!N20-Personnel!M20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="O23" s="43">
-        <f>MAX(0,Personnel!O21-Personnel!N21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!O20-Personnel!N20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="P23" s="43">
-        <f>MAX(0,Personnel!P21-Personnel!O21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!P20-Personnel!O20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="Q23" s="43">
-        <f>MAX(0,Personnel!Q21-Personnel!P21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!Q20-Personnel!P20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="R23" s="43">
-        <f>MAX(0,Personnel!R21-Personnel!Q21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!R20-Personnel!Q20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="S23" s="43">
-        <f>MAX(0,Personnel!S21-Personnel!R21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!S20-Personnel!R20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="T23" s="43">
-        <f>MAX(0,Personnel!T21-Personnel!S21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!T20-Personnel!S20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="U23" s="43">
-        <f>MAX(0,Personnel!U21-Personnel!T21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!U20-Personnel!T20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="V23" s="43">
-        <f>MAX(0,Personnel!V21-Personnel!U21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!V20-Personnel!U20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="W23" s="43">
-        <f>MAX(0,Personnel!W21-Personnel!V21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!W20-Personnel!V20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="X23" s="43">
-        <f>MAX(0,Personnel!X21-Personnel!W21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!X20-Personnel!W20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="Y23" s="43">
-        <f>MAX(0,Personnel!Y21-Personnel!X21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!Y20-Personnel!X20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="Z23" s="43">
-        <f>MAX(0,Personnel!Z21-Personnel!Y21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!Z20-Personnel!Y20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AA23" s="43">
-        <f>MAX(0,Personnel!AA21-Personnel!Z21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AA20-Personnel!Z20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AB23" s="43">
-        <f>MAX(0,Personnel!AB21-Personnel!AA21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AB20-Personnel!AA20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AC23" s="43">
-        <f>MAX(0,Personnel!AC21-Personnel!AB21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AC20-Personnel!AB20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AD23" s="43">
-        <f>MAX(0,Personnel!AD21-Personnel!AC21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AD20-Personnel!AC20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AE23" s="43">
-        <f>MAX(0,Personnel!AE21-Personnel!AD21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AE20-Personnel!AD20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AF23" s="43">
-        <f>MAX(0,Personnel!AF21-Personnel!AE21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AF20-Personnel!AE20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AG23" s="43">
-        <f>MAX(0,Personnel!AG21-Personnel!AF21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AG20-Personnel!AF20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AH23" s="43">
-        <f>MAX(0,Personnel!AH21-Personnel!AG21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AH20-Personnel!AG20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AI23" s="43">
-        <f>MAX(0,Personnel!AI21-Personnel!AH21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AI20-Personnel!AH20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AJ23" s="43">
-        <f>MAX(0,Personnel!AJ21-Personnel!AI21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AJ20-Personnel!AI20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AK23" s="43">
-        <f>MAX(0,Personnel!AK21-Personnel!AJ21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AK20-Personnel!AJ20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AL23" s="43">
-        <f>MAX(0,Personnel!AL21-Personnel!AK21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AL20-Personnel!AK20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AM23" s="43">
-        <f>MAX(0,Personnel!AM21-Personnel!AL21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AM20-Personnel!AL20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AN23" s="43">
-        <f>MAX(0,Personnel!AN21-Personnel!AM21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AN20-Personnel!AM20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AO23" s="43">
-        <f>MAX(0,Personnel!AO21-Personnel!AN21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AO20-Personnel!AN20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AP23" s="43">
-        <f>MAX(0,Personnel!AP21-Personnel!AO21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AP20-Personnel!AO20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AQ23" s="43">
-        <f>MAX(0,Personnel!AQ21-Personnel!AP21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AQ20-Personnel!AP20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AR23" s="43">
-        <f>MAX(0,Personnel!AR21-Personnel!AQ21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AR20-Personnel!AQ20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AS23" s="43">
-        <f>MAX(0,Personnel!AS21-Personnel!AR21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AS20-Personnel!AR20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AT23" s="43">
-        <f>MAX(0,Personnel!AT21-Personnel!AS21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AT20-Personnel!AS20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AU23" s="43">
-        <f>MAX(0,Personnel!AU21-Personnel!AT21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AU20-Personnel!AT20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AV23" s="43">
-        <f>MAX(0,Personnel!AV21-Personnel!AU21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AV20-Personnel!AU20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AW23" s="43">
-        <f>MAX(0,Personnel!AW21-Personnel!AV21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AW20-Personnel!AV20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AX23" s="43">
-        <f>MAX(0,Personnel!AX21-Personnel!AW21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AX20-Personnel!AW20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AY23" s="43">
-        <f>MAX(0,Personnel!AY21-Personnel!AX21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AY20-Personnel!AX20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="AZ23" s="43">
-        <f>MAX(0,Personnel!AZ21-Personnel!AY21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!AZ20-Personnel!AY20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BA23" s="43">
-        <f>MAX(0,Personnel!BA21-Personnel!AZ21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!BA20-Personnel!AZ20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BB23" s="43">
-        <f>MAX(0,Personnel!BB21-Personnel!BA21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!BB20-Personnel!BA20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BC23" s="43">
-        <f>MAX(0,Personnel!BC21-Personnel!BB21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!BC20-Personnel!BB20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BD23" s="43">
-        <f>MAX(0,Personnel!BD21-Personnel!BC21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!BD20-Personnel!BC20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BE23" s="43">
-        <f>MAX(0,Personnel!BE21-Personnel!BD21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!BE20-Personnel!BD20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BF23" s="43">
-        <f>MAX(0,Personnel!BF21-Personnel!BE21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!BF20-Personnel!BE20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BG23" s="43">
-        <f>MAX(0,Personnel!BG21-Personnel!BF21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!BG20-Personnel!BF20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BH23" s="43">
-        <f>MAX(0,Personnel!BH21-Personnel!BG21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!BH20-Personnel!BG20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BI23" s="43">
-        <f>MAX(0,Personnel!BI21-Personnel!BH21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!BI20-Personnel!BH20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BJ23" s="43">
-        <f>MAX(0,Personnel!BJ21-Personnel!BI21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!BJ20-Personnel!BI20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BK23" s="43">
-        <f>MAX(0,Personnel!BK21-Personnel!BJ21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!BK20-Personnel!BJ20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BL23" s="43">
-        <f>MAX(0,Personnel!BL21-Personnel!BK21)*Assumptions!$F$138</f>
+        <f>MAX(0,Personnel!BL20-Personnel!BK20)*Assumptions!$F$134</f>
         <v/>
       </c>
       <c r="BN23" s="44">
@@ -36972,243 +36872,243 @@
         </is>
       </c>
       <c r="E25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(E$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(F$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(G$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(H$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(I$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(J$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(K$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(L$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(M$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(N$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(O$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(P$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(Q$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(R$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(S$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(T$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(U$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(V$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(W$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(X$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(Y$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(Z$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AA$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AB$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AC$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AD$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AE$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AF$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AG$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AH$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AI$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AJ$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AK$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AL$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AM$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AN$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AO$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AP$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AQ$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AR$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AS$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AT$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AU$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AV$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AW$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AX$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AY$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(AZ$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(BA$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(BB$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(BC$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(BD$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(BE$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(BF$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(BG$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(BH$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(BI$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(BJ$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(BK$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL25" s="43">
-        <f>Assumptions!$F$140*(1+Assumptions!$F$144)^(YEAR(BL$3)-2026)</f>
+        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN25" s="44">
@@ -37244,243 +37144,243 @@
         </is>
       </c>
       <c r="E26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(E$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(F$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(G$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(H$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(I$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(J$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(K$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(L$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(M$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(N$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(O$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(P$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(Q$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(R$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(S$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(T$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(U$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(V$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(W$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(X$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(Y$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(Z$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AA$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AB$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AC$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AD$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AE$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AF$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AG$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AH$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AI$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AJ$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AK$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AL$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AM$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AN$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AO$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AP$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AQ$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AR$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AS$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AT$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AU$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AV$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AW$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AX$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AY$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(AZ$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(BA$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(BB$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(BC$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(BD$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(BE$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(BF$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(BG$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(BH$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(BI$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(BJ$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(BK$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL26" s="43">
-        <f>Assumptions!$F$141*(1+Assumptions!$F$144)^(YEAR(BL$3)-2026)</f>
+        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN26" s="44">
@@ -43767,7 +43667,7 @@
     <row r="16">
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Quality and certification</t>
+          <t>R&amp;D engineers</t>
         </is>
       </c>
       <c r="C16" s="42" t="inlineStr">
@@ -43776,243 +43676,243 @@
         </is>
       </c>
       <c r="E16" s="54">
-        <f>HLOOKUP(YEAR(E$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(E$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="F16" s="54">
-        <f>HLOOKUP(YEAR(F$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(F$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="G16" s="54">
-        <f>HLOOKUP(YEAR(G$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(G$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="H16" s="54">
-        <f>HLOOKUP(YEAR(H$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(H$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="I16" s="54">
-        <f>HLOOKUP(YEAR(I$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(I$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="J16" s="54">
-        <f>HLOOKUP(YEAR(J$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(J$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="K16" s="54">
-        <f>HLOOKUP(YEAR(K$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(K$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="L16" s="54">
-        <f>HLOOKUP(YEAR(L$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(L$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="M16" s="54">
-        <f>HLOOKUP(YEAR(M$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(M$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="N16" s="54">
-        <f>HLOOKUP(YEAR(N$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(N$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="O16" s="54">
-        <f>HLOOKUP(YEAR(O$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(O$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="P16" s="54">
-        <f>HLOOKUP(YEAR(P$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(P$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="Q16" s="54">
-        <f>HLOOKUP(YEAR(Q$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(Q$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="R16" s="54">
-        <f>HLOOKUP(YEAR(R$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(R$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="S16" s="54">
-        <f>HLOOKUP(YEAR(S$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(S$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="T16" s="54">
-        <f>HLOOKUP(YEAR(T$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(T$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="U16" s="54">
-        <f>HLOOKUP(YEAR(U$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(U$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="V16" s="54">
-        <f>HLOOKUP(YEAR(V$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(V$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="W16" s="54">
-        <f>HLOOKUP(YEAR(W$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(W$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="X16" s="54">
-        <f>HLOOKUP(YEAR(X$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(X$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="Y16" s="54">
-        <f>HLOOKUP(YEAR(Y$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(Y$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="Z16" s="54">
-        <f>HLOOKUP(YEAR(Z$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(Z$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AA16" s="54">
-        <f>HLOOKUP(YEAR(AA$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AA$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AB16" s="54">
-        <f>HLOOKUP(YEAR(AB$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AB$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AC16" s="54">
-        <f>HLOOKUP(YEAR(AC$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AC$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AD16" s="54">
-        <f>HLOOKUP(YEAR(AD$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AD$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AE16" s="54">
-        <f>HLOOKUP(YEAR(AE$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AE$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AF16" s="54">
-        <f>HLOOKUP(YEAR(AF$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AF$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AG16" s="54">
-        <f>HLOOKUP(YEAR(AG$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AG$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AH16" s="54">
-        <f>HLOOKUP(YEAR(AH$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AH$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AI16" s="54">
-        <f>HLOOKUP(YEAR(AI$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AI$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AJ16" s="54">
-        <f>HLOOKUP(YEAR(AJ$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AJ$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AK16" s="54">
-        <f>HLOOKUP(YEAR(AK$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AK$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AL16" s="54">
-        <f>HLOOKUP(YEAR(AL$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AL$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AM16" s="54">
-        <f>HLOOKUP(YEAR(AM$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AM$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AN16" s="54">
-        <f>HLOOKUP(YEAR(AN$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AN$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AO16" s="54">
-        <f>HLOOKUP(YEAR(AO$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AO$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AP16" s="54">
-        <f>HLOOKUP(YEAR(AP$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AP$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AQ16" s="54">
-        <f>HLOOKUP(YEAR(AQ$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AQ$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AR16" s="54">
-        <f>HLOOKUP(YEAR(AR$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AR$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AS16" s="54">
-        <f>HLOOKUP(YEAR(AS$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AS$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AT16" s="54">
-        <f>HLOOKUP(YEAR(AT$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AT$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AU16" s="54">
-        <f>HLOOKUP(YEAR(AU$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AU$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AV16" s="54">
-        <f>HLOOKUP(YEAR(AV$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AV$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AW16" s="54">
-        <f>HLOOKUP(YEAR(AW$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AW$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AX16" s="54">
-        <f>HLOOKUP(YEAR(AX$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AX$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AY16" s="54">
-        <f>HLOOKUP(YEAR(AY$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AY$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="AZ16" s="54">
-        <f>HLOOKUP(YEAR(AZ$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AZ$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BA16" s="54">
-        <f>HLOOKUP(YEAR(BA$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BA$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BB16" s="54">
-        <f>HLOOKUP(YEAR(BB$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BB$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BC16" s="54">
-        <f>HLOOKUP(YEAR(BC$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BC$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BD16" s="54">
-        <f>HLOOKUP(YEAR(BD$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BD$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BE16" s="54">
-        <f>HLOOKUP(YEAR(BE$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BE$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BF16" s="54">
-        <f>HLOOKUP(YEAR(BF$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BF$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BG16" s="54">
-        <f>HLOOKUP(YEAR(BG$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BG$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BH16" s="54">
-        <f>HLOOKUP(YEAR(BH$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BH$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BI16" s="54">
-        <f>HLOOKUP(YEAR(BI$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BI$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BJ16" s="54">
-        <f>HLOOKUP(YEAR(BJ$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BJ$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BK16" s="54">
-        <f>HLOOKUP(YEAR(BK$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BK$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BL16" s="54">
-        <f>HLOOKUP(YEAR(BL$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
+        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BL$3),Assumptions!$D$103:$H$103)</f>
         <v/>
       </c>
       <c r="BN16" s="55">
@@ -44034,12 +43934,17 @@
       <c r="BR16" s="55">
         <f>BL16</f>
         <v/>
+      </c>
+      <c r="BT16" s="20" t="inlineStr">
+        <is>
+          <t>the founding engineers plus everyone hired up to and including this year</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>R&amp;D engineers</t>
+          <t>Leadership, finance, HR, IT and legal</t>
         </is>
       </c>
       <c r="C17" s="42" t="inlineStr">
@@ -44048,243 +43953,243 @@
         </is>
       </c>
       <c r="E17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(E$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(E$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="F17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(F$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(F$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="G17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(G$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(G$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="H17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(H$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(H$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="I17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(I$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(I$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="J17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(J$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(J$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="K17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(K$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(K$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="L17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(L$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(L$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="M17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(M$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(M$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="N17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(N$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(N$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="O17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(O$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(O$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="P17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(P$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(P$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="Q17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(Q$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(Q$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="R17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(R$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(R$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="S17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(S$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(S$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="T17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(T$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(T$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="U17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(U$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(U$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="V17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(V$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(V$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="W17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(W$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(W$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="X17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(X$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(X$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="Y17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(Y$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(Y$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="Z17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(Z$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(Z$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AA17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AA$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AA$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AB17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AB$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AB$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AC17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AC$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AC$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AD17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AD$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AD$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AE17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AE$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AE$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AF17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AF$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AF$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AG17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AG$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AG$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AH17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AH$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AH$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AI17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AI$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AI$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AJ17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AJ$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AJ$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AK17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AK$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AK$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AL17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AL$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AL$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AM17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AM$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AM$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AN17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AN$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AN$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AO17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AO$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AO$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AP17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AP$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AP$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AQ17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AQ$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AQ$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AR17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AR$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AR$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AS17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AS$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AS$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AT17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AT$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AT$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AU17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AU$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AU$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AV17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AV$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AV$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AW17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AW$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AW$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AX17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AX$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AX$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AY17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AY$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AY$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="AZ17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(AZ$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(AZ$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BA17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BA$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(BA$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BB17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BB$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(BB$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BC17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BC$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(BC$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BD17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BD$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(BD$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BE17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BE$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(BE$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BF17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BF$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(BF$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BG17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BG$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(BG$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BH17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BH$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(BH$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BI17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BI$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(BI$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BJ17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BJ$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(BJ$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BK17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BK$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(BK$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BL17" s="54">
-        <f>Assumptions!$F$105+SUMIF(Assumptions!$D$100:$H$100,"&lt;="&amp;YEAR(BL$3),Assumptions!$D$103:$H$103)</f>
+        <f>HLOOKUP(YEAR(BL$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
         <v/>
       </c>
       <c r="BN17" s="55">
@@ -44309,14 +44214,14 @@
       </c>
       <c r="BT17" s="20" t="inlineStr">
         <is>
-          <t>the founding engineers plus everyone hired up to and including this year</t>
+          <t>the whole back office, typed per year on Assumptions</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Leadership, finance, HR, IT and legal</t>
+          <t>Field service engineers</t>
         </is>
       </c>
       <c r="C18" s="42" t="inlineStr">
@@ -44325,243 +44230,243 @@
         </is>
       </c>
       <c r="E18" s="54">
-        <f>HLOOKUP(YEAR(E$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!E41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="F18" s="54">
-        <f>HLOOKUP(YEAR(F$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!F41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="G18" s="54">
-        <f>HLOOKUP(YEAR(G$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!G41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="H18" s="54">
-        <f>HLOOKUP(YEAR(H$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!H41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="I18" s="54">
-        <f>HLOOKUP(YEAR(I$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!I41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="J18" s="54">
-        <f>HLOOKUP(YEAR(J$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!J41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="K18" s="54">
-        <f>HLOOKUP(YEAR(K$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!K41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="L18" s="54">
-        <f>HLOOKUP(YEAR(L$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!L41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="M18" s="54">
-        <f>HLOOKUP(YEAR(M$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!M41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="N18" s="54">
-        <f>HLOOKUP(YEAR(N$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!N41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="O18" s="54">
-        <f>HLOOKUP(YEAR(O$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!O41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="P18" s="54">
-        <f>HLOOKUP(YEAR(P$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!P41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="Q18" s="54">
-        <f>HLOOKUP(YEAR(Q$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!Q41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="R18" s="54">
-        <f>HLOOKUP(YEAR(R$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!R41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="S18" s="54">
-        <f>HLOOKUP(YEAR(S$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!S41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="T18" s="54">
-        <f>HLOOKUP(YEAR(T$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!T41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="U18" s="54">
-        <f>HLOOKUP(YEAR(U$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!U41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="V18" s="54">
-        <f>HLOOKUP(YEAR(V$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!V41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="W18" s="54">
-        <f>HLOOKUP(YEAR(W$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!W41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="X18" s="54">
-        <f>HLOOKUP(YEAR(X$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!X41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="Y18" s="54">
-        <f>HLOOKUP(YEAR(Y$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!Y41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="Z18" s="54">
-        <f>HLOOKUP(YEAR(Z$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!Z41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AA18" s="54">
-        <f>HLOOKUP(YEAR(AA$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AA41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AB18" s="54">
-        <f>HLOOKUP(YEAR(AB$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AB41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AC18" s="54">
-        <f>HLOOKUP(YEAR(AC$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AC41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AD18" s="54">
-        <f>HLOOKUP(YEAR(AD$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AD41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AE18" s="54">
-        <f>HLOOKUP(YEAR(AE$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AE41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AF18" s="54">
-        <f>HLOOKUP(YEAR(AF$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AF41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AG18" s="54">
-        <f>HLOOKUP(YEAR(AG$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AG41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AH18" s="54">
-        <f>HLOOKUP(YEAR(AH$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AH41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AI18" s="54">
-        <f>HLOOKUP(YEAR(AI$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AI41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AJ18" s="54">
-        <f>HLOOKUP(YEAR(AJ$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AJ41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AK18" s="54">
-        <f>HLOOKUP(YEAR(AK$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AK41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AL18" s="54">
-        <f>HLOOKUP(YEAR(AL$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AL41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AM18" s="54">
-        <f>HLOOKUP(YEAR(AM$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AM41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AN18" s="54">
-        <f>HLOOKUP(YEAR(AN$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AN41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AO18" s="54">
-        <f>HLOOKUP(YEAR(AO$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AO41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AP18" s="54">
-        <f>HLOOKUP(YEAR(AP$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AP41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AQ18" s="54">
-        <f>HLOOKUP(YEAR(AQ$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AQ41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AR18" s="54">
-        <f>HLOOKUP(YEAR(AR$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AR41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AS18" s="54">
-        <f>HLOOKUP(YEAR(AS$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AS41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AT18" s="54">
-        <f>HLOOKUP(YEAR(AT$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AT41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AU18" s="54">
-        <f>HLOOKUP(YEAR(AU$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AU41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AV18" s="54">
-        <f>HLOOKUP(YEAR(AV$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AV41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AW18" s="54">
-        <f>HLOOKUP(YEAR(AW$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AW41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AX18" s="54">
-        <f>HLOOKUP(YEAR(AX$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AX41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AY18" s="54">
-        <f>HLOOKUP(YEAR(AY$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AY41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="AZ18" s="54">
-        <f>HLOOKUP(YEAR(AZ$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!AZ41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BA18" s="54">
-        <f>HLOOKUP(YEAR(BA$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!BA41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BB18" s="54">
-        <f>HLOOKUP(YEAR(BB$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!BB41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BC18" s="54">
-        <f>HLOOKUP(YEAR(BC$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!BC41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BD18" s="54">
-        <f>HLOOKUP(YEAR(BD$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!BD41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BE18" s="54">
-        <f>HLOOKUP(YEAR(BE$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!BE41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BF18" s="54">
-        <f>HLOOKUP(YEAR(BF$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!BF41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BG18" s="54">
-        <f>HLOOKUP(YEAR(BG$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!BG41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BH18" s="54">
-        <f>HLOOKUP(YEAR(BH$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!BH41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BI18" s="54">
-        <f>HLOOKUP(YEAR(BI$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!BI41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BJ18" s="54">
-        <f>HLOOKUP(YEAR(BJ$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!BJ41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BK18" s="54">
-        <f>HLOOKUP(YEAR(BK$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!BK41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BL18" s="54">
-        <f>HLOOKUP(YEAR(BL$3),Assumptions!$D$117:$H$120,4,FALSE)</f>
+        <f>ROUND('Revenue Forecast'!BL41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
         <v/>
       </c>
       <c r="BN18" s="55">
@@ -44586,833 +44491,556 @@
       </c>
       <c r="BT18" s="20" t="inlineStr">
         <is>
-          <t>the whole back office, typed per year on Assumptions</t>
+          <t>salaried staff: boilers on a service contract divided by the boilers one engineer can look after</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Field service engineers</t>
-        </is>
-      </c>
-      <c r="C19" s="42" t="inlineStr">
+      <c r="B19" s="50" t="inlineStr">
+        <is>
+          <t>Operations, support and administration</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
       </c>
-      <c r="E19" s="54">
-        <f>ROUND('Revenue Forecast'!E41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="54">
-        <f>ROUND('Revenue Forecast'!F41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="54">
-        <f>ROUND('Revenue Forecast'!G41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="H19" s="54">
-        <f>ROUND('Revenue Forecast'!H41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="I19" s="54">
-        <f>ROUND('Revenue Forecast'!I41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="J19" s="54">
-        <f>ROUND('Revenue Forecast'!J41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="K19" s="54">
-        <f>ROUND('Revenue Forecast'!K41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="L19" s="54">
-        <f>ROUND('Revenue Forecast'!L41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="M19" s="54">
-        <f>ROUND('Revenue Forecast'!M41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="N19" s="54">
-        <f>ROUND('Revenue Forecast'!N41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="O19" s="54">
-        <f>ROUND('Revenue Forecast'!O41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="P19" s="54">
-        <f>ROUND('Revenue Forecast'!P41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="54">
-        <f>ROUND('Revenue Forecast'!Q41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="R19" s="54">
-        <f>ROUND('Revenue Forecast'!R41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="S19" s="54">
-        <f>ROUND('Revenue Forecast'!S41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="T19" s="54">
-        <f>ROUND('Revenue Forecast'!T41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="U19" s="54">
-        <f>ROUND('Revenue Forecast'!U41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="V19" s="54">
-        <f>ROUND('Revenue Forecast'!V41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="W19" s="54">
-        <f>ROUND('Revenue Forecast'!W41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="X19" s="54">
-        <f>ROUND('Revenue Forecast'!X41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="Y19" s="54">
-        <f>ROUND('Revenue Forecast'!Y41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="Z19" s="54">
-        <f>ROUND('Revenue Forecast'!Z41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AA19" s="54">
-        <f>ROUND('Revenue Forecast'!AA41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AB19" s="54">
-        <f>ROUND('Revenue Forecast'!AB41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AC19" s="54">
-        <f>ROUND('Revenue Forecast'!AC41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AD19" s="54">
-        <f>ROUND('Revenue Forecast'!AD41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AE19" s="54">
-        <f>ROUND('Revenue Forecast'!AE41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AF19" s="54">
-        <f>ROUND('Revenue Forecast'!AF41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AG19" s="54">
-        <f>ROUND('Revenue Forecast'!AG41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AH19" s="54">
-        <f>ROUND('Revenue Forecast'!AH41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AI19" s="54">
-        <f>ROUND('Revenue Forecast'!AI41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AJ19" s="54">
-        <f>ROUND('Revenue Forecast'!AJ41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AK19" s="54">
-        <f>ROUND('Revenue Forecast'!AK41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AL19" s="54">
-        <f>ROUND('Revenue Forecast'!AL41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AM19" s="54">
-        <f>ROUND('Revenue Forecast'!AM41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AN19" s="54">
-        <f>ROUND('Revenue Forecast'!AN41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AO19" s="54">
-        <f>ROUND('Revenue Forecast'!AO41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AP19" s="54">
-        <f>ROUND('Revenue Forecast'!AP41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AQ19" s="54">
-        <f>ROUND('Revenue Forecast'!AQ41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AR19" s="54">
-        <f>ROUND('Revenue Forecast'!AR41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AS19" s="54">
-        <f>ROUND('Revenue Forecast'!AS41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AT19" s="54">
-        <f>ROUND('Revenue Forecast'!AT41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AU19" s="54">
-        <f>ROUND('Revenue Forecast'!AU41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AV19" s="54">
-        <f>ROUND('Revenue Forecast'!AV41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AW19" s="54">
-        <f>ROUND('Revenue Forecast'!AW41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AX19" s="54">
-        <f>ROUND('Revenue Forecast'!AX41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AY19" s="54">
-        <f>ROUND('Revenue Forecast'!AY41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="AZ19" s="54">
-        <f>ROUND('Revenue Forecast'!AZ41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BA19" s="54">
-        <f>ROUND('Revenue Forecast'!BA41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BB19" s="54">
-        <f>ROUND('Revenue Forecast'!BB41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BC19" s="54">
-        <f>ROUND('Revenue Forecast'!BC41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BD19" s="54">
-        <f>ROUND('Revenue Forecast'!BD41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BE19" s="54">
-        <f>ROUND('Revenue Forecast'!BE41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BF19" s="54">
-        <f>ROUND('Revenue Forecast'!BF41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BG19" s="54">
-        <f>ROUND('Revenue Forecast'!BG41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BH19" s="54">
-        <f>ROUND('Revenue Forecast'!BH41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BI19" s="54">
-        <f>ROUND('Revenue Forecast'!BI41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BJ19" s="54">
-        <f>ROUND('Revenue Forecast'!BJ41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BK19" s="54">
-        <f>ROUND('Revenue Forecast'!BK41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BL19" s="54">
-        <f>ROUND('Revenue Forecast'!BL41*Assumptions!$F$45/Assumptions!$F$122,0)</f>
-        <v/>
-      </c>
-      <c r="BN19" s="55">
+      <c r="E19" s="38">
+        <f>SUM(E12:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="38">
+        <f>SUM(F12:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="38">
+        <f>SUM(G12:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="38">
+        <f>SUM(H12:H18)</f>
+        <v/>
+      </c>
+      <c r="I19" s="38">
+        <f>SUM(I12:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="38">
+        <f>SUM(J12:J18)</f>
+        <v/>
+      </c>
+      <c r="K19" s="38">
+        <f>SUM(K12:K18)</f>
+        <v/>
+      </c>
+      <c r="L19" s="38">
+        <f>SUM(L12:L18)</f>
+        <v/>
+      </c>
+      <c r="M19" s="38">
+        <f>SUM(M12:M18)</f>
+        <v/>
+      </c>
+      <c r="N19" s="38">
+        <f>SUM(N12:N18)</f>
+        <v/>
+      </c>
+      <c r="O19" s="38">
+        <f>SUM(O12:O18)</f>
+        <v/>
+      </c>
+      <c r="P19" s="38">
+        <f>SUM(P12:P18)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="38">
+        <f>SUM(Q12:Q18)</f>
+        <v/>
+      </c>
+      <c r="R19" s="38">
+        <f>SUM(R12:R18)</f>
+        <v/>
+      </c>
+      <c r="S19" s="38">
+        <f>SUM(S12:S18)</f>
+        <v/>
+      </c>
+      <c r="T19" s="38">
+        <f>SUM(T12:T18)</f>
+        <v/>
+      </c>
+      <c r="U19" s="38">
+        <f>SUM(U12:U18)</f>
+        <v/>
+      </c>
+      <c r="V19" s="38">
+        <f>SUM(V12:V18)</f>
+        <v/>
+      </c>
+      <c r="W19" s="38">
+        <f>SUM(W12:W18)</f>
+        <v/>
+      </c>
+      <c r="X19" s="38">
+        <f>SUM(X12:X18)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="38">
+        <f>SUM(Y12:Y18)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="38">
+        <f>SUM(Z12:Z18)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="38">
+        <f>SUM(AA12:AA18)</f>
+        <v/>
+      </c>
+      <c r="AB19" s="38">
+        <f>SUM(AB12:AB18)</f>
+        <v/>
+      </c>
+      <c r="AC19" s="38">
+        <f>SUM(AC12:AC18)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="38">
+        <f>SUM(AD12:AD18)</f>
+        <v/>
+      </c>
+      <c r="AE19" s="38">
+        <f>SUM(AE12:AE18)</f>
+        <v/>
+      </c>
+      <c r="AF19" s="38">
+        <f>SUM(AF12:AF18)</f>
+        <v/>
+      </c>
+      <c r="AG19" s="38">
+        <f>SUM(AG12:AG18)</f>
+        <v/>
+      </c>
+      <c r="AH19" s="38">
+        <f>SUM(AH12:AH18)</f>
+        <v/>
+      </c>
+      <c r="AI19" s="38">
+        <f>SUM(AI12:AI18)</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="38">
+        <f>SUM(AJ12:AJ18)</f>
+        <v/>
+      </c>
+      <c r="AK19" s="38">
+        <f>SUM(AK12:AK18)</f>
+        <v/>
+      </c>
+      <c r="AL19" s="38">
+        <f>SUM(AL12:AL18)</f>
+        <v/>
+      </c>
+      <c r="AM19" s="38">
+        <f>SUM(AM12:AM18)</f>
+        <v/>
+      </c>
+      <c r="AN19" s="38">
+        <f>SUM(AN12:AN18)</f>
+        <v/>
+      </c>
+      <c r="AO19" s="38">
+        <f>SUM(AO12:AO18)</f>
+        <v/>
+      </c>
+      <c r="AP19" s="38">
+        <f>SUM(AP12:AP18)</f>
+        <v/>
+      </c>
+      <c r="AQ19" s="38">
+        <f>SUM(AQ12:AQ18)</f>
+        <v/>
+      </c>
+      <c r="AR19" s="38">
+        <f>SUM(AR12:AR18)</f>
+        <v/>
+      </c>
+      <c r="AS19" s="38">
+        <f>SUM(AS12:AS18)</f>
+        <v/>
+      </c>
+      <c r="AT19" s="38">
+        <f>SUM(AT12:AT18)</f>
+        <v/>
+      </c>
+      <c r="AU19" s="38">
+        <f>SUM(AU12:AU18)</f>
+        <v/>
+      </c>
+      <c r="AV19" s="38">
+        <f>SUM(AV12:AV18)</f>
+        <v/>
+      </c>
+      <c r="AW19" s="38">
+        <f>SUM(AW12:AW18)</f>
+        <v/>
+      </c>
+      <c r="AX19" s="38">
+        <f>SUM(AX12:AX18)</f>
+        <v/>
+      </c>
+      <c r="AY19" s="38">
+        <f>SUM(AY12:AY18)</f>
+        <v/>
+      </c>
+      <c r="AZ19" s="38">
+        <f>SUM(AZ12:AZ18)</f>
+        <v/>
+      </c>
+      <c r="BA19" s="38">
+        <f>SUM(BA12:BA18)</f>
+        <v/>
+      </c>
+      <c r="BB19" s="38">
+        <f>SUM(BB12:BB18)</f>
+        <v/>
+      </c>
+      <c r="BC19" s="38">
+        <f>SUM(BC12:BC18)</f>
+        <v/>
+      </c>
+      <c r="BD19" s="38">
+        <f>SUM(BD12:BD18)</f>
+        <v/>
+      </c>
+      <c r="BE19" s="38">
+        <f>SUM(BE12:BE18)</f>
+        <v/>
+      </c>
+      <c r="BF19" s="38">
+        <f>SUM(BF12:BF18)</f>
+        <v/>
+      </c>
+      <c r="BG19" s="38">
+        <f>SUM(BG12:BG18)</f>
+        <v/>
+      </c>
+      <c r="BH19" s="38">
+        <f>SUM(BH12:BH18)</f>
+        <v/>
+      </c>
+      <c r="BI19" s="38">
+        <f>SUM(BI12:BI18)</f>
+        <v/>
+      </c>
+      <c r="BJ19" s="38">
+        <f>SUM(BJ12:BJ18)</f>
+        <v/>
+      </c>
+      <c r="BK19" s="38">
+        <f>SUM(BK12:BK18)</f>
+        <v/>
+      </c>
+      <c r="BL19" s="38">
+        <f>SUM(BL12:BL18)</f>
+        <v/>
+      </c>
+      <c r="BN19" s="38">
         <f>P19</f>
         <v/>
       </c>
-      <c r="BO19" s="55">
+      <c r="BO19" s="38">
         <f>AB19</f>
         <v/>
       </c>
-      <c r="BP19" s="55">
+      <c r="BP19" s="38">
         <f>AN19</f>
         <v/>
       </c>
-      <c r="BQ19" s="55">
+      <c r="BQ19" s="38">
         <f>AZ19</f>
         <v/>
       </c>
-      <c r="BR19" s="55">
+      <c r="BR19" s="38">
         <f>BL19</f>
         <v/>
-      </c>
-      <c r="BT19" s="20" t="inlineStr">
-        <is>
-          <t>salaried staff: boilers on a service contract divided by the boilers one engineer can look after</t>
-        </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="50" t="inlineStr">
-        <is>
-          <t>Operations, support and administration</t>
-        </is>
-      </c>
-      <c r="C20" s="51" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>Total headcount</t>
+        </is>
+      </c>
+      <c r="C20" s="45" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
       </c>
-      <c r="E20" s="38">
-        <f>SUM(E12:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="38">
-        <f>SUM(F12:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="38">
-        <f>SUM(G12:G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="38">
-        <f>SUM(H12:H19)</f>
-        <v/>
-      </c>
-      <c r="I20" s="38">
-        <f>SUM(I12:I19)</f>
-        <v/>
-      </c>
-      <c r="J20" s="38">
-        <f>SUM(J12:J19)</f>
-        <v/>
-      </c>
-      <c r="K20" s="38">
-        <f>SUM(K12:K19)</f>
-        <v/>
-      </c>
-      <c r="L20" s="38">
-        <f>SUM(L12:L19)</f>
-        <v/>
-      </c>
-      <c r="M20" s="38">
-        <f>SUM(M12:M19)</f>
-        <v/>
-      </c>
-      <c r="N20" s="38">
-        <f>SUM(N12:N19)</f>
-        <v/>
-      </c>
-      <c r="O20" s="38">
-        <f>SUM(O12:O19)</f>
-        <v/>
-      </c>
-      <c r="P20" s="38">
-        <f>SUM(P12:P19)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="38">
-        <f>SUM(Q12:Q19)</f>
-        <v/>
-      </c>
-      <c r="R20" s="38">
-        <f>SUM(R12:R19)</f>
-        <v/>
-      </c>
-      <c r="S20" s="38">
-        <f>SUM(S12:S19)</f>
-        <v/>
-      </c>
-      <c r="T20" s="38">
-        <f>SUM(T12:T19)</f>
-        <v/>
-      </c>
-      <c r="U20" s="38">
-        <f>SUM(U12:U19)</f>
-        <v/>
-      </c>
-      <c r="V20" s="38">
-        <f>SUM(V12:V19)</f>
-        <v/>
-      </c>
-      <c r="W20" s="38">
-        <f>SUM(W12:W19)</f>
-        <v/>
-      </c>
-      <c r="X20" s="38">
-        <f>SUM(X12:X19)</f>
-        <v/>
-      </c>
-      <c r="Y20" s="38">
-        <f>SUM(Y12:Y19)</f>
-        <v/>
-      </c>
-      <c r="Z20" s="38">
-        <f>SUM(Z12:Z19)</f>
-        <v/>
-      </c>
-      <c r="AA20" s="38">
-        <f>SUM(AA12:AA19)</f>
-        <v/>
-      </c>
-      <c r="AB20" s="38">
-        <f>SUM(AB12:AB19)</f>
-        <v/>
-      </c>
-      <c r="AC20" s="38">
-        <f>SUM(AC12:AC19)</f>
-        <v/>
-      </c>
-      <c r="AD20" s="38">
-        <f>SUM(AD12:AD19)</f>
-        <v/>
-      </c>
-      <c r="AE20" s="38">
-        <f>SUM(AE12:AE19)</f>
-        <v/>
-      </c>
-      <c r="AF20" s="38">
-        <f>SUM(AF12:AF19)</f>
-        <v/>
-      </c>
-      <c r="AG20" s="38">
-        <f>SUM(AG12:AG19)</f>
-        <v/>
-      </c>
-      <c r="AH20" s="38">
-        <f>SUM(AH12:AH19)</f>
-        <v/>
-      </c>
-      <c r="AI20" s="38">
-        <f>SUM(AI12:AI19)</f>
-        <v/>
-      </c>
-      <c r="AJ20" s="38">
-        <f>SUM(AJ12:AJ19)</f>
-        <v/>
-      </c>
-      <c r="AK20" s="38">
-        <f>SUM(AK12:AK19)</f>
-        <v/>
-      </c>
-      <c r="AL20" s="38">
-        <f>SUM(AL12:AL19)</f>
-        <v/>
-      </c>
-      <c r="AM20" s="38">
-        <f>SUM(AM12:AM19)</f>
-        <v/>
-      </c>
-      <c r="AN20" s="38">
-        <f>SUM(AN12:AN19)</f>
-        <v/>
-      </c>
-      <c r="AO20" s="38">
-        <f>SUM(AO12:AO19)</f>
-        <v/>
-      </c>
-      <c r="AP20" s="38">
-        <f>SUM(AP12:AP19)</f>
-        <v/>
-      </c>
-      <c r="AQ20" s="38">
-        <f>SUM(AQ12:AQ19)</f>
-        <v/>
-      </c>
-      <c r="AR20" s="38">
-        <f>SUM(AR12:AR19)</f>
-        <v/>
-      </c>
-      <c r="AS20" s="38">
-        <f>SUM(AS12:AS19)</f>
-        <v/>
-      </c>
-      <c r="AT20" s="38">
-        <f>SUM(AT12:AT19)</f>
-        <v/>
-      </c>
-      <c r="AU20" s="38">
-        <f>SUM(AU12:AU19)</f>
-        <v/>
-      </c>
-      <c r="AV20" s="38">
-        <f>SUM(AV12:AV19)</f>
-        <v/>
-      </c>
-      <c r="AW20" s="38">
-        <f>SUM(AW12:AW19)</f>
-        <v/>
-      </c>
-      <c r="AX20" s="38">
-        <f>SUM(AX12:AX19)</f>
-        <v/>
-      </c>
-      <c r="AY20" s="38">
-        <f>SUM(AY12:AY19)</f>
-        <v/>
-      </c>
-      <c r="AZ20" s="38">
-        <f>SUM(AZ12:AZ19)</f>
-        <v/>
-      </c>
-      <c r="BA20" s="38">
-        <f>SUM(BA12:BA19)</f>
-        <v/>
-      </c>
-      <c r="BB20" s="38">
-        <f>SUM(BB12:BB19)</f>
-        <v/>
-      </c>
-      <c r="BC20" s="38">
-        <f>SUM(BC12:BC19)</f>
-        <v/>
-      </c>
-      <c r="BD20" s="38">
-        <f>SUM(BD12:BD19)</f>
-        <v/>
-      </c>
-      <c r="BE20" s="38">
-        <f>SUM(BE12:BE19)</f>
-        <v/>
-      </c>
-      <c r="BF20" s="38">
-        <f>SUM(BF12:BF19)</f>
-        <v/>
-      </c>
-      <c r="BG20" s="38">
-        <f>SUM(BG12:BG19)</f>
-        <v/>
-      </c>
-      <c r="BH20" s="38">
-        <f>SUM(BH12:BH19)</f>
-        <v/>
-      </c>
-      <c r="BI20" s="38">
-        <f>SUM(BI12:BI19)</f>
-        <v/>
-      </c>
-      <c r="BJ20" s="38">
-        <f>SUM(BJ12:BJ19)</f>
-        <v/>
-      </c>
-      <c r="BK20" s="38">
-        <f>SUM(BK12:BK19)</f>
-        <v/>
-      </c>
-      <c r="BL20" s="38">
-        <f>SUM(BL12:BL19)</f>
-        <v/>
-      </c>
-      <c r="BN20" s="38">
+      <c r="D20" s="1" t="n"/>
+      <c r="E20" s="69">
+        <f>E11+E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="69">
+        <f>F11+F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="69">
+        <f>G11+G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="69">
+        <f>H11+H19</f>
+        <v/>
+      </c>
+      <c r="I20" s="69">
+        <f>I11+I19</f>
+        <v/>
+      </c>
+      <c r="J20" s="69">
+        <f>J11+J19</f>
+        <v/>
+      </c>
+      <c r="K20" s="69">
+        <f>K11+K19</f>
+        <v/>
+      </c>
+      <c r="L20" s="69">
+        <f>L11+L19</f>
+        <v/>
+      </c>
+      <c r="M20" s="69">
+        <f>M11+M19</f>
+        <v/>
+      </c>
+      <c r="N20" s="69">
+        <f>N11+N19</f>
+        <v/>
+      </c>
+      <c r="O20" s="69">
+        <f>O11+O19</f>
+        <v/>
+      </c>
+      <c r="P20" s="69">
+        <f>P11+P19</f>
+        <v/>
+      </c>
+      <c r="Q20" s="69">
+        <f>Q11+Q19</f>
+        <v/>
+      </c>
+      <c r="R20" s="69">
+        <f>R11+R19</f>
+        <v/>
+      </c>
+      <c r="S20" s="69">
+        <f>S11+S19</f>
+        <v/>
+      </c>
+      <c r="T20" s="69">
+        <f>T11+T19</f>
+        <v/>
+      </c>
+      <c r="U20" s="69">
+        <f>U11+U19</f>
+        <v/>
+      </c>
+      <c r="V20" s="69">
+        <f>V11+V19</f>
+        <v/>
+      </c>
+      <c r="W20" s="69">
+        <f>W11+W19</f>
+        <v/>
+      </c>
+      <c r="X20" s="69">
+        <f>X11+X19</f>
+        <v/>
+      </c>
+      <c r="Y20" s="69">
+        <f>Y11+Y19</f>
+        <v/>
+      </c>
+      <c r="Z20" s="69">
+        <f>Z11+Z19</f>
+        <v/>
+      </c>
+      <c r="AA20" s="69">
+        <f>AA11+AA19</f>
+        <v/>
+      </c>
+      <c r="AB20" s="69">
+        <f>AB11+AB19</f>
+        <v/>
+      </c>
+      <c r="AC20" s="69">
+        <f>AC11+AC19</f>
+        <v/>
+      </c>
+      <c r="AD20" s="69">
+        <f>AD11+AD19</f>
+        <v/>
+      </c>
+      <c r="AE20" s="69">
+        <f>AE11+AE19</f>
+        <v/>
+      </c>
+      <c r="AF20" s="69">
+        <f>AF11+AF19</f>
+        <v/>
+      </c>
+      <c r="AG20" s="69">
+        <f>AG11+AG19</f>
+        <v/>
+      </c>
+      <c r="AH20" s="69">
+        <f>AH11+AH19</f>
+        <v/>
+      </c>
+      <c r="AI20" s="69">
+        <f>AI11+AI19</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="69">
+        <f>AJ11+AJ19</f>
+        <v/>
+      </c>
+      <c r="AK20" s="69">
+        <f>AK11+AK19</f>
+        <v/>
+      </c>
+      <c r="AL20" s="69">
+        <f>AL11+AL19</f>
+        <v/>
+      </c>
+      <c r="AM20" s="69">
+        <f>AM11+AM19</f>
+        <v/>
+      </c>
+      <c r="AN20" s="69">
+        <f>AN11+AN19</f>
+        <v/>
+      </c>
+      <c r="AO20" s="69">
+        <f>AO11+AO19</f>
+        <v/>
+      </c>
+      <c r="AP20" s="69">
+        <f>AP11+AP19</f>
+        <v/>
+      </c>
+      <c r="AQ20" s="69">
+        <f>AQ11+AQ19</f>
+        <v/>
+      </c>
+      <c r="AR20" s="69">
+        <f>AR11+AR19</f>
+        <v/>
+      </c>
+      <c r="AS20" s="69">
+        <f>AS11+AS19</f>
+        <v/>
+      </c>
+      <c r="AT20" s="69">
+        <f>AT11+AT19</f>
+        <v/>
+      </c>
+      <c r="AU20" s="69">
+        <f>AU11+AU19</f>
+        <v/>
+      </c>
+      <c r="AV20" s="69">
+        <f>AV11+AV19</f>
+        <v/>
+      </c>
+      <c r="AW20" s="69">
+        <f>AW11+AW19</f>
+        <v/>
+      </c>
+      <c r="AX20" s="69">
+        <f>AX11+AX19</f>
+        <v/>
+      </c>
+      <c r="AY20" s="69">
+        <f>AY11+AY19</f>
+        <v/>
+      </c>
+      <c r="AZ20" s="69">
+        <f>AZ11+AZ19</f>
+        <v/>
+      </c>
+      <c r="BA20" s="69">
+        <f>BA11+BA19</f>
+        <v/>
+      </c>
+      <c r="BB20" s="69">
+        <f>BB11+BB19</f>
+        <v/>
+      </c>
+      <c r="BC20" s="69">
+        <f>BC11+BC19</f>
+        <v/>
+      </c>
+      <c r="BD20" s="69">
+        <f>BD11+BD19</f>
+        <v/>
+      </c>
+      <c r="BE20" s="69">
+        <f>BE11+BE19</f>
+        <v/>
+      </c>
+      <c r="BF20" s="69">
+        <f>BF11+BF19</f>
+        <v/>
+      </c>
+      <c r="BG20" s="69">
+        <f>BG11+BG19</f>
+        <v/>
+      </c>
+      <c r="BH20" s="69">
+        <f>BH11+BH19</f>
+        <v/>
+      </c>
+      <c r="BI20" s="69">
+        <f>BI11+BI19</f>
+        <v/>
+      </c>
+      <c r="BJ20" s="69">
+        <f>BJ11+BJ19</f>
+        <v/>
+      </c>
+      <c r="BK20" s="69">
+        <f>BK11+BK19</f>
+        <v/>
+      </c>
+      <c r="BL20" s="69">
+        <f>BL11+BL19</f>
+        <v/>
+      </c>
+      <c r="BM20" s="1" t="n"/>
+      <c r="BN20" s="69">
         <f>P20</f>
         <v/>
       </c>
-      <c r="BO20" s="38">
+      <c r="BO20" s="69">
         <f>AB20</f>
         <v/>
       </c>
-      <c r="BP20" s="38">
+      <c r="BP20" s="69">
         <f>AN20</f>
         <v/>
       </c>
-      <c r="BQ20" s="38">
+      <c r="BQ20" s="69">
         <f>AZ20</f>
         <v/>
       </c>
-      <c r="BR20" s="38">
+      <c r="BR20" s="69">
         <f>BL20</f>
         <v/>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t>Total headcount</t>
-        </is>
-      </c>
-      <c r="C21" s="45" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n"/>
-      <c r="E21" s="69">
-        <f>E11+E20</f>
-        <v/>
-      </c>
-      <c r="F21" s="69">
-        <f>F11+F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="69">
-        <f>G11+G20</f>
-        <v/>
-      </c>
-      <c r="H21" s="69">
-        <f>H11+H20</f>
-        <v/>
-      </c>
-      <c r="I21" s="69">
-        <f>I11+I20</f>
-        <v/>
-      </c>
-      <c r="J21" s="69">
-        <f>J11+J20</f>
-        <v/>
-      </c>
-      <c r="K21" s="69">
-        <f>K11+K20</f>
-        <v/>
-      </c>
-      <c r="L21" s="69">
-        <f>L11+L20</f>
-        <v/>
-      </c>
-      <c r="M21" s="69">
-        <f>M11+M20</f>
-        <v/>
-      </c>
-      <c r="N21" s="69">
-        <f>N11+N20</f>
-        <v/>
-      </c>
-      <c r="O21" s="69">
-        <f>O11+O20</f>
-        <v/>
-      </c>
-      <c r="P21" s="69">
-        <f>P11+P20</f>
-        <v/>
-      </c>
-      <c r="Q21" s="69">
-        <f>Q11+Q20</f>
-        <v/>
-      </c>
-      <c r="R21" s="69">
-        <f>R11+R20</f>
-        <v/>
-      </c>
-      <c r="S21" s="69">
-        <f>S11+S20</f>
-        <v/>
-      </c>
-      <c r="T21" s="69">
-        <f>T11+T20</f>
-        <v/>
-      </c>
-      <c r="U21" s="69">
-        <f>U11+U20</f>
-        <v/>
-      </c>
-      <c r="V21" s="69">
-        <f>V11+V20</f>
-        <v/>
-      </c>
-      <c r="W21" s="69">
-        <f>W11+W20</f>
-        <v/>
-      </c>
-      <c r="X21" s="69">
-        <f>X11+X20</f>
-        <v/>
-      </c>
-      <c r="Y21" s="69">
-        <f>Y11+Y20</f>
-        <v/>
-      </c>
-      <c r="Z21" s="69">
-        <f>Z11+Z20</f>
-        <v/>
-      </c>
-      <c r="AA21" s="69">
-        <f>AA11+AA20</f>
-        <v/>
-      </c>
-      <c r="AB21" s="69">
-        <f>AB11+AB20</f>
-        <v/>
-      </c>
-      <c r="AC21" s="69">
-        <f>AC11+AC20</f>
-        <v/>
-      </c>
-      <c r="AD21" s="69">
-        <f>AD11+AD20</f>
-        <v/>
-      </c>
-      <c r="AE21" s="69">
-        <f>AE11+AE20</f>
-        <v/>
-      </c>
-      <c r="AF21" s="69">
-        <f>AF11+AF20</f>
-        <v/>
-      </c>
-      <c r="AG21" s="69">
-        <f>AG11+AG20</f>
-        <v/>
-      </c>
-      <c r="AH21" s="69">
-        <f>AH11+AH20</f>
-        <v/>
-      </c>
-      <c r="AI21" s="69">
-        <f>AI11+AI20</f>
-        <v/>
-      </c>
-      <c r="AJ21" s="69">
-        <f>AJ11+AJ20</f>
-        <v/>
-      </c>
-      <c r="AK21" s="69">
-        <f>AK11+AK20</f>
-        <v/>
-      </c>
-      <c r="AL21" s="69">
-        <f>AL11+AL20</f>
-        <v/>
-      </c>
-      <c r="AM21" s="69">
-        <f>AM11+AM20</f>
-        <v/>
-      </c>
-      <c r="AN21" s="69">
-        <f>AN11+AN20</f>
-        <v/>
-      </c>
-      <c r="AO21" s="69">
-        <f>AO11+AO20</f>
-        <v/>
-      </c>
-      <c r="AP21" s="69">
-        <f>AP11+AP20</f>
-        <v/>
-      </c>
-      <c r="AQ21" s="69">
-        <f>AQ11+AQ20</f>
-        <v/>
-      </c>
-      <c r="AR21" s="69">
-        <f>AR11+AR20</f>
-        <v/>
-      </c>
-      <c r="AS21" s="69">
-        <f>AS11+AS20</f>
-        <v/>
-      </c>
-      <c r="AT21" s="69">
-        <f>AT11+AT20</f>
-        <v/>
-      </c>
-      <c r="AU21" s="69">
-        <f>AU11+AU20</f>
-        <v/>
-      </c>
-      <c r="AV21" s="69">
-        <f>AV11+AV20</f>
-        <v/>
-      </c>
-      <c r="AW21" s="69">
-        <f>AW11+AW20</f>
-        <v/>
-      </c>
-      <c r="AX21" s="69">
-        <f>AX11+AX20</f>
-        <v/>
-      </c>
-      <c r="AY21" s="69">
-        <f>AY11+AY20</f>
-        <v/>
-      </c>
-      <c r="AZ21" s="69">
-        <f>AZ11+AZ20</f>
-        <v/>
-      </c>
-      <c r="BA21" s="69">
-        <f>BA11+BA20</f>
-        <v/>
-      </c>
-      <c r="BB21" s="69">
-        <f>BB11+BB20</f>
-        <v/>
-      </c>
-      <c r="BC21" s="69">
-        <f>BC11+BC20</f>
-        <v/>
-      </c>
-      <c r="BD21" s="69">
-        <f>BD11+BD20</f>
-        <v/>
-      </c>
-      <c r="BE21" s="69">
-        <f>BE11+BE20</f>
-        <v/>
-      </c>
-      <c r="BF21" s="69">
-        <f>BF11+BF20</f>
-        <v/>
-      </c>
-      <c r="BG21" s="69">
-        <f>BG11+BG20</f>
-        <v/>
-      </c>
-      <c r="BH21" s="69">
-        <f>BH11+BH20</f>
-        <v/>
-      </c>
-      <c r="BI21" s="69">
-        <f>BI11+BI20</f>
-        <v/>
-      </c>
-      <c r="BJ21" s="69">
-        <f>BJ11+BJ20</f>
-        <v/>
-      </c>
-      <c r="BK21" s="69">
-        <f>BK11+BK20</f>
-        <v/>
-      </c>
-      <c r="BL21" s="69">
-        <f>BL11+BL20</f>
-        <v/>
-      </c>
-      <c r="BM21" s="1" t="n"/>
-      <c r="BN21" s="69">
-        <f>P21</f>
-        <v/>
-      </c>
-      <c r="BO21" s="69">
-        <f>AB21</f>
-        <v/>
-      </c>
-      <c r="BP21" s="69">
-        <f>AN21</f>
-        <v/>
-      </c>
-      <c r="BQ21" s="69">
-        <f>AZ21</f>
-        <v/>
-      </c>
-      <c r="BR21" s="69">
-        <f>BL21</f>
-        <v/>
-      </c>
-      <c r="BS21" s="1" t="n"/>
+      <c r="BS20" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="39" t="inlineStr">
@@ -45502,243 +45130,243 @@
         </is>
       </c>
       <c r="E26" s="43">
-        <f>E17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
+        <f>E16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F26" s="43">
-        <f>F17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
+        <f>F16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G26" s="43">
-        <f>G17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
+        <f>G16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H26" s="43">
-        <f>H17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
+        <f>H16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I26" s="43">
-        <f>I17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
+        <f>I16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J26" s="43">
-        <f>J17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
+        <f>J16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K26" s="43">
-        <f>K17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
+        <f>K16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L26" s="43">
-        <f>L17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
+        <f>L16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M26" s="43">
-        <f>M17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
+        <f>M16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N26" s="43">
-        <f>N17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
+        <f>N16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O26" s="43">
-        <f>O17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
+        <f>O16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P26" s="43">
-        <f>P17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
+        <f>P16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q26" s="43">
-        <f>Q17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
+        <f>Q16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R26" s="43">
-        <f>R17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
+        <f>R16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S26" s="43">
-        <f>S17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
+        <f>S16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T26" s="43">
-        <f>T17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
+        <f>T16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U26" s="43">
-        <f>U17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
+        <f>U16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V26" s="43">
-        <f>V17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
+        <f>V16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W26" s="43">
-        <f>W17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
+        <f>W16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X26" s="43">
-        <f>X17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
+        <f>X16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y26" s="43">
-        <f>Y17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
+        <f>Y16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z26" s="43">
-        <f>Z17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
+        <f>Z16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA26" s="43">
-        <f>AA17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
+        <f>AA16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB26" s="43">
-        <f>AB17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
+        <f>AB16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC26" s="43">
-        <f>AC17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
+        <f>AC16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD26" s="43">
-        <f>AD17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
+        <f>AD16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE26" s="43">
-        <f>AE17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
+        <f>AE16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF26" s="43">
-        <f>AF17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
+        <f>AF16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG26" s="43">
-        <f>AG17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
+        <f>AG16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH26" s="43">
-        <f>AH17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
+        <f>AH16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI26" s="43">
-        <f>AI17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
+        <f>AI16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ26" s="43">
-        <f>AJ17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
+        <f>AJ16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK26" s="43">
-        <f>AK17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
+        <f>AK16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL26" s="43">
-        <f>AL17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
+        <f>AL16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM26" s="43">
-        <f>AM17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
+        <f>AM16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN26" s="43">
-        <f>AN17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
+        <f>AN16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO26" s="43">
-        <f>AO17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
+        <f>AO16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP26" s="43">
-        <f>AP17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
+        <f>AP16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ26" s="43">
-        <f>AQ17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
+        <f>AQ16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR26" s="43">
-        <f>AR17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
+        <f>AR16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS26" s="43">
-        <f>AS17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
+        <f>AS16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT26" s="43">
-        <f>AT17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
+        <f>AT16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU26" s="43">
-        <f>AU17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
+        <f>AU16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV26" s="43">
-        <f>AV17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
+        <f>AV16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW26" s="43">
-        <f>AW17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
+        <f>AW16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX26" s="43">
-        <f>AX17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
+        <f>AX16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY26" s="43">
-        <f>AY17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
+        <f>AY16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ26" s="43">
-        <f>AZ17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
+        <f>AZ16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA26" s="43">
-        <f>BA17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
+        <f>BA16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB26" s="43">
-        <f>BB17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
+        <f>BB16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC26" s="43">
-        <f>BC17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
+        <f>BC16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD26" s="43">
-        <f>BD17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
+        <f>BD16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE26" s="43">
-        <f>BE17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
+        <f>BE16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF26" s="43">
-        <f>BF17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
+        <f>BF16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG26" s="43">
-        <f>BG17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
+        <f>BG16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH26" s="43">
-        <f>BH17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
+        <f>BH16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI26" s="43">
-        <f>BI17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
+        <f>BI16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ26" s="43">
-        <f>BJ17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
+        <f>BJ16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK26" s="43">
-        <f>BK17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
+        <f>BK16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL26" s="43">
-        <f>BL17*Assumptions!$F$131*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
+        <f>BL16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN26" s="44">
@@ -45774,243 +45402,243 @@
         </is>
       </c>
       <c r="E27" s="43">
-        <f>(E6*Assumptions!$F$125+E7*Assumptions!$F$126+(E8+E9+E10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
+        <f>(E6*Assumptions!$F$121+E7*Assumptions!$F$122+(E8+E9+E10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F27" s="43">
-        <f>(F6*Assumptions!$F$125+F7*Assumptions!$F$126+(F8+F9+F10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
+        <f>(F6*Assumptions!$F$121+F7*Assumptions!$F$122+(F8+F9+F10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G27" s="43">
-        <f>(G6*Assumptions!$F$125+G7*Assumptions!$F$126+(G8+G9+G10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
+        <f>(G6*Assumptions!$F$121+G7*Assumptions!$F$122+(G8+G9+G10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H27" s="43">
-        <f>(H6*Assumptions!$F$125+H7*Assumptions!$F$126+(H8+H9+H10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
+        <f>(H6*Assumptions!$F$121+H7*Assumptions!$F$122+(H8+H9+H10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I27" s="43">
-        <f>(I6*Assumptions!$F$125+I7*Assumptions!$F$126+(I8+I9+I10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
+        <f>(I6*Assumptions!$F$121+I7*Assumptions!$F$122+(I8+I9+I10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J27" s="43">
-        <f>(J6*Assumptions!$F$125+J7*Assumptions!$F$126+(J8+J9+J10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
+        <f>(J6*Assumptions!$F$121+J7*Assumptions!$F$122+(J8+J9+J10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K27" s="43">
-        <f>(K6*Assumptions!$F$125+K7*Assumptions!$F$126+(K8+K9+K10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
+        <f>(K6*Assumptions!$F$121+K7*Assumptions!$F$122+(K8+K9+K10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L27" s="43">
-        <f>(L6*Assumptions!$F$125+L7*Assumptions!$F$126+(L8+L9+L10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
+        <f>(L6*Assumptions!$F$121+L7*Assumptions!$F$122+(L8+L9+L10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M27" s="43">
-        <f>(M6*Assumptions!$F$125+M7*Assumptions!$F$126+(M8+M9+M10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
+        <f>(M6*Assumptions!$F$121+M7*Assumptions!$F$122+(M8+M9+M10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N27" s="43">
-        <f>(N6*Assumptions!$F$125+N7*Assumptions!$F$126+(N8+N9+N10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
+        <f>(N6*Assumptions!$F$121+N7*Assumptions!$F$122+(N8+N9+N10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O27" s="43">
-        <f>(O6*Assumptions!$F$125+O7*Assumptions!$F$126+(O8+O9+O10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
+        <f>(O6*Assumptions!$F$121+O7*Assumptions!$F$122+(O8+O9+O10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P27" s="43">
-        <f>(P6*Assumptions!$F$125+P7*Assumptions!$F$126+(P8+P9+P10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
+        <f>(P6*Assumptions!$F$121+P7*Assumptions!$F$122+(P8+P9+P10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q27" s="43">
-        <f>(Q6*Assumptions!$F$125+Q7*Assumptions!$F$126+(Q8+Q9+Q10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
+        <f>(Q6*Assumptions!$F$121+Q7*Assumptions!$F$122+(Q8+Q9+Q10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R27" s="43">
-        <f>(R6*Assumptions!$F$125+R7*Assumptions!$F$126+(R8+R9+R10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
+        <f>(R6*Assumptions!$F$121+R7*Assumptions!$F$122+(R8+R9+R10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S27" s="43">
-        <f>(S6*Assumptions!$F$125+S7*Assumptions!$F$126+(S8+S9+S10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
+        <f>(S6*Assumptions!$F$121+S7*Assumptions!$F$122+(S8+S9+S10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T27" s="43">
-        <f>(T6*Assumptions!$F$125+T7*Assumptions!$F$126+(T8+T9+T10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
+        <f>(T6*Assumptions!$F$121+T7*Assumptions!$F$122+(T8+T9+T10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U27" s="43">
-        <f>(U6*Assumptions!$F$125+U7*Assumptions!$F$126+(U8+U9+U10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
+        <f>(U6*Assumptions!$F$121+U7*Assumptions!$F$122+(U8+U9+U10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V27" s="43">
-        <f>(V6*Assumptions!$F$125+V7*Assumptions!$F$126+(V8+V9+V10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
+        <f>(V6*Assumptions!$F$121+V7*Assumptions!$F$122+(V8+V9+V10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W27" s="43">
-        <f>(W6*Assumptions!$F$125+W7*Assumptions!$F$126+(W8+W9+W10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
+        <f>(W6*Assumptions!$F$121+W7*Assumptions!$F$122+(W8+W9+W10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X27" s="43">
-        <f>(X6*Assumptions!$F$125+X7*Assumptions!$F$126+(X8+X9+X10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
+        <f>(X6*Assumptions!$F$121+X7*Assumptions!$F$122+(X8+X9+X10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y27" s="43">
-        <f>(Y6*Assumptions!$F$125+Y7*Assumptions!$F$126+(Y8+Y9+Y10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
+        <f>(Y6*Assumptions!$F$121+Y7*Assumptions!$F$122+(Y8+Y9+Y10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z27" s="43">
-        <f>(Z6*Assumptions!$F$125+Z7*Assumptions!$F$126+(Z8+Z9+Z10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
+        <f>(Z6*Assumptions!$F$121+Z7*Assumptions!$F$122+(Z8+Z9+Z10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA27" s="43">
-        <f>(AA6*Assumptions!$F$125+AA7*Assumptions!$F$126+(AA8+AA9+AA10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
+        <f>(AA6*Assumptions!$F$121+AA7*Assumptions!$F$122+(AA8+AA9+AA10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB27" s="43">
-        <f>(AB6*Assumptions!$F$125+AB7*Assumptions!$F$126+(AB8+AB9+AB10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
+        <f>(AB6*Assumptions!$F$121+AB7*Assumptions!$F$122+(AB8+AB9+AB10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC27" s="43">
-        <f>(AC6*Assumptions!$F$125+AC7*Assumptions!$F$126+(AC8+AC9+AC10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
+        <f>(AC6*Assumptions!$F$121+AC7*Assumptions!$F$122+(AC8+AC9+AC10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD27" s="43">
-        <f>(AD6*Assumptions!$F$125+AD7*Assumptions!$F$126+(AD8+AD9+AD10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
+        <f>(AD6*Assumptions!$F$121+AD7*Assumptions!$F$122+(AD8+AD9+AD10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE27" s="43">
-        <f>(AE6*Assumptions!$F$125+AE7*Assumptions!$F$126+(AE8+AE9+AE10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
+        <f>(AE6*Assumptions!$F$121+AE7*Assumptions!$F$122+(AE8+AE9+AE10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF27" s="43">
-        <f>(AF6*Assumptions!$F$125+AF7*Assumptions!$F$126+(AF8+AF9+AF10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
+        <f>(AF6*Assumptions!$F$121+AF7*Assumptions!$F$122+(AF8+AF9+AF10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG27" s="43">
-        <f>(AG6*Assumptions!$F$125+AG7*Assumptions!$F$126+(AG8+AG9+AG10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
+        <f>(AG6*Assumptions!$F$121+AG7*Assumptions!$F$122+(AG8+AG9+AG10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH27" s="43">
-        <f>(AH6*Assumptions!$F$125+AH7*Assumptions!$F$126+(AH8+AH9+AH10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
+        <f>(AH6*Assumptions!$F$121+AH7*Assumptions!$F$122+(AH8+AH9+AH10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI27" s="43">
-        <f>(AI6*Assumptions!$F$125+AI7*Assumptions!$F$126+(AI8+AI9+AI10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
+        <f>(AI6*Assumptions!$F$121+AI7*Assumptions!$F$122+(AI8+AI9+AI10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ27" s="43">
-        <f>(AJ6*Assumptions!$F$125+AJ7*Assumptions!$F$126+(AJ8+AJ9+AJ10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
+        <f>(AJ6*Assumptions!$F$121+AJ7*Assumptions!$F$122+(AJ8+AJ9+AJ10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK27" s="43">
-        <f>(AK6*Assumptions!$F$125+AK7*Assumptions!$F$126+(AK8+AK9+AK10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
+        <f>(AK6*Assumptions!$F$121+AK7*Assumptions!$F$122+(AK8+AK9+AK10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL27" s="43">
-        <f>(AL6*Assumptions!$F$125+AL7*Assumptions!$F$126+(AL8+AL9+AL10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
+        <f>(AL6*Assumptions!$F$121+AL7*Assumptions!$F$122+(AL8+AL9+AL10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM27" s="43">
-        <f>(AM6*Assumptions!$F$125+AM7*Assumptions!$F$126+(AM8+AM9+AM10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
+        <f>(AM6*Assumptions!$F$121+AM7*Assumptions!$F$122+(AM8+AM9+AM10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN27" s="43">
-        <f>(AN6*Assumptions!$F$125+AN7*Assumptions!$F$126+(AN8+AN9+AN10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
+        <f>(AN6*Assumptions!$F$121+AN7*Assumptions!$F$122+(AN8+AN9+AN10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO27" s="43">
-        <f>(AO6*Assumptions!$F$125+AO7*Assumptions!$F$126+(AO8+AO9+AO10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
+        <f>(AO6*Assumptions!$F$121+AO7*Assumptions!$F$122+(AO8+AO9+AO10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP27" s="43">
-        <f>(AP6*Assumptions!$F$125+AP7*Assumptions!$F$126+(AP8+AP9+AP10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
+        <f>(AP6*Assumptions!$F$121+AP7*Assumptions!$F$122+(AP8+AP9+AP10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ27" s="43">
-        <f>(AQ6*Assumptions!$F$125+AQ7*Assumptions!$F$126+(AQ8+AQ9+AQ10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
+        <f>(AQ6*Assumptions!$F$121+AQ7*Assumptions!$F$122+(AQ8+AQ9+AQ10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR27" s="43">
-        <f>(AR6*Assumptions!$F$125+AR7*Assumptions!$F$126+(AR8+AR9+AR10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
+        <f>(AR6*Assumptions!$F$121+AR7*Assumptions!$F$122+(AR8+AR9+AR10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS27" s="43">
-        <f>(AS6*Assumptions!$F$125+AS7*Assumptions!$F$126+(AS8+AS9+AS10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
+        <f>(AS6*Assumptions!$F$121+AS7*Assumptions!$F$122+(AS8+AS9+AS10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT27" s="43">
-        <f>(AT6*Assumptions!$F$125+AT7*Assumptions!$F$126+(AT8+AT9+AT10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
+        <f>(AT6*Assumptions!$F$121+AT7*Assumptions!$F$122+(AT8+AT9+AT10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU27" s="43">
-        <f>(AU6*Assumptions!$F$125+AU7*Assumptions!$F$126+(AU8+AU9+AU10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
+        <f>(AU6*Assumptions!$F$121+AU7*Assumptions!$F$122+(AU8+AU9+AU10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV27" s="43">
-        <f>(AV6*Assumptions!$F$125+AV7*Assumptions!$F$126+(AV8+AV9+AV10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
+        <f>(AV6*Assumptions!$F$121+AV7*Assumptions!$F$122+(AV8+AV9+AV10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW27" s="43">
-        <f>(AW6*Assumptions!$F$125+AW7*Assumptions!$F$126+(AW8+AW9+AW10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
+        <f>(AW6*Assumptions!$F$121+AW7*Assumptions!$F$122+(AW8+AW9+AW10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX27" s="43">
-        <f>(AX6*Assumptions!$F$125+AX7*Assumptions!$F$126+(AX8+AX9+AX10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
+        <f>(AX6*Assumptions!$F$121+AX7*Assumptions!$F$122+(AX8+AX9+AX10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY27" s="43">
-        <f>(AY6*Assumptions!$F$125+AY7*Assumptions!$F$126+(AY8+AY9+AY10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
+        <f>(AY6*Assumptions!$F$121+AY7*Assumptions!$F$122+(AY8+AY9+AY10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ27" s="43">
-        <f>(AZ6*Assumptions!$F$125+AZ7*Assumptions!$F$126+(AZ8+AZ9+AZ10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
+        <f>(AZ6*Assumptions!$F$121+AZ7*Assumptions!$F$122+(AZ8+AZ9+AZ10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA27" s="43">
-        <f>(BA6*Assumptions!$F$125+BA7*Assumptions!$F$126+(BA8+BA9+BA10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
+        <f>(BA6*Assumptions!$F$121+BA7*Assumptions!$F$122+(BA8+BA9+BA10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB27" s="43">
-        <f>(BB6*Assumptions!$F$125+BB7*Assumptions!$F$126+(BB8+BB9+BB10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
+        <f>(BB6*Assumptions!$F$121+BB7*Assumptions!$F$122+(BB8+BB9+BB10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC27" s="43">
-        <f>(BC6*Assumptions!$F$125+BC7*Assumptions!$F$126+(BC8+BC9+BC10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
+        <f>(BC6*Assumptions!$F$121+BC7*Assumptions!$F$122+(BC8+BC9+BC10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD27" s="43">
-        <f>(BD6*Assumptions!$F$125+BD7*Assumptions!$F$126+(BD8+BD9+BD10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
+        <f>(BD6*Assumptions!$F$121+BD7*Assumptions!$F$122+(BD8+BD9+BD10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE27" s="43">
-        <f>(BE6*Assumptions!$F$125+BE7*Assumptions!$F$126+(BE8+BE9+BE10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
+        <f>(BE6*Assumptions!$F$121+BE7*Assumptions!$F$122+(BE8+BE9+BE10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF27" s="43">
-        <f>(BF6*Assumptions!$F$125+BF7*Assumptions!$F$126+(BF8+BF9+BF10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
+        <f>(BF6*Assumptions!$F$121+BF7*Assumptions!$F$122+(BF8+BF9+BF10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG27" s="43">
-        <f>(BG6*Assumptions!$F$125+BG7*Assumptions!$F$126+(BG8+BG9+BG10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
+        <f>(BG6*Assumptions!$F$121+BG7*Assumptions!$F$122+(BG8+BG9+BG10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH27" s="43">
-        <f>(BH6*Assumptions!$F$125+BH7*Assumptions!$F$126+(BH8+BH9+BH10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
+        <f>(BH6*Assumptions!$F$121+BH7*Assumptions!$F$122+(BH8+BH9+BH10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI27" s="43">
-        <f>(BI6*Assumptions!$F$125+BI7*Assumptions!$F$126+(BI8+BI9+BI10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
+        <f>(BI6*Assumptions!$F$121+BI7*Assumptions!$F$122+(BI8+BI9+BI10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ27" s="43">
-        <f>(BJ6*Assumptions!$F$125+BJ7*Assumptions!$F$126+(BJ8+BJ9+BJ10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
+        <f>(BJ6*Assumptions!$F$121+BJ7*Assumptions!$F$122+(BJ8+BJ9+BJ10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK27" s="43">
-        <f>(BK6*Assumptions!$F$125+BK7*Assumptions!$F$126+(BK8+BK9+BK10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
+        <f>(BK6*Assumptions!$F$121+BK7*Assumptions!$F$122+(BK8+BK9+BK10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL27" s="43">
-        <f>(BL6*Assumptions!$F$125+BL7*Assumptions!$F$126+(BL8+BL9+BL10)*Assumptions!$F$127)*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
+        <f>(BL6*Assumptions!$F$121+BL7*Assumptions!$F$122+(BL8+BL9+BL10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN27" s="44">
@@ -46046,243 +45674,243 @@
         </is>
       </c>
       <c r="E28" s="43">
-        <f>((E12+E13)*Assumptions!$F$128+(E14+E15)*Assumptions!$F$129+(E16+E18)*Assumptions!$F$130+E19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
+        <f>((E12+E13)*Assumptions!$F$124+(E14+E15)*Assumptions!$F$125+E17*Assumptions!$F$126+E18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F28" s="43">
-        <f>((F12+F13)*Assumptions!$F$128+(F14+F15)*Assumptions!$F$129+(F16+F18)*Assumptions!$F$130+F19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
+        <f>((F12+F13)*Assumptions!$F$124+(F14+F15)*Assumptions!$F$125+F17*Assumptions!$F$126+F18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G28" s="43">
-        <f>((G12+G13)*Assumptions!$F$128+(G14+G15)*Assumptions!$F$129+(G16+G18)*Assumptions!$F$130+G19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
+        <f>((G12+G13)*Assumptions!$F$124+(G14+G15)*Assumptions!$F$125+G17*Assumptions!$F$126+G18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H28" s="43">
-        <f>((H12+H13)*Assumptions!$F$128+(H14+H15)*Assumptions!$F$129+(H16+H18)*Assumptions!$F$130+H19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
+        <f>((H12+H13)*Assumptions!$F$124+(H14+H15)*Assumptions!$F$125+H17*Assumptions!$F$126+H18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I28" s="43">
-        <f>((I12+I13)*Assumptions!$F$128+(I14+I15)*Assumptions!$F$129+(I16+I18)*Assumptions!$F$130+I19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
+        <f>((I12+I13)*Assumptions!$F$124+(I14+I15)*Assumptions!$F$125+I17*Assumptions!$F$126+I18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J28" s="43">
-        <f>((J12+J13)*Assumptions!$F$128+(J14+J15)*Assumptions!$F$129+(J16+J18)*Assumptions!$F$130+J19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
+        <f>((J12+J13)*Assumptions!$F$124+(J14+J15)*Assumptions!$F$125+J17*Assumptions!$F$126+J18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K28" s="43">
-        <f>((K12+K13)*Assumptions!$F$128+(K14+K15)*Assumptions!$F$129+(K16+K18)*Assumptions!$F$130+K19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
+        <f>((K12+K13)*Assumptions!$F$124+(K14+K15)*Assumptions!$F$125+K17*Assumptions!$F$126+K18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L28" s="43">
-        <f>((L12+L13)*Assumptions!$F$128+(L14+L15)*Assumptions!$F$129+(L16+L18)*Assumptions!$F$130+L19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
+        <f>((L12+L13)*Assumptions!$F$124+(L14+L15)*Assumptions!$F$125+L17*Assumptions!$F$126+L18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M28" s="43">
-        <f>((M12+M13)*Assumptions!$F$128+(M14+M15)*Assumptions!$F$129+(M16+M18)*Assumptions!$F$130+M19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
+        <f>((M12+M13)*Assumptions!$F$124+(M14+M15)*Assumptions!$F$125+M17*Assumptions!$F$126+M18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N28" s="43">
-        <f>((N12+N13)*Assumptions!$F$128+(N14+N15)*Assumptions!$F$129+(N16+N18)*Assumptions!$F$130+N19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
+        <f>((N12+N13)*Assumptions!$F$124+(N14+N15)*Assumptions!$F$125+N17*Assumptions!$F$126+N18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O28" s="43">
-        <f>((O12+O13)*Assumptions!$F$128+(O14+O15)*Assumptions!$F$129+(O16+O18)*Assumptions!$F$130+O19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
+        <f>((O12+O13)*Assumptions!$F$124+(O14+O15)*Assumptions!$F$125+O17*Assumptions!$F$126+O18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P28" s="43">
-        <f>((P12+P13)*Assumptions!$F$128+(P14+P15)*Assumptions!$F$129+(P16+P18)*Assumptions!$F$130+P19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
+        <f>((P12+P13)*Assumptions!$F$124+(P14+P15)*Assumptions!$F$125+P17*Assumptions!$F$126+P18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q28" s="43">
-        <f>((Q12+Q13)*Assumptions!$F$128+(Q14+Q15)*Assumptions!$F$129+(Q16+Q18)*Assumptions!$F$130+Q19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
+        <f>((Q12+Q13)*Assumptions!$F$124+(Q14+Q15)*Assumptions!$F$125+Q17*Assumptions!$F$126+Q18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R28" s="43">
-        <f>((R12+R13)*Assumptions!$F$128+(R14+R15)*Assumptions!$F$129+(R16+R18)*Assumptions!$F$130+R19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
+        <f>((R12+R13)*Assumptions!$F$124+(R14+R15)*Assumptions!$F$125+R17*Assumptions!$F$126+R18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S28" s="43">
-        <f>((S12+S13)*Assumptions!$F$128+(S14+S15)*Assumptions!$F$129+(S16+S18)*Assumptions!$F$130+S19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
+        <f>((S12+S13)*Assumptions!$F$124+(S14+S15)*Assumptions!$F$125+S17*Assumptions!$F$126+S18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T28" s="43">
-        <f>((T12+T13)*Assumptions!$F$128+(T14+T15)*Assumptions!$F$129+(T16+T18)*Assumptions!$F$130+T19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
+        <f>((T12+T13)*Assumptions!$F$124+(T14+T15)*Assumptions!$F$125+T17*Assumptions!$F$126+T18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U28" s="43">
-        <f>((U12+U13)*Assumptions!$F$128+(U14+U15)*Assumptions!$F$129+(U16+U18)*Assumptions!$F$130+U19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
+        <f>((U12+U13)*Assumptions!$F$124+(U14+U15)*Assumptions!$F$125+U17*Assumptions!$F$126+U18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V28" s="43">
-        <f>((V12+V13)*Assumptions!$F$128+(V14+V15)*Assumptions!$F$129+(V16+V18)*Assumptions!$F$130+V19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
+        <f>((V12+V13)*Assumptions!$F$124+(V14+V15)*Assumptions!$F$125+V17*Assumptions!$F$126+V18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W28" s="43">
-        <f>((W12+W13)*Assumptions!$F$128+(W14+W15)*Assumptions!$F$129+(W16+W18)*Assumptions!$F$130+W19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
+        <f>((W12+W13)*Assumptions!$F$124+(W14+W15)*Assumptions!$F$125+W17*Assumptions!$F$126+W18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X28" s="43">
-        <f>((X12+X13)*Assumptions!$F$128+(X14+X15)*Assumptions!$F$129+(X16+X18)*Assumptions!$F$130+X19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
+        <f>((X12+X13)*Assumptions!$F$124+(X14+X15)*Assumptions!$F$125+X17*Assumptions!$F$126+X18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y28" s="43">
-        <f>((Y12+Y13)*Assumptions!$F$128+(Y14+Y15)*Assumptions!$F$129+(Y16+Y18)*Assumptions!$F$130+Y19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
+        <f>((Y12+Y13)*Assumptions!$F$124+(Y14+Y15)*Assumptions!$F$125+Y17*Assumptions!$F$126+Y18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z28" s="43">
-        <f>((Z12+Z13)*Assumptions!$F$128+(Z14+Z15)*Assumptions!$F$129+(Z16+Z18)*Assumptions!$F$130+Z19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
+        <f>((Z12+Z13)*Assumptions!$F$124+(Z14+Z15)*Assumptions!$F$125+Z17*Assumptions!$F$126+Z18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA28" s="43">
-        <f>((AA12+AA13)*Assumptions!$F$128+(AA14+AA15)*Assumptions!$F$129+(AA16+AA18)*Assumptions!$F$130+AA19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
+        <f>((AA12+AA13)*Assumptions!$F$124+(AA14+AA15)*Assumptions!$F$125+AA17*Assumptions!$F$126+AA18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB28" s="43">
-        <f>((AB12+AB13)*Assumptions!$F$128+(AB14+AB15)*Assumptions!$F$129+(AB16+AB18)*Assumptions!$F$130+AB19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
+        <f>((AB12+AB13)*Assumptions!$F$124+(AB14+AB15)*Assumptions!$F$125+AB17*Assumptions!$F$126+AB18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC28" s="43">
-        <f>((AC12+AC13)*Assumptions!$F$128+(AC14+AC15)*Assumptions!$F$129+(AC16+AC18)*Assumptions!$F$130+AC19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
+        <f>((AC12+AC13)*Assumptions!$F$124+(AC14+AC15)*Assumptions!$F$125+AC17*Assumptions!$F$126+AC18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD28" s="43">
-        <f>((AD12+AD13)*Assumptions!$F$128+(AD14+AD15)*Assumptions!$F$129+(AD16+AD18)*Assumptions!$F$130+AD19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
+        <f>((AD12+AD13)*Assumptions!$F$124+(AD14+AD15)*Assumptions!$F$125+AD17*Assumptions!$F$126+AD18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE28" s="43">
-        <f>((AE12+AE13)*Assumptions!$F$128+(AE14+AE15)*Assumptions!$F$129+(AE16+AE18)*Assumptions!$F$130+AE19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
+        <f>((AE12+AE13)*Assumptions!$F$124+(AE14+AE15)*Assumptions!$F$125+AE17*Assumptions!$F$126+AE18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF28" s="43">
-        <f>((AF12+AF13)*Assumptions!$F$128+(AF14+AF15)*Assumptions!$F$129+(AF16+AF18)*Assumptions!$F$130+AF19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
+        <f>((AF12+AF13)*Assumptions!$F$124+(AF14+AF15)*Assumptions!$F$125+AF17*Assumptions!$F$126+AF18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG28" s="43">
-        <f>((AG12+AG13)*Assumptions!$F$128+(AG14+AG15)*Assumptions!$F$129+(AG16+AG18)*Assumptions!$F$130+AG19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
+        <f>((AG12+AG13)*Assumptions!$F$124+(AG14+AG15)*Assumptions!$F$125+AG17*Assumptions!$F$126+AG18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH28" s="43">
-        <f>((AH12+AH13)*Assumptions!$F$128+(AH14+AH15)*Assumptions!$F$129+(AH16+AH18)*Assumptions!$F$130+AH19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
+        <f>((AH12+AH13)*Assumptions!$F$124+(AH14+AH15)*Assumptions!$F$125+AH17*Assumptions!$F$126+AH18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI28" s="43">
-        <f>((AI12+AI13)*Assumptions!$F$128+(AI14+AI15)*Assumptions!$F$129+(AI16+AI18)*Assumptions!$F$130+AI19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
+        <f>((AI12+AI13)*Assumptions!$F$124+(AI14+AI15)*Assumptions!$F$125+AI17*Assumptions!$F$126+AI18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ28" s="43">
-        <f>((AJ12+AJ13)*Assumptions!$F$128+(AJ14+AJ15)*Assumptions!$F$129+(AJ16+AJ18)*Assumptions!$F$130+AJ19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
+        <f>((AJ12+AJ13)*Assumptions!$F$124+(AJ14+AJ15)*Assumptions!$F$125+AJ17*Assumptions!$F$126+AJ18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK28" s="43">
-        <f>((AK12+AK13)*Assumptions!$F$128+(AK14+AK15)*Assumptions!$F$129+(AK16+AK18)*Assumptions!$F$130+AK19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
+        <f>((AK12+AK13)*Assumptions!$F$124+(AK14+AK15)*Assumptions!$F$125+AK17*Assumptions!$F$126+AK18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL28" s="43">
-        <f>((AL12+AL13)*Assumptions!$F$128+(AL14+AL15)*Assumptions!$F$129+(AL16+AL18)*Assumptions!$F$130+AL19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
+        <f>((AL12+AL13)*Assumptions!$F$124+(AL14+AL15)*Assumptions!$F$125+AL17*Assumptions!$F$126+AL18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM28" s="43">
-        <f>((AM12+AM13)*Assumptions!$F$128+(AM14+AM15)*Assumptions!$F$129+(AM16+AM18)*Assumptions!$F$130+AM19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
+        <f>((AM12+AM13)*Assumptions!$F$124+(AM14+AM15)*Assumptions!$F$125+AM17*Assumptions!$F$126+AM18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN28" s="43">
-        <f>((AN12+AN13)*Assumptions!$F$128+(AN14+AN15)*Assumptions!$F$129+(AN16+AN18)*Assumptions!$F$130+AN19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
+        <f>((AN12+AN13)*Assumptions!$F$124+(AN14+AN15)*Assumptions!$F$125+AN17*Assumptions!$F$126+AN18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO28" s="43">
-        <f>((AO12+AO13)*Assumptions!$F$128+(AO14+AO15)*Assumptions!$F$129+(AO16+AO18)*Assumptions!$F$130+AO19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
+        <f>((AO12+AO13)*Assumptions!$F$124+(AO14+AO15)*Assumptions!$F$125+AO17*Assumptions!$F$126+AO18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP28" s="43">
-        <f>((AP12+AP13)*Assumptions!$F$128+(AP14+AP15)*Assumptions!$F$129+(AP16+AP18)*Assumptions!$F$130+AP19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
+        <f>((AP12+AP13)*Assumptions!$F$124+(AP14+AP15)*Assumptions!$F$125+AP17*Assumptions!$F$126+AP18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ28" s="43">
-        <f>((AQ12+AQ13)*Assumptions!$F$128+(AQ14+AQ15)*Assumptions!$F$129+(AQ16+AQ18)*Assumptions!$F$130+AQ19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
+        <f>((AQ12+AQ13)*Assumptions!$F$124+(AQ14+AQ15)*Assumptions!$F$125+AQ17*Assumptions!$F$126+AQ18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR28" s="43">
-        <f>((AR12+AR13)*Assumptions!$F$128+(AR14+AR15)*Assumptions!$F$129+(AR16+AR18)*Assumptions!$F$130+AR19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
+        <f>((AR12+AR13)*Assumptions!$F$124+(AR14+AR15)*Assumptions!$F$125+AR17*Assumptions!$F$126+AR18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS28" s="43">
-        <f>((AS12+AS13)*Assumptions!$F$128+(AS14+AS15)*Assumptions!$F$129+(AS16+AS18)*Assumptions!$F$130+AS19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
+        <f>((AS12+AS13)*Assumptions!$F$124+(AS14+AS15)*Assumptions!$F$125+AS17*Assumptions!$F$126+AS18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT28" s="43">
-        <f>((AT12+AT13)*Assumptions!$F$128+(AT14+AT15)*Assumptions!$F$129+(AT16+AT18)*Assumptions!$F$130+AT19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
+        <f>((AT12+AT13)*Assumptions!$F$124+(AT14+AT15)*Assumptions!$F$125+AT17*Assumptions!$F$126+AT18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU28" s="43">
-        <f>((AU12+AU13)*Assumptions!$F$128+(AU14+AU15)*Assumptions!$F$129+(AU16+AU18)*Assumptions!$F$130+AU19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
+        <f>((AU12+AU13)*Assumptions!$F$124+(AU14+AU15)*Assumptions!$F$125+AU17*Assumptions!$F$126+AU18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV28" s="43">
-        <f>((AV12+AV13)*Assumptions!$F$128+(AV14+AV15)*Assumptions!$F$129+(AV16+AV18)*Assumptions!$F$130+AV19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
+        <f>((AV12+AV13)*Assumptions!$F$124+(AV14+AV15)*Assumptions!$F$125+AV17*Assumptions!$F$126+AV18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW28" s="43">
-        <f>((AW12+AW13)*Assumptions!$F$128+(AW14+AW15)*Assumptions!$F$129+(AW16+AW18)*Assumptions!$F$130+AW19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
+        <f>((AW12+AW13)*Assumptions!$F$124+(AW14+AW15)*Assumptions!$F$125+AW17*Assumptions!$F$126+AW18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX28" s="43">
-        <f>((AX12+AX13)*Assumptions!$F$128+(AX14+AX15)*Assumptions!$F$129+(AX16+AX18)*Assumptions!$F$130+AX19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
+        <f>((AX12+AX13)*Assumptions!$F$124+(AX14+AX15)*Assumptions!$F$125+AX17*Assumptions!$F$126+AX18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY28" s="43">
-        <f>((AY12+AY13)*Assumptions!$F$128+(AY14+AY15)*Assumptions!$F$129+(AY16+AY18)*Assumptions!$F$130+AY19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
+        <f>((AY12+AY13)*Assumptions!$F$124+(AY14+AY15)*Assumptions!$F$125+AY17*Assumptions!$F$126+AY18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ28" s="43">
-        <f>((AZ12+AZ13)*Assumptions!$F$128+(AZ14+AZ15)*Assumptions!$F$129+(AZ16+AZ18)*Assumptions!$F$130+AZ19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
+        <f>((AZ12+AZ13)*Assumptions!$F$124+(AZ14+AZ15)*Assumptions!$F$125+AZ17*Assumptions!$F$126+AZ18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA28" s="43">
-        <f>((BA12+BA13)*Assumptions!$F$128+(BA14+BA15)*Assumptions!$F$129+(BA16+BA18)*Assumptions!$F$130+BA19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
+        <f>((BA12+BA13)*Assumptions!$F$124+(BA14+BA15)*Assumptions!$F$125+BA17*Assumptions!$F$126+BA18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB28" s="43">
-        <f>((BB12+BB13)*Assumptions!$F$128+(BB14+BB15)*Assumptions!$F$129+(BB16+BB18)*Assumptions!$F$130+BB19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
+        <f>((BB12+BB13)*Assumptions!$F$124+(BB14+BB15)*Assumptions!$F$125+BB17*Assumptions!$F$126+BB18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC28" s="43">
-        <f>((BC12+BC13)*Assumptions!$F$128+(BC14+BC15)*Assumptions!$F$129+(BC16+BC18)*Assumptions!$F$130+BC19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
+        <f>((BC12+BC13)*Assumptions!$F$124+(BC14+BC15)*Assumptions!$F$125+BC17*Assumptions!$F$126+BC18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD28" s="43">
-        <f>((BD12+BD13)*Assumptions!$F$128+(BD14+BD15)*Assumptions!$F$129+(BD16+BD18)*Assumptions!$F$130+BD19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
+        <f>((BD12+BD13)*Assumptions!$F$124+(BD14+BD15)*Assumptions!$F$125+BD17*Assumptions!$F$126+BD18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE28" s="43">
-        <f>((BE12+BE13)*Assumptions!$F$128+(BE14+BE15)*Assumptions!$F$129+(BE16+BE18)*Assumptions!$F$130+BE19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
+        <f>((BE12+BE13)*Assumptions!$F$124+(BE14+BE15)*Assumptions!$F$125+BE17*Assumptions!$F$126+BE18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF28" s="43">
-        <f>((BF12+BF13)*Assumptions!$F$128+(BF14+BF15)*Assumptions!$F$129+(BF16+BF18)*Assumptions!$F$130+BF19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
+        <f>((BF12+BF13)*Assumptions!$F$124+(BF14+BF15)*Assumptions!$F$125+BF17*Assumptions!$F$126+BF18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG28" s="43">
-        <f>((BG12+BG13)*Assumptions!$F$128+(BG14+BG15)*Assumptions!$F$129+(BG16+BG18)*Assumptions!$F$130+BG19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
+        <f>((BG12+BG13)*Assumptions!$F$124+(BG14+BG15)*Assumptions!$F$125+BG17*Assumptions!$F$126+BG18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH28" s="43">
-        <f>((BH12+BH13)*Assumptions!$F$128+(BH14+BH15)*Assumptions!$F$129+(BH16+BH18)*Assumptions!$F$130+BH19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
+        <f>((BH12+BH13)*Assumptions!$F$124+(BH14+BH15)*Assumptions!$F$125+BH17*Assumptions!$F$126+BH18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI28" s="43">
-        <f>((BI12+BI13)*Assumptions!$F$128+(BI14+BI15)*Assumptions!$F$129+(BI16+BI18)*Assumptions!$F$130+BI19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
+        <f>((BI12+BI13)*Assumptions!$F$124+(BI14+BI15)*Assumptions!$F$125+BI17*Assumptions!$F$126+BI18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ28" s="43">
-        <f>((BJ12+BJ13)*Assumptions!$F$128+(BJ14+BJ15)*Assumptions!$F$129+(BJ16+BJ18)*Assumptions!$F$130+BJ19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
+        <f>((BJ12+BJ13)*Assumptions!$F$124+(BJ14+BJ15)*Assumptions!$F$125+BJ17*Assumptions!$F$126+BJ18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK28" s="43">
-        <f>((BK12+BK13)*Assumptions!$F$128+(BK14+BK15)*Assumptions!$F$129+(BK16+BK18)*Assumptions!$F$130+BK19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
+        <f>((BK12+BK13)*Assumptions!$F$124+(BK14+BK15)*Assumptions!$F$125+BK17*Assumptions!$F$126+BK18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL28" s="43">
-        <f>((BL12+BL13)*Assumptions!$F$128+(BL14+BL15)*Assumptions!$F$129+(BL16+BL18)*Assumptions!$F$130+BL19*Assumptions!$F$132)*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
+        <f>((BL12+BL13)*Assumptions!$F$124+(BL14+BL15)*Assumptions!$F$125+BL17*Assumptions!$F$126+BL18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN28" s="44">
@@ -46590,243 +46218,243 @@
         </is>
       </c>
       <c r="E31" s="65">
-        <f>IFERROR(E29/E21,0)</f>
+        <f>IFERROR(E29/E20,0)</f>
         <v/>
       </c>
       <c r="F31" s="65">
-        <f>IFERROR(F29/F21,0)</f>
+        <f>IFERROR(F29/F20,0)</f>
         <v/>
       </c>
       <c r="G31" s="65">
-        <f>IFERROR(G29/G21,0)</f>
+        <f>IFERROR(G29/G20,0)</f>
         <v/>
       </c>
       <c r="H31" s="65">
-        <f>IFERROR(H29/H21,0)</f>
+        <f>IFERROR(H29/H20,0)</f>
         <v/>
       </c>
       <c r="I31" s="65">
-        <f>IFERROR(I29/I21,0)</f>
+        <f>IFERROR(I29/I20,0)</f>
         <v/>
       </c>
       <c r="J31" s="65">
-        <f>IFERROR(J29/J21,0)</f>
+        <f>IFERROR(J29/J20,0)</f>
         <v/>
       </c>
       <c r="K31" s="65">
-        <f>IFERROR(K29/K21,0)</f>
+        <f>IFERROR(K29/K20,0)</f>
         <v/>
       </c>
       <c r="L31" s="65">
-        <f>IFERROR(L29/L21,0)</f>
+        <f>IFERROR(L29/L20,0)</f>
         <v/>
       </c>
       <c r="M31" s="65">
-        <f>IFERROR(M29/M21,0)</f>
+        <f>IFERROR(M29/M20,0)</f>
         <v/>
       </c>
       <c r="N31" s="65">
-        <f>IFERROR(N29/N21,0)</f>
+        <f>IFERROR(N29/N20,0)</f>
         <v/>
       </c>
       <c r="O31" s="65">
-        <f>IFERROR(O29/O21,0)</f>
+        <f>IFERROR(O29/O20,0)</f>
         <v/>
       </c>
       <c r="P31" s="65">
-        <f>IFERROR(P29/P21,0)</f>
+        <f>IFERROR(P29/P20,0)</f>
         <v/>
       </c>
       <c r="Q31" s="65">
-        <f>IFERROR(Q29/Q21,0)</f>
+        <f>IFERROR(Q29/Q20,0)</f>
         <v/>
       </c>
       <c r="R31" s="65">
-        <f>IFERROR(R29/R21,0)</f>
+        <f>IFERROR(R29/R20,0)</f>
         <v/>
       </c>
       <c r="S31" s="65">
-        <f>IFERROR(S29/S21,0)</f>
+        <f>IFERROR(S29/S20,0)</f>
         <v/>
       </c>
       <c r="T31" s="65">
-        <f>IFERROR(T29/T21,0)</f>
+        <f>IFERROR(T29/T20,0)</f>
         <v/>
       </c>
       <c r="U31" s="65">
-        <f>IFERROR(U29/U21,0)</f>
+        <f>IFERROR(U29/U20,0)</f>
         <v/>
       </c>
       <c r="V31" s="65">
-        <f>IFERROR(V29/V21,0)</f>
+        <f>IFERROR(V29/V20,0)</f>
         <v/>
       </c>
       <c r="W31" s="65">
-        <f>IFERROR(W29/W21,0)</f>
+        <f>IFERROR(W29/W20,0)</f>
         <v/>
       </c>
       <c r="X31" s="65">
-        <f>IFERROR(X29/X21,0)</f>
+        <f>IFERROR(X29/X20,0)</f>
         <v/>
       </c>
       <c r="Y31" s="65">
-        <f>IFERROR(Y29/Y21,0)</f>
+        <f>IFERROR(Y29/Y20,0)</f>
         <v/>
       </c>
       <c r="Z31" s="65">
-        <f>IFERROR(Z29/Z21,0)</f>
+        <f>IFERROR(Z29/Z20,0)</f>
         <v/>
       </c>
       <c r="AA31" s="65">
-        <f>IFERROR(AA29/AA21,0)</f>
+        <f>IFERROR(AA29/AA20,0)</f>
         <v/>
       </c>
       <c r="AB31" s="65">
-        <f>IFERROR(AB29/AB21,0)</f>
+        <f>IFERROR(AB29/AB20,0)</f>
         <v/>
       </c>
       <c r="AC31" s="65">
-        <f>IFERROR(AC29/AC21,0)</f>
+        <f>IFERROR(AC29/AC20,0)</f>
         <v/>
       </c>
       <c r="AD31" s="65">
-        <f>IFERROR(AD29/AD21,0)</f>
+        <f>IFERROR(AD29/AD20,0)</f>
         <v/>
       </c>
       <c r="AE31" s="65">
-        <f>IFERROR(AE29/AE21,0)</f>
+        <f>IFERROR(AE29/AE20,0)</f>
         <v/>
       </c>
       <c r="AF31" s="65">
-        <f>IFERROR(AF29/AF21,0)</f>
+        <f>IFERROR(AF29/AF20,0)</f>
         <v/>
       </c>
       <c r="AG31" s="65">
-        <f>IFERROR(AG29/AG21,0)</f>
+        <f>IFERROR(AG29/AG20,0)</f>
         <v/>
       </c>
       <c r="AH31" s="65">
-        <f>IFERROR(AH29/AH21,0)</f>
+        <f>IFERROR(AH29/AH20,0)</f>
         <v/>
       </c>
       <c r="AI31" s="65">
-        <f>IFERROR(AI29/AI21,0)</f>
+        <f>IFERROR(AI29/AI20,0)</f>
         <v/>
       </c>
       <c r="AJ31" s="65">
-        <f>IFERROR(AJ29/AJ21,0)</f>
+        <f>IFERROR(AJ29/AJ20,0)</f>
         <v/>
       </c>
       <c r="AK31" s="65">
-        <f>IFERROR(AK29/AK21,0)</f>
+        <f>IFERROR(AK29/AK20,0)</f>
         <v/>
       </c>
       <c r="AL31" s="65">
-        <f>IFERROR(AL29/AL21,0)</f>
+        <f>IFERROR(AL29/AL20,0)</f>
         <v/>
       </c>
       <c r="AM31" s="65">
-        <f>IFERROR(AM29/AM21,0)</f>
+        <f>IFERROR(AM29/AM20,0)</f>
         <v/>
       </c>
       <c r="AN31" s="65">
-        <f>IFERROR(AN29/AN21,0)</f>
+        <f>IFERROR(AN29/AN20,0)</f>
         <v/>
       </c>
       <c r="AO31" s="65">
-        <f>IFERROR(AO29/AO21,0)</f>
+        <f>IFERROR(AO29/AO20,0)</f>
         <v/>
       </c>
       <c r="AP31" s="65">
-        <f>IFERROR(AP29/AP21,0)</f>
+        <f>IFERROR(AP29/AP20,0)</f>
         <v/>
       </c>
       <c r="AQ31" s="65">
-        <f>IFERROR(AQ29/AQ21,0)</f>
+        <f>IFERROR(AQ29/AQ20,0)</f>
         <v/>
       </c>
       <c r="AR31" s="65">
-        <f>IFERROR(AR29/AR21,0)</f>
+        <f>IFERROR(AR29/AR20,0)</f>
         <v/>
       </c>
       <c r="AS31" s="65">
-        <f>IFERROR(AS29/AS21,0)</f>
+        <f>IFERROR(AS29/AS20,0)</f>
         <v/>
       </c>
       <c r="AT31" s="65">
-        <f>IFERROR(AT29/AT21,0)</f>
+        <f>IFERROR(AT29/AT20,0)</f>
         <v/>
       </c>
       <c r="AU31" s="65">
-        <f>IFERROR(AU29/AU21,0)</f>
+        <f>IFERROR(AU29/AU20,0)</f>
         <v/>
       </c>
       <c r="AV31" s="65">
-        <f>IFERROR(AV29/AV21,0)</f>
+        <f>IFERROR(AV29/AV20,0)</f>
         <v/>
       </c>
       <c r="AW31" s="65">
-        <f>IFERROR(AW29/AW21,0)</f>
+        <f>IFERROR(AW29/AW20,0)</f>
         <v/>
       </c>
       <c r="AX31" s="65">
-        <f>IFERROR(AX29/AX21,0)</f>
+        <f>IFERROR(AX29/AX20,0)</f>
         <v/>
       </c>
       <c r="AY31" s="65">
-        <f>IFERROR(AY29/AY21,0)</f>
+        <f>IFERROR(AY29/AY20,0)</f>
         <v/>
       </c>
       <c r="AZ31" s="65">
-        <f>IFERROR(AZ29/AZ21,0)</f>
+        <f>IFERROR(AZ29/AZ20,0)</f>
         <v/>
       </c>
       <c r="BA31" s="65">
-        <f>IFERROR(BA29/BA21,0)</f>
+        <f>IFERROR(BA29/BA20,0)</f>
         <v/>
       </c>
       <c r="BB31" s="65">
-        <f>IFERROR(BB29/BB21,0)</f>
+        <f>IFERROR(BB29/BB20,0)</f>
         <v/>
       </c>
       <c r="BC31" s="65">
-        <f>IFERROR(BC29/BC21,0)</f>
+        <f>IFERROR(BC29/BC20,0)</f>
         <v/>
       </c>
       <c r="BD31" s="65">
-        <f>IFERROR(BD29/BD21,0)</f>
+        <f>IFERROR(BD29/BD20,0)</f>
         <v/>
       </c>
       <c r="BE31" s="65">
-        <f>IFERROR(BE29/BE21,0)</f>
+        <f>IFERROR(BE29/BE20,0)</f>
         <v/>
       </c>
       <c r="BF31" s="65">
-        <f>IFERROR(BF29/BF21,0)</f>
+        <f>IFERROR(BF29/BF20,0)</f>
         <v/>
       </c>
       <c r="BG31" s="65">
-        <f>IFERROR(BG29/BG21,0)</f>
+        <f>IFERROR(BG29/BG20,0)</f>
         <v/>
       </c>
       <c r="BH31" s="65">
-        <f>IFERROR(BH29/BH21,0)</f>
+        <f>IFERROR(BH29/BH20,0)</f>
         <v/>
       </c>
       <c r="BI31" s="65">
-        <f>IFERROR(BI29/BI21,0)</f>
+        <f>IFERROR(BI29/BI20,0)</f>
         <v/>
       </c>
       <c r="BJ31" s="65">
-        <f>IFERROR(BJ29/BJ21,0)</f>
+        <f>IFERROR(BJ29/BJ20,0)</f>
         <v/>
       </c>
       <c r="BK31" s="65">
-        <f>IFERROR(BK29/BK21,0)</f>
+        <f>IFERROR(BK29/BK20,0)</f>
         <v/>
       </c>
       <c r="BL31" s="65">
-        <f>IFERROR(BL29/BL21,0)</f>
+        <f>IFERROR(BL29/BL20,0)</f>
         <v/>
       </c>
       <c r="BN31" s="66">
@@ -47295,23 +46923,23 @@
         </is>
       </c>
       <c r="D23" s="54">
-        <f>Personnel!BN19</f>
+        <f>Personnel!BN18</f>
         <v/>
       </c>
       <c r="E23" s="54">
-        <f>Personnel!BO19</f>
+        <f>Personnel!BO18</f>
         <v/>
       </c>
       <c r="F23" s="54">
-        <f>Personnel!BP19</f>
+        <f>Personnel!BP18</f>
         <v/>
       </c>
       <c r="G23" s="54">
-        <f>Personnel!BQ19</f>
+        <f>Personnel!BQ18</f>
         <v/>
       </c>
       <c r="H23" s="54">
-        <f>Personnel!BR19</f>
+        <f>Personnel!BR18</f>
         <v/>
       </c>
     </row>
@@ -47322,23 +46950,23 @@
         </is>
       </c>
       <c r="D24" s="38">
-        <f>Personnel!BN21</f>
+        <f>Personnel!BN20</f>
         <v/>
       </c>
       <c r="E24" s="38">
-        <f>Personnel!BO21</f>
+        <f>Personnel!BO20</f>
         <v/>
       </c>
       <c r="F24" s="38">
-        <f>Personnel!BP21</f>
+        <f>Personnel!BP20</f>
         <v/>
       </c>
       <c r="G24" s="38">
-        <f>Personnel!BQ21</f>
+        <f>Personnel!BQ20</f>
         <v/>
       </c>
       <c r="H24" s="38">
-        <f>Personnel!BR21</f>
+        <f>Personnel!BR20</f>
         <v/>
       </c>
     </row>

--- a/models/Tarnoc_v2_2026-09-01.xlsx
+++ b/models/Tarnoc_v2_2026-09-01.xlsx
@@ -4092,7 +4092,7 @@
     <row r="126">
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Leadership, finance, HR, IT and legal</t>
+          <t>Leadership and back office</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">

--- a/models/Tarnoc_v2_2026-09-01.xlsx
+++ b/models/Tarnoc_v2_2026-09-01.xlsx
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Hardcoded input. These are the only cells to change, and they all live on Assumptions.</t>
+          <t>Hardcoded input. These are the only cells to change. They live on Assumptions, plus the back-office headcount row on Personnel.</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
     <row r="13">
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Assumptions   -&gt;   every other tab. Nothing is hardcoded anywhere else.</t>
+          <t>Assumptions   -&gt;   every other tab. The only other typed numbers are the back-office headcount on Personnel and the committed 2026 plan on OPEX.</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J148"/>
+  <dimension ref="B1:J144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3788,201 +3788,185 @@
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="31" t="inlineStr">
-        <is>
-          <t>Leadership, finance, HR, IT and legal</t>
-        </is>
-      </c>
-      <c r="C113" s="32" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="D113" s="33" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E113" s="33" t="n">
-        <v>2027</v>
-      </c>
-      <c r="F113" s="33" t="n">
-        <v>2028</v>
-      </c>
-      <c r="G113" s="33" t="n">
-        <v>2029</v>
-      </c>
-      <c r="H113" s="33" t="n">
-        <v>2030</v>
-      </c>
+      <c r="B113" s="21" t="n"/>
+      <c r="C113" s="21" t="n"/>
+      <c r="D113" s="22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E113" s="22" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F113" s="22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G113" s="21" t="n"/>
+      <c r="H113" s="21" t="n"/>
       <c r="I113" s="21" t="n"/>
-      <c r="J113" s="34" t="inlineStr">
-        <is>
-          <t>the whole back office, typed per year: leadership in post by end 2026, then finance, HR, IT and legal as the company grows</t>
-        </is>
-      </c>
+      <c r="J113" s="21" t="n"/>
     </row>
     <row r="114">
-      <c r="B114" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Base</t>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>Boilers one field engineer can look after</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
+        <is>
+          <t>boilers</t>
         </is>
       </c>
       <c r="D114" s="29" t="n">
-        <v>3</v>
+        <v>750</v>
       </c>
       <c r="E114" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="F114" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="G114" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H114" s="29" t="n">
-        <v>8</v>
+        <v>750</v>
+      </c>
+      <c r="F114" s="30">
+        <f>IF(Assumptions!$E$5=2,E114,D114)</f>
+        <v/>
+      </c>
+      <c r="J114" s="20" t="inlineStr">
+        <is>
+          <t>sizes the field service team: boilers on a service contract divided by this number = engineers to hire. Each boiler gets one visit a year, an engineer does three to four a day</t>
+        </is>
       </c>
     </row>
     <row r="115">
-      <c r="B115" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Aggressive</t>
-        </is>
-      </c>
-      <c r="D115" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E115" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="F115" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G115" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="H115" s="29" t="n">
-        <v>18</v>
-      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>LOADED COST PER PERSON  (employer cost, including taxes)</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n"/>
+      <c r="D115" s="1" t="n"/>
+      <c r="E115" s="1" t="n"/>
+      <c r="F115" s="1" t="n"/>
+      <c r="G115" s="1" t="n"/>
+      <c r="H115" s="1" t="n"/>
+      <c r="I115" s="1" t="n"/>
+      <c r="J115" s="1" t="n"/>
     </row>
     <row r="116">
-      <c r="B116" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Live (per case)</t>
-        </is>
-      </c>
-      <c r="D116" s="30">
-        <f>IF(Assumptions!$E$5=2,D115,D114)</f>
-        <v/>
-      </c>
-      <c r="E116" s="30">
-        <f>IF(Assumptions!$E$5=2,E115,E114)</f>
-        <v/>
-      </c>
-      <c r="F116" s="30">
-        <f>IF(Assumptions!$E$5=2,F115,F114)</f>
-        <v/>
-      </c>
-      <c r="G116" s="30">
-        <f>IF(Assumptions!$E$5=2,G115,G114)</f>
-        <v/>
-      </c>
-      <c r="H116" s="30">
-        <f>IF(Assumptions!$E$5=2,H115,H114)</f>
-        <v/>
-      </c>
+      <c r="B116" s="21" t="n"/>
+      <c r="C116" s="21" t="n"/>
+      <c r="D116" s="22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E116" s="22" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F116" s="22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G116" s="21" t="n"/>
+      <c r="H116" s="21" t="n"/>
+      <c r="I116" s="21" t="n"/>
+      <c r="J116" s="21" t="n"/>
     </row>
     <row r="117">
-      <c r="B117" s="21" t="n"/>
-      <c r="C117" s="21" t="n"/>
-      <c r="D117" s="22" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E117" s="22" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F117" s="22" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G117" s="21" t="n"/>
-      <c r="H117" s="21" t="n"/>
-      <c r="I117" s="21" t="n"/>
-      <c r="J117" s="21" t="n"/>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>Sales rep</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D117" s="23" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E117" s="23" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F117" s="24">
+        <f>IF(Assumptions!$E$5=2,E117,D117)</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Boilers one field engineer can look after</t>
+          <t>Partner manager</t>
         </is>
       </c>
       <c r="C118" s="18" t="inlineStr">
         <is>
-          <t>boilers</t>
-        </is>
-      </c>
-      <c r="D118" s="29" t="n">
-        <v>750</v>
-      </c>
-      <c r="E118" s="29" t="n">
-        <v>750</v>
-      </c>
-      <c r="F118" s="30">
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D118" s="23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E118" s="23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F118" s="24">
         <f>IF(Assumptions!$E$5=2,E118,D118)</f>
         <v/>
-      </c>
-      <c r="J118" s="20" t="inlineStr">
-        <is>
-          <t>sizes the field service team: boilers on a service contract divided by this number = engineers to hire. Each boiler gets one visit a year, an engineer does three to four a day</t>
-        </is>
       </c>
     </row>
     <row r="119">
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>LOADED COST PER PERSON  (employer cost, including taxes)</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="n"/>
-      <c r="D119" s="1" t="n"/>
-      <c r="E119" s="1" t="n"/>
-      <c r="F119" s="1" t="n"/>
-      <c r="G119" s="1" t="n"/>
-      <c r="H119" s="1" t="n"/>
-      <c r="I119" s="1" t="n"/>
-      <c r="J119" s="1" t="n"/>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>Trainer, order desk, marketing</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D119" s="23" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E119" s="23" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F119" s="24">
+        <f>IF(Assumptions!$E$5=2,E119,D119)</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
-      <c r="B120" s="21" t="n"/>
-      <c r="C120" s="21" t="n"/>
-      <c r="D120" s="22" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E120" s="22" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F120" s="22" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G120" s="21" t="n"/>
-      <c r="H120" s="21" t="n"/>
-      <c r="I120" s="21" t="n"/>
-      <c r="J120" s="21" t="n"/>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>Supply chain and production</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D120" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E120" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F120" s="24">
+        <f>IF(Assumptions!$E$5=2,E120,D120)</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Sales rep</t>
+          <t>Support and escalation</t>
         </is>
       </c>
       <c r="C121" s="18" t="inlineStr">
@@ -3991,10 +3975,10 @@
         </is>
       </c>
       <c r="D121" s="23" t="n">
-        <v>7500</v>
+        <v>4800</v>
       </c>
       <c r="E121" s="23" t="n">
-        <v>7500</v>
+        <v>4800</v>
       </c>
       <c r="F121" s="24">
         <f>IF(Assumptions!$E$5=2,E121,D121)</f>
@@ -4004,7 +3988,7 @@
     <row r="122">
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Partner manager</t>
+          <t>Leadership and back office</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
@@ -4013,10 +3997,10 @@
         </is>
       </c>
       <c r="D122" s="23" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="E122" s="23" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="F122" s="24">
         <f>IF(Assumptions!$E$5=2,E122,D122)</f>
@@ -4026,7 +4010,7 @@
     <row r="123">
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Trainer, order desk, marketing</t>
+          <t>R&amp;D engineer</t>
         </is>
       </c>
       <c r="C123" s="18" t="inlineStr">
@@ -4035,20 +4019,25 @@
         </is>
       </c>
       <c r="D123" s="23" t="n">
-        <v>7000</v>
+        <v>5700</v>
       </c>
       <c r="E123" s="23" t="n">
-        <v>7000</v>
+        <v>5700</v>
       </c>
       <c r="F123" s="24">
         <f>IF(Assumptions!$E$5=2,E123,D123)</f>
         <v/>
+      </c>
+      <c r="J123" s="20" t="inlineStr">
+        <is>
+          <t>the blended cost of the seven engineers already in post</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Supply chain and production</t>
+          <t>Field service engineer</t>
         </is>
       </c>
       <c r="C124" s="18" t="inlineStr">
@@ -4057,10 +4046,10 @@
         </is>
       </c>
       <c r="D124" s="23" t="n">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="E124" s="23" t="n">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="F124" s="24">
         <f>IF(Assumptions!$E$5=2,E124,D124)</f>
@@ -4068,53 +4057,47 @@
       </c>
     </row>
     <row r="125">
-      <c r="B125" s="9" t="inlineStr">
-        <is>
-          <t>Support and escalation</t>
-        </is>
-      </c>
-      <c r="C125" s="18" t="inlineStr">
-        <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D125" s="23" t="n">
-        <v>4800</v>
-      </c>
-      <c r="E125" s="23" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F125" s="24">
-        <f>IF(Assumptions!$E$5=2,E125,D125)</f>
-        <v/>
-      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>OVERHEADS AND OTHER OPERATING COSTS</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n"/>
+      <c r="D125" s="1" t="n"/>
+      <c r="E125" s="1" t="n"/>
+      <c r="F125" s="1" t="n"/>
+      <c r="G125" s="1" t="n"/>
+      <c r="H125" s="1" t="n"/>
+      <c r="I125" s="1" t="n"/>
+      <c r="J125" s="1" t="n"/>
     </row>
     <row r="126">
-      <c r="B126" s="9" t="inlineStr">
-        <is>
-          <t>Leadership and back office</t>
-        </is>
-      </c>
-      <c r="C126" s="18" t="inlineStr">
-        <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D126" s="23" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E126" s="23" t="n">
-        <v>7000</v>
-      </c>
-      <c r="F126" s="24">
-        <f>IF(Assumptions!$E$5=2,E126,D126)</f>
-        <v/>
-      </c>
+      <c r="B126" s="21" t="n"/>
+      <c r="C126" s="21" t="n"/>
+      <c r="D126" s="22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E126" s="22" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F126" s="22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G126" s="21" t="n"/>
+      <c r="H126" s="21" t="n"/>
+      <c r="I126" s="21" t="n"/>
+      <c r="J126" s="21" t="n"/>
     </row>
     <row r="127">
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>R&amp;D engineer</t>
+          <t>Offices and facilities per person</t>
         </is>
       </c>
       <c r="C127" s="18" t="inlineStr">
@@ -4123,25 +4106,20 @@
         </is>
       </c>
       <c r="D127" s="23" t="n">
-        <v>5700</v>
+        <v>700</v>
       </c>
       <c r="E127" s="23" t="n">
-        <v>5700</v>
+        <v>700</v>
       </c>
       <c r="F127" s="24">
         <f>IF(Assumptions!$E$5=2,E127,D127)</f>
         <v/>
-      </c>
-      <c r="J127" s="20" t="inlineStr">
-        <is>
-          <t>the blended cost of the seven engineers already in post</t>
-        </is>
       </c>
     </row>
     <row r="128">
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Field service engineer</t>
+          <t>IT and software per person</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
@@ -4150,10 +4128,10 @@
         </is>
       </c>
       <c r="D128" s="23" t="n">
-        <v>6500</v>
+        <v>250</v>
       </c>
       <c r="E128" s="23" t="n">
-        <v>6500</v>
+        <v>250</v>
       </c>
       <c r="F128" s="24">
         <f>IF(Assumptions!$E$5=2,E128,D128)</f>
@@ -4161,59 +4139,65 @@
       </c>
     </row>
     <row r="129">
-      <c r="B129" s="7" t="inlineStr">
-        <is>
-          <t>OVERHEADS AND OTHER OPERATING COSTS</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="n"/>
-      <c r="D129" s="1" t="n"/>
-      <c r="E129" s="1" t="n"/>
-      <c r="F129" s="1" t="n"/>
-      <c r="G129" s="1" t="n"/>
-      <c r="H129" s="1" t="n"/>
-      <c r="I129" s="1" t="n"/>
-      <c r="J129" s="1" t="n"/>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>Travel per person</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="inlineStr">
+        <is>
+          <t>EUR/month</t>
+        </is>
+      </c>
+      <c r="D129" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="E129" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="F129" s="24">
+        <f>IF(Assumptions!$E$5=2,E129,D129)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
-      <c r="B130" s="21" t="n"/>
-      <c r="C130" s="21" t="n"/>
-      <c r="D130" s="22" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E130" s="22" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F130" s="22" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G130" s="21" t="n"/>
-      <c r="H130" s="21" t="n"/>
-      <c r="I130" s="21" t="n"/>
-      <c r="J130" s="21" t="n"/>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>Recruitment per net new hire</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D130" s="23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E130" s="23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F130" s="24">
+        <f>IF(Assumptions!$E$5=2,E130,D130)</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Offices and facilities per person</t>
+          <t>Installer training and demo unit per new partner</t>
         </is>
       </c>
       <c r="C131" s="18" t="inlineStr">
         <is>
-          <t>EUR/month</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D131" s="23" t="n">
-        <v>700</v>
+        <v>3500</v>
       </c>
       <c r="E131" s="23" t="n">
-        <v>700</v>
+        <v>3500</v>
       </c>
       <c r="F131" s="24">
         <f>IF(Assumptions!$E$5=2,E131,D131)</f>
@@ -4223,7 +4207,7 @@
     <row r="132">
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>IT and software per person</t>
+          <t>Finance and legal</t>
         </is>
       </c>
       <c r="C132" s="18" t="inlineStr">
@@ -4232,10 +4216,10 @@
         </is>
       </c>
       <c r="D132" s="23" t="n">
-        <v>250</v>
+        <v>7000</v>
       </c>
       <c r="E132" s="23" t="n">
-        <v>250</v>
+        <v>7000</v>
       </c>
       <c r="F132" s="24">
         <f>IF(Assumptions!$E$5=2,E132,D132)</f>
@@ -4245,7 +4229,7 @@
     <row r="133">
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Travel per person</t>
+          <t>Other general</t>
         </is>
       </c>
       <c r="C133" s="18" t="inlineStr">
@@ -4254,10 +4238,10 @@
         </is>
       </c>
       <c r="D133" s="23" t="n">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="E133" s="23" t="n">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="F133" s="24">
         <f>IF(Assumptions!$E$5=2,E133,D133)</f>
@@ -4267,12 +4251,12 @@
     <row r="134">
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Recruitment per net new hire</t>
+          <t>Ongoing development</t>
         </is>
       </c>
       <c r="C134" s="18" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>EUR/month</t>
         </is>
       </c>
       <c r="D134" s="23" t="n">
@@ -4289,19 +4273,19 @@
     <row r="135">
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Installer training and demo unit per new partner</t>
+          <t>Third party product development</t>
         </is>
       </c>
       <c r="C135" s="18" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>EUR/month</t>
         </is>
       </c>
       <c r="D135" s="23" t="n">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="E135" s="23" t="n">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="F135" s="24">
         <f>IF(Assumptions!$E$5=2,E135,D135)</f>
@@ -4311,87 +4295,81 @@
     <row r="136">
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Finance and legal</t>
+          <t>Annual increase on the costs above</t>
         </is>
       </c>
       <c r="C136" s="18" t="inlineStr">
         <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D136" s="23" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E136" s="23" t="n">
-        <v>7000</v>
-      </c>
-      <c r="F136" s="24">
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D136" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E136" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F136" s="26">
         <f>IF(Assumptions!$E$5=2,E136,D136)</f>
         <v/>
       </c>
     </row>
     <row r="137">
-      <c r="B137" s="9" t="inlineStr">
-        <is>
-          <t>Other general</t>
-        </is>
-      </c>
-      <c r="C137" s="18" t="inlineStr">
-        <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D137" s="23" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E137" s="23" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F137" s="24">
-        <f>IF(Assumptions!$E$5=2,E137,D137)</f>
-        <v/>
-      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>FUNDING</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="n"/>
+      <c r="D137" s="1" t="n"/>
+      <c r="E137" s="1" t="n"/>
+      <c r="F137" s="1" t="n"/>
+      <c r="G137" s="1" t="n"/>
+      <c r="H137" s="1" t="n"/>
+      <c r="I137" s="1" t="n"/>
+      <c r="J137" s="1" t="n"/>
     </row>
     <row r="138">
-      <c r="B138" s="9" t="inlineStr">
-        <is>
-          <t>Ongoing development</t>
-        </is>
-      </c>
-      <c r="C138" s="18" t="inlineStr">
-        <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D138" s="23" t="n">
-        <v>8000</v>
-      </c>
-      <c r="E138" s="23" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F138" s="24">
-        <f>IF(Assumptions!$E$5=2,E138,D138)</f>
-        <v/>
-      </c>
+      <c r="B138" s="21" t="n"/>
+      <c r="C138" s="21" t="n"/>
+      <c r="D138" s="22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E138" s="22" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F138" s="22" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="G138" s="21" t="n"/>
+      <c r="H138" s="21" t="n"/>
+      <c r="I138" s="21" t="n"/>
+      <c r="J138" s="21" t="n"/>
     </row>
     <row r="139">
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>Third party product development</t>
+          <t>First round, money in</t>
         </is>
       </c>
       <c r="C139" s="18" t="inlineStr">
         <is>
-          <t>EUR/month</t>
-        </is>
-      </c>
-      <c r="D139" s="23" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E139" s="23" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F139" s="24">
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D139" s="27" t="n">
+        <v>46143</v>
+      </c>
+      <c r="E139" s="27" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F139" s="28">
         <f>IF(Assumptions!$E$5=2,E139,D139)</f>
         <v/>
       </c>
@@ -4399,81 +4377,92 @@
     <row r="140">
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>Annual increase on the costs above</t>
+          <t>First round, amount</t>
         </is>
       </c>
       <c r="C140" s="18" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D140" s="25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E140" s="25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F140" s="26">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D140" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E140" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F140" s="24">
         <f>IF(Assumptions!$E$5=2,E140,D140)</f>
         <v/>
       </c>
     </row>
     <row r="141">
-      <c r="B141" s="7" t="inlineStr">
-        <is>
-          <t>FUNDING</t>
-        </is>
-      </c>
-      <c r="C141" s="1" t="n"/>
-      <c r="D141" s="1" t="n"/>
-      <c r="E141" s="1" t="n"/>
-      <c r="F141" s="1" t="n"/>
-      <c r="G141" s="1" t="n"/>
-      <c r="H141" s="1" t="n"/>
-      <c r="I141" s="1" t="n"/>
-      <c r="J141" s="1" t="n"/>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>Second round, money in</t>
+        </is>
+      </c>
+      <c r="C141" s="18" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D141" s="27" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E141" s="27" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F141" s="28">
+        <f>IF(Assumptions!$E$5=2,E141,D141)</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
-      <c r="B142" s="21" t="n"/>
-      <c r="C142" s="21" t="n"/>
-      <c r="D142" s="22" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E142" s="22" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="F142" s="22" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="G142" s="21" t="n"/>
-      <c r="H142" s="21" t="n"/>
-      <c r="I142" s="21" t="n"/>
-      <c r="J142" s="21" t="n"/>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>Second round, amount</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D142" s="23" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E142" s="23" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F142" s="24">
+        <f>IF(Assumptions!$E$5=2,E142,D142)</f>
+        <v/>
+      </c>
+      <c r="J142" s="20" t="inlineStr">
+        <is>
+          <t>this is the raise the model is built to justify</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>First round, money in</t>
+          <t>Convertible loan drawn</t>
         </is>
       </c>
       <c r="C143" s="18" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D143" s="27" t="n">
-        <v>46143</v>
-      </c>
-      <c r="E143" s="27" t="n">
-        <v>46143</v>
-      </c>
-      <c r="F143" s="28">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D143" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E143" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F143" s="24">
         <f>IF(Assumptions!$E$5=2,E143,D143)</f>
         <v/>
       </c>
@@ -4481,115 +4470,22 @@
     <row r="144">
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>First round, amount</t>
+          <t>Loan drawn on</t>
         </is>
       </c>
       <c r="C144" s="18" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D144" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E144" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F144" s="24">
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D144" s="27" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E144" s="27" t="n">
+        <v>46204</v>
+      </c>
+      <c r="F144" s="28">
         <f>IF(Assumptions!$E$5=2,E144,D144)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145">
-      <c r="B145" s="9" t="inlineStr">
-        <is>
-          <t>Second round, money in</t>
-        </is>
-      </c>
-      <c r="C145" s="18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D145" s="27" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E145" s="27" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F145" s="28">
-        <f>IF(Assumptions!$E$5=2,E145,D145)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="B146" s="9" t="inlineStr">
-        <is>
-          <t>Second round, amount</t>
-        </is>
-      </c>
-      <c r="C146" s="18" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D146" s="23" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="E146" s="23" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="F146" s="24">
-        <f>IF(Assumptions!$E$5=2,E146,D146)</f>
-        <v/>
-      </c>
-      <c r="J146" s="20" t="inlineStr">
-        <is>
-          <t>this is the raise the model is built to justify</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="B147" s="9" t="inlineStr">
-        <is>
-          <t>Convertible loan drawn</t>
-        </is>
-      </c>
-      <c r="C147" s="18" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D147" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E147" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F147" s="24">
-        <f>IF(Assumptions!$E$5=2,E147,D147)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="B148" s="9" t="inlineStr">
-        <is>
-          <t>Loan drawn on</t>
-        </is>
-      </c>
-      <c r="C148" s="18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D148" s="27" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E148" s="27" t="n">
-        <v>46204</v>
-      </c>
-      <c r="F148" s="28">
-        <f>IF(Assumptions!$E$5=2,E148,D148)</f>
         <v/>
       </c>
     </row>
@@ -11682,243 +11578,243 @@
         </is>
       </c>
       <c r="E35" s="43">
-        <f>IF(E$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(E$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(E$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(E$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="F35" s="43">
-        <f>IF(F$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(F$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(F$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(F$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="G35" s="43">
-        <f>IF(G$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(G$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(G$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(G$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="H35" s="43">
-        <f>IF(H$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(H$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(H$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(H$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="I35" s="43">
-        <f>IF(I$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(I$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(I$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(I$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="J35" s="43">
-        <f>IF(J$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(J$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(J$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(J$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="K35" s="43">
-        <f>IF(K$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(K$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(K$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(K$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="L35" s="43">
-        <f>IF(L$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(L$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(L$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(L$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="M35" s="43">
-        <f>IF(M$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(M$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(M$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(M$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="N35" s="43">
-        <f>IF(N$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(N$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(N$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(N$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="O35" s="43">
-        <f>IF(O$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(O$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(O$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(O$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="P35" s="43">
-        <f>IF(P$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(P$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(P$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(P$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="Q35" s="43">
-        <f>IF(Q$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(Q$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(Q$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(Q$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="R35" s="43">
-        <f>IF(R$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(R$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(R$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(R$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="S35" s="43">
-        <f>IF(S$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(S$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(S$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(S$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="T35" s="43">
-        <f>IF(T$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(T$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(T$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(T$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="U35" s="43">
-        <f>IF(U$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(U$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(U$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(U$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="V35" s="43">
-        <f>IF(V$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(V$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(V$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(V$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="W35" s="43">
-        <f>IF(W$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(W$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(W$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(W$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="X35" s="43">
-        <f>IF(X$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(X$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(X$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(X$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="Y35" s="43">
-        <f>IF(Y$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(Y$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(Y$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(Y$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="Z35" s="43">
-        <f>IF(Z$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(Z$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(Z$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(Z$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AA35" s="43">
-        <f>IF(AA$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AA$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AA$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AA$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AB35" s="43">
-        <f>IF(AB$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AB$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AB$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AB$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AC35" s="43">
-        <f>IF(AC$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AC$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AC$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AC$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AD35" s="43">
-        <f>IF(AD$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AD$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AD$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AD$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AE35" s="43">
-        <f>IF(AE$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AE$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AE$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AE$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AF35" s="43">
-        <f>IF(AF$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AF$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AF$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AF$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AG35" s="43">
-        <f>IF(AG$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AG$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AG$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AG$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AH35" s="43">
-        <f>IF(AH$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AH$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AH$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AH$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AI35" s="43">
-        <f>IF(AI$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AI$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AI$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AI$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AJ35" s="43">
-        <f>IF(AJ$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AJ$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AJ$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AJ$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AK35" s="43">
-        <f>IF(AK$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AK$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AK$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AK$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AL35" s="43">
-        <f>IF(AL$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AL$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AL$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AL$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AM35" s="43">
-        <f>IF(AM$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AM$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AM$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AM$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AN35" s="43">
-        <f>IF(AN$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AN$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AN$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AN$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AO35" s="43">
-        <f>IF(AO$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AO$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AO$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AO$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AP35" s="43">
-        <f>IF(AP$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AP$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AP$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AP$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AQ35" s="43">
-        <f>IF(AQ$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AQ$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AQ$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AQ$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AR35" s="43">
-        <f>IF(AR$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AR$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AR$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AR$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AS35" s="43">
-        <f>IF(AS$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AS$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AS$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AS$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AT35" s="43">
-        <f>IF(AT$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AT$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AT$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AT$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AU35" s="43">
-        <f>IF(AU$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AU$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AU$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AU$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AV35" s="43">
-        <f>IF(AV$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AV$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AV$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AV$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AW35" s="43">
-        <f>IF(AW$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AW$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AW$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AW$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AX35" s="43">
-        <f>IF(AX$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AX$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AX$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AX$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AY35" s="43">
-        <f>IF(AY$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AY$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AY$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AY$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="AZ35" s="43">
-        <f>IF(AZ$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(AZ$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(AZ$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(AZ$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BA35" s="43">
-        <f>IF(BA$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BA$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(BA$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(BA$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BB35" s="43">
-        <f>IF(BB$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BB$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(BB$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(BB$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BC35" s="43">
-        <f>IF(BC$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BC$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(BC$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(BC$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BD35" s="43">
-        <f>IF(BD$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BD$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(BD$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(BD$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BE35" s="43">
-        <f>IF(BE$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BE$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(BE$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(BE$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BF35" s="43">
-        <f>IF(BF$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BF$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(BF$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(BF$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BG35" s="43">
-        <f>IF(BG$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BG$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(BG$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(BG$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BH35" s="43">
-        <f>IF(BH$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BH$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(BH$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(BH$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BI35" s="43">
-        <f>IF(BI$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BI$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(BI$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(BI$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BJ35" s="43">
-        <f>IF(BJ$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BJ$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(BJ$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(BJ$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BK35" s="43">
-        <f>IF(BK$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BK$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(BK$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(BK$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BL35" s="43">
-        <f>IF(BL$3=Assumptions!$F$143,Assumptions!$F$144,0)+IF(BL$3=Assumptions!$F$145,Assumptions!$F$146,0)</f>
+        <f>IF(BL$3=Assumptions!$F$139,Assumptions!$F$140,0)+IF(BL$3=Assumptions!$F$141,Assumptions!$F$142,0)</f>
         <v/>
       </c>
       <c r="BN35" s="44">
@@ -11959,243 +11855,243 @@
         </is>
       </c>
       <c r="E36" s="43">
-        <f>IF(E$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(E$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="F36" s="43">
-        <f>IF(F$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(F$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="G36" s="43">
-        <f>IF(G$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(G$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="H36" s="43">
-        <f>IF(H$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(H$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="I36" s="43">
-        <f>IF(I$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(I$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="J36" s="43">
-        <f>IF(J$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(J$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="K36" s="43">
-        <f>IF(K$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(K$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="L36" s="43">
-        <f>IF(L$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(L$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="M36" s="43">
-        <f>IF(M$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(M$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="N36" s="43">
-        <f>IF(N$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(N$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="O36" s="43">
-        <f>IF(O$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(O$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="P36" s="43">
-        <f>IF(P$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(P$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="Q36" s="43">
-        <f>IF(Q$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(Q$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="R36" s="43">
-        <f>IF(R$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(R$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="S36" s="43">
-        <f>IF(S$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(S$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="T36" s="43">
-        <f>IF(T$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(T$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="U36" s="43">
-        <f>IF(U$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(U$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="V36" s="43">
-        <f>IF(V$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(V$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="W36" s="43">
-        <f>IF(W$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(W$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="X36" s="43">
-        <f>IF(X$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(X$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="Y36" s="43">
-        <f>IF(Y$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(Y$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="Z36" s="43">
-        <f>IF(Z$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(Z$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AA36" s="43">
-        <f>IF(AA$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AA$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AB36" s="43">
-        <f>IF(AB$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AB$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AC36" s="43">
-        <f>IF(AC$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AC$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AD36" s="43">
-        <f>IF(AD$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AD$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AE36" s="43">
-        <f>IF(AE$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AE$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AF36" s="43">
-        <f>IF(AF$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AF$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AG36" s="43">
-        <f>IF(AG$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AG$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AH36" s="43">
-        <f>IF(AH$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AH$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AI36" s="43">
-        <f>IF(AI$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AI$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AJ36" s="43">
-        <f>IF(AJ$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AJ$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AK36" s="43">
-        <f>IF(AK$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AK$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AL36" s="43">
-        <f>IF(AL$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AL$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AM36" s="43">
-        <f>IF(AM$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AM$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AN36" s="43">
-        <f>IF(AN$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AN$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AO36" s="43">
-        <f>IF(AO$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AO$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AP36" s="43">
-        <f>IF(AP$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AP$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AQ36" s="43">
-        <f>IF(AQ$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AQ$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AR36" s="43">
-        <f>IF(AR$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AR$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AS36" s="43">
-        <f>IF(AS$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AS$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AT36" s="43">
-        <f>IF(AT$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AT$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AU36" s="43">
-        <f>IF(AU$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AU$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AV36" s="43">
-        <f>IF(AV$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AV$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AW36" s="43">
-        <f>IF(AW$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AW$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AX36" s="43">
-        <f>IF(AX$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AX$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AY36" s="43">
-        <f>IF(AY$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AY$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="AZ36" s="43">
-        <f>IF(AZ$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(AZ$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BA36" s="43">
-        <f>IF(BA$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(BA$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BB36" s="43">
-        <f>IF(BB$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(BB$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BC36" s="43">
-        <f>IF(BC$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(BC$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BD36" s="43">
-        <f>IF(BD$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(BD$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BE36" s="43">
-        <f>IF(BE$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(BE$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BF36" s="43">
-        <f>IF(BF$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(BF$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BG36" s="43">
-        <f>IF(BG$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(BG$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BH36" s="43">
-        <f>IF(BH$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(BH$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BI36" s="43">
-        <f>IF(BI$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(BI$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BJ36" s="43">
-        <f>IF(BJ$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(BJ$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BK36" s="43">
-        <f>IF(BK$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(BK$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BL36" s="43">
-        <f>IF(BL$3=Assumptions!$F$148,Assumptions!$F$147,0)</f>
+        <f>IF(BL$3=Assumptions!$F$144,Assumptions!$F$143,0)</f>
         <v/>
       </c>
       <c r="BN36" s="44">
@@ -34534,243 +34430,243 @@
         </is>
       </c>
       <c r="E13" s="43">
-        <f>'Revenue Forecast'!E19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!E19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="F13" s="43">
-        <f>'Revenue Forecast'!F19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!F19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="G13" s="43">
-        <f>'Revenue Forecast'!G19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!G19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="H13" s="43">
-        <f>'Revenue Forecast'!H19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!H19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="I13" s="43">
-        <f>'Revenue Forecast'!I19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!I19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="J13" s="43">
-        <f>'Revenue Forecast'!J19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!J19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="K13" s="43">
-        <f>'Revenue Forecast'!K19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!K19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="L13" s="43">
-        <f>'Revenue Forecast'!L19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!L19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="M13" s="43">
-        <f>'Revenue Forecast'!M19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!M19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="N13" s="43">
-        <f>'Revenue Forecast'!N19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!N19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="O13" s="43">
-        <f>'Revenue Forecast'!O19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!O19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="P13" s="43">
-        <f>'Revenue Forecast'!P19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!P19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="Q13" s="43">
-        <f>'Revenue Forecast'!Q19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!Q19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="R13" s="43">
-        <f>'Revenue Forecast'!R19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!R19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="S13" s="43">
-        <f>'Revenue Forecast'!S19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!S19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="T13" s="43">
-        <f>'Revenue Forecast'!T19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!T19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="U13" s="43">
-        <f>'Revenue Forecast'!U19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!U19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="V13" s="43">
-        <f>'Revenue Forecast'!V19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!V19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="W13" s="43">
-        <f>'Revenue Forecast'!W19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!W19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="X13" s="43">
-        <f>'Revenue Forecast'!X19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!X19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="Y13" s="43">
-        <f>'Revenue Forecast'!Y19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!Y19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="Z13" s="43">
-        <f>'Revenue Forecast'!Z19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!Z19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AA13" s="43">
-        <f>'Revenue Forecast'!AA19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AA19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AB13" s="43">
-        <f>'Revenue Forecast'!AB19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AB19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AC13" s="43">
-        <f>'Revenue Forecast'!AC19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AC19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AD13" s="43">
-        <f>'Revenue Forecast'!AD19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AD19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AE13" s="43">
-        <f>'Revenue Forecast'!AE19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AE19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AF13" s="43">
-        <f>'Revenue Forecast'!AF19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AF19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AG13" s="43">
-        <f>'Revenue Forecast'!AG19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AG19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AH13" s="43">
-        <f>'Revenue Forecast'!AH19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AH19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AI13" s="43">
-        <f>'Revenue Forecast'!AI19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AI19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AJ13" s="43">
-        <f>'Revenue Forecast'!AJ19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AJ19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AK13" s="43">
-        <f>'Revenue Forecast'!AK19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AK19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AL13" s="43">
-        <f>'Revenue Forecast'!AL19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AL19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AM13" s="43">
-        <f>'Revenue Forecast'!AM19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AM19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AN13" s="43">
-        <f>'Revenue Forecast'!AN19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AN19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AO13" s="43">
-        <f>'Revenue Forecast'!AO19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AO19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AP13" s="43">
-        <f>'Revenue Forecast'!AP19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AP19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AQ13" s="43">
-        <f>'Revenue Forecast'!AQ19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AQ19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AR13" s="43">
-        <f>'Revenue Forecast'!AR19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AR19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AS13" s="43">
-        <f>'Revenue Forecast'!AS19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AS19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AT13" s="43">
-        <f>'Revenue Forecast'!AT19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AT19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AU13" s="43">
-        <f>'Revenue Forecast'!AU19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AU19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AV13" s="43">
-        <f>'Revenue Forecast'!AV19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AV19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AW13" s="43">
-        <f>'Revenue Forecast'!AW19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AW19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AX13" s="43">
-        <f>'Revenue Forecast'!AX19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AX19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AY13" s="43">
-        <f>'Revenue Forecast'!AY19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AY19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="AZ13" s="43">
-        <f>'Revenue Forecast'!AZ19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!AZ19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BA13" s="43">
-        <f>'Revenue Forecast'!BA19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!BA19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BB13" s="43">
-        <f>'Revenue Forecast'!BB19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!BB19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BC13" s="43">
-        <f>'Revenue Forecast'!BC19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!BC19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BD13" s="43">
-        <f>'Revenue Forecast'!BD19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!BD19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BE13" s="43">
-        <f>'Revenue Forecast'!BE19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!BE19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BF13" s="43">
-        <f>'Revenue Forecast'!BF19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!BF19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BG13" s="43">
-        <f>'Revenue Forecast'!BG19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!BG19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BH13" s="43">
-        <f>'Revenue Forecast'!BH19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!BH19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BI13" s="43">
-        <f>'Revenue Forecast'!BI19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!BI19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BJ13" s="43">
-        <f>'Revenue Forecast'!BJ19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!BJ19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BK13" s="43">
-        <f>'Revenue Forecast'!BK19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!BK19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BL13" s="43">
-        <f>'Revenue Forecast'!BL19*Assumptions!$F$135</f>
+        <f>'Revenue Forecast'!BL19*Assumptions!$F$131</f>
         <v/>
       </c>
       <c r="BN13" s="44">
@@ -35154,243 +35050,243 @@
         </is>
       </c>
       <c r="E17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(E$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(F$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(G$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(H$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(I$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(J$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(K$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(L$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(M$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(N$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(O$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(P$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(Q$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(R$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(S$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(T$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(U$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(V$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(W$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(X$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(Y$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(Z$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AA$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AB$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AC$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AD$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AE$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AF$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AG$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AH$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AI$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AJ$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AK$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AL$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AM$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AN$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AO$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AP$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AQ$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AR$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AS$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AT$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AU$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AV$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AW$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AX$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AY$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(AZ$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BA$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BB$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BC$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BD$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BE$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BF$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BG$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BH$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BI$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BJ$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BK$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL17" s="43">
-        <f>Assumptions!$F$138*(1+Assumptions!$F$140)^(YEAR(BL$3)-2026)</f>
+        <f>Assumptions!$F$134*(1+Assumptions!$F$136)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN17" s="44">
@@ -35426,243 +35322,243 @@
         </is>
       </c>
       <c r="E18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(E$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(F$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(G$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(H$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(I$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(J$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(K$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(L$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(M$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(N$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(O$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(P$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(Q$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(R$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(S$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(T$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(U$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(V$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(W$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(X$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(Y$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(Z$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AA$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AB$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AC$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AD$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AE$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AF$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AG$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AH$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AI$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AJ$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AK$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AL$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AM$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AN$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AO$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AP$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AQ$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AR$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AS$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AT$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AU$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AV$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AW$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AX$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AY$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(AZ$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BA$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BB$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BC$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BD$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BE$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BF$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BG$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BH$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BI$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BJ$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BK$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL18" s="43">
-        <f>Assumptions!$F$139*(1+Assumptions!$F$140)^(YEAR(BL$3)-2026)</f>
+        <f>Assumptions!$F$135*(1+Assumptions!$F$136)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN18" s="44">
@@ -36046,243 +35942,243 @@
         </is>
       </c>
       <c r="E22" s="43">
-        <f>Personnel!E20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!E20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="F22" s="43">
-        <f>Personnel!F20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!F20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="G22" s="43">
-        <f>Personnel!G20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!G20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="H22" s="43">
-        <f>Personnel!H20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!H20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="I22" s="43">
-        <f>Personnel!I20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!I20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="J22" s="43">
-        <f>Personnel!J20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!J20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="K22" s="43">
-        <f>Personnel!K20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!K20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="L22" s="43">
-        <f>Personnel!L20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!L20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="M22" s="43">
-        <f>Personnel!M20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!M20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="N22" s="43">
-        <f>Personnel!N20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!N20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="O22" s="43">
-        <f>Personnel!O20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!O20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="P22" s="43">
-        <f>Personnel!P20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!P20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="Q22" s="43">
-        <f>Personnel!Q20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!Q20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="R22" s="43">
-        <f>Personnel!R20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!R20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="S22" s="43">
-        <f>Personnel!S20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!S20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="T22" s="43">
-        <f>Personnel!T20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!T20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="U22" s="43">
-        <f>Personnel!U20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!U20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="V22" s="43">
-        <f>Personnel!V20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!V20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="W22" s="43">
-        <f>Personnel!W20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!W20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="X22" s="43">
-        <f>Personnel!X20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!X20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="Y22" s="43">
-        <f>Personnel!Y20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!Y20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="Z22" s="43">
-        <f>Personnel!Z20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!Z20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AA22" s="43">
-        <f>Personnel!AA20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AA20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AB22" s="43">
-        <f>Personnel!AB20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AB20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AC22" s="43">
-        <f>Personnel!AC20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AC20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AD22" s="43">
-        <f>Personnel!AD20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AD20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AE22" s="43">
-        <f>Personnel!AE20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AE20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AF22" s="43">
-        <f>Personnel!AF20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AF20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AG22" s="43">
-        <f>Personnel!AG20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AG20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AH22" s="43">
-        <f>Personnel!AH20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AH20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AI22" s="43">
-        <f>Personnel!AI20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AI20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AJ22" s="43">
-        <f>Personnel!AJ20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AJ20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AK22" s="43">
-        <f>Personnel!AK20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AK20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AL22" s="43">
-        <f>Personnel!AL20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AL20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AM22" s="43">
-        <f>Personnel!AM20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AM20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AN22" s="43">
-        <f>Personnel!AN20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AN20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AO22" s="43">
-        <f>Personnel!AO20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AO20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AP22" s="43">
-        <f>Personnel!AP20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AP20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AQ22" s="43">
-        <f>Personnel!AQ20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AQ20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AR22" s="43">
-        <f>Personnel!AR20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AR20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AS22" s="43">
-        <f>Personnel!AS20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AS20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AT22" s="43">
-        <f>Personnel!AT20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AT20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AU22" s="43">
-        <f>Personnel!AU20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AU20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AV22" s="43">
-        <f>Personnel!AV20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AV20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AW22" s="43">
-        <f>Personnel!AW20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AW20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AX22" s="43">
-        <f>Personnel!AX20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AX20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AY22" s="43">
-        <f>Personnel!AY20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AY20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="AZ22" s="43">
-        <f>Personnel!AZ20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!AZ20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BA22" s="43">
-        <f>Personnel!BA20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!BA20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BB22" s="43">
-        <f>Personnel!BB20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!BB20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BC22" s="43">
-        <f>Personnel!BC20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!BC20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BD22" s="43">
-        <f>Personnel!BD20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!BD20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BE22" s="43">
-        <f>Personnel!BE20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!BE20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BF22" s="43">
-        <f>Personnel!BF20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!BF20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BG22" s="43">
-        <f>Personnel!BG20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!BG20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BH22" s="43">
-        <f>Personnel!BH20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!BH20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BI22" s="43">
-        <f>Personnel!BI20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!BI20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BJ22" s="43">
-        <f>Personnel!BJ20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!BJ20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BK22" s="43">
-        <f>Personnel!BK20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!BK20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BL22" s="43">
-        <f>Personnel!BL20*(Assumptions!$F$131+Assumptions!$F$132+Assumptions!$F$133)</f>
+        <f>Personnel!BL20*(Assumptions!$F$127+Assumptions!$F$128+Assumptions!$F$129)</f>
         <v/>
       </c>
       <c r="BN22" s="44">
@@ -36327,239 +36223,239 @@
         <v/>
       </c>
       <c r="F23" s="43">
-        <f>MAX(0,Personnel!F20-Personnel!E20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!F20-Personnel!E20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="G23" s="43">
-        <f>MAX(0,Personnel!G20-Personnel!F20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!G20-Personnel!F20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="H23" s="43">
-        <f>MAX(0,Personnel!H20-Personnel!G20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!H20-Personnel!G20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="I23" s="43">
-        <f>MAX(0,Personnel!I20-Personnel!H20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!I20-Personnel!H20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="J23" s="43">
-        <f>MAX(0,Personnel!J20-Personnel!I20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!J20-Personnel!I20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="K23" s="43">
-        <f>MAX(0,Personnel!K20-Personnel!J20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!K20-Personnel!J20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="L23" s="43">
-        <f>MAX(0,Personnel!L20-Personnel!K20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!L20-Personnel!K20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="M23" s="43">
-        <f>MAX(0,Personnel!M20-Personnel!L20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!M20-Personnel!L20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="N23" s="43">
-        <f>MAX(0,Personnel!N20-Personnel!M20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!N20-Personnel!M20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="O23" s="43">
-        <f>MAX(0,Personnel!O20-Personnel!N20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!O20-Personnel!N20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="P23" s="43">
-        <f>MAX(0,Personnel!P20-Personnel!O20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!P20-Personnel!O20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="Q23" s="43">
-        <f>MAX(0,Personnel!Q20-Personnel!P20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!Q20-Personnel!P20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="R23" s="43">
-        <f>MAX(0,Personnel!R20-Personnel!Q20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!R20-Personnel!Q20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="S23" s="43">
-        <f>MAX(0,Personnel!S20-Personnel!R20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!S20-Personnel!R20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="T23" s="43">
-        <f>MAX(0,Personnel!T20-Personnel!S20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!T20-Personnel!S20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="U23" s="43">
-        <f>MAX(0,Personnel!U20-Personnel!T20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!U20-Personnel!T20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="V23" s="43">
-        <f>MAX(0,Personnel!V20-Personnel!U20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!V20-Personnel!U20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="W23" s="43">
-        <f>MAX(0,Personnel!W20-Personnel!V20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!W20-Personnel!V20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="X23" s="43">
-        <f>MAX(0,Personnel!X20-Personnel!W20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!X20-Personnel!W20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="Y23" s="43">
-        <f>MAX(0,Personnel!Y20-Personnel!X20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!Y20-Personnel!X20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="Z23" s="43">
-        <f>MAX(0,Personnel!Z20-Personnel!Y20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!Z20-Personnel!Y20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AA23" s="43">
-        <f>MAX(0,Personnel!AA20-Personnel!Z20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AA20-Personnel!Z20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AB23" s="43">
-        <f>MAX(0,Personnel!AB20-Personnel!AA20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AB20-Personnel!AA20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AC23" s="43">
-        <f>MAX(0,Personnel!AC20-Personnel!AB20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AC20-Personnel!AB20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AD23" s="43">
-        <f>MAX(0,Personnel!AD20-Personnel!AC20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AD20-Personnel!AC20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AE23" s="43">
-        <f>MAX(0,Personnel!AE20-Personnel!AD20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AE20-Personnel!AD20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AF23" s="43">
-        <f>MAX(0,Personnel!AF20-Personnel!AE20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AF20-Personnel!AE20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AG23" s="43">
-        <f>MAX(0,Personnel!AG20-Personnel!AF20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AG20-Personnel!AF20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AH23" s="43">
-        <f>MAX(0,Personnel!AH20-Personnel!AG20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AH20-Personnel!AG20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AI23" s="43">
-        <f>MAX(0,Personnel!AI20-Personnel!AH20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AI20-Personnel!AH20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AJ23" s="43">
-        <f>MAX(0,Personnel!AJ20-Personnel!AI20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AJ20-Personnel!AI20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AK23" s="43">
-        <f>MAX(0,Personnel!AK20-Personnel!AJ20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AK20-Personnel!AJ20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AL23" s="43">
-        <f>MAX(0,Personnel!AL20-Personnel!AK20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AL20-Personnel!AK20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AM23" s="43">
-        <f>MAX(0,Personnel!AM20-Personnel!AL20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AM20-Personnel!AL20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AN23" s="43">
-        <f>MAX(0,Personnel!AN20-Personnel!AM20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AN20-Personnel!AM20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AO23" s="43">
-        <f>MAX(0,Personnel!AO20-Personnel!AN20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AO20-Personnel!AN20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AP23" s="43">
-        <f>MAX(0,Personnel!AP20-Personnel!AO20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AP20-Personnel!AO20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AQ23" s="43">
-        <f>MAX(0,Personnel!AQ20-Personnel!AP20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AQ20-Personnel!AP20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AR23" s="43">
-        <f>MAX(0,Personnel!AR20-Personnel!AQ20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AR20-Personnel!AQ20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AS23" s="43">
-        <f>MAX(0,Personnel!AS20-Personnel!AR20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AS20-Personnel!AR20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AT23" s="43">
-        <f>MAX(0,Personnel!AT20-Personnel!AS20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AT20-Personnel!AS20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AU23" s="43">
-        <f>MAX(0,Personnel!AU20-Personnel!AT20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AU20-Personnel!AT20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AV23" s="43">
-        <f>MAX(0,Personnel!AV20-Personnel!AU20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AV20-Personnel!AU20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AW23" s="43">
-        <f>MAX(0,Personnel!AW20-Personnel!AV20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AW20-Personnel!AV20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AX23" s="43">
-        <f>MAX(0,Personnel!AX20-Personnel!AW20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AX20-Personnel!AW20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AY23" s="43">
-        <f>MAX(0,Personnel!AY20-Personnel!AX20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AY20-Personnel!AX20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="AZ23" s="43">
-        <f>MAX(0,Personnel!AZ20-Personnel!AY20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!AZ20-Personnel!AY20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BA23" s="43">
-        <f>MAX(0,Personnel!BA20-Personnel!AZ20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!BA20-Personnel!AZ20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BB23" s="43">
-        <f>MAX(0,Personnel!BB20-Personnel!BA20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!BB20-Personnel!BA20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BC23" s="43">
-        <f>MAX(0,Personnel!BC20-Personnel!BB20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!BC20-Personnel!BB20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BD23" s="43">
-        <f>MAX(0,Personnel!BD20-Personnel!BC20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!BD20-Personnel!BC20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BE23" s="43">
-        <f>MAX(0,Personnel!BE20-Personnel!BD20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!BE20-Personnel!BD20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BF23" s="43">
-        <f>MAX(0,Personnel!BF20-Personnel!BE20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!BF20-Personnel!BE20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BG23" s="43">
-        <f>MAX(0,Personnel!BG20-Personnel!BF20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!BG20-Personnel!BF20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BH23" s="43">
-        <f>MAX(0,Personnel!BH20-Personnel!BG20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!BH20-Personnel!BG20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BI23" s="43">
-        <f>MAX(0,Personnel!BI20-Personnel!BH20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!BI20-Personnel!BH20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BJ23" s="43">
-        <f>MAX(0,Personnel!BJ20-Personnel!BI20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!BJ20-Personnel!BI20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BK23" s="43">
-        <f>MAX(0,Personnel!BK20-Personnel!BJ20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!BK20-Personnel!BJ20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BL23" s="43">
-        <f>MAX(0,Personnel!BL20-Personnel!BK20)*Assumptions!$F$134</f>
+        <f>MAX(0,Personnel!BL20-Personnel!BK20)*Assumptions!$F$130</f>
         <v/>
       </c>
       <c r="BN23" s="44">
@@ -36872,243 +36768,243 @@
         </is>
       </c>
       <c r="E25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(E$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(F$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(G$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(H$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(I$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(J$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(K$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(L$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(M$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(N$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(O$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(P$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(Q$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(R$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(S$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(T$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(U$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(V$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(W$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(X$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(Y$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(Z$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AA$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AB$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AC$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AD$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AE$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AF$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AG$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AH$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AI$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AJ$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AK$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AL$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AM$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AN$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AO$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AP$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AQ$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AR$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AS$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AT$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AU$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AV$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AW$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AX$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AY$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(AZ$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BA$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BB$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BC$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BD$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BE$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BF$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BG$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BH$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BI$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BJ$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BK$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL25" s="43">
-        <f>Assumptions!$F$136*(1+Assumptions!$F$140)^(YEAR(BL$3)-2026)</f>
+        <f>Assumptions!$F$132*(1+Assumptions!$F$136)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN25" s="44">
@@ -37144,243 +37040,243 @@
         </is>
       </c>
       <c r="E26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(E$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(F$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(G$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(H$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(I$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(J$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(K$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(L$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(M$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(N$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(O$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(P$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(Q$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(R$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(S$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(T$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(U$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(V$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(W$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(X$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(Y$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(Z$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AA$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AB$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AC$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AD$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AE$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AF$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AG$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AH$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AI$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AJ$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AK$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AL$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AM$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AN$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AO$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AP$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AQ$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AR$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AS$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AT$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AU$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AV$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AW$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AX$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AY$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(AZ$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BA$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BB$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BC$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BD$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BE$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BF$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BG$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BH$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BI$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BJ$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BK$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL26" s="43">
-        <f>Assumptions!$F$137*(1+Assumptions!$F$140)^(YEAR(BL$3)-2026)</f>
+        <f>Assumptions!$F$133*(1+Assumptions!$F$136)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN26" s="44">
@@ -40642,7 +40538,7 @@
     <row r="2">
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Headcount by team. Every number is driven by whatever creates the work: units, installed base, partners signed or marketing spend.</t>
+          <t>Headcount by team. Every number is driven by whatever creates the work: units, installed base, partners signed or marketing spend. The back office is typed in directly.</t>
         </is>
       </c>
     </row>
@@ -43952,245 +43848,185 @@
           <t>FTE</t>
         </is>
       </c>
-      <c r="E17" s="54">
-        <f>HLOOKUP(YEAR(E$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F17" s="54">
-        <f>HLOOKUP(YEAR(F$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="G17" s="54">
-        <f>HLOOKUP(YEAR(G$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="H17" s="54">
-        <f>HLOOKUP(YEAR(H$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I17" s="54">
-        <f>HLOOKUP(YEAR(I$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="J17" s="54">
-        <f>HLOOKUP(YEAR(J$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="K17" s="54">
-        <f>HLOOKUP(YEAR(K$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="L17" s="54">
-        <f>HLOOKUP(YEAR(L$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="M17" s="54">
-        <f>HLOOKUP(YEAR(M$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="N17" s="54">
-        <f>HLOOKUP(YEAR(N$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="O17" s="54">
-        <f>HLOOKUP(YEAR(O$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="P17" s="54">
-        <f>HLOOKUP(YEAR(P$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="54">
-        <f>HLOOKUP(YEAR(Q$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="R17" s="54">
-        <f>HLOOKUP(YEAR(R$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="S17" s="54">
-        <f>HLOOKUP(YEAR(S$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="T17" s="54">
-        <f>HLOOKUP(YEAR(T$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="U17" s="54">
-        <f>HLOOKUP(YEAR(U$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V17" s="54">
-        <f>HLOOKUP(YEAR(V$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="W17" s="54">
-        <f>HLOOKUP(YEAR(W$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X17" s="54">
-        <f>HLOOKUP(YEAR(X$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="Y17" s="54">
-        <f>HLOOKUP(YEAR(Y$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="Z17" s="54">
-        <f>HLOOKUP(YEAR(Z$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AA17" s="54">
-        <f>HLOOKUP(YEAR(AA$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB17" s="54">
-        <f>HLOOKUP(YEAR(AB$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC17" s="54">
-        <f>HLOOKUP(YEAR(AC$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AD17" s="54">
-        <f>HLOOKUP(YEAR(AD$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AE17" s="54">
-        <f>HLOOKUP(YEAR(AE$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AF17" s="54">
-        <f>HLOOKUP(YEAR(AF$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AG17" s="54">
-        <f>HLOOKUP(YEAR(AG$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AH17" s="54">
-        <f>HLOOKUP(YEAR(AH$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AI17" s="54">
-        <f>HLOOKUP(YEAR(AI$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AJ17" s="54">
-        <f>HLOOKUP(YEAR(AJ$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AK17" s="54">
-        <f>HLOOKUP(YEAR(AK$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AL17" s="54">
-        <f>HLOOKUP(YEAR(AL$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AM17" s="54">
-        <f>HLOOKUP(YEAR(AM$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AN17" s="54">
-        <f>HLOOKUP(YEAR(AN$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AO17" s="54">
-        <f>HLOOKUP(YEAR(AO$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AP17" s="54">
-        <f>HLOOKUP(YEAR(AP$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AQ17" s="54">
-        <f>HLOOKUP(YEAR(AQ$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AR17" s="54">
-        <f>HLOOKUP(YEAR(AR$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AS17" s="54">
-        <f>HLOOKUP(YEAR(AS$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AT17" s="54">
-        <f>HLOOKUP(YEAR(AT$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AU17" s="54">
-        <f>HLOOKUP(YEAR(AU$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AV17" s="54">
-        <f>HLOOKUP(YEAR(AV$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AW17" s="54">
-        <f>HLOOKUP(YEAR(AW$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AX17" s="54">
-        <f>HLOOKUP(YEAR(AX$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AY17" s="54">
-        <f>HLOOKUP(YEAR(AY$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AZ17" s="54">
-        <f>HLOOKUP(YEAR(AZ$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="BA17" s="54">
-        <f>HLOOKUP(YEAR(BA$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="BB17" s="54">
-        <f>HLOOKUP(YEAR(BB$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="BC17" s="54">
-        <f>HLOOKUP(YEAR(BC$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="BD17" s="54">
-        <f>HLOOKUP(YEAR(BD$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="BE17" s="54">
-        <f>HLOOKUP(YEAR(BE$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="BF17" s="54">
-        <f>HLOOKUP(YEAR(BF$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="BG17" s="54">
-        <f>HLOOKUP(YEAR(BG$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="BH17" s="54">
-        <f>HLOOKUP(YEAR(BH$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="BI17" s="54">
-        <f>HLOOKUP(YEAR(BI$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="BJ17" s="54">
-        <f>HLOOKUP(YEAR(BJ$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="BK17" s="54">
-        <f>HLOOKUP(YEAR(BK$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
-      </c>
-      <c r="BL17" s="54">
-        <f>HLOOKUP(YEAR(BL$3),Assumptions!$D$113:$H$116,4,FALSE)</f>
-        <v/>
+      <c r="E17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="W17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="X17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA17" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB17" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC17" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD17" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE17" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF17" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG17" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH17" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI17" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ17" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK17" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL17" s="29" t="n">
+        <v>8</v>
       </c>
       <c r="BN17" s="55">
         <f>P17</f>
@@ -44214,7 +44050,7 @@
       </c>
       <c r="BT17" s="20" t="inlineStr">
         <is>
-          <t>the whole back office, typed per year on Assumptions</t>
+          <t>typed here, not driven: the leadership team, then finance, HR, IT and legal as the company grows. Same in both cases</t>
         </is>
       </c>
     </row>
@@ -44230,243 +44066,243 @@
         </is>
       </c>
       <c r="E18" s="54">
-        <f>ROUND('Revenue Forecast'!E41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!E41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="F18" s="54">
-        <f>ROUND('Revenue Forecast'!F41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!F41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="G18" s="54">
-        <f>ROUND('Revenue Forecast'!G41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!G41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="H18" s="54">
-        <f>ROUND('Revenue Forecast'!H41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!H41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="I18" s="54">
-        <f>ROUND('Revenue Forecast'!I41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!I41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="J18" s="54">
-        <f>ROUND('Revenue Forecast'!J41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!J41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="K18" s="54">
-        <f>ROUND('Revenue Forecast'!K41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!K41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="L18" s="54">
-        <f>ROUND('Revenue Forecast'!L41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!L41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="M18" s="54">
-        <f>ROUND('Revenue Forecast'!M41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!M41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="N18" s="54">
-        <f>ROUND('Revenue Forecast'!N41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!N41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="O18" s="54">
-        <f>ROUND('Revenue Forecast'!O41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!O41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="P18" s="54">
-        <f>ROUND('Revenue Forecast'!P41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!P41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="Q18" s="54">
-        <f>ROUND('Revenue Forecast'!Q41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!Q41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="R18" s="54">
-        <f>ROUND('Revenue Forecast'!R41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!R41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="S18" s="54">
-        <f>ROUND('Revenue Forecast'!S41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!S41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="T18" s="54">
-        <f>ROUND('Revenue Forecast'!T41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!T41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="U18" s="54">
-        <f>ROUND('Revenue Forecast'!U41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!U41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="V18" s="54">
-        <f>ROUND('Revenue Forecast'!V41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!V41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="W18" s="54">
-        <f>ROUND('Revenue Forecast'!W41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!W41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="X18" s="54">
-        <f>ROUND('Revenue Forecast'!X41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!X41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="Y18" s="54">
-        <f>ROUND('Revenue Forecast'!Y41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!Y41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="Z18" s="54">
-        <f>ROUND('Revenue Forecast'!Z41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!Z41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AA18" s="54">
-        <f>ROUND('Revenue Forecast'!AA41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AA41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AB18" s="54">
-        <f>ROUND('Revenue Forecast'!AB41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AB41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AC18" s="54">
-        <f>ROUND('Revenue Forecast'!AC41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AC41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AD18" s="54">
-        <f>ROUND('Revenue Forecast'!AD41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AD41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AE18" s="54">
-        <f>ROUND('Revenue Forecast'!AE41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AE41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AF18" s="54">
-        <f>ROUND('Revenue Forecast'!AF41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AF41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AG18" s="54">
-        <f>ROUND('Revenue Forecast'!AG41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AG41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AH18" s="54">
-        <f>ROUND('Revenue Forecast'!AH41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AH41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AI18" s="54">
-        <f>ROUND('Revenue Forecast'!AI41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AI41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AJ18" s="54">
-        <f>ROUND('Revenue Forecast'!AJ41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AJ41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AK18" s="54">
-        <f>ROUND('Revenue Forecast'!AK41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AK41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AL18" s="54">
-        <f>ROUND('Revenue Forecast'!AL41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AL41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AM18" s="54">
-        <f>ROUND('Revenue Forecast'!AM41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AM41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AN18" s="54">
-        <f>ROUND('Revenue Forecast'!AN41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AN41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AO18" s="54">
-        <f>ROUND('Revenue Forecast'!AO41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AO41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AP18" s="54">
-        <f>ROUND('Revenue Forecast'!AP41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AP41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AQ18" s="54">
-        <f>ROUND('Revenue Forecast'!AQ41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AQ41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AR18" s="54">
-        <f>ROUND('Revenue Forecast'!AR41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AR41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AS18" s="54">
-        <f>ROUND('Revenue Forecast'!AS41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AS41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AT18" s="54">
-        <f>ROUND('Revenue Forecast'!AT41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AT41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AU18" s="54">
-        <f>ROUND('Revenue Forecast'!AU41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AU41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AV18" s="54">
-        <f>ROUND('Revenue Forecast'!AV41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AV41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AW18" s="54">
-        <f>ROUND('Revenue Forecast'!AW41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AW41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AX18" s="54">
-        <f>ROUND('Revenue Forecast'!AX41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AX41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AY18" s="54">
-        <f>ROUND('Revenue Forecast'!AY41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AY41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="AZ18" s="54">
-        <f>ROUND('Revenue Forecast'!AZ41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!AZ41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BA18" s="54">
-        <f>ROUND('Revenue Forecast'!BA41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!BA41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BB18" s="54">
-        <f>ROUND('Revenue Forecast'!BB41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!BB41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BC18" s="54">
-        <f>ROUND('Revenue Forecast'!BC41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!BC41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BD18" s="54">
-        <f>ROUND('Revenue Forecast'!BD41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!BD41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BE18" s="54">
-        <f>ROUND('Revenue Forecast'!BE41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!BE41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BF18" s="54">
-        <f>ROUND('Revenue Forecast'!BF41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!BF41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BG18" s="54">
-        <f>ROUND('Revenue Forecast'!BG41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!BG41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BH18" s="54">
-        <f>ROUND('Revenue Forecast'!BH41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!BH41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BI18" s="54">
-        <f>ROUND('Revenue Forecast'!BI41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!BI41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BJ18" s="54">
-        <f>ROUND('Revenue Forecast'!BJ41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!BJ41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BK18" s="54">
-        <f>ROUND('Revenue Forecast'!BK41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!BK41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BL18" s="54">
-        <f>ROUND('Revenue Forecast'!BL41*Assumptions!$F$45/Assumptions!$F$118,0)</f>
+        <f>ROUND('Revenue Forecast'!BL41*Assumptions!$F$45/Assumptions!$F$114,0)</f>
         <v/>
       </c>
       <c r="BN18" s="55">
@@ -45130,243 +44966,243 @@
         </is>
       </c>
       <c r="E26" s="43">
-        <f>E16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
+        <f>E16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F26" s="43">
-        <f>F16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
+        <f>F16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G26" s="43">
-        <f>G16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
+        <f>G16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H26" s="43">
-        <f>H16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
+        <f>H16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I26" s="43">
-        <f>I16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
+        <f>I16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J26" s="43">
-        <f>J16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
+        <f>J16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K26" s="43">
-        <f>K16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
+        <f>K16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L26" s="43">
-        <f>L16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
+        <f>L16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M26" s="43">
-        <f>M16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
+        <f>M16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N26" s="43">
-        <f>N16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
+        <f>N16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O26" s="43">
-        <f>O16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
+        <f>O16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P26" s="43">
-        <f>P16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
+        <f>P16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q26" s="43">
-        <f>Q16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
+        <f>Q16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R26" s="43">
-        <f>R16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
+        <f>R16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S26" s="43">
-        <f>S16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
+        <f>S16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T26" s="43">
-        <f>T16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
+        <f>T16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U26" s="43">
-        <f>U16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
+        <f>U16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V26" s="43">
-        <f>V16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
+        <f>V16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W26" s="43">
-        <f>W16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
+        <f>W16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X26" s="43">
-        <f>X16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
+        <f>X16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y26" s="43">
-        <f>Y16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
+        <f>Y16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z26" s="43">
-        <f>Z16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
+        <f>Z16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA26" s="43">
-        <f>AA16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
+        <f>AA16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB26" s="43">
-        <f>AB16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
+        <f>AB16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC26" s="43">
-        <f>AC16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
+        <f>AC16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD26" s="43">
-        <f>AD16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
+        <f>AD16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE26" s="43">
-        <f>AE16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
+        <f>AE16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF26" s="43">
-        <f>AF16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
+        <f>AF16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG26" s="43">
-        <f>AG16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
+        <f>AG16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH26" s="43">
-        <f>AH16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
+        <f>AH16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI26" s="43">
-        <f>AI16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
+        <f>AI16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ26" s="43">
-        <f>AJ16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
+        <f>AJ16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK26" s="43">
-        <f>AK16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
+        <f>AK16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL26" s="43">
-        <f>AL16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
+        <f>AL16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM26" s="43">
-        <f>AM16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
+        <f>AM16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN26" s="43">
-        <f>AN16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
+        <f>AN16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO26" s="43">
-        <f>AO16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
+        <f>AO16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP26" s="43">
-        <f>AP16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
+        <f>AP16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ26" s="43">
-        <f>AQ16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
+        <f>AQ16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR26" s="43">
-        <f>AR16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
+        <f>AR16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS26" s="43">
-        <f>AS16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
+        <f>AS16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT26" s="43">
-        <f>AT16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
+        <f>AT16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU26" s="43">
-        <f>AU16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
+        <f>AU16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV26" s="43">
-        <f>AV16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
+        <f>AV16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW26" s="43">
-        <f>AW16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
+        <f>AW16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX26" s="43">
-        <f>AX16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
+        <f>AX16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY26" s="43">
-        <f>AY16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
+        <f>AY16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ26" s="43">
-        <f>AZ16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
+        <f>AZ16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA26" s="43">
-        <f>BA16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
+        <f>BA16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB26" s="43">
-        <f>BB16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
+        <f>BB16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC26" s="43">
-        <f>BC16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
+        <f>BC16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD26" s="43">
-        <f>BD16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
+        <f>BD16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE26" s="43">
-        <f>BE16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
+        <f>BE16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF26" s="43">
-        <f>BF16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
+        <f>BF16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG26" s="43">
-        <f>BG16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
+        <f>BG16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH26" s="43">
-        <f>BH16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
+        <f>BH16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI26" s="43">
-        <f>BI16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
+        <f>BI16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ26" s="43">
-        <f>BJ16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
+        <f>BJ16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK26" s="43">
-        <f>BK16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
+        <f>BK16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL26" s="43">
-        <f>BL16*Assumptions!$F$127*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
+        <f>BL16*Assumptions!$F$123*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN26" s="44">
@@ -45402,243 +45238,243 @@
         </is>
       </c>
       <c r="E27" s="43">
-        <f>(E6*Assumptions!$F$121+E7*Assumptions!$F$122+(E8+E9+E10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
+        <f>(E6*Assumptions!$F$117+E7*Assumptions!$F$118+(E8+E9+E10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F27" s="43">
-        <f>(F6*Assumptions!$F$121+F7*Assumptions!$F$122+(F8+F9+F10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
+        <f>(F6*Assumptions!$F$117+F7*Assumptions!$F$118+(F8+F9+F10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G27" s="43">
-        <f>(G6*Assumptions!$F$121+G7*Assumptions!$F$122+(G8+G9+G10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
+        <f>(G6*Assumptions!$F$117+G7*Assumptions!$F$118+(G8+G9+G10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H27" s="43">
-        <f>(H6*Assumptions!$F$121+H7*Assumptions!$F$122+(H8+H9+H10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
+        <f>(H6*Assumptions!$F$117+H7*Assumptions!$F$118+(H8+H9+H10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I27" s="43">
-        <f>(I6*Assumptions!$F$121+I7*Assumptions!$F$122+(I8+I9+I10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
+        <f>(I6*Assumptions!$F$117+I7*Assumptions!$F$118+(I8+I9+I10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J27" s="43">
-        <f>(J6*Assumptions!$F$121+J7*Assumptions!$F$122+(J8+J9+J10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
+        <f>(J6*Assumptions!$F$117+J7*Assumptions!$F$118+(J8+J9+J10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K27" s="43">
-        <f>(K6*Assumptions!$F$121+K7*Assumptions!$F$122+(K8+K9+K10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
+        <f>(K6*Assumptions!$F$117+K7*Assumptions!$F$118+(K8+K9+K10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L27" s="43">
-        <f>(L6*Assumptions!$F$121+L7*Assumptions!$F$122+(L8+L9+L10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
+        <f>(L6*Assumptions!$F$117+L7*Assumptions!$F$118+(L8+L9+L10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M27" s="43">
-        <f>(M6*Assumptions!$F$121+M7*Assumptions!$F$122+(M8+M9+M10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
+        <f>(M6*Assumptions!$F$117+M7*Assumptions!$F$118+(M8+M9+M10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N27" s="43">
-        <f>(N6*Assumptions!$F$121+N7*Assumptions!$F$122+(N8+N9+N10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
+        <f>(N6*Assumptions!$F$117+N7*Assumptions!$F$118+(N8+N9+N10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O27" s="43">
-        <f>(O6*Assumptions!$F$121+O7*Assumptions!$F$122+(O8+O9+O10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
+        <f>(O6*Assumptions!$F$117+O7*Assumptions!$F$118+(O8+O9+O10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P27" s="43">
-        <f>(P6*Assumptions!$F$121+P7*Assumptions!$F$122+(P8+P9+P10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
+        <f>(P6*Assumptions!$F$117+P7*Assumptions!$F$118+(P8+P9+P10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q27" s="43">
-        <f>(Q6*Assumptions!$F$121+Q7*Assumptions!$F$122+(Q8+Q9+Q10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
+        <f>(Q6*Assumptions!$F$117+Q7*Assumptions!$F$118+(Q8+Q9+Q10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R27" s="43">
-        <f>(R6*Assumptions!$F$121+R7*Assumptions!$F$122+(R8+R9+R10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
+        <f>(R6*Assumptions!$F$117+R7*Assumptions!$F$118+(R8+R9+R10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S27" s="43">
-        <f>(S6*Assumptions!$F$121+S7*Assumptions!$F$122+(S8+S9+S10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
+        <f>(S6*Assumptions!$F$117+S7*Assumptions!$F$118+(S8+S9+S10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T27" s="43">
-        <f>(T6*Assumptions!$F$121+T7*Assumptions!$F$122+(T8+T9+T10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
+        <f>(T6*Assumptions!$F$117+T7*Assumptions!$F$118+(T8+T9+T10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U27" s="43">
-        <f>(U6*Assumptions!$F$121+U7*Assumptions!$F$122+(U8+U9+U10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
+        <f>(U6*Assumptions!$F$117+U7*Assumptions!$F$118+(U8+U9+U10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V27" s="43">
-        <f>(V6*Assumptions!$F$121+V7*Assumptions!$F$122+(V8+V9+V10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
+        <f>(V6*Assumptions!$F$117+V7*Assumptions!$F$118+(V8+V9+V10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W27" s="43">
-        <f>(W6*Assumptions!$F$121+W7*Assumptions!$F$122+(W8+W9+W10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
+        <f>(W6*Assumptions!$F$117+W7*Assumptions!$F$118+(W8+W9+W10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X27" s="43">
-        <f>(X6*Assumptions!$F$121+X7*Assumptions!$F$122+(X8+X9+X10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
+        <f>(X6*Assumptions!$F$117+X7*Assumptions!$F$118+(X8+X9+X10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y27" s="43">
-        <f>(Y6*Assumptions!$F$121+Y7*Assumptions!$F$122+(Y8+Y9+Y10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
+        <f>(Y6*Assumptions!$F$117+Y7*Assumptions!$F$118+(Y8+Y9+Y10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z27" s="43">
-        <f>(Z6*Assumptions!$F$121+Z7*Assumptions!$F$122+(Z8+Z9+Z10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
+        <f>(Z6*Assumptions!$F$117+Z7*Assumptions!$F$118+(Z8+Z9+Z10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA27" s="43">
-        <f>(AA6*Assumptions!$F$121+AA7*Assumptions!$F$122+(AA8+AA9+AA10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
+        <f>(AA6*Assumptions!$F$117+AA7*Assumptions!$F$118+(AA8+AA9+AA10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB27" s="43">
-        <f>(AB6*Assumptions!$F$121+AB7*Assumptions!$F$122+(AB8+AB9+AB10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
+        <f>(AB6*Assumptions!$F$117+AB7*Assumptions!$F$118+(AB8+AB9+AB10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC27" s="43">
-        <f>(AC6*Assumptions!$F$121+AC7*Assumptions!$F$122+(AC8+AC9+AC10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
+        <f>(AC6*Assumptions!$F$117+AC7*Assumptions!$F$118+(AC8+AC9+AC10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD27" s="43">
-        <f>(AD6*Assumptions!$F$121+AD7*Assumptions!$F$122+(AD8+AD9+AD10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
+        <f>(AD6*Assumptions!$F$117+AD7*Assumptions!$F$118+(AD8+AD9+AD10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE27" s="43">
-        <f>(AE6*Assumptions!$F$121+AE7*Assumptions!$F$122+(AE8+AE9+AE10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
+        <f>(AE6*Assumptions!$F$117+AE7*Assumptions!$F$118+(AE8+AE9+AE10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF27" s="43">
-        <f>(AF6*Assumptions!$F$121+AF7*Assumptions!$F$122+(AF8+AF9+AF10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
+        <f>(AF6*Assumptions!$F$117+AF7*Assumptions!$F$118+(AF8+AF9+AF10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG27" s="43">
-        <f>(AG6*Assumptions!$F$121+AG7*Assumptions!$F$122+(AG8+AG9+AG10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
+        <f>(AG6*Assumptions!$F$117+AG7*Assumptions!$F$118+(AG8+AG9+AG10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH27" s="43">
-        <f>(AH6*Assumptions!$F$121+AH7*Assumptions!$F$122+(AH8+AH9+AH10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
+        <f>(AH6*Assumptions!$F$117+AH7*Assumptions!$F$118+(AH8+AH9+AH10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI27" s="43">
-        <f>(AI6*Assumptions!$F$121+AI7*Assumptions!$F$122+(AI8+AI9+AI10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
+        <f>(AI6*Assumptions!$F$117+AI7*Assumptions!$F$118+(AI8+AI9+AI10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ27" s="43">
-        <f>(AJ6*Assumptions!$F$121+AJ7*Assumptions!$F$122+(AJ8+AJ9+AJ10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
+        <f>(AJ6*Assumptions!$F$117+AJ7*Assumptions!$F$118+(AJ8+AJ9+AJ10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK27" s="43">
-        <f>(AK6*Assumptions!$F$121+AK7*Assumptions!$F$122+(AK8+AK9+AK10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
+        <f>(AK6*Assumptions!$F$117+AK7*Assumptions!$F$118+(AK8+AK9+AK10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL27" s="43">
-        <f>(AL6*Assumptions!$F$121+AL7*Assumptions!$F$122+(AL8+AL9+AL10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
+        <f>(AL6*Assumptions!$F$117+AL7*Assumptions!$F$118+(AL8+AL9+AL10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM27" s="43">
-        <f>(AM6*Assumptions!$F$121+AM7*Assumptions!$F$122+(AM8+AM9+AM10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
+        <f>(AM6*Assumptions!$F$117+AM7*Assumptions!$F$118+(AM8+AM9+AM10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN27" s="43">
-        <f>(AN6*Assumptions!$F$121+AN7*Assumptions!$F$122+(AN8+AN9+AN10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
+        <f>(AN6*Assumptions!$F$117+AN7*Assumptions!$F$118+(AN8+AN9+AN10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO27" s="43">
-        <f>(AO6*Assumptions!$F$121+AO7*Assumptions!$F$122+(AO8+AO9+AO10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
+        <f>(AO6*Assumptions!$F$117+AO7*Assumptions!$F$118+(AO8+AO9+AO10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP27" s="43">
-        <f>(AP6*Assumptions!$F$121+AP7*Assumptions!$F$122+(AP8+AP9+AP10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
+        <f>(AP6*Assumptions!$F$117+AP7*Assumptions!$F$118+(AP8+AP9+AP10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ27" s="43">
-        <f>(AQ6*Assumptions!$F$121+AQ7*Assumptions!$F$122+(AQ8+AQ9+AQ10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
+        <f>(AQ6*Assumptions!$F$117+AQ7*Assumptions!$F$118+(AQ8+AQ9+AQ10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR27" s="43">
-        <f>(AR6*Assumptions!$F$121+AR7*Assumptions!$F$122+(AR8+AR9+AR10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
+        <f>(AR6*Assumptions!$F$117+AR7*Assumptions!$F$118+(AR8+AR9+AR10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS27" s="43">
-        <f>(AS6*Assumptions!$F$121+AS7*Assumptions!$F$122+(AS8+AS9+AS10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
+        <f>(AS6*Assumptions!$F$117+AS7*Assumptions!$F$118+(AS8+AS9+AS10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT27" s="43">
-        <f>(AT6*Assumptions!$F$121+AT7*Assumptions!$F$122+(AT8+AT9+AT10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
+        <f>(AT6*Assumptions!$F$117+AT7*Assumptions!$F$118+(AT8+AT9+AT10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU27" s="43">
-        <f>(AU6*Assumptions!$F$121+AU7*Assumptions!$F$122+(AU8+AU9+AU10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
+        <f>(AU6*Assumptions!$F$117+AU7*Assumptions!$F$118+(AU8+AU9+AU10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV27" s="43">
-        <f>(AV6*Assumptions!$F$121+AV7*Assumptions!$F$122+(AV8+AV9+AV10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
+        <f>(AV6*Assumptions!$F$117+AV7*Assumptions!$F$118+(AV8+AV9+AV10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW27" s="43">
-        <f>(AW6*Assumptions!$F$121+AW7*Assumptions!$F$122+(AW8+AW9+AW10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
+        <f>(AW6*Assumptions!$F$117+AW7*Assumptions!$F$118+(AW8+AW9+AW10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX27" s="43">
-        <f>(AX6*Assumptions!$F$121+AX7*Assumptions!$F$122+(AX8+AX9+AX10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
+        <f>(AX6*Assumptions!$F$117+AX7*Assumptions!$F$118+(AX8+AX9+AX10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY27" s="43">
-        <f>(AY6*Assumptions!$F$121+AY7*Assumptions!$F$122+(AY8+AY9+AY10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
+        <f>(AY6*Assumptions!$F$117+AY7*Assumptions!$F$118+(AY8+AY9+AY10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ27" s="43">
-        <f>(AZ6*Assumptions!$F$121+AZ7*Assumptions!$F$122+(AZ8+AZ9+AZ10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
+        <f>(AZ6*Assumptions!$F$117+AZ7*Assumptions!$F$118+(AZ8+AZ9+AZ10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA27" s="43">
-        <f>(BA6*Assumptions!$F$121+BA7*Assumptions!$F$122+(BA8+BA9+BA10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
+        <f>(BA6*Assumptions!$F$117+BA7*Assumptions!$F$118+(BA8+BA9+BA10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB27" s="43">
-        <f>(BB6*Assumptions!$F$121+BB7*Assumptions!$F$122+(BB8+BB9+BB10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
+        <f>(BB6*Assumptions!$F$117+BB7*Assumptions!$F$118+(BB8+BB9+BB10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC27" s="43">
-        <f>(BC6*Assumptions!$F$121+BC7*Assumptions!$F$122+(BC8+BC9+BC10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
+        <f>(BC6*Assumptions!$F$117+BC7*Assumptions!$F$118+(BC8+BC9+BC10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD27" s="43">
-        <f>(BD6*Assumptions!$F$121+BD7*Assumptions!$F$122+(BD8+BD9+BD10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
+        <f>(BD6*Assumptions!$F$117+BD7*Assumptions!$F$118+(BD8+BD9+BD10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE27" s="43">
-        <f>(BE6*Assumptions!$F$121+BE7*Assumptions!$F$122+(BE8+BE9+BE10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
+        <f>(BE6*Assumptions!$F$117+BE7*Assumptions!$F$118+(BE8+BE9+BE10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF27" s="43">
-        <f>(BF6*Assumptions!$F$121+BF7*Assumptions!$F$122+(BF8+BF9+BF10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
+        <f>(BF6*Assumptions!$F$117+BF7*Assumptions!$F$118+(BF8+BF9+BF10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG27" s="43">
-        <f>(BG6*Assumptions!$F$121+BG7*Assumptions!$F$122+(BG8+BG9+BG10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
+        <f>(BG6*Assumptions!$F$117+BG7*Assumptions!$F$118+(BG8+BG9+BG10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH27" s="43">
-        <f>(BH6*Assumptions!$F$121+BH7*Assumptions!$F$122+(BH8+BH9+BH10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
+        <f>(BH6*Assumptions!$F$117+BH7*Assumptions!$F$118+(BH8+BH9+BH10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI27" s="43">
-        <f>(BI6*Assumptions!$F$121+BI7*Assumptions!$F$122+(BI8+BI9+BI10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
+        <f>(BI6*Assumptions!$F$117+BI7*Assumptions!$F$118+(BI8+BI9+BI10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ27" s="43">
-        <f>(BJ6*Assumptions!$F$121+BJ7*Assumptions!$F$122+(BJ8+BJ9+BJ10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
+        <f>(BJ6*Assumptions!$F$117+BJ7*Assumptions!$F$118+(BJ8+BJ9+BJ10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK27" s="43">
-        <f>(BK6*Assumptions!$F$121+BK7*Assumptions!$F$122+(BK8+BK9+BK10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
+        <f>(BK6*Assumptions!$F$117+BK7*Assumptions!$F$118+(BK8+BK9+BK10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL27" s="43">
-        <f>(BL6*Assumptions!$F$121+BL7*Assumptions!$F$122+(BL8+BL9+BL10)*Assumptions!$F$123)*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
+        <f>(BL6*Assumptions!$F$117+BL7*Assumptions!$F$118+(BL8+BL9+BL10)*Assumptions!$F$119)*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN27" s="44">
@@ -45674,243 +45510,243 @@
         </is>
       </c>
       <c r="E28" s="43">
-        <f>((E12+E13)*Assumptions!$F$124+(E14+E15)*Assumptions!$F$125+E17*Assumptions!$F$126+E18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
+        <f>((E12+E13)*Assumptions!$F$120+(E14+E15)*Assumptions!$F$121+E17*Assumptions!$F$122+E18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F28" s="43">
-        <f>((F12+F13)*Assumptions!$F$124+(F14+F15)*Assumptions!$F$125+F17*Assumptions!$F$126+F18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
+        <f>((F12+F13)*Assumptions!$F$120+(F14+F15)*Assumptions!$F$121+F17*Assumptions!$F$122+F18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G28" s="43">
-        <f>((G12+G13)*Assumptions!$F$124+(G14+G15)*Assumptions!$F$125+G17*Assumptions!$F$126+G18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
+        <f>((G12+G13)*Assumptions!$F$120+(G14+G15)*Assumptions!$F$121+G17*Assumptions!$F$122+G18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H28" s="43">
-        <f>((H12+H13)*Assumptions!$F$124+(H14+H15)*Assumptions!$F$125+H17*Assumptions!$F$126+H18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
+        <f>((H12+H13)*Assumptions!$F$120+(H14+H15)*Assumptions!$F$121+H17*Assumptions!$F$122+H18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I28" s="43">
-        <f>((I12+I13)*Assumptions!$F$124+(I14+I15)*Assumptions!$F$125+I17*Assumptions!$F$126+I18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
+        <f>((I12+I13)*Assumptions!$F$120+(I14+I15)*Assumptions!$F$121+I17*Assumptions!$F$122+I18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J28" s="43">
-        <f>((J12+J13)*Assumptions!$F$124+(J14+J15)*Assumptions!$F$125+J17*Assumptions!$F$126+J18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
+        <f>((J12+J13)*Assumptions!$F$120+(J14+J15)*Assumptions!$F$121+J17*Assumptions!$F$122+J18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K28" s="43">
-        <f>((K12+K13)*Assumptions!$F$124+(K14+K15)*Assumptions!$F$125+K17*Assumptions!$F$126+K18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
+        <f>((K12+K13)*Assumptions!$F$120+(K14+K15)*Assumptions!$F$121+K17*Assumptions!$F$122+K18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L28" s="43">
-        <f>((L12+L13)*Assumptions!$F$124+(L14+L15)*Assumptions!$F$125+L17*Assumptions!$F$126+L18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
+        <f>((L12+L13)*Assumptions!$F$120+(L14+L15)*Assumptions!$F$121+L17*Assumptions!$F$122+L18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M28" s="43">
-        <f>((M12+M13)*Assumptions!$F$124+(M14+M15)*Assumptions!$F$125+M17*Assumptions!$F$126+M18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
+        <f>((M12+M13)*Assumptions!$F$120+(M14+M15)*Assumptions!$F$121+M17*Assumptions!$F$122+M18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N28" s="43">
-        <f>((N12+N13)*Assumptions!$F$124+(N14+N15)*Assumptions!$F$125+N17*Assumptions!$F$126+N18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
+        <f>((N12+N13)*Assumptions!$F$120+(N14+N15)*Assumptions!$F$121+N17*Assumptions!$F$122+N18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O28" s="43">
-        <f>((O12+O13)*Assumptions!$F$124+(O14+O15)*Assumptions!$F$125+O17*Assumptions!$F$126+O18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
+        <f>((O12+O13)*Assumptions!$F$120+(O14+O15)*Assumptions!$F$121+O17*Assumptions!$F$122+O18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P28" s="43">
-        <f>((P12+P13)*Assumptions!$F$124+(P14+P15)*Assumptions!$F$125+P17*Assumptions!$F$126+P18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
+        <f>((P12+P13)*Assumptions!$F$120+(P14+P15)*Assumptions!$F$121+P17*Assumptions!$F$122+P18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q28" s="43">
-        <f>((Q12+Q13)*Assumptions!$F$124+(Q14+Q15)*Assumptions!$F$125+Q17*Assumptions!$F$126+Q18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
+        <f>((Q12+Q13)*Assumptions!$F$120+(Q14+Q15)*Assumptions!$F$121+Q17*Assumptions!$F$122+Q18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R28" s="43">
-        <f>((R12+R13)*Assumptions!$F$124+(R14+R15)*Assumptions!$F$125+R17*Assumptions!$F$126+R18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
+        <f>((R12+R13)*Assumptions!$F$120+(R14+R15)*Assumptions!$F$121+R17*Assumptions!$F$122+R18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S28" s="43">
-        <f>((S12+S13)*Assumptions!$F$124+(S14+S15)*Assumptions!$F$125+S17*Assumptions!$F$126+S18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
+        <f>((S12+S13)*Assumptions!$F$120+(S14+S15)*Assumptions!$F$121+S17*Assumptions!$F$122+S18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T28" s="43">
-        <f>((T12+T13)*Assumptions!$F$124+(T14+T15)*Assumptions!$F$125+T17*Assumptions!$F$126+T18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
+        <f>((T12+T13)*Assumptions!$F$120+(T14+T15)*Assumptions!$F$121+T17*Assumptions!$F$122+T18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U28" s="43">
-        <f>((U12+U13)*Assumptions!$F$124+(U14+U15)*Assumptions!$F$125+U17*Assumptions!$F$126+U18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
+        <f>((U12+U13)*Assumptions!$F$120+(U14+U15)*Assumptions!$F$121+U17*Assumptions!$F$122+U18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V28" s="43">
-        <f>((V12+V13)*Assumptions!$F$124+(V14+V15)*Assumptions!$F$125+V17*Assumptions!$F$126+V18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
+        <f>((V12+V13)*Assumptions!$F$120+(V14+V15)*Assumptions!$F$121+V17*Assumptions!$F$122+V18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W28" s="43">
-        <f>((W12+W13)*Assumptions!$F$124+(W14+W15)*Assumptions!$F$125+W17*Assumptions!$F$126+W18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
+        <f>((W12+W13)*Assumptions!$F$120+(W14+W15)*Assumptions!$F$121+W17*Assumptions!$F$122+W18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X28" s="43">
-        <f>((X12+X13)*Assumptions!$F$124+(X14+X15)*Assumptions!$F$125+X17*Assumptions!$F$126+X18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
+        <f>((X12+X13)*Assumptions!$F$120+(X14+X15)*Assumptions!$F$121+X17*Assumptions!$F$122+X18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y28" s="43">
-        <f>((Y12+Y13)*Assumptions!$F$124+(Y14+Y15)*Assumptions!$F$125+Y17*Assumptions!$F$126+Y18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
+        <f>((Y12+Y13)*Assumptions!$F$120+(Y14+Y15)*Assumptions!$F$121+Y17*Assumptions!$F$122+Y18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z28" s="43">
-        <f>((Z12+Z13)*Assumptions!$F$124+(Z14+Z15)*Assumptions!$F$125+Z17*Assumptions!$F$126+Z18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
+        <f>((Z12+Z13)*Assumptions!$F$120+(Z14+Z15)*Assumptions!$F$121+Z17*Assumptions!$F$122+Z18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA28" s="43">
-        <f>((AA12+AA13)*Assumptions!$F$124+(AA14+AA15)*Assumptions!$F$125+AA17*Assumptions!$F$126+AA18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
+        <f>((AA12+AA13)*Assumptions!$F$120+(AA14+AA15)*Assumptions!$F$121+AA17*Assumptions!$F$122+AA18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB28" s="43">
-        <f>((AB12+AB13)*Assumptions!$F$124+(AB14+AB15)*Assumptions!$F$125+AB17*Assumptions!$F$126+AB18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
+        <f>((AB12+AB13)*Assumptions!$F$120+(AB14+AB15)*Assumptions!$F$121+AB17*Assumptions!$F$122+AB18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC28" s="43">
-        <f>((AC12+AC13)*Assumptions!$F$124+(AC14+AC15)*Assumptions!$F$125+AC17*Assumptions!$F$126+AC18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
+        <f>((AC12+AC13)*Assumptions!$F$120+(AC14+AC15)*Assumptions!$F$121+AC17*Assumptions!$F$122+AC18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD28" s="43">
-        <f>((AD12+AD13)*Assumptions!$F$124+(AD14+AD15)*Assumptions!$F$125+AD17*Assumptions!$F$126+AD18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
+        <f>((AD12+AD13)*Assumptions!$F$120+(AD14+AD15)*Assumptions!$F$121+AD17*Assumptions!$F$122+AD18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE28" s="43">
-        <f>((AE12+AE13)*Assumptions!$F$124+(AE14+AE15)*Assumptions!$F$125+AE17*Assumptions!$F$126+AE18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
+        <f>((AE12+AE13)*Assumptions!$F$120+(AE14+AE15)*Assumptions!$F$121+AE17*Assumptions!$F$122+AE18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF28" s="43">
-        <f>((AF12+AF13)*Assumptions!$F$124+(AF14+AF15)*Assumptions!$F$125+AF17*Assumptions!$F$126+AF18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
+        <f>((AF12+AF13)*Assumptions!$F$120+(AF14+AF15)*Assumptions!$F$121+AF17*Assumptions!$F$122+AF18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG28" s="43">
-        <f>((AG12+AG13)*Assumptions!$F$124+(AG14+AG15)*Assumptions!$F$125+AG17*Assumptions!$F$126+AG18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
+        <f>((AG12+AG13)*Assumptions!$F$120+(AG14+AG15)*Assumptions!$F$121+AG17*Assumptions!$F$122+AG18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH28" s="43">
-        <f>((AH12+AH13)*Assumptions!$F$124+(AH14+AH15)*Assumptions!$F$125+AH17*Assumptions!$F$126+AH18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
+        <f>((AH12+AH13)*Assumptions!$F$120+(AH14+AH15)*Assumptions!$F$121+AH17*Assumptions!$F$122+AH18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI28" s="43">
-        <f>((AI12+AI13)*Assumptions!$F$124+(AI14+AI15)*Assumptions!$F$125+AI17*Assumptions!$F$126+AI18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
+        <f>((AI12+AI13)*Assumptions!$F$120+(AI14+AI15)*Assumptions!$F$121+AI17*Assumptions!$F$122+AI18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ28" s="43">
-        <f>((AJ12+AJ13)*Assumptions!$F$124+(AJ14+AJ15)*Assumptions!$F$125+AJ17*Assumptions!$F$126+AJ18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
+        <f>((AJ12+AJ13)*Assumptions!$F$120+(AJ14+AJ15)*Assumptions!$F$121+AJ17*Assumptions!$F$122+AJ18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK28" s="43">
-        <f>((AK12+AK13)*Assumptions!$F$124+(AK14+AK15)*Assumptions!$F$125+AK17*Assumptions!$F$126+AK18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
+        <f>((AK12+AK13)*Assumptions!$F$120+(AK14+AK15)*Assumptions!$F$121+AK17*Assumptions!$F$122+AK18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL28" s="43">
-        <f>((AL12+AL13)*Assumptions!$F$124+(AL14+AL15)*Assumptions!$F$125+AL17*Assumptions!$F$126+AL18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
+        <f>((AL12+AL13)*Assumptions!$F$120+(AL14+AL15)*Assumptions!$F$121+AL17*Assumptions!$F$122+AL18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM28" s="43">
-        <f>((AM12+AM13)*Assumptions!$F$124+(AM14+AM15)*Assumptions!$F$125+AM17*Assumptions!$F$126+AM18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
+        <f>((AM12+AM13)*Assumptions!$F$120+(AM14+AM15)*Assumptions!$F$121+AM17*Assumptions!$F$122+AM18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN28" s="43">
-        <f>((AN12+AN13)*Assumptions!$F$124+(AN14+AN15)*Assumptions!$F$125+AN17*Assumptions!$F$126+AN18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
+        <f>((AN12+AN13)*Assumptions!$F$120+(AN14+AN15)*Assumptions!$F$121+AN17*Assumptions!$F$122+AN18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO28" s="43">
-        <f>((AO12+AO13)*Assumptions!$F$124+(AO14+AO15)*Assumptions!$F$125+AO17*Assumptions!$F$126+AO18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
+        <f>((AO12+AO13)*Assumptions!$F$120+(AO14+AO15)*Assumptions!$F$121+AO17*Assumptions!$F$122+AO18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP28" s="43">
-        <f>((AP12+AP13)*Assumptions!$F$124+(AP14+AP15)*Assumptions!$F$125+AP17*Assumptions!$F$126+AP18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
+        <f>((AP12+AP13)*Assumptions!$F$120+(AP14+AP15)*Assumptions!$F$121+AP17*Assumptions!$F$122+AP18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ28" s="43">
-        <f>((AQ12+AQ13)*Assumptions!$F$124+(AQ14+AQ15)*Assumptions!$F$125+AQ17*Assumptions!$F$126+AQ18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
+        <f>((AQ12+AQ13)*Assumptions!$F$120+(AQ14+AQ15)*Assumptions!$F$121+AQ17*Assumptions!$F$122+AQ18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR28" s="43">
-        <f>((AR12+AR13)*Assumptions!$F$124+(AR14+AR15)*Assumptions!$F$125+AR17*Assumptions!$F$126+AR18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
+        <f>((AR12+AR13)*Assumptions!$F$120+(AR14+AR15)*Assumptions!$F$121+AR17*Assumptions!$F$122+AR18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS28" s="43">
-        <f>((AS12+AS13)*Assumptions!$F$124+(AS14+AS15)*Assumptions!$F$125+AS17*Assumptions!$F$126+AS18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
+        <f>((AS12+AS13)*Assumptions!$F$120+(AS14+AS15)*Assumptions!$F$121+AS17*Assumptions!$F$122+AS18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT28" s="43">
-        <f>((AT12+AT13)*Assumptions!$F$124+(AT14+AT15)*Assumptions!$F$125+AT17*Assumptions!$F$126+AT18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
+        <f>((AT12+AT13)*Assumptions!$F$120+(AT14+AT15)*Assumptions!$F$121+AT17*Assumptions!$F$122+AT18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU28" s="43">
-        <f>((AU12+AU13)*Assumptions!$F$124+(AU14+AU15)*Assumptions!$F$125+AU17*Assumptions!$F$126+AU18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
+        <f>((AU12+AU13)*Assumptions!$F$120+(AU14+AU15)*Assumptions!$F$121+AU17*Assumptions!$F$122+AU18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV28" s="43">
-        <f>((AV12+AV13)*Assumptions!$F$124+(AV14+AV15)*Assumptions!$F$125+AV17*Assumptions!$F$126+AV18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
+        <f>((AV12+AV13)*Assumptions!$F$120+(AV14+AV15)*Assumptions!$F$121+AV17*Assumptions!$F$122+AV18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW28" s="43">
-        <f>((AW12+AW13)*Assumptions!$F$124+(AW14+AW15)*Assumptions!$F$125+AW17*Assumptions!$F$126+AW18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
+        <f>((AW12+AW13)*Assumptions!$F$120+(AW14+AW15)*Assumptions!$F$121+AW17*Assumptions!$F$122+AW18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX28" s="43">
-        <f>((AX12+AX13)*Assumptions!$F$124+(AX14+AX15)*Assumptions!$F$125+AX17*Assumptions!$F$126+AX18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
+        <f>((AX12+AX13)*Assumptions!$F$120+(AX14+AX15)*Assumptions!$F$121+AX17*Assumptions!$F$122+AX18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY28" s="43">
-        <f>((AY12+AY13)*Assumptions!$F$124+(AY14+AY15)*Assumptions!$F$125+AY17*Assumptions!$F$126+AY18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
+        <f>((AY12+AY13)*Assumptions!$F$120+(AY14+AY15)*Assumptions!$F$121+AY17*Assumptions!$F$122+AY18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ28" s="43">
-        <f>((AZ12+AZ13)*Assumptions!$F$124+(AZ14+AZ15)*Assumptions!$F$125+AZ17*Assumptions!$F$126+AZ18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
+        <f>((AZ12+AZ13)*Assumptions!$F$120+(AZ14+AZ15)*Assumptions!$F$121+AZ17*Assumptions!$F$122+AZ18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA28" s="43">
-        <f>((BA12+BA13)*Assumptions!$F$124+(BA14+BA15)*Assumptions!$F$125+BA17*Assumptions!$F$126+BA18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
+        <f>((BA12+BA13)*Assumptions!$F$120+(BA14+BA15)*Assumptions!$F$121+BA17*Assumptions!$F$122+BA18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB28" s="43">
-        <f>((BB12+BB13)*Assumptions!$F$124+(BB14+BB15)*Assumptions!$F$125+BB17*Assumptions!$F$126+BB18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
+        <f>((BB12+BB13)*Assumptions!$F$120+(BB14+BB15)*Assumptions!$F$121+BB17*Assumptions!$F$122+BB18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC28" s="43">
-        <f>((BC12+BC13)*Assumptions!$F$124+(BC14+BC15)*Assumptions!$F$125+BC17*Assumptions!$F$126+BC18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
+        <f>((BC12+BC13)*Assumptions!$F$120+(BC14+BC15)*Assumptions!$F$121+BC17*Assumptions!$F$122+BC18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD28" s="43">
-        <f>((BD12+BD13)*Assumptions!$F$124+(BD14+BD15)*Assumptions!$F$125+BD17*Assumptions!$F$126+BD18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
+        <f>((BD12+BD13)*Assumptions!$F$120+(BD14+BD15)*Assumptions!$F$121+BD17*Assumptions!$F$122+BD18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE28" s="43">
-        <f>((BE12+BE13)*Assumptions!$F$124+(BE14+BE15)*Assumptions!$F$125+BE17*Assumptions!$F$126+BE18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
+        <f>((BE12+BE13)*Assumptions!$F$120+(BE14+BE15)*Assumptions!$F$121+BE17*Assumptions!$F$122+BE18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF28" s="43">
-        <f>((BF12+BF13)*Assumptions!$F$124+(BF14+BF15)*Assumptions!$F$125+BF17*Assumptions!$F$126+BF18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
+        <f>((BF12+BF13)*Assumptions!$F$120+(BF14+BF15)*Assumptions!$F$121+BF17*Assumptions!$F$122+BF18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG28" s="43">
-        <f>((BG12+BG13)*Assumptions!$F$124+(BG14+BG15)*Assumptions!$F$125+BG17*Assumptions!$F$126+BG18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
+        <f>((BG12+BG13)*Assumptions!$F$120+(BG14+BG15)*Assumptions!$F$121+BG17*Assumptions!$F$122+BG18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH28" s="43">
-        <f>((BH12+BH13)*Assumptions!$F$124+(BH14+BH15)*Assumptions!$F$125+BH17*Assumptions!$F$126+BH18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
+        <f>((BH12+BH13)*Assumptions!$F$120+(BH14+BH15)*Assumptions!$F$121+BH17*Assumptions!$F$122+BH18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI28" s="43">
-        <f>((BI12+BI13)*Assumptions!$F$124+(BI14+BI15)*Assumptions!$F$125+BI17*Assumptions!$F$126+BI18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
+        <f>((BI12+BI13)*Assumptions!$F$120+(BI14+BI15)*Assumptions!$F$121+BI17*Assumptions!$F$122+BI18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ28" s="43">
-        <f>((BJ12+BJ13)*Assumptions!$F$124+(BJ14+BJ15)*Assumptions!$F$125+BJ17*Assumptions!$F$126+BJ18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
+        <f>((BJ12+BJ13)*Assumptions!$F$120+(BJ14+BJ15)*Assumptions!$F$121+BJ17*Assumptions!$F$122+BJ18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK28" s="43">
-        <f>((BK12+BK13)*Assumptions!$F$124+(BK14+BK15)*Assumptions!$F$125+BK17*Assumptions!$F$126+BK18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
+        <f>((BK12+BK13)*Assumptions!$F$120+(BK14+BK15)*Assumptions!$F$121+BK17*Assumptions!$F$122+BK18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL28" s="43">
-        <f>((BL12+BL13)*Assumptions!$F$124+(BL14+BL15)*Assumptions!$F$125+BL17*Assumptions!$F$126+BL18*Assumptions!$F$128)*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
+        <f>((BL12+BL13)*Assumptions!$F$120+(BL14+BL15)*Assumptions!$F$121+BL17*Assumptions!$F$122+BL18*Assumptions!$F$124)*(1+Assumptions!$F$10)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN28" s="44">

--- a/models/Tarnoc_v2_2026-09-01.xlsx
+++ b/models/Tarnoc_v2_2026-09-01.xlsx
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="20" t="inlineStr">
         <is>

--- a/models/Tarnoc_v2_2026-09-01.xlsx
+++ b/models/Tarnoc_v2_2026-09-01.xlsx
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F21" s="30">
         <f>IF(Assumptions!$E$5=2,E21,D21)</f>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>the aggressive case carries stock, the base case does not</t>
+          <t>the assembly partner holds the stock; nothing sits on our balance sheet</t>
         </is>
       </c>
     </row>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E28" s="25" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="F28" s="26">
         <f>IF(Assumptions!$E$5=2,E28,D28)</f>
@@ -3507,16 +3507,16 @@
         <v>0</v>
       </c>
       <c r="E101" s="29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F101" s="29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G101" s="29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H101" s="29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102">

--- a/models/Tarnoc_v2_2026-09-01.xlsx
+++ b/models/Tarnoc_v2_2026-09-01.xlsx
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E28" s="25" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F28" s="26">
         <f>IF(Assumptions!$E$5=2,E28,D28)</f>
@@ -3093,7 +3093,7 @@
         <v>49310</v>
       </c>
       <c r="E82" s="27" t="n">
-        <v>46935</v>
+        <v>46692</v>
       </c>
       <c r="F82" s="28">
         <f>IF(Assumptions!$E$5=2,E82,D82)</f>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J82" s="20" t="inlineStr">
         <is>
-          <t>set well past the horizon to mean never, so the capex lead time cannot pull spend in</t>
+          <t>base: set well past the horizon to mean never. Aggressive: paid for in November 2026, the first month after the raise lands</t>
         </is>
       </c>
     </row>

--- a/models/Tarnoc_v2_2026-09-01.xlsx
+++ b/models/Tarnoc_v2_2026-09-01.xlsx
@@ -2967,7 +2967,7 @@
     <row r="77">
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Installer partner commission, share of boiler price</t>
+          <t>Installer partner commission, share of unit price</t>
         </is>
       </c>
       <c r="C77" s="18" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="J77" s="20" t="inlineStr">
         <is>
-          <t>paid on every unit sold through the channel, on the boiler price only, not on installation or upsell</t>
+          <t>paid on every unit sold through the channel, on the turbineketel or Combi+ system price only, not on installation, upsell or service</t>
         </is>
       </c>
     </row>
@@ -3786,12 +3786,12 @@
     <row r="113">
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Boilers one field engineer can look after</t>
+          <t>Installed units one field engineer can look after</t>
         </is>
       </c>
       <c r="C113" s="18" t="inlineStr">
         <is>
-          <t>boilers</t>
+          <t>units</t>
         </is>
       </c>
       <c r="D113" s="29" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="J113" s="20" t="inlineStr">
         <is>
-          <t>sizes the field service team: boilers on a service contract divided by this number = engineers to hire. Each boiler gets one visit a year, an engineer does three to four a day</t>
+          <t>sizes the field service team: units on a service contract divided by this number = engineers to hire. Each unit gets one visit a year, an engineer does three to four a day</t>
         </is>
       </c>
     </row>
@@ -31945,7 +31945,7 @@
       </c>
       <c r="BT18" s="20" t="inlineStr">
         <is>
-          <t>boiler revenue on the channel share of units, times the commission rate</t>
+          <t>turbineketel and Combi+ revenue on the channel share of units, times the commission rate</t>
         </is>
       </c>
     </row>
@@ -44300,7 +44300,7 @@
       </c>
       <c r="BT18" s="20" t="inlineStr">
         <is>
-          <t>salaried staff: boilers on a service contract divided by the boilers one engineer can look after</t>
+          <t>salaried staff: installed units on a service contract divided by the units one engineer can look after</t>
         </is>
       </c>
     </row>

--- a/models/Tarnoc_v2_2026-09-01.xlsx
+++ b/models/Tarnoc_v2_2026-09-01.xlsx
@@ -1524,7 +1524,7 @@
     <row r="12">
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Interest on the working capital loan</t>
+          <t>Interest on the convertible loan</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -5987,23 +5987,23 @@
         <v/>
       </c>
       <c r="BN9" s="49">
-        <f>IFERROR(AVERAGE(E9:P9),0)</f>
+        <f>IFERROR(BN8/BN6,0)</f>
         <v/>
       </c>
       <c r="BO9" s="49">
-        <f>IFERROR(AVERAGE(Q9:AB9),0)</f>
+        <f>IFERROR(BO8/BO6,0)</f>
         <v/>
       </c>
       <c r="BP9" s="49">
-        <f>IFERROR(AVERAGE(AC9:AN9),0)</f>
+        <f>IFERROR(BP8/BP6,0)</f>
         <v/>
       </c>
       <c r="BQ9" s="49">
-        <f>IFERROR(AVERAGE(AO9:AZ9),0)</f>
+        <f>IFERROR(BQ8/BQ6,0)</f>
         <v/>
       </c>
       <c r="BR9" s="49">
-        <f>IFERROR(AVERAGE(BA9:BL9),0)</f>
+        <f>IFERROR(BR8/BR6,0)</f>
         <v/>
       </c>
     </row>
@@ -7622,23 +7622,23 @@
         <v/>
       </c>
       <c r="BN17" s="49">
-        <f>IFERROR(AVERAGE(E17:P17),0)</f>
+        <f>IFERROR(BN16/BN6,0)</f>
         <v/>
       </c>
       <c r="BO17" s="49">
-        <f>IFERROR(AVERAGE(Q17:AB17),0)</f>
+        <f>IFERROR(BO16/BO6,0)</f>
         <v/>
       </c>
       <c r="BP17" s="49">
-        <f>IFERROR(AVERAGE(AC17:AN17),0)</f>
+        <f>IFERROR(BP16/BP6,0)</f>
         <v/>
       </c>
       <c r="BQ17" s="49">
-        <f>IFERROR(AVERAGE(AO17:AZ17),0)</f>
+        <f>IFERROR(BQ16/BQ6,0)</f>
         <v/>
       </c>
       <c r="BR17" s="49">
-        <f>IFERROR(AVERAGE(BA17:BL17),0)</f>
+        <f>IFERROR(BR16/BR6,0)</f>
         <v/>
       </c>
     </row>
@@ -9267,23 +9267,23 @@
         <v/>
       </c>
       <c r="BN24" s="49">
-        <f>IFERROR(AVERAGE(E24:P24),0)</f>
+        <f>IFERROR(BN23/BN6,0)</f>
         <v/>
       </c>
       <c r="BO24" s="49">
-        <f>IFERROR(AVERAGE(Q24:AB24),0)</f>
+        <f>IFERROR(BO23/BO6,0)</f>
         <v/>
       </c>
       <c r="BP24" s="49">
-        <f>IFERROR(AVERAGE(AC24:AN24),0)</f>
+        <f>IFERROR(BP23/BP6,0)</f>
         <v/>
       </c>
       <c r="BQ24" s="49">
-        <f>IFERROR(AVERAGE(AO24:AZ24),0)</f>
+        <f>IFERROR(BQ23/BQ6,0)</f>
         <v/>
       </c>
       <c r="BR24" s="49">
-        <f>IFERROR(AVERAGE(BA24:BL24),0)</f>
+        <f>IFERROR(BR23/BR6,0)</f>
         <v/>
       </c>
     </row>
@@ -12884,23 +12884,23 @@
         <v/>
       </c>
       <c r="BN39" s="44">
-        <f>P39</f>
+        <f>E39</f>
         <v/>
       </c>
       <c r="BO39" s="44">
-        <f>AB39</f>
+        <f>Q39</f>
         <v/>
       </c>
       <c r="BP39" s="44">
-        <f>AN39</f>
+        <f>AC39</f>
         <v/>
       </c>
       <c r="BQ39" s="44">
-        <f>AZ39</f>
+        <f>AO39</f>
         <v/>
       </c>
       <c r="BR39" s="44">
-        <f>BL39</f>
+        <f>BA39</f>
         <v/>
       </c>
     </row>
@@ -13536,243 +13536,243 @@
         </is>
       </c>
       <c r="E44" s="43">
-        <f>Assumptions!$F$19/30*E6</f>
+        <f>Assumptions!$F$19/30*(E6-'Revenue Forecast'!E49)</f>
         <v/>
       </c>
       <c r="F44" s="43">
-        <f>Assumptions!$F$19/30*F6</f>
+        <f>Assumptions!$F$19/30*(F6-'Revenue Forecast'!F49)</f>
         <v/>
       </c>
       <c r="G44" s="43">
-        <f>Assumptions!$F$19/30*G6</f>
+        <f>Assumptions!$F$19/30*(G6-'Revenue Forecast'!G49)</f>
         <v/>
       </c>
       <c r="H44" s="43">
-        <f>Assumptions!$F$19/30*H6</f>
+        <f>Assumptions!$F$19/30*(H6-'Revenue Forecast'!H49)</f>
         <v/>
       </c>
       <c r="I44" s="43">
-        <f>Assumptions!$F$19/30*I6</f>
+        <f>Assumptions!$F$19/30*(I6-'Revenue Forecast'!I49)</f>
         <v/>
       </c>
       <c r="J44" s="43">
-        <f>Assumptions!$F$19/30*J6</f>
+        <f>Assumptions!$F$19/30*(J6-'Revenue Forecast'!J49)</f>
         <v/>
       </c>
       <c r="K44" s="43">
-        <f>Assumptions!$F$19/30*K6</f>
+        <f>Assumptions!$F$19/30*(K6-'Revenue Forecast'!K49)</f>
         <v/>
       </c>
       <c r="L44" s="43">
-        <f>Assumptions!$F$19/30*L6</f>
+        <f>Assumptions!$F$19/30*(L6-'Revenue Forecast'!L49)</f>
         <v/>
       </c>
       <c r="M44" s="43">
-        <f>Assumptions!$F$19/30*M6</f>
+        <f>Assumptions!$F$19/30*(M6-'Revenue Forecast'!M49)</f>
         <v/>
       </c>
       <c r="N44" s="43">
-        <f>Assumptions!$F$19/30*N6</f>
+        <f>Assumptions!$F$19/30*(N6-'Revenue Forecast'!N49)</f>
         <v/>
       </c>
       <c r="O44" s="43">
-        <f>Assumptions!$F$19/30*O6</f>
+        <f>Assumptions!$F$19/30*(O6-'Revenue Forecast'!O49)</f>
         <v/>
       </c>
       <c r="P44" s="43">
-        <f>Assumptions!$F$19/30*P6</f>
+        <f>Assumptions!$F$19/30*(P6-'Revenue Forecast'!P49)</f>
         <v/>
       </c>
       <c r="Q44" s="43">
-        <f>Assumptions!$F$19/30*Q6</f>
+        <f>Assumptions!$F$19/30*(Q6-'Revenue Forecast'!Q49)</f>
         <v/>
       </c>
       <c r="R44" s="43">
-        <f>Assumptions!$F$19/30*R6</f>
+        <f>Assumptions!$F$19/30*(R6-'Revenue Forecast'!R49)</f>
         <v/>
       </c>
       <c r="S44" s="43">
-        <f>Assumptions!$F$19/30*S6</f>
+        <f>Assumptions!$F$19/30*(S6-'Revenue Forecast'!S49)</f>
         <v/>
       </c>
       <c r="T44" s="43">
-        <f>Assumptions!$F$19/30*T6</f>
+        <f>Assumptions!$F$19/30*(T6-'Revenue Forecast'!T49)</f>
         <v/>
       </c>
       <c r="U44" s="43">
-        <f>Assumptions!$F$19/30*U6</f>
+        <f>Assumptions!$F$19/30*(U6-'Revenue Forecast'!U49)</f>
         <v/>
       </c>
       <c r="V44" s="43">
-        <f>Assumptions!$F$19/30*V6</f>
+        <f>Assumptions!$F$19/30*(V6-'Revenue Forecast'!V49)</f>
         <v/>
       </c>
       <c r="W44" s="43">
-        <f>Assumptions!$F$19/30*W6</f>
+        <f>Assumptions!$F$19/30*(W6-'Revenue Forecast'!W49)</f>
         <v/>
       </c>
       <c r="X44" s="43">
-        <f>Assumptions!$F$19/30*X6</f>
+        <f>Assumptions!$F$19/30*(X6-'Revenue Forecast'!X49)</f>
         <v/>
       </c>
       <c r="Y44" s="43">
-        <f>Assumptions!$F$19/30*Y6</f>
+        <f>Assumptions!$F$19/30*(Y6-'Revenue Forecast'!Y49)</f>
         <v/>
       </c>
       <c r="Z44" s="43">
-        <f>Assumptions!$F$19/30*Z6</f>
+        <f>Assumptions!$F$19/30*(Z6-'Revenue Forecast'!Z49)</f>
         <v/>
       </c>
       <c r="AA44" s="43">
-        <f>Assumptions!$F$19/30*AA6</f>
+        <f>Assumptions!$F$19/30*(AA6-'Revenue Forecast'!AA49)</f>
         <v/>
       </c>
       <c r="AB44" s="43">
-        <f>Assumptions!$F$19/30*AB6</f>
+        <f>Assumptions!$F$19/30*(AB6-'Revenue Forecast'!AB49)</f>
         <v/>
       </c>
       <c r="AC44" s="43">
-        <f>Assumptions!$F$19/30*AC6</f>
+        <f>Assumptions!$F$19/30*(AC6-'Revenue Forecast'!AC49)</f>
         <v/>
       </c>
       <c r="AD44" s="43">
-        <f>Assumptions!$F$19/30*AD6</f>
+        <f>Assumptions!$F$19/30*(AD6-'Revenue Forecast'!AD49)</f>
         <v/>
       </c>
       <c r="AE44" s="43">
-        <f>Assumptions!$F$19/30*AE6</f>
+        <f>Assumptions!$F$19/30*(AE6-'Revenue Forecast'!AE49)</f>
         <v/>
       </c>
       <c r="AF44" s="43">
-        <f>Assumptions!$F$19/30*AF6</f>
+        <f>Assumptions!$F$19/30*(AF6-'Revenue Forecast'!AF49)</f>
         <v/>
       </c>
       <c r="AG44" s="43">
-        <f>Assumptions!$F$19/30*AG6</f>
+        <f>Assumptions!$F$19/30*(AG6-'Revenue Forecast'!AG49)</f>
         <v/>
       </c>
       <c r="AH44" s="43">
-        <f>Assumptions!$F$19/30*AH6</f>
+        <f>Assumptions!$F$19/30*(AH6-'Revenue Forecast'!AH49)</f>
         <v/>
       </c>
       <c r="AI44" s="43">
-        <f>Assumptions!$F$19/30*AI6</f>
+        <f>Assumptions!$F$19/30*(AI6-'Revenue Forecast'!AI49)</f>
         <v/>
       </c>
       <c r="AJ44" s="43">
-        <f>Assumptions!$F$19/30*AJ6</f>
+        <f>Assumptions!$F$19/30*(AJ6-'Revenue Forecast'!AJ49)</f>
         <v/>
       </c>
       <c r="AK44" s="43">
-        <f>Assumptions!$F$19/30*AK6</f>
+        <f>Assumptions!$F$19/30*(AK6-'Revenue Forecast'!AK49)</f>
         <v/>
       </c>
       <c r="AL44" s="43">
-        <f>Assumptions!$F$19/30*AL6</f>
+        <f>Assumptions!$F$19/30*(AL6-'Revenue Forecast'!AL49)</f>
         <v/>
       </c>
       <c r="AM44" s="43">
-        <f>Assumptions!$F$19/30*AM6</f>
+        <f>Assumptions!$F$19/30*(AM6-'Revenue Forecast'!AM49)</f>
         <v/>
       </c>
       <c r="AN44" s="43">
-        <f>Assumptions!$F$19/30*AN6</f>
+        <f>Assumptions!$F$19/30*(AN6-'Revenue Forecast'!AN49)</f>
         <v/>
       </c>
       <c r="AO44" s="43">
-        <f>Assumptions!$F$19/30*AO6</f>
+        <f>Assumptions!$F$19/30*(AO6-'Revenue Forecast'!AO49)</f>
         <v/>
       </c>
       <c r="AP44" s="43">
-        <f>Assumptions!$F$19/30*AP6</f>
+        <f>Assumptions!$F$19/30*(AP6-'Revenue Forecast'!AP49)</f>
         <v/>
       </c>
       <c r="AQ44" s="43">
-        <f>Assumptions!$F$19/30*AQ6</f>
+        <f>Assumptions!$F$19/30*(AQ6-'Revenue Forecast'!AQ49)</f>
         <v/>
       </c>
       <c r="AR44" s="43">
-        <f>Assumptions!$F$19/30*AR6</f>
+        <f>Assumptions!$F$19/30*(AR6-'Revenue Forecast'!AR49)</f>
         <v/>
       </c>
       <c r="AS44" s="43">
-        <f>Assumptions!$F$19/30*AS6</f>
+        <f>Assumptions!$F$19/30*(AS6-'Revenue Forecast'!AS49)</f>
         <v/>
       </c>
       <c r="AT44" s="43">
-        <f>Assumptions!$F$19/30*AT6</f>
+        <f>Assumptions!$F$19/30*(AT6-'Revenue Forecast'!AT49)</f>
         <v/>
       </c>
       <c r="AU44" s="43">
-        <f>Assumptions!$F$19/30*AU6</f>
+        <f>Assumptions!$F$19/30*(AU6-'Revenue Forecast'!AU49)</f>
         <v/>
       </c>
       <c r="AV44" s="43">
-        <f>Assumptions!$F$19/30*AV6</f>
+        <f>Assumptions!$F$19/30*(AV6-'Revenue Forecast'!AV49)</f>
         <v/>
       </c>
       <c r="AW44" s="43">
-        <f>Assumptions!$F$19/30*AW6</f>
+        <f>Assumptions!$F$19/30*(AW6-'Revenue Forecast'!AW49)</f>
         <v/>
       </c>
       <c r="AX44" s="43">
-        <f>Assumptions!$F$19/30*AX6</f>
+        <f>Assumptions!$F$19/30*(AX6-'Revenue Forecast'!AX49)</f>
         <v/>
       </c>
       <c r="AY44" s="43">
-        <f>Assumptions!$F$19/30*AY6</f>
+        <f>Assumptions!$F$19/30*(AY6-'Revenue Forecast'!AY49)</f>
         <v/>
       </c>
       <c r="AZ44" s="43">
-        <f>Assumptions!$F$19/30*AZ6</f>
+        <f>Assumptions!$F$19/30*(AZ6-'Revenue Forecast'!AZ49)</f>
         <v/>
       </c>
       <c r="BA44" s="43">
-        <f>Assumptions!$F$19/30*BA6</f>
+        <f>Assumptions!$F$19/30*(BA6-'Revenue Forecast'!BA49)</f>
         <v/>
       </c>
       <c r="BB44" s="43">
-        <f>Assumptions!$F$19/30*BB6</f>
+        <f>Assumptions!$F$19/30*(BB6-'Revenue Forecast'!BB49)</f>
         <v/>
       </c>
       <c r="BC44" s="43">
-        <f>Assumptions!$F$19/30*BC6</f>
+        <f>Assumptions!$F$19/30*(BC6-'Revenue Forecast'!BC49)</f>
         <v/>
       </c>
       <c r="BD44" s="43">
-        <f>Assumptions!$F$19/30*BD6</f>
+        <f>Assumptions!$F$19/30*(BD6-'Revenue Forecast'!BD49)</f>
         <v/>
       </c>
       <c r="BE44" s="43">
-        <f>Assumptions!$F$19/30*BE6</f>
+        <f>Assumptions!$F$19/30*(BE6-'Revenue Forecast'!BE49)</f>
         <v/>
       </c>
       <c r="BF44" s="43">
-        <f>Assumptions!$F$19/30*BF6</f>
+        <f>Assumptions!$F$19/30*(BF6-'Revenue Forecast'!BF49)</f>
         <v/>
       </c>
       <c r="BG44" s="43">
-        <f>Assumptions!$F$19/30*BG6</f>
+        <f>Assumptions!$F$19/30*(BG6-'Revenue Forecast'!BG49)</f>
         <v/>
       </c>
       <c r="BH44" s="43">
-        <f>Assumptions!$F$19/30*BH6</f>
+        <f>Assumptions!$F$19/30*(BH6-'Revenue Forecast'!BH49)</f>
         <v/>
       </c>
       <c r="BI44" s="43">
-        <f>Assumptions!$F$19/30*BI6</f>
+        <f>Assumptions!$F$19/30*(BI6-'Revenue Forecast'!BI49)</f>
         <v/>
       </c>
       <c r="BJ44" s="43">
-        <f>Assumptions!$F$19/30*BJ6</f>
+        <f>Assumptions!$F$19/30*(BJ6-'Revenue Forecast'!BJ49)</f>
         <v/>
       </c>
       <c r="BK44" s="43">
-        <f>Assumptions!$F$19/30*BK6</f>
+        <f>Assumptions!$F$19/30*(BK6-'Revenue Forecast'!BK49)</f>
         <v/>
       </c>
       <c r="BL44" s="43">
-        <f>Assumptions!$F$19/30*BL6</f>
+        <f>Assumptions!$F$19/30*(BL6-'Revenue Forecast'!BL49)</f>
         <v/>
       </c>
       <c r="BN44" s="44">
@@ -13794,6 +13794,11 @@
       <c r="BR44" s="44">
         <f>BL44</f>
         <v/>
+      </c>
+      <c r="BT44" s="20" t="inlineStr">
+        <is>
+          <t>on trading revenue only; the subsidy is a cash receipt, not an invoice</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -23418,23 +23423,23 @@
         <v/>
       </c>
       <c r="BN24" s="63">
-        <f>IFERROR(AVERAGE(E24:P24),0)</f>
+        <f>IFERROR(BN34/BN22,0)</f>
         <v/>
       </c>
       <c r="BO24" s="63">
-        <f>IFERROR(AVERAGE(Q24:AB24),0)</f>
+        <f>IFERROR(BO34/BO22,0)</f>
         <v/>
       </c>
       <c r="BP24" s="63">
-        <f>IFERROR(AVERAGE(AC24:AN24),0)</f>
+        <f>IFERROR(BP34/BP22,0)</f>
         <v/>
       </c>
       <c r="BQ24" s="63">
-        <f>IFERROR(AVERAGE(AO24:AZ24),0)</f>
+        <f>IFERROR(BQ34/BQ22,0)</f>
         <v/>
       </c>
       <c r="BR24" s="63">
-        <f>IFERROR(AVERAGE(BA24:BL24),0)</f>
+        <f>IFERROR(BR34/BR22,0)</f>
         <v/>
       </c>
     </row>
@@ -25215,23 +25220,23 @@
         <v/>
       </c>
       <c r="BN35" s="63">
-        <f>IFERROR(AVERAGE(E35:P35),0)</f>
+        <f>IFERROR(BN34/BN31,0)</f>
         <v/>
       </c>
       <c r="BO35" s="63">
-        <f>IFERROR(AVERAGE(Q35:AB35),0)</f>
+        <f>IFERROR(BO34/BO31,0)</f>
         <v/>
       </c>
       <c r="BP35" s="63">
-        <f>IFERROR(AVERAGE(AC35:AN35),0)</f>
+        <f>IFERROR(BP34/BP31,0)</f>
         <v/>
       </c>
       <c r="BQ35" s="63">
-        <f>IFERROR(AVERAGE(AO35:AZ35),0)</f>
+        <f>IFERROR(BQ34/BQ31,0)</f>
         <v/>
       </c>
       <c r="BR35" s="63">
-        <f>IFERROR(AVERAGE(BA35:BL35),0)</f>
+        <f>IFERROR(BR34/BR31,0)</f>
         <v/>
       </c>
     </row>
@@ -28377,23 +28382,23 @@
         <v/>
       </c>
       <c r="BN51" s="66">
-        <f>IFERROR(AVERAGE(E51:P51),0)</f>
+        <f>IFERROR((BN50-BN49)/BN34,0)</f>
         <v/>
       </c>
       <c r="BO51" s="66">
-        <f>IFERROR(AVERAGE(Q51:AB51),0)</f>
+        <f>IFERROR((BO50-BO49)/BO34,0)</f>
         <v/>
       </c>
       <c r="BP51" s="66">
-        <f>IFERROR(AVERAGE(AC51:AN51),0)</f>
+        <f>IFERROR((BP50-BP49)/BP34,0)</f>
         <v/>
       </c>
       <c r="BQ51" s="66">
-        <f>IFERROR(AVERAGE(AO51:AZ51),0)</f>
+        <f>IFERROR((BQ50-BQ49)/BQ34,0)</f>
         <v/>
       </c>
       <c r="BR51" s="66">
-        <f>IFERROR(AVERAGE(BA51:BL51),0)</f>
+        <f>IFERROR((BR50-BR49)/BR34,0)</f>
         <v/>
       </c>
     </row>
@@ -32476,23 +32481,23 @@
         <v/>
       </c>
       <c r="BN21" s="66">
-        <f>IFERROR(AVERAGE(E21:P21),0)</f>
+        <f>IFERROR(('Revenue Forecast'!BN50-BN19)/'Revenue Forecast'!BN34,0)</f>
         <v/>
       </c>
       <c r="BO21" s="66">
-        <f>IFERROR(AVERAGE(Q21:AB21),0)</f>
+        <f>IFERROR(('Revenue Forecast'!BO50-BO19)/'Revenue Forecast'!BO34,0)</f>
         <v/>
       </c>
       <c r="BP21" s="66">
-        <f>IFERROR(AVERAGE(AC21:AN21),0)</f>
+        <f>IFERROR(('Revenue Forecast'!BP50-BP19)/'Revenue Forecast'!BP34,0)</f>
         <v/>
       </c>
       <c r="BQ21" s="66">
-        <f>IFERROR(AVERAGE(AO21:AZ21),0)</f>
+        <f>IFERROR(('Revenue Forecast'!BQ50-BQ19)/'Revenue Forecast'!BQ34,0)</f>
         <v/>
       </c>
       <c r="BR21" s="66">
-        <f>IFERROR(AVERAGE(BA21:BL21),0)</f>
+        <f>IFERROR(('Revenue Forecast'!BR50-BR19)/'Revenue Forecast'!BR34,0)</f>
         <v/>
       </c>
     </row>
@@ -34403,243 +34408,243 @@
         </is>
       </c>
       <c r="E13" s="43">
-        <f>'Revenue Forecast'!E19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!E19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F13" s="43">
-        <f>'Revenue Forecast'!F19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!F19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G13" s="43">
-        <f>'Revenue Forecast'!G19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!G19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H13" s="43">
-        <f>'Revenue Forecast'!H19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!H19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I13" s="43">
-        <f>'Revenue Forecast'!I19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!I19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J13" s="43">
-        <f>'Revenue Forecast'!J19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!J19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K13" s="43">
-        <f>'Revenue Forecast'!K19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!K19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L13" s="43">
-        <f>'Revenue Forecast'!L19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!L19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M13" s="43">
-        <f>'Revenue Forecast'!M19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!M19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N13" s="43">
-        <f>'Revenue Forecast'!N19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!N19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O13" s="43">
-        <f>'Revenue Forecast'!O19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!O19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P13" s="43">
-        <f>'Revenue Forecast'!P19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!P19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q13" s="43">
-        <f>'Revenue Forecast'!Q19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!Q19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R13" s="43">
-        <f>'Revenue Forecast'!R19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!R19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S13" s="43">
-        <f>'Revenue Forecast'!S19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!S19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T13" s="43">
-        <f>'Revenue Forecast'!T19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!T19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U13" s="43">
-        <f>'Revenue Forecast'!U19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!U19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V13" s="43">
-        <f>'Revenue Forecast'!V19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!V19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W13" s="43">
-        <f>'Revenue Forecast'!W19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!W19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X13" s="43">
-        <f>'Revenue Forecast'!X19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!X19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y13" s="43">
-        <f>'Revenue Forecast'!Y19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!Y19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z13" s="43">
-        <f>'Revenue Forecast'!Z19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!Z19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA13" s="43">
-        <f>'Revenue Forecast'!AA19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AA19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB13" s="43">
-        <f>'Revenue Forecast'!AB19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AB19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC13" s="43">
-        <f>'Revenue Forecast'!AC19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AC19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD13" s="43">
-        <f>'Revenue Forecast'!AD19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AD19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE13" s="43">
-        <f>'Revenue Forecast'!AE19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AE19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF13" s="43">
-        <f>'Revenue Forecast'!AF19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AF19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG13" s="43">
-        <f>'Revenue Forecast'!AG19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AG19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH13" s="43">
-        <f>'Revenue Forecast'!AH19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AH19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI13" s="43">
-        <f>'Revenue Forecast'!AI19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AI19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ13" s="43">
-        <f>'Revenue Forecast'!AJ19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AJ19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK13" s="43">
-        <f>'Revenue Forecast'!AK19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AK19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL13" s="43">
-        <f>'Revenue Forecast'!AL19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AL19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM13" s="43">
-        <f>'Revenue Forecast'!AM19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AM19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN13" s="43">
-        <f>'Revenue Forecast'!AN19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AN19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO13" s="43">
-        <f>'Revenue Forecast'!AO19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AO19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP13" s="43">
-        <f>'Revenue Forecast'!AP19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AP19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ13" s="43">
-        <f>'Revenue Forecast'!AQ19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AQ19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR13" s="43">
-        <f>'Revenue Forecast'!AR19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AR19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS13" s="43">
-        <f>'Revenue Forecast'!AS19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AS19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT13" s="43">
-        <f>'Revenue Forecast'!AT19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AT19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU13" s="43">
-        <f>'Revenue Forecast'!AU19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AU19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV13" s="43">
-        <f>'Revenue Forecast'!AV19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AV19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW13" s="43">
-        <f>'Revenue Forecast'!AW19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AW19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX13" s="43">
-        <f>'Revenue Forecast'!AX19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AX19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY13" s="43">
-        <f>'Revenue Forecast'!AY19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AY19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ13" s="43">
-        <f>'Revenue Forecast'!AZ19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!AZ19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA13" s="43">
-        <f>'Revenue Forecast'!BA19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!BA19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB13" s="43">
-        <f>'Revenue Forecast'!BB19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!BB19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC13" s="43">
-        <f>'Revenue Forecast'!BC19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!BC19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD13" s="43">
-        <f>'Revenue Forecast'!BD19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!BD19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE13" s="43">
-        <f>'Revenue Forecast'!BE19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!BE19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF13" s="43">
-        <f>'Revenue Forecast'!BF19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!BF19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG13" s="43">
-        <f>'Revenue Forecast'!BG19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!BG19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH13" s="43">
-        <f>'Revenue Forecast'!BH19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!BH19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI13" s="43">
-        <f>'Revenue Forecast'!BI19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!BI19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ13" s="43">
-        <f>'Revenue Forecast'!BJ19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!BJ19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK13" s="43">
-        <f>'Revenue Forecast'!BK19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!BK19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL13" s="43">
-        <f>'Revenue Forecast'!BL19*Assumptions!$F$130</f>
+        <f>'Revenue Forecast'!BL19*Assumptions!$F$130*(1+Assumptions!$F$135)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN13" s="44">
@@ -35915,243 +35920,243 @@
         </is>
       </c>
       <c r="E22" s="43">
-        <f>Personnel!E20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!E20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(E$3)-2026)</f>
         <v/>
       </c>
       <c r="F22" s="43">
-        <f>Personnel!F20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!F20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G22" s="43">
-        <f>Personnel!G20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!G20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H22" s="43">
-        <f>Personnel!H20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!H20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I22" s="43">
-        <f>Personnel!I20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!I20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J22" s="43">
-        <f>Personnel!J20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!J20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K22" s="43">
-        <f>Personnel!K20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!K20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L22" s="43">
-        <f>Personnel!L20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!L20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M22" s="43">
-        <f>Personnel!M20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!M20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N22" s="43">
-        <f>Personnel!N20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!N20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O22" s="43">
-        <f>Personnel!O20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!O20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P22" s="43">
-        <f>Personnel!P20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!P20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q22" s="43">
-        <f>Personnel!Q20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!Q20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R22" s="43">
-        <f>Personnel!R20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!R20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S22" s="43">
-        <f>Personnel!S20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!S20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T22" s="43">
-        <f>Personnel!T20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!T20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U22" s="43">
-        <f>Personnel!U20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!U20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V22" s="43">
-        <f>Personnel!V20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!V20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W22" s="43">
-        <f>Personnel!W20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!W20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X22" s="43">
-        <f>Personnel!X20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!X20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y22" s="43">
-        <f>Personnel!Y20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!Y20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z22" s="43">
-        <f>Personnel!Z20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!Z20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA22" s="43">
-        <f>Personnel!AA20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AA20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB22" s="43">
-        <f>Personnel!AB20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AB20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC22" s="43">
-        <f>Personnel!AC20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AC20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD22" s="43">
-        <f>Personnel!AD20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AD20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE22" s="43">
-        <f>Personnel!AE20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AE20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF22" s="43">
-        <f>Personnel!AF20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AF20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG22" s="43">
-        <f>Personnel!AG20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AG20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH22" s="43">
-        <f>Personnel!AH20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AH20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI22" s="43">
-        <f>Personnel!AI20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AI20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ22" s="43">
-        <f>Personnel!AJ20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AJ20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK22" s="43">
-        <f>Personnel!AK20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AK20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL22" s="43">
-        <f>Personnel!AL20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AL20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM22" s="43">
-        <f>Personnel!AM20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AM20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN22" s="43">
-        <f>Personnel!AN20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AN20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO22" s="43">
-        <f>Personnel!AO20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AO20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP22" s="43">
-        <f>Personnel!AP20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AP20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ22" s="43">
-        <f>Personnel!AQ20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AQ20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR22" s="43">
-        <f>Personnel!AR20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AR20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS22" s="43">
-        <f>Personnel!AS20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AS20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT22" s="43">
-        <f>Personnel!AT20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AT20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU22" s="43">
-        <f>Personnel!AU20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AU20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV22" s="43">
-        <f>Personnel!AV20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AV20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW22" s="43">
-        <f>Personnel!AW20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AW20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX22" s="43">
-        <f>Personnel!AX20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AX20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY22" s="43">
-        <f>Personnel!AY20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AY20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ22" s="43">
-        <f>Personnel!AZ20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!AZ20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA22" s="43">
-        <f>Personnel!BA20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!BA20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB22" s="43">
-        <f>Personnel!BB20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!BB20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC22" s="43">
-        <f>Personnel!BC20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!BC20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD22" s="43">
-        <f>Personnel!BD20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!BD20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE22" s="43">
-        <f>Personnel!BE20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!BE20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF22" s="43">
-        <f>Personnel!BF20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!BF20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG22" s="43">
-        <f>Personnel!BG20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!BG20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH22" s="43">
-        <f>Personnel!BH20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!BH20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI22" s="43">
-        <f>Personnel!BI20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!BI20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ22" s="43">
-        <f>Personnel!BJ20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!BJ20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK22" s="43">
-        <f>Personnel!BK20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!BK20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL22" s="43">
-        <f>Personnel!BL20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)</f>
+        <f>Personnel!BL20*(Assumptions!$F$126+Assumptions!$F$127+Assumptions!$F$128)*(1+Assumptions!$F$135)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN22" s="44">
@@ -36176,7 +36181,7 @@
       </c>
       <c r="BT22" s="20" t="inlineStr">
         <is>
-          <t>scales with the number of people on the payroll</t>
+          <t>scales with the number of people on the payroll, inflated like every other cost</t>
         </is>
       </c>
     </row>
@@ -36196,239 +36201,239 @@
         <v/>
       </c>
       <c r="F23" s="43">
-        <f>MAX(0,Personnel!F20-Personnel!E20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!F20-Personnel!E20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(F$3)-2026)</f>
         <v/>
       </c>
       <c r="G23" s="43">
-        <f>MAX(0,Personnel!G20-Personnel!F20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!G20-Personnel!F20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(G$3)-2026)</f>
         <v/>
       </c>
       <c r="H23" s="43">
-        <f>MAX(0,Personnel!H20-Personnel!G20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!H20-Personnel!G20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(H$3)-2026)</f>
         <v/>
       </c>
       <c r="I23" s="43">
-        <f>MAX(0,Personnel!I20-Personnel!H20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!I20-Personnel!H20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(I$3)-2026)</f>
         <v/>
       </c>
       <c r="J23" s="43">
-        <f>MAX(0,Personnel!J20-Personnel!I20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!J20-Personnel!I20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(J$3)-2026)</f>
         <v/>
       </c>
       <c r="K23" s="43">
-        <f>MAX(0,Personnel!K20-Personnel!J20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!K20-Personnel!J20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(K$3)-2026)</f>
         <v/>
       </c>
       <c r="L23" s="43">
-        <f>MAX(0,Personnel!L20-Personnel!K20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!L20-Personnel!K20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(L$3)-2026)</f>
         <v/>
       </c>
       <c r="M23" s="43">
-        <f>MAX(0,Personnel!M20-Personnel!L20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!M20-Personnel!L20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(M$3)-2026)</f>
         <v/>
       </c>
       <c r="N23" s="43">
-        <f>MAX(0,Personnel!N20-Personnel!M20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!N20-Personnel!M20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(N$3)-2026)</f>
         <v/>
       </c>
       <c r="O23" s="43">
-        <f>MAX(0,Personnel!O20-Personnel!N20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!O20-Personnel!N20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(O$3)-2026)</f>
         <v/>
       </c>
       <c r="P23" s="43">
-        <f>MAX(0,Personnel!P20-Personnel!O20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!P20-Personnel!O20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(P$3)-2026)</f>
         <v/>
       </c>
       <c r="Q23" s="43">
-        <f>MAX(0,Personnel!Q20-Personnel!P20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!Q20-Personnel!P20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(Q$3)-2026)</f>
         <v/>
       </c>
       <c r="R23" s="43">
-        <f>MAX(0,Personnel!R20-Personnel!Q20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!R20-Personnel!Q20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(R$3)-2026)</f>
         <v/>
       </c>
       <c r="S23" s="43">
-        <f>MAX(0,Personnel!S20-Personnel!R20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!S20-Personnel!R20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(S$3)-2026)</f>
         <v/>
       </c>
       <c r="T23" s="43">
-        <f>MAX(0,Personnel!T20-Personnel!S20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!T20-Personnel!S20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(T$3)-2026)</f>
         <v/>
       </c>
       <c r="U23" s="43">
-        <f>MAX(0,Personnel!U20-Personnel!T20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!U20-Personnel!T20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(U$3)-2026)</f>
         <v/>
       </c>
       <c r="V23" s="43">
-        <f>MAX(0,Personnel!V20-Personnel!U20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!V20-Personnel!U20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(V$3)-2026)</f>
         <v/>
       </c>
       <c r="W23" s="43">
-        <f>MAX(0,Personnel!W20-Personnel!V20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!W20-Personnel!V20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(W$3)-2026)</f>
         <v/>
       </c>
       <c r="X23" s="43">
-        <f>MAX(0,Personnel!X20-Personnel!W20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!X20-Personnel!W20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(X$3)-2026)</f>
         <v/>
       </c>
       <c r="Y23" s="43">
-        <f>MAX(0,Personnel!Y20-Personnel!X20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!Y20-Personnel!X20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(Y$3)-2026)</f>
         <v/>
       </c>
       <c r="Z23" s="43">
-        <f>MAX(0,Personnel!Z20-Personnel!Y20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!Z20-Personnel!Y20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(Z$3)-2026)</f>
         <v/>
       </c>
       <c r="AA23" s="43">
-        <f>MAX(0,Personnel!AA20-Personnel!Z20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AA20-Personnel!Z20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AA$3)-2026)</f>
         <v/>
       </c>
       <c r="AB23" s="43">
-        <f>MAX(0,Personnel!AB20-Personnel!AA20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AB20-Personnel!AA20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AB$3)-2026)</f>
         <v/>
       </c>
       <c r="AC23" s="43">
-        <f>MAX(0,Personnel!AC20-Personnel!AB20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AC20-Personnel!AB20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AC$3)-2026)</f>
         <v/>
       </c>
       <c r="AD23" s="43">
-        <f>MAX(0,Personnel!AD20-Personnel!AC20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AD20-Personnel!AC20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AD$3)-2026)</f>
         <v/>
       </c>
       <c r="AE23" s="43">
-        <f>MAX(0,Personnel!AE20-Personnel!AD20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AE20-Personnel!AD20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AE$3)-2026)</f>
         <v/>
       </c>
       <c r="AF23" s="43">
-        <f>MAX(0,Personnel!AF20-Personnel!AE20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AF20-Personnel!AE20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AF$3)-2026)</f>
         <v/>
       </c>
       <c r="AG23" s="43">
-        <f>MAX(0,Personnel!AG20-Personnel!AF20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AG20-Personnel!AF20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AG$3)-2026)</f>
         <v/>
       </c>
       <c r="AH23" s="43">
-        <f>MAX(0,Personnel!AH20-Personnel!AG20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AH20-Personnel!AG20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AH$3)-2026)</f>
         <v/>
       </c>
       <c r="AI23" s="43">
-        <f>MAX(0,Personnel!AI20-Personnel!AH20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AI20-Personnel!AH20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AI$3)-2026)</f>
         <v/>
       </c>
       <c r="AJ23" s="43">
-        <f>MAX(0,Personnel!AJ20-Personnel!AI20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AJ20-Personnel!AI20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AJ$3)-2026)</f>
         <v/>
       </c>
       <c r="AK23" s="43">
-        <f>MAX(0,Personnel!AK20-Personnel!AJ20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AK20-Personnel!AJ20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AK$3)-2026)</f>
         <v/>
       </c>
       <c r="AL23" s="43">
-        <f>MAX(0,Personnel!AL20-Personnel!AK20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AL20-Personnel!AK20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AL$3)-2026)</f>
         <v/>
       </c>
       <c r="AM23" s="43">
-        <f>MAX(0,Personnel!AM20-Personnel!AL20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AM20-Personnel!AL20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AM$3)-2026)</f>
         <v/>
       </c>
       <c r="AN23" s="43">
-        <f>MAX(0,Personnel!AN20-Personnel!AM20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AN20-Personnel!AM20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AN$3)-2026)</f>
         <v/>
       </c>
       <c r="AO23" s="43">
-        <f>MAX(0,Personnel!AO20-Personnel!AN20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AO20-Personnel!AN20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AO$3)-2026)</f>
         <v/>
       </c>
       <c r="AP23" s="43">
-        <f>MAX(0,Personnel!AP20-Personnel!AO20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AP20-Personnel!AO20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AP$3)-2026)</f>
         <v/>
       </c>
       <c r="AQ23" s="43">
-        <f>MAX(0,Personnel!AQ20-Personnel!AP20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AQ20-Personnel!AP20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AQ$3)-2026)</f>
         <v/>
       </c>
       <c r="AR23" s="43">
-        <f>MAX(0,Personnel!AR20-Personnel!AQ20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AR20-Personnel!AQ20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AR$3)-2026)</f>
         <v/>
       </c>
       <c r="AS23" s="43">
-        <f>MAX(0,Personnel!AS20-Personnel!AR20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AS20-Personnel!AR20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AS$3)-2026)</f>
         <v/>
       </c>
       <c r="AT23" s="43">
-        <f>MAX(0,Personnel!AT20-Personnel!AS20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AT20-Personnel!AS20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AT$3)-2026)</f>
         <v/>
       </c>
       <c r="AU23" s="43">
-        <f>MAX(0,Personnel!AU20-Personnel!AT20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AU20-Personnel!AT20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AU$3)-2026)</f>
         <v/>
       </c>
       <c r="AV23" s="43">
-        <f>MAX(0,Personnel!AV20-Personnel!AU20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AV20-Personnel!AU20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AV$3)-2026)</f>
         <v/>
       </c>
       <c r="AW23" s="43">
-        <f>MAX(0,Personnel!AW20-Personnel!AV20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AW20-Personnel!AV20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AW$3)-2026)</f>
         <v/>
       </c>
       <c r="AX23" s="43">
-        <f>MAX(0,Personnel!AX20-Personnel!AW20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AX20-Personnel!AW20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AX$3)-2026)</f>
         <v/>
       </c>
       <c r="AY23" s="43">
-        <f>MAX(0,Personnel!AY20-Personnel!AX20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AY20-Personnel!AX20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AY$3)-2026)</f>
         <v/>
       </c>
       <c r="AZ23" s="43">
-        <f>MAX(0,Personnel!AZ20-Personnel!AY20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!AZ20-Personnel!AY20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(AZ$3)-2026)</f>
         <v/>
       </c>
       <c r="BA23" s="43">
-        <f>MAX(0,Personnel!BA20-Personnel!AZ20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!BA20-Personnel!AZ20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(BA$3)-2026)</f>
         <v/>
       </c>
       <c r="BB23" s="43">
-        <f>MAX(0,Personnel!BB20-Personnel!BA20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!BB20-Personnel!BA20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(BB$3)-2026)</f>
         <v/>
       </c>
       <c r="BC23" s="43">
-        <f>MAX(0,Personnel!BC20-Personnel!BB20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!BC20-Personnel!BB20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(BC$3)-2026)</f>
         <v/>
       </c>
       <c r="BD23" s="43">
-        <f>MAX(0,Personnel!BD20-Personnel!BC20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!BD20-Personnel!BC20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(BD$3)-2026)</f>
         <v/>
       </c>
       <c r="BE23" s="43">
-        <f>MAX(0,Personnel!BE20-Personnel!BD20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!BE20-Personnel!BD20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(BE$3)-2026)</f>
         <v/>
       </c>
       <c r="BF23" s="43">
-        <f>MAX(0,Personnel!BF20-Personnel!BE20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!BF20-Personnel!BE20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(BF$3)-2026)</f>
         <v/>
       </c>
       <c r="BG23" s="43">
-        <f>MAX(0,Personnel!BG20-Personnel!BF20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!BG20-Personnel!BF20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(BG$3)-2026)</f>
         <v/>
       </c>
       <c r="BH23" s="43">
-        <f>MAX(0,Personnel!BH20-Personnel!BG20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!BH20-Personnel!BG20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(BH$3)-2026)</f>
         <v/>
       </c>
       <c r="BI23" s="43">
-        <f>MAX(0,Personnel!BI20-Personnel!BH20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!BI20-Personnel!BH20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(BI$3)-2026)</f>
         <v/>
       </c>
       <c r="BJ23" s="43">
-        <f>MAX(0,Personnel!BJ20-Personnel!BI20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!BJ20-Personnel!BI20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(BJ$3)-2026)</f>
         <v/>
       </c>
       <c r="BK23" s="43">
-        <f>MAX(0,Personnel!BK20-Personnel!BJ20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!BK20-Personnel!BJ20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(BK$3)-2026)</f>
         <v/>
       </c>
       <c r="BL23" s="43">
-        <f>MAX(0,Personnel!BL20-Personnel!BK20)*Assumptions!$F$129</f>
+        <f>MAX(0,Personnel!BL20-Personnel!BK20)*Assumptions!$F$129*(1+Assumptions!$F$135)^(YEAR(BL$3)-2026)</f>
         <v/>
       </c>
       <c r="BN23" s="44">
@@ -38964,23 +38969,23 @@
         <v/>
       </c>
       <c r="BN35" s="49">
-        <f>IFERROR(AVERAGE(E35:P35),0)</f>
+        <f>IFERROR(BN33/'Revenue Forecast'!BN50,0)</f>
         <v/>
       </c>
       <c r="BO35" s="49">
-        <f>IFERROR(AVERAGE(Q35:AB35),0)</f>
+        <f>IFERROR(BO33/'Revenue Forecast'!BO50,0)</f>
         <v/>
       </c>
       <c r="BP35" s="49">
-        <f>IFERROR(AVERAGE(AC35:AN35),0)</f>
+        <f>IFERROR(BP33/'Revenue Forecast'!BP50,0)</f>
         <v/>
       </c>
       <c r="BQ35" s="49">
-        <f>IFERROR(AVERAGE(AO35:AZ35),0)</f>
+        <f>IFERROR(BQ33/'Revenue Forecast'!BQ50,0)</f>
         <v/>
       </c>
       <c r="BR35" s="49">
-        <f>IFERROR(AVERAGE(BA35:BL35),0)</f>
+        <f>IFERROR(BR33/'Revenue Forecast'!BR50,0)</f>
         <v/>
       </c>
     </row>
@@ -39101,156 +39106,56 @@
       <c r="N38" s="23" t="n">
         <v>61620</v>
       </c>
-      <c r="O38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL38" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="O38" s="43" t="n"/>
+      <c r="P38" s="43" t="n"/>
+      <c r="Q38" s="43" t="n"/>
+      <c r="R38" s="43" t="n"/>
+      <c r="S38" s="43" t="n"/>
+      <c r="T38" s="43" t="n"/>
+      <c r="U38" s="43" t="n"/>
+      <c r="V38" s="43" t="n"/>
+      <c r="W38" s="43" t="n"/>
+      <c r="X38" s="43" t="n"/>
+      <c r="Y38" s="43" t="n"/>
+      <c r="Z38" s="43" t="n"/>
+      <c r="AA38" s="43" t="n"/>
+      <c r="AB38" s="43" t="n"/>
+      <c r="AC38" s="43" t="n"/>
+      <c r="AD38" s="43" t="n"/>
+      <c r="AE38" s="43" t="n"/>
+      <c r="AF38" s="43" t="n"/>
+      <c r="AG38" s="43" t="n"/>
+      <c r="AH38" s="43" t="n"/>
+      <c r="AI38" s="43" t="n"/>
+      <c r="AJ38" s="43" t="n"/>
+      <c r="AK38" s="43" t="n"/>
+      <c r="AL38" s="43" t="n"/>
+      <c r="AM38" s="43" t="n"/>
+      <c r="AN38" s="43" t="n"/>
+      <c r="AO38" s="43" t="n"/>
+      <c r="AP38" s="43" t="n"/>
+      <c r="AQ38" s="43" t="n"/>
+      <c r="AR38" s="43" t="n"/>
+      <c r="AS38" s="43" t="n"/>
+      <c r="AT38" s="43" t="n"/>
+      <c r="AU38" s="43" t="n"/>
+      <c r="AV38" s="43" t="n"/>
+      <c r="AW38" s="43" t="n"/>
+      <c r="AX38" s="43" t="n"/>
+      <c r="AY38" s="43" t="n"/>
+      <c r="AZ38" s="43" t="n"/>
+      <c r="BA38" s="43" t="n"/>
+      <c r="BB38" s="43" t="n"/>
+      <c r="BC38" s="43" t="n"/>
+      <c r="BD38" s="43" t="n"/>
+      <c r="BE38" s="43" t="n"/>
+      <c r="BF38" s="43" t="n"/>
+      <c r="BG38" s="43" t="n"/>
+      <c r="BH38" s="43" t="n"/>
+      <c r="BI38" s="43" t="n"/>
+      <c r="BJ38" s="43" t="n"/>
+      <c r="BK38" s="43" t="n"/>
+      <c r="BL38" s="43" t="n"/>
       <c r="BN38" s="44">
         <f>SUM(E38:P38)</f>
         <v/>
@@ -39318,156 +39223,56 @@
       <c r="N39" s="23" t="n">
         <v>19800</v>
       </c>
-      <c r="O39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK39" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL39" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="O39" s="43" t="n"/>
+      <c r="P39" s="43" t="n"/>
+      <c r="Q39" s="43" t="n"/>
+      <c r="R39" s="43" t="n"/>
+      <c r="S39" s="43" t="n"/>
+      <c r="T39" s="43" t="n"/>
+      <c r="U39" s="43" t="n"/>
+      <c r="V39" s="43" t="n"/>
+      <c r="W39" s="43" t="n"/>
+      <c r="X39" s="43" t="n"/>
+      <c r="Y39" s="43" t="n"/>
+      <c r="Z39" s="43" t="n"/>
+      <c r="AA39" s="43" t="n"/>
+      <c r="AB39" s="43" t="n"/>
+      <c r="AC39" s="43" t="n"/>
+      <c r="AD39" s="43" t="n"/>
+      <c r="AE39" s="43" t="n"/>
+      <c r="AF39" s="43" t="n"/>
+      <c r="AG39" s="43" t="n"/>
+      <c r="AH39" s="43" t="n"/>
+      <c r="AI39" s="43" t="n"/>
+      <c r="AJ39" s="43" t="n"/>
+      <c r="AK39" s="43" t="n"/>
+      <c r="AL39" s="43" t="n"/>
+      <c r="AM39" s="43" t="n"/>
+      <c r="AN39" s="43" t="n"/>
+      <c r="AO39" s="43" t="n"/>
+      <c r="AP39" s="43" t="n"/>
+      <c r="AQ39" s="43" t="n"/>
+      <c r="AR39" s="43" t="n"/>
+      <c r="AS39" s="43" t="n"/>
+      <c r="AT39" s="43" t="n"/>
+      <c r="AU39" s="43" t="n"/>
+      <c r="AV39" s="43" t="n"/>
+      <c r="AW39" s="43" t="n"/>
+      <c r="AX39" s="43" t="n"/>
+      <c r="AY39" s="43" t="n"/>
+      <c r="AZ39" s="43" t="n"/>
+      <c r="BA39" s="43" t="n"/>
+      <c r="BB39" s="43" t="n"/>
+      <c r="BC39" s="43" t="n"/>
+      <c r="BD39" s="43" t="n"/>
+      <c r="BE39" s="43" t="n"/>
+      <c r="BF39" s="43" t="n"/>
+      <c r="BG39" s="43" t="n"/>
+      <c r="BH39" s="43" t="n"/>
+      <c r="BI39" s="43" t="n"/>
+      <c r="BJ39" s="43" t="n"/>
+      <c r="BK39" s="43" t="n"/>
+      <c r="BL39" s="43" t="n"/>
       <c r="BN39" s="44">
         <f>SUM(E39:P39)</f>
         <v/>
@@ -39530,156 +39335,56 @@
       <c r="N40" s="23" t="n">
         <v>21420</v>
       </c>
-      <c r="O40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL40" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="O40" s="43" t="n"/>
+      <c r="P40" s="43" t="n"/>
+      <c r="Q40" s="43" t="n"/>
+      <c r="R40" s="43" t="n"/>
+      <c r="S40" s="43" t="n"/>
+      <c r="T40" s="43" t="n"/>
+      <c r="U40" s="43" t="n"/>
+      <c r="V40" s="43" t="n"/>
+      <c r="W40" s="43" t="n"/>
+      <c r="X40" s="43" t="n"/>
+      <c r="Y40" s="43" t="n"/>
+      <c r="Z40" s="43" t="n"/>
+      <c r="AA40" s="43" t="n"/>
+      <c r="AB40" s="43" t="n"/>
+      <c r="AC40" s="43" t="n"/>
+      <c r="AD40" s="43" t="n"/>
+      <c r="AE40" s="43" t="n"/>
+      <c r="AF40" s="43" t="n"/>
+      <c r="AG40" s="43" t="n"/>
+      <c r="AH40" s="43" t="n"/>
+      <c r="AI40" s="43" t="n"/>
+      <c r="AJ40" s="43" t="n"/>
+      <c r="AK40" s="43" t="n"/>
+      <c r="AL40" s="43" t="n"/>
+      <c r="AM40" s="43" t="n"/>
+      <c r="AN40" s="43" t="n"/>
+      <c r="AO40" s="43" t="n"/>
+      <c r="AP40" s="43" t="n"/>
+      <c r="AQ40" s="43" t="n"/>
+      <c r="AR40" s="43" t="n"/>
+      <c r="AS40" s="43" t="n"/>
+      <c r="AT40" s="43" t="n"/>
+      <c r="AU40" s="43" t="n"/>
+      <c r="AV40" s="43" t="n"/>
+      <c r="AW40" s="43" t="n"/>
+      <c r="AX40" s="43" t="n"/>
+      <c r="AY40" s="43" t="n"/>
+      <c r="AZ40" s="43" t="n"/>
+      <c r="BA40" s="43" t="n"/>
+      <c r="BB40" s="43" t="n"/>
+      <c r="BC40" s="43" t="n"/>
+      <c r="BD40" s="43" t="n"/>
+      <c r="BE40" s="43" t="n"/>
+      <c r="BF40" s="43" t="n"/>
+      <c r="BG40" s="43" t="n"/>
+      <c r="BH40" s="43" t="n"/>
+      <c r="BI40" s="43" t="n"/>
+      <c r="BJ40" s="43" t="n"/>
+      <c r="BK40" s="43" t="n"/>
+      <c r="BL40" s="43" t="n"/>
       <c r="BN40" s="44">
         <f>SUM(E40:P40)</f>
         <v/>
@@ -39742,156 +39447,56 @@
       <c r="N41" s="23" t="n">
         <v>125000</v>
       </c>
-      <c r="O41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK41" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL41" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="O41" s="43" t="n"/>
+      <c r="P41" s="43" t="n"/>
+      <c r="Q41" s="43" t="n"/>
+      <c r="R41" s="43" t="n"/>
+      <c r="S41" s="43" t="n"/>
+      <c r="T41" s="43" t="n"/>
+      <c r="U41" s="43" t="n"/>
+      <c r="V41" s="43" t="n"/>
+      <c r="W41" s="43" t="n"/>
+      <c r="X41" s="43" t="n"/>
+      <c r="Y41" s="43" t="n"/>
+      <c r="Z41" s="43" t="n"/>
+      <c r="AA41" s="43" t="n"/>
+      <c r="AB41" s="43" t="n"/>
+      <c r="AC41" s="43" t="n"/>
+      <c r="AD41" s="43" t="n"/>
+      <c r="AE41" s="43" t="n"/>
+      <c r="AF41" s="43" t="n"/>
+      <c r="AG41" s="43" t="n"/>
+      <c r="AH41" s="43" t="n"/>
+      <c r="AI41" s="43" t="n"/>
+      <c r="AJ41" s="43" t="n"/>
+      <c r="AK41" s="43" t="n"/>
+      <c r="AL41" s="43" t="n"/>
+      <c r="AM41" s="43" t="n"/>
+      <c r="AN41" s="43" t="n"/>
+      <c r="AO41" s="43" t="n"/>
+      <c r="AP41" s="43" t="n"/>
+      <c r="AQ41" s="43" t="n"/>
+      <c r="AR41" s="43" t="n"/>
+      <c r="AS41" s="43" t="n"/>
+      <c r="AT41" s="43" t="n"/>
+      <c r="AU41" s="43" t="n"/>
+      <c r="AV41" s="43" t="n"/>
+      <c r="AW41" s="43" t="n"/>
+      <c r="AX41" s="43" t="n"/>
+      <c r="AY41" s="43" t="n"/>
+      <c r="AZ41" s="43" t="n"/>
+      <c r="BA41" s="43" t="n"/>
+      <c r="BB41" s="43" t="n"/>
+      <c r="BC41" s="43" t="n"/>
+      <c r="BD41" s="43" t="n"/>
+      <c r="BE41" s="43" t="n"/>
+      <c r="BF41" s="43" t="n"/>
+      <c r="BG41" s="43" t="n"/>
+      <c r="BH41" s="43" t="n"/>
+      <c r="BI41" s="43" t="n"/>
+      <c r="BJ41" s="43" t="n"/>
+      <c r="BK41" s="43" t="n"/>
+      <c r="BL41" s="43" t="n"/>
       <c r="BN41" s="44">
         <f>SUM(E41:P41)</f>
         <v/>
@@ -39954,156 +39559,56 @@
       <c r="N42" s="23" t="n">
         <v>24000</v>
       </c>
-      <c r="O42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK42" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL42" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="O42" s="43" t="n"/>
+      <c r="P42" s="43" t="n"/>
+      <c r="Q42" s="43" t="n"/>
+      <c r="R42" s="43" t="n"/>
+      <c r="S42" s="43" t="n"/>
+      <c r="T42" s="43" t="n"/>
+      <c r="U42" s="43" t="n"/>
+      <c r="V42" s="43" t="n"/>
+      <c r="W42" s="43" t="n"/>
+      <c r="X42" s="43" t="n"/>
+      <c r="Y42" s="43" t="n"/>
+      <c r="Z42" s="43" t="n"/>
+      <c r="AA42" s="43" t="n"/>
+      <c r="AB42" s="43" t="n"/>
+      <c r="AC42" s="43" t="n"/>
+      <c r="AD42" s="43" t="n"/>
+      <c r="AE42" s="43" t="n"/>
+      <c r="AF42" s="43" t="n"/>
+      <c r="AG42" s="43" t="n"/>
+      <c r="AH42" s="43" t="n"/>
+      <c r="AI42" s="43" t="n"/>
+      <c r="AJ42" s="43" t="n"/>
+      <c r="AK42" s="43" t="n"/>
+      <c r="AL42" s="43" t="n"/>
+      <c r="AM42" s="43" t="n"/>
+      <c r="AN42" s="43" t="n"/>
+      <c r="AO42" s="43" t="n"/>
+      <c r="AP42" s="43" t="n"/>
+      <c r="AQ42" s="43" t="n"/>
+      <c r="AR42" s="43" t="n"/>
+      <c r="AS42" s="43" t="n"/>
+      <c r="AT42" s="43" t="n"/>
+      <c r="AU42" s="43" t="n"/>
+      <c r="AV42" s="43" t="n"/>
+      <c r="AW42" s="43" t="n"/>
+      <c r="AX42" s="43" t="n"/>
+      <c r="AY42" s="43" t="n"/>
+      <c r="AZ42" s="43" t="n"/>
+      <c r="BA42" s="43" t="n"/>
+      <c r="BB42" s="43" t="n"/>
+      <c r="BC42" s="43" t="n"/>
+      <c r="BD42" s="43" t="n"/>
+      <c r="BE42" s="43" t="n"/>
+      <c r="BF42" s="43" t="n"/>
+      <c r="BG42" s="43" t="n"/>
+      <c r="BH42" s="43" t="n"/>
+      <c r="BI42" s="43" t="n"/>
+      <c r="BJ42" s="43" t="n"/>
+      <c r="BK42" s="43" t="n"/>
+      <c r="BL42" s="43" t="n"/>
       <c r="BN42" s="44">
         <f>SUM(E42:P42)</f>
         <v/>
@@ -40166,156 +39671,56 @@
       <c r="N43" s="23" t="n">
         <v>20000</v>
       </c>
-      <c r="O43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL43" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="O43" s="43" t="n"/>
+      <c r="P43" s="43" t="n"/>
+      <c r="Q43" s="43" t="n"/>
+      <c r="R43" s="43" t="n"/>
+      <c r="S43" s="43" t="n"/>
+      <c r="T43" s="43" t="n"/>
+      <c r="U43" s="43" t="n"/>
+      <c r="V43" s="43" t="n"/>
+      <c r="W43" s="43" t="n"/>
+      <c r="X43" s="43" t="n"/>
+      <c r="Y43" s="43" t="n"/>
+      <c r="Z43" s="43" t="n"/>
+      <c r="AA43" s="43" t="n"/>
+      <c r="AB43" s="43" t="n"/>
+      <c r="AC43" s="43" t="n"/>
+      <c r="AD43" s="43" t="n"/>
+      <c r="AE43" s="43" t="n"/>
+      <c r="AF43" s="43" t="n"/>
+      <c r="AG43" s="43" t="n"/>
+      <c r="AH43" s="43" t="n"/>
+      <c r="AI43" s="43" t="n"/>
+      <c r="AJ43" s="43" t="n"/>
+      <c r="AK43" s="43" t="n"/>
+      <c r="AL43" s="43" t="n"/>
+      <c r="AM43" s="43" t="n"/>
+      <c r="AN43" s="43" t="n"/>
+      <c r="AO43" s="43" t="n"/>
+      <c r="AP43" s="43" t="n"/>
+      <c r="AQ43" s="43" t="n"/>
+      <c r="AR43" s="43" t="n"/>
+      <c r="AS43" s="43" t="n"/>
+      <c r="AT43" s="43" t="n"/>
+      <c r="AU43" s="43" t="n"/>
+      <c r="AV43" s="43" t="n"/>
+      <c r="AW43" s="43" t="n"/>
+      <c r="AX43" s="43" t="n"/>
+      <c r="AY43" s="43" t="n"/>
+      <c r="AZ43" s="43" t="n"/>
+      <c r="BA43" s="43" t="n"/>
+      <c r="BB43" s="43" t="n"/>
+      <c r="BC43" s="43" t="n"/>
+      <c r="BD43" s="43" t="n"/>
+      <c r="BE43" s="43" t="n"/>
+      <c r="BF43" s="43" t="n"/>
+      <c r="BG43" s="43" t="n"/>
+      <c r="BH43" s="43" t="n"/>
+      <c r="BI43" s="43" t="n"/>
+      <c r="BJ43" s="43" t="n"/>
+      <c r="BK43" s="43" t="n"/>
+      <c r="BL43" s="43" t="n"/>
       <c r="BN43" s="44">
         <f>SUM(E43:P43)</f>
         <v/>
@@ -46267,24 +45672,29 @@
         <v/>
       </c>
       <c r="BN31" s="66">
-        <f>IFERROR(AVERAGE(E31:P31),0)</f>
+        <f>IFERROR(BN29/12/BN20,0)</f>
         <v/>
       </c>
       <c r="BO31" s="66">
-        <f>IFERROR(AVERAGE(Q31:AB31),0)</f>
+        <f>IFERROR(BO29/12/BO20,0)</f>
         <v/>
       </c>
       <c r="BP31" s="66">
-        <f>IFERROR(AVERAGE(AC31:AN31),0)</f>
+        <f>IFERROR(BP29/12/BP20,0)</f>
         <v/>
       </c>
       <c r="BQ31" s="66">
-        <f>IFERROR(AVERAGE(AO31:AZ31),0)</f>
+        <f>IFERROR(BQ29/12/BQ20,0)</f>
         <v/>
       </c>
       <c r="BR31" s="66">
-        <f>IFERROR(AVERAGE(BA31:BL31),0)</f>
-        <v/>
+        <f>IFERROR(BR29/12/BR20,0)</f>
+        <v/>
+      </c>
+      <c r="BT31" s="20" t="inlineStr">
+        <is>
+          <t>annual column: the year's people cost over twelve, per head at December</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -46786,23 +46196,23 @@
         </is>
       </c>
       <c r="D26" s="43">
-        <f>IFERROR(D14/D25,0)</f>
+        <f>IFERROR(D14/D24,0)</f>
         <v/>
       </c>
       <c r="E26" s="43">
-        <f>IFERROR(E14/E25,0)</f>
+        <f>IFERROR(E14/E24,0)</f>
         <v/>
       </c>
       <c r="F26" s="43">
-        <f>IFERROR(F14/F25,0)</f>
+        <f>IFERROR(F14/F24,0)</f>
         <v/>
       </c>
       <c r="G26" s="43">
-        <f>IFERROR(G14/G25,0)</f>
+        <f>IFERROR(G14/G24,0)</f>
         <v/>
       </c>
       <c r="H26" s="43">
-        <f>IFERROR(H14/H25,0)</f>
+        <f>IFERROR(H14/H24,0)</f>
         <v/>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -46977,7 +46387,7 @@
         </is>
       </c>
       <c r="D37" s="43">
-        <f>MIN('Financial Statements'!$N$40:$BL$40)</f>
+        <f>MIN(INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$140,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$40:$BL$40,60))</f>
         <v/>
       </c>
       <c r="J37" s="20" t="inlineStr">
@@ -46993,7 +46403,7 @@
         </is>
       </c>
       <c r="D38" s="71">
-        <f>INDEX('Financial Statements'!$E$3:$BL$3,MATCH(D37,'Financial Statements'!$N$40:$BL$40,0)+9)</f>
+        <f>INDEX('Financial Statements'!$E$3:$BL$3,MATCH(D37,INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$140,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$40:$BL$40,60),0)+MATCH(Assumptions!$F$140,'Financial Statements'!$E$3:$BL$3,0)-1)</f>
         <v/>
       </c>
     </row>
@@ -47122,7 +46532,7 @@
         </is>
       </c>
       <c r="D50" s="43">
-        <f>'Financial Statements'!N40</f>
+        <f>INDEX('Financial Statements'!$E$40:$BL$40,MATCH(Assumptions!$F$140,'Financial Statements'!$E$3:$BL$3,0))</f>
         <v/>
       </c>
     </row>
@@ -47144,7 +46554,7 @@
         </is>
       </c>
       <c r="D52" s="72">
-        <f>IFERROR(D51/SUM('Financial Statements'!N35:BL35),0)</f>
+        <f>IFERROR(D51/SUM(INDEX('Financial Statements'!$E$35:$BL$35,MATCH(Assumptions!$F$140,'Financial Statements'!$E$3:$BL$3,0)):INDEX('Financial Statements'!$E$35:$BL$35,60)),0)</f>
         <v/>
       </c>
       <c r="J52" s="20" t="inlineStr">
@@ -47160,12 +46570,12 @@
         </is>
       </c>
       <c r="D53" s="60">
-        <f>IFERROR(D37/(-'Financial Statements'!BP14/12),0)</f>
+        <f>IFERROR(D37/(-HLOOKUP(YEAR(D38),'Financial Statements'!$BN$3:$BR$14,12,FALSE)/12),0)</f>
         <v/>
       </c>
       <c r="J53" s="20" t="inlineStr">
         <is>
-          <t>a plan of this size wants three months or more here</t>
+          <t>cash at the low point over that year's average monthly operating cost. Three months or more is comfortable</t>
         </is>
       </c>
     </row>
